--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,6 @@
           <t>Les changements sociaux de la fin du XIXᵉ&amp;nbsp;siècle ont permis à tout un chacun d’accéder aux jardins d’agrément.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -552,7 +551,6 @@
           <t>Retour sur l’histoire d’un club new-yorkais qui, durant la Seconde Guerre mondiale, a redonné vie à un club sportif juif autrichien dissous par les nazis.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -585,7 +583,6 @@
           <t>Retour sur l’histoire méconnue des hauts plateaux kényans, marqués par la colonisation britannique et devenus le berceau du marathon mondial.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -618,7 +615,6 @@
           <t>Pendant et après la Première Guerre mondiale, des milliers de femmes américaines ont joué le rôle de mères auprès d’orphelins français. Une facette méconnue de l’histoire transatlantique.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -651,7 +647,6 @@
           <t>Une décision de la chambre d’instruction de la Cour d’appel de Paris est susceptible de relancer un processus judiciaire, dont les implications dépassent largement le cas de la seule accusée, veuve du président rwandais assassiné en 1994.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -684,7 +679,6 @@
           <t>En consacrant un dyptique au général de Gaulle, Antonin&amp;nbsp;Baudry s’inscrit dans la tendance actuelle des biopics, qui accordent davantage d’importance à la proximité émotionnelle avec les grandes figures qu’à la portée historique de leur parcours.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -717,7 +711,6 @@
           <t>Pour éviter les abus mémoriels des entreprises, des chercheurs plaident pour une nouvelle éthique de la mémoire organisationnelle.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -750,7 +743,6 @@
           <t>Femmes qui s’évanouissent, fleurs lancées sur scène, foules en délire : la légende de la Lisztomanie a traversé les siècles. Pourtant, les témoignages qui l’ont façonnée étaient souvent empreints de sensationnalisme, de misogynie et de jugements moraux.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -783,7 +775,6 @@
           <t>De George&amp;nbsp;Washington à Donald&amp;nbsp;Trump, les anniversaires des présidents ont toujours mêlé pouvoir et spectacle. Avec ses 80&amp;nbsp;ans, Trump pousse le rituel au show politique.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -816,7 +807,6 @@
           <t>Caucase du Nord, Tatarstan, Bouriatie, Iakoutie…&amp;nbsp;: bien des régions de la Fédération de Russie ont été conquises par la force au cours des siècles.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -849,7 +839,6 @@
           <t>Longues journées de travail, accélération des communications, fatigue mentale&amp;nbsp;: les angoisses associées au burn out existaient déjà au XIXᵉ&amp;nbsp;siècle. Les réponses apportées à l’époque pourraient encore nourrir nos réflexions sur le bien-être aujourd’hui.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -882,7 +871,6 @@
           <t>En examinant près de 600 billets coloniaux à l’aide de techniques d’imagerie avancées, des chercheurs ont découvert que Benjamin Franklin expérimentait déjà des solutions de lutte contre la contrefaçon fondées sur les propriétés physiques du papier et de l’encre.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -915,7 +903,6 @@
           <t>Et si la célèbre «&amp;nbsp;marche miraculeuse&amp;nbsp;» d’Harold n’avait jamais eu lieu&amp;nbsp;? En réexaminant les chroniques du XIᵉ&amp;nbsp;siècle, l’historien Tom Licence avance que le roi anglais a utilisé sa flotte pour mener sa campagne contre les vikings, puis contre Guillaume le Conquérant.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -948,7 +935,6 @@
           <t>Au Moyen Âge, les abeilles irlandaises possédaient un statut juridique, car elles étaient considérées comme du bétail domestique.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -981,7 +967,6 @@
           <t>Surreprésentées dans les salles de classe, les enseignantes ont été oubliées par l’histoire&amp;nbsp;: qui sont ces pionnières de la pédagogie qui ont contribué à créer l’école que nous connaissons aujourd’hui&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1014,7 +999,6 @@
           <t>L’histoire des réserves d’or américaines stockées à Fort Knox depuis une centaine d’années fait régulièrement émerger des théories du complot.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1047,7 +1031,6 @@
           <t>Ces sépultures collectives circulaires étaient remplies d’ossements humains et animaux, souvent soigneusement disposés autour d’une figure centrale.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1080,7 +1063,6 @@
           <t>En raison des aléas liés à ses partitions manuscrites et de la méconnaissance dont ont longtemps souffert les compositrices, Bembo et son opéra sont restés dans l’ombre pendant des siècles.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1113,7 +1095,6 @@
           <t>Le 25 mai 1926, un Juif de Bessarabie dont une partie de la famille avait été tuée dans des pogromes tuait à Paris l’ex-président de l’Ukraine indépendante pour son rôle dans ces massacres.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1146,7 +1127,6 @@
           <t>Selon le Kama-sutra, une vie sexuelle épanouie ne peut se construire que grâce à une communication efficace et à une compréhension mutuelle. Le consentement en est la clé.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1179,7 +1159,6 @@
           <t>La guerre russo-ukrainienne se déploie aussi dans les querelles entre milieux d’extrême droite des deux pays, chacun présentant le sien comme le territoire d’origine des «&amp;nbsp;vrais&amp;nbsp;» Indo-Européens.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1212,7 +1191,6 @@
           <t>Bien avant qu’Emmanuel Macron en fasse une priorité géopolitique, Madeleine Ly-Tio-Fane avait théorisé l’Indo-Pacifique comme espace stratégique de l’expansion coloniale française.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1245,7 +1223,6 @@
           <t>La rivalité entre les États-Unis et la Chine donne souvent lieu à l'invocation du «&amp;nbsp;piège de Thucydide&amp;nbsp;» — la guerre «&amp;nbsp;inévitable&amp;nbsp;» ayant opposé Athènes à Sparte au Vᵉ siècle avant notre ère. Or de nombreux spécialistes de la Grèce antique contestent cette lecture simplifiée de l’histoire.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1278,7 +1255,6 @@
           <t>De la mascotte « Coalie » aux slogans sur le « charbon propre », l’administration Trump recycle une longue tradition de communication destinée à présenter le charbon comme une énergie inoffensive.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1311,7 +1287,6 @@
           <t>Retrouvé à l’intérieur d’une momie égyptienne de l’époque romaine, un fragment de l’«&amp;nbsp;Iliade&amp;nbsp;» révèle l’immense place occupée par Homère dans la culture quotidienne de l’Empire romain, bien au-delà des cercles savants.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1344,7 +1319,6 @@
           <t>À Polytechnique, la cérémonie de remise des diplômes a été perturbée par des étudiants dénonçant l’influence de grands groupes sur les formations et les ravages de l’industrie sur l’environnement.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1377,7 +1351,6 @@
           <t>Présentée au fil de l’histoire tour à tour comme une déviance ou comme un espace de ressourcement, la solitude est devenue un problème public dont s’emparent les politiques et candidats à la présidentielle.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1410,7 +1383,6 @@
           <t>La question du travail domestique est abordée dans le débat public sous l’angle de l’inégale répartition des tâches entre femmes et hommes. Mais qu’en est-il de la participation des enfants&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1443,7 +1415,6 @@
           <t>La proposition de loi visant à protéger les enfants contre les violences en milieu scolaire a été adoptée à l’unanimité, actant un changement de regard sur l’enfant dans la société.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1476,7 +1447,6 @@
           <t>Face à des sujets jugés trop difficiles, ou des programmes chargés, les candidats au bac n’hésitent plus à lancer des pétitions. Que nous dit ce phénomène du rapport à l’institution scolaire&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1509,7 +1479,6 @@
           <t>La lecture est l’une des compétences les plus difficiles à acquérir. Les supports numériques rendent-ils ce processus encore plus complexe&amp;nbsp;? Que dit la recherche&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1542,7 +1511,6 @@
           <t>Alors que débute la phase d’admission sur Parcoursup, retour sur le modèle des classes prépas. Quels avantages garde-t-il à l’heure où se développent d’autres voies d’accès aux grandes écoles&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1575,7 +1543,6 @@
           <t>Dans un monde en pleine mutation, il ne s’agit plus tant d’accumuler des savoirs que d’apprendre à apprendre. Mais comment adapter le modèle scolaire actuel pour l’orienter vers ces enjeux complexes&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1608,7 +1575,6 @@
           <t>Suffit-il d’ouvrir les portes des musées aux enfants et aux adolescents pour leur donner accès à l’art&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1641,7 +1607,6 @@
           <t>Avant de s’inscrire dans un établissement, les étudiants sont à l’affût d’indicateurs de qualité. Mais les labels et les accréditations peuvent-ils les renseigner sur les atouts pédagogiques d’un cursus&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1674,7 +1639,6 @@
           <t>De Salman Rushdie à Morton Schapiro, plusieurs personnalités invitées à s’adresser aux diplômés ont récemment été contestées ou désinvitées. Une évolution qui relance le débat sur la liberté d’expression dans l’enseignement supérieur.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1707,7 +1671,6 @@
           <t>Pour lutter contre l’autocensure des filles et leur ouvrir des perspectives de carrières dans les sciences, une école explore la piste de stages en écoles d’ingénieurs pour les lycéennes.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1740,7 +1703,6 @@
           <t>Une étude analyse les raisons pour lesquelles les chercheurs deviennent entrepreneurs et leur propension à valoriser leurs travaux par la création d’entreprise.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1773,7 +1735,6 @@
           <t>Écouter ne consiste pas simplement à se taire en attendant son tour pour répondre. C’est une compétence exigeante, essentielle à la vie démocratique, que l’école comme les réseaux sociaux nous apprennent encore trop peu.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1806,7 +1767,6 @@
           <t>Les termes d’«&amp;nbsp;écoanxiété&amp;nbsp;» et d’«&amp;nbsp;anxiété climatique&amp;nbsp;» sont les plus fréquemment utilisés, mais ils ne reflètent pas toute la complexité de la détresse ressentie par certaines personnes.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1839,7 +1799,6 @@
           <t>Ni définie par la loi ni véritablement encadrée, la lettre de motivation participe pourtant à l’examen des candidatures sur Parcoursup. Quelques réflexions avant le début de la phase d’admission.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1872,7 +1831,6 @@
           <t>La stratégie annoncée en avril 2026 pour renforcer l’attractivité de la France auprès des étudiants étrangers renforce une mesure controversée, celle des frais d’inscription universitaires différenciés.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1905,7 +1863,6 @@
           <t>Le harcèlement scolaire ne dépend pas seulement des élèves eux-mêmes ou de leur environnement familial. Une étude menée aux États-Unis montre que les classes les plus chaotiques et perturbées favorisent davantage les comportements de harcèlement à l’école primaire.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1938,7 +1895,6 @@
           <t>Construire des cabanes avec des outils, grimper très haut ou explorer la forêt&amp;nbsp;: au Danemark, ces expériences font partie du développement normal des enfants&amp;nbsp;– et seraient bénéfiques pour leur santé mentale.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1971,7 +1927,6 @@
           <t>Jouer à faire semblant n’est pas qu’un divertissement : dès le plus jeune âge, ces jeux d’imitation participent au développement émotionnel des enfants.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2004,7 +1959,6 @@
           <t>En France, plus que dans d’autres pays, l’échec scolaire est socialement marqué. Comment changer l’école pour qu’elle soit réellement un espace d’égalité des chances ?</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2037,7 +1991,6 @@
           <t>Pour les lycéens professionnels, l’épreuve de l’orientation dans le supérieur commence bien avant l’ouverture de Parcoursup, là où se fabrique leur rapport à l’institution scolaire.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2070,7 +2023,6 @@
           <t>Pression scolaire, comparaison sociale, construction de soi&amp;nbsp;: noter précocement les élèves pourrait fragiliser leur santé mentale, particulièrement celle des adolescentes.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2103,7 +2055,6 @@
           <t>Les flux de marchandises, amplifiés par la mondialisation, offrent des prises aux acteurs qui veulent perturber ou rançonner les économies ouvertes.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2136,7 +2087,6 @@
           <t>Abelardo de la Espriella, classé à l’ultradroite, est favori à la présidentielle colombienne de dimanche.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2169,7 +2119,6 @@
           <t>L’Iran compte des milliers de prisonniers d’opinion, dont Narges Mohammadi, prix Nobel de la paix 2023. Leur sort n’est aucunement évoqué dans l’accord entre Trump et Téhéran.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2202,7 +2151,6 @@
           <t>Depuis 2023, Israël durcit détentions et sanctions contre les Palestiniens. Une dérive sécuritaire et judiciaire récemment matérialisée par une loi punissant de mort certains actes terroristes.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2235,7 +2183,6 @@
           <t>Les États-Unis ont largement recours au «&amp;nbsp;lawfare&amp;nbsp;» (usage stratégique du droit) dans leur bras de fer avec Pékin.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2268,7 +2215,6 @@
           <t>Analyse des marchés brassicoles des trois&amp;nbsp;pays hôtes de la Coupe du monde masculine de football et de leur interdépendance, des champs d’orge à la canette d’aluminium.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2301,7 +2247,6 @@
           <t>La puissance passe désormais plus par le contrôle des flux que par celui des territoires.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2334,7 +2279,6 @@
           <t>Face aux pressions russes, chinoises et américaines, l’UE cherche à bâtir une autonomie robuste, fondée sur la défense, l’industrie et le droit.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2367,7 +2311,6 @@
           <t>C’est en Europe que l’exploitation des terres rares a commencé, mais ce monopole est détenu désormais par la Chine. Comment redonner à l’Europe une place dans cette histoire ?</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2400,7 +2343,6 @@
           <t>Les élections législatives ont vu la victoire du premier ministre sortant, le 7&amp;nbsp;juin dernier. Nikol&amp;nbsp;Pachinian cherche à diversifier les alliances de la république du Caucase du Sud, notamment en se rapprochant de l’Union européenne.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2433,7 +2375,6 @@
           <t>Le Japon accueille aujourd’hui un nombre record de touristes et de travailleurs étrangers. Pourtant, une nouvelle enquête montre qu’une large majorité de Japonais soutient un durcissement des règles encadrant leur présence et leurs activités.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2466,7 +2407,6 @@
           <t>La figure des «&amp;nbsp;cholitas futbolistas&amp;nbsp;» oscille entre reconnaissance et folklorisation des identités autochtones.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2499,7 +2439,6 @@
           <t>Passionnés par le football, bien plus que les autres communautés du pays, les Hispaniques des États-Unis ont pourtant un rapport distancié à l’égard de l’équipe nationale et du championnat local.</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2532,7 +2471,6 @@
           <t>Grâce à un algorithme d’apprentissage automatique combinant cotes des bookmakers, performances des joueurs et historiques des matchs, des chercheurs ont calculé les chances de chaque sélection.</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2565,7 +2503,6 @@
           <t>Plus qu’un virage anti-chinois, la visite de Matthew&amp;nbsp;Wale à Canberra révèle les fragilités internes et les calculs d’équilibre des îles Salomon.</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2598,7 +2535,6 @@
           <t>Sous la présidence de Nayib&amp;nbsp;Bukele, le Salvador est passé du chaos des gangs à un modèle qui allie ordre, pouvoir centralisé, innovations numériques et restrictions des libertés.</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2631,7 +2567,6 @@
           <t>L’installation, que Trump veut pérenne, d’une arène de MMA symbolise un pouvoir fondé sur la force et le spectacle.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2664,7 +2599,6 @@
           <t>La Coupe du monde 2026 comptera un nombre record de joueurs nés à l’étranger. Loin d’être une anomalie, cette réalité reflète l’histoire des migrations mondiales et pourrait même constituer un avantage compétitif pour certaines sélections.</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2697,7 +2631,6 @@
           <t>Marjane Satrapi a permis de mieux comprendre l’Iran&amp;nbsp;: pas seulement à ses lecteurs occidentaux, mais aussi aux Iraniens exilés.</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2730,7 +2663,6 @@
           <t>Fermeture des frontières des États-Unis à de nombreux fans, participation de l’Iran, tensions avec les villes démocrates&amp;nbsp;: la compétition ne se déroulera pas que sur le terrain sportif.</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2763,7 +2695,6 @@
           <t>Huitième épisode de notre rendez-vous quotidien avec la Coupe du monde. Consultez ici les épisodes précédents. L’article Parmi les favoris, le Portugal est la plus grande déception de ce début de Coupe du monde est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2796,7 +2727,6 @@
           <t>Israël, le seul pays membre de l’ONU qui reconnaît le Somaliland, a accueilli mardi 16 juin l’ouverture d’une ambassade à Jérusalem. L’article Pourquoi Israël opère-t-il un rapprochement avec le Somaliland&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2829,7 +2759,6 @@
           <t>Quatre signaux faibles indiquent que Pékin pourrait être le véritable vainqueur de la guerre contre Téhéran. L’article La Chine a-t-elle gagné la guerre en Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2862,7 +2791,6 @@
           <t>L’appel du candidat à la présidentielle pour un 18 juin européen. L’article Le moment gaullien de l’Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2895,7 +2823,6 @@
           <t>Selon le commandant des Forces de systèmes sans pilote de l’armée ukrainienne, le coût moyen de la neutralisation d’un soldat russe se situe à environ 918 dollars. L’article Tuer un soldat russe avec un drone sur le front en Ukraine coûterait moins de 1 000 dollars est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2928,7 +2855,6 @@
           <t>En ce 18 juin, nous avons demandé à son plus grand biographe britannique de nous expliquer pourquoi De Gaulle n’est pas Jeanne d’Arc, mais Tintin. L’article L’étrange victoire du Général est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2961,7 +2887,6 @@
           <t>Les États-Unis ont échoué. L’Union est marginalisée. Pour peser dans la nouvelle compétition régionale qui commence, il faut tirer quelques leçons. L’article L’Europe après la guerre en Iran&amp;#160;: un bilan à chaud est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2994,7 +2919,6 @@
           <t>Lionel Messi entre un peu plus dans l’histoire, tandis que Luka Modrić et Cristiano Ronaldo s’apprêtent peut-être à disputer leur dernier Mondial. L’article Donald Trump soulèvera-t-il la Coupe du monde&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3027,7 +2951,6 @@
           <t>L’entreprise spatiale fondée par Elon Musk affiche une capitalisation boursière de 2 700 milliards de dollars, devançant ainsi Amazon, alors que ses revenus sont 40 fois inférieurs. L’article Cinq jours après son introduction en bourse, la capitalisation de SpaceX a dépassé celle d’Amazon est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3060,7 +2983,6 @@
           <t>L’amélioration des capacités ukrainiennes en matière de drones à moyenne distance a conduit à un effondrement du trafic de 60&amp;#160;% sur l'autoroute reliant la Russie à la Crimée. L’article L’armée ukrainienne peut-elle couper la Crimée de la Russie&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3093,7 +3015,6 @@
           <t>Donald Trump, enfin rattrapé par la justice? nardon@ifri.org jeu 23/03/2023 - 10:06 22/03/2023 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche L'ancien président a annoncé être bientôt inculpé, et ce pour avoir acheté le silence d'une ancienne actrice porno, Stormy Daniels, avec l'argent de sa campagne. Photo Laurence NARDON Intitulé du poste Responsable du Programme Amériques de l'Ifri Voir plus Référence contenu Centres et Programmes Programme Amériques Contenu i</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3126,7 +3047,6 @@
           <t>Rencontre avec Tidjane Thiam : Impact du contexte macroéconomique sur les marchés émergents afrique@ifri.org ven 24/06/2022 - 12:37 Image Conférence Mercredi 6 juillet 2022 - 09:30 - Mercredi 6 juillet 2022 - 11:00 mar 05/07/2022 - 16:00 Économie Développement économique Sociétés Afrique subsaharienne Afrique subsaharienne L'Afrique dans les relations internationales Mutations sociales et économiques de l'Afrique Éditoriaux Image principale L’enjeu des dettes publiques en Afrique. Une cristallis</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3159,7 +3079,6 @@
           <t>Boko Haram dans la région de l’extrême-Nord du Cameroun : L’arbre qui cache la forêt afrique@ifri.org ven 03/06/2022 - 12:37 Date de publication 08/06/2022 Notes Droit d'accès legend-public Accroche La région de l’Extrême-Nord du Cameroun est secouée depuis 2013 par le conflit dû à Boko Haram dont l’origine et l’épicentre sont le nord-est du Nigeria (l’État de Borno) et qui s’étend à quatre pays (Nigeria, Cameroun, Tchad et Niger). Les interactions complexes entre le mouvement djihadiste Boko Ha</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3192,7 +3111,6 @@
           <t>Les villes africaines peuvent-elles être un moteur de développement économique pour l’Afrique ? afrique@ifri.org mar 24/05/2022 - 17:43 15/04/2022 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche Comment les villes africaines vont absorber la croissance&amp;nbsp;démographique rapide ? Comment améliorer la bonne gouvernance urbaine en Afrique ? Comment combler le financement des infrastructures urbaines ? Logo Référence contenu Centres et Programmes Centre Afrique subsah</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3225,7 +3143,6 @@
           <t xml:space="preserve">Lapidation au Nigeria : «La radicalité religieuse, seule boussole» d'une partie de la population musulmane afrique@ifri.org jeu 19/05/2022 - 10:24 18/05/2022 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche Pour&amp;nbsp; Benjamin Augé, chercheur associé à l'Ifri , le meurtre de l'étudiante chrétienne Deborah Samuel s'inscrit dans un engrenage infernal où pauvreté et insécurité favorisent l'islamisme. Pour un simple message WhatsApp où elle remet en cause la légitimité </t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3258,7 +3175,6 @@
           <t>Etat de siège en RDC : "un échec prévisible" selon Thierry Vircoulon afrique@ifri.org ven 13/05/2022 - 11:27 13/05/2022 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche Après un an d'état de siège, le niveau de violence a augmenté au Nord-Kivu et en Ituri. Selon les chiffres du baromètre de sécurité du Kivu (KST), il y a deux fois plus de morts depuis l'instauration de cette mesure dans l'Est de la RDC. Pour le chercher associé à l'IFRI, Thierry Vircoulon, l'état de</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3291,7 +3207,6 @@
           <t>Accords militaires avec la Russie : de Madagascar au Cameroun, Moscou en "phase d'accélération" en Afrique afrique@ifri.org mer 11/05/2022 - 16:33 21/04/2022 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche Madagascar, puis le Cameroun. Ce mois-ci, la signature de deux nouveaux accords militaires de pays africains avec la Russie ont été révélés. Ces signatures interrogent sur les rapprochements entre certains États du continent et Moscou.&amp;nbsp; Photo Thierry VIRCOUL</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3324,7 +3239,6 @@
           <t>Légalisation du bitcoin en Centrafrique : l’ombre de la Russie ? afrique@ifri.org lun 09/05/2022 - 12:31 29/04/2022 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche Deuxième pays le moins développé au monde, la République centrafricaine, en proie à une guerre civile depuis 2013, a annoncé ce&amp;nbsp;27&amp;nbsp;avril reconnaître le bitcoin comme monnaie légale. Une mesure «&amp;nbsp;surréaliste&amp;nbsp;» pour de nombreux observateurs, et qui pourrait bien profiter à la Russie pou</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3357,7 +3271,6 @@
           <t>Débat : Retrait du Mali des forces françaises et européennes : nouvelle donne en Afrique de l'Ouest ? afrique@ifri.org lun 21/02/2022 - 15:04 17/02/2022 Type d'interventions médiatiques Presse - contenus repris sur le site Accroche La France et ses partenaires européens ont annoncé leur retrait militaire du Mali mais affirment vouloir rester engagés au Sahel et dans les pays du golfe de Guinée. Quel va être l'impact du redéploiement sécuritaire de la France et de l'Europe&amp;nbsp;au Sahel&amp;nbsp;? Ph</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3390,7 +3303,6 @@
           <t>Les enjeux du 6e Sommet Union africaine - Union européenne avec Maud Arnould (Vidéo) afrique@ifri.org mer 16/02/2022 - 11:40 16/02/2022 Type d'interventions médiatiques Vidéo Accroche Interview de Maud Arnould, Conseillère Afrique du Haut Représentant de l'Union Européenne pour les affaires étrangères. Référence contenu Centres et Programmes Centre Afrique subsaharienne Contenu intervention médiatique "L'enjeu, c'est vraiment d'essayer de faire de l'Europe le partenaire de choix des pays africai</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3423,7 +3335,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1201920272?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3456,7 +3367,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1201920273?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3489,7 +3399,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1201920592?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3522,7 +3431,6 @@
           <t>L&amp;#8217;APHG vous donne rendez-vous à Montpellier pour quatre journées alliant réflexion scientifique, découverte du terrain et moments de convivialité. Au programme : une conférence inaugurale de Christian Amalvi, des excursions au choix (Pont du Gard, Aigues-Mortes, Tautavel, Sète…), des conférences en histoire et géographie, des visites thématiques de Montpellier aux choix, et une conférence de [&amp;#8230;] L’article Les Agoras de l&amp;rsquo;APHG 2026 — Montpellier est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3555,7 +3463,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200227374?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3588,7 +3495,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200227281?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3621,7 +3527,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200227162?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3654,7 +3559,6 @@
           <t>Cette exposition prolonge celle qu&amp;#8217;Étienne Bloch avait conçue à la fin du XXe siècle, et c&amp;#8217;est toute la famille qui a souhaité renouveler ce geste pour les générations actuelles d&amp;#8217;enseignants. Un grand merci à toutes celles et ceux qui ont œuvré à ce projet : Joëlle Alazard (présidente de l&amp;#8217;APHG), Catherine Cimaz-Leroy, Catherine Pidutti et [&amp;#8230;] L’article Exposition « Marc Bloch : vie, combats, héritages » est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3687,7 +3591,6 @@
           <t>L&amp;#8217;ouvrage Jean-David Morvan (scénariste) écrit de nombreux genres. Auteur engagé, il a reçu pour sa série Madeleine Résistante le prix René-Goscinny. Petite-fille de Marc Bloch, Suzette Bloch est journaliste et auteure d’un documentaire Arte/ Ex Nihilo sur Auschwitz. Laurent Bidot (dessin) a publié de nombreux ouvrages dont l’adaptation du témoignage de Joseph Weismann, Après la Rafle. [&amp;#8230;] L’article Marc Bloch, l&amp;rsquo;historien combattant &amp;#8211; ressources pédagogiques est apparu e</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3720,7 +3623,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio et vidéo pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200226909?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3753,7 +3655,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200226912?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3786,7 +3687,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200227377?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3819,7 +3719,6 @@
           <t xml:space="preserve">Avec Sylvain Kahn, nous réunirons de nombreux spécialistes, universitaires et observateurs du monde contemporain pour réfléchir ensemble aux tensions, crises et recompositions qui traversent aujourd’hui le projet européen. Guerre aux frontières de l’Union, montée des populismes, enjeux démocratiques, défis économiques, puissance géopolitique, transition écologique : jamais sans doute la question européenne n’a paru aussi décisive. [&amp;#8230;] L’article Journée d&amp;rsquo;étude : L&amp;rsquo;Europe, état </t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3852,7 +3751,6 @@
           <t>Zérodeconduite.net propose à cette occasion un dossier pédagogique complet à destination des enseignants, à partir de la 4e. Au programme : chronologie des faits, présentation des personnages, lexique, suites judiciaires, et des séquences d&amp;#8217;activités autour de la laïcité, des responsabilités individuelles et de l&amp;#8217;analyse du film. 🗂️ Le dossier pédagogique : labandon-dossierpedagogique &amp;#160; 🌐 Toutes les [&amp;#8230;] L’article L&amp;rsquo;Abandon, dossier pédagogique est apparu en premier s</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3885,7 +3783,6 @@
           <t>Cette journée aura lieu au lycée Belliard à Paris. Vous pouvez télécharger le programme de la journée en cliquant sur ce lien. Inscriptions jusqu’au 28 mai : inscriptionsaphg@gmail.com L’article Les âges de l&amp;rsquo;enseignement professionnel &amp;#8211; une journée d&amp;rsquo;étude coorganisée par l&amp;rsquo;APHG et le CHIMEN le 30 mai 2026 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3918,7 +3815,6 @@
           <t>L’article Sommaire n°473 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3951,7 +3847,6 @@
           <t>L’article ÉDITORIAL &amp;#8211; LE PRINTEMPS, MALGRÉ TOUT. est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3984,7 +3879,6 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. Vous pouvez également télécharger une bibliographie complémentaire proposée par Anne Rauner en cliquant sur ce lien &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe [&amp;#8230;] L’article Nicole Bériou, Héloïse Kolebka, Anne Rauner, Abbes Zouche &amp;#821</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4017,7 +3911,6 @@
           <t>Nous tenons à rappeler au Ministre de l&amp;#8217;Éducation Nationale et à la Ministre déléguée chargée de l&amp;#8217;Enseignement professionnel et de l&amp;#8217;Apprentissage quelles sont nos priorités fondamentales. Les lycées professionnels accueillent un tiers des lycéens français, parmi lesquels une large part d&amp;#8217;élèves en grande difficulté scolaire &amp;#8211; en CAP comme en Baccalauréat professionnel &amp;#8211; et un [&amp;#8230;] L’article Communiqué de l&amp;rsquo;Atelier Lycée Professionnel sur la fin de</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4050,7 +3943,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1183770683?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4083,7 +3975,6 @@
           <t>Marc Bloch, un historien pour aujourd’hui Emmanuel Macron a annoncé la décision de faire entrer au Panthéon le [23] juin 2026 Marc Bloch, grand historien et résistant, assassiné en 1944. De Marc Bloch (1886-1944), la parole présidentielle et médiatique retient, et c’est justice, le républicain, le héros des deux guerres mondiales, le résistant et martyr, [&amp;#8230;] L’article Panthéonisation de Marc Bloch &amp;#8211; Toutes les ressources pédagogiques est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4116,7 +4007,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1182329815?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4149,7 +4039,6 @@
           <t>Vous retrouverez sur cette page le podcast de la session ainsi que des supports proposés par l’équipe Coup de pouce Capes Interne. Pour vous inscrire au dispositif, une seule adresse : c2pcapesinterne.aphg@gmail.com L&amp;#8217;équipe Coup de pouce Capes interne vous propose également les sujets qui ont été traités pendant la visio : &amp;#160; Enseigner-Bourgeoisies-marchandes-negoces-internationaux-traites-negrieres-et-esclavage-au-XVIIIe-siecle-4e &amp;#160; Enseigner-les-villes-a-lechelle-mondiale-Premi</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4182,7 +4071,6 @@
           <t>La tâche est d&amp;#8217;autant plus complexe que ces questions sont désormais traversées par des phénomènes de désinformation, de manipulation de l&amp;#8217;information et de récits alternatifs qui s&amp;#8217;imposent dans l&amp;#8217;espace public et jusque dans nos classes. Face à des élèves exposés à des discours concurrents, parfois complotistes ou révisionnistes, les enseignants doivent plus que jamais s&amp;#8217;appuyer [&amp;#8230;] L’article Les questions socialement vives en histoire-géographie-EMC : une j</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4215,7 +4103,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1177960131?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4248,7 +4135,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1177960064?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4281,7 +4167,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio avec diaporama intégré pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1177959991?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; </t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4314,7 +4199,6 @@
           <t>Michelle Perrot souligne tout d’abord que, pour sa génération, les livres tenaient une place centrale, mais que cette place n’est sans doute pas éternelle, et qu’il y a d’autres manières de lire que de lire des livres. Les premiers livres qu’elle a fréquentés sont ceux de la bibliothèque de ses grands-parents, une bibliothèque qui reproduisait [&amp;#8230;] L’article Michelle Perrot : « Chacun ici a son chemin des livres, qui est une manière de reparcourir sa vie. » est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4347,7 +4231,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1177959937?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4380,7 +4263,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1177959881?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4413,7 +4295,6 @@
           <t>Vous retrouverez sur cette page le podcast de la session ainsi que des supports proposés par l’équipe Coup de pouce Capes Interne. Pour vous inscrire au dispositif, une seule adresse : c2pcapesinterne.aphg@gmail.com &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1173558497?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; all</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4446,7 +4327,6 @@
           <t xml:space="preserve">Antiquité Moyen Âge Période moderne Période contemporaine Thèmes transversaux Historiographie Liens utiles N.B. Les documents portant sur les séquences intermédiaires entre plusieurs ères (antiquité tardive, transition Moyen Âge / première modernité, période révolutionnaire) peuvent se trouver dans les deux pages concernées. Principes du projet et avertissements Pour valoriser et partager ces efforts conséquents, cette page [&amp;#8230;] L’article L’histoire par les textes est apparu en premier sur </t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4479,7 +4359,6 @@
           <t>Vous pouvez retrouver sur cette page une séance de préparation aux épreuves orales avec une mise au point scientifique et didactique proposée par Arthur Hérisson autour du thème « La France et l’unité italienne ». Le podcast est proposé en version audio hybride avec diaporama intégré. Pour vous inscrire au dispositif, une seule adresse : coupdepouceaphg@gmail.com L’article Coup de pouce Agrégation interne &amp;#8211; La France et l’unité italienne est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4512,7 +4391,6 @@
           <t>Voix aux chapitres : autour de Marc Bloch et de son ouvrage Les rois thaumaturges. Informations et vidéos : www.ehess.fr/voix-aux-chapitres Contact : jerome.malois@ehess.fr L’article Voix aux chapitres &amp;#8211; Les rois thaumaturges est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4545,7 +4423,6 @@
           <t>Journée d’étude : Michelle Perrot, Le chemin des livres Jeudi 19 mars 2026 : 9h30 – 17hArchives nationales, Site de Pierrefitte-sur-Seine Les Archives nationales et l’Université Paris 8 organisent une journée d’étude consacrée à Michelle Perrot, figure majeure de l’histoire des femmes et du genre en France. À l’occasion de l’entrée de ses archives (cote 757 AP) aux [&amp;#8230;] L’article Journée d’étude : Michelle Perrot, Le chemin des livres est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4578,7 +4455,6 @@
           <t>Vous retrouverez sur cette page le podcast de la session ainsi que des supports proposés par l’équipe Coup de pouce Capes Interne. Pour vous inscrire au dispositif, une seule adresse : c2pcapesinterne.aphg@gmail.com Vous pouvez télécharger les supports de cette séance ci-dessous : coup_de_pouce_-_oral_1_ conseils_de_fiches_a_re_aliser_pour_l_e_preuve_d_admission pre_parer_l_oral_du_capes_interne-2 L’article Opération Coup de pouce pour le Capes interne &amp;#8211; La préparation de l’oral est apparu</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4611,7 +4487,6 @@
           <t>Programme : 9h : Accueil &amp;#8211; Joëlle Alazard (Présidente APHG) / Muriel Le Roux (IHMC) 9h15-10h10 : Jean-Marie Le Gall (IHMC &amp;#8211; Paris 1) « La notion de guerre de religion à l’époque moderne » 10h10-11h05 : Paul Vo-Ha (IHMC &amp;#8211; Paris 1) « Roi de guerre, roi de paix. Guerre et souveraineté à l’époque moderne en France et en Europe » 11h05-12h : [&amp;#8230;] L’article Guerres en perspective(s) &amp;#8211; une journée d’étude coorganisée par l’APHG et l’IHMC le 7 février 2026, en Sorbonne est a</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4644,7 +4519,6 @@
           <t>Vous trouverez ci-dessous le sommaire complet et pouvez accéder au numéro à l’adresse suivante : https://journals.openedition.org/bahmuf/1821 Dossier thématique « L’âge des révolutions (années 1770 &amp;#8211; 1804) » Matthieu Ferradou, « La Révolution d’Irlande et la guerre pour la République atlantique (1770-1804) » Antoine Renglet, « Révolutions, occupations et transformations policières aux marges impériales : une approche comparée entre l’espace belge et la Louisiane [&amp;#8230;] L’article Parutio</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4677,7 +4551,6 @@
           <t>Les « prépa HEC » dispensaient un enseignement axé sur les mathématiques et l’histoire et géographie économiques, l’ « histégé ». Devenues « prépa ECG », elles enseignent désormais l’Histoire, géographie et géopolitique du monde contemporain (HGGMC), enseignement très populaire chez les étudiants. Ce sont toujours des professeurs d’histoire et de géographie qui assurent cet enseignement. En prépa ECG, l’histoire, géographie [&amp;#8230;] L’article Tribune : de l’importance de l’HGGSP pour une orient</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -4710,7 +4583,6 @@
           <t>14h : Accueil &amp;#8211; Joëlle Alazard (Présidente APHG)14h05-14h40 : Sophie Blanchy (Ethnologue, Directrice de recherche émérite au CNRS, Laboratoire d’ethnologie et de sociologie comparative)« Comprendre les circulations des Comoriens et questionner la « submersion migratoire » à Mayotte »14h55-15h30 : Emmanuelle Surmont (Géographe, docteure en géographie et enseignante en classes préparatoires)« Mayotte, un laboratoire des changements globaux ? »Pause15h55-16h30 : Florence Troin (Géographe et c</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4743,7 +4615,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Bertrand Van Ruymbeke pour la présentation de son ouvrage à paraître prochainement : 1776. L’année américaine. Vous retrouverez également [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Bertrand Van Ruymbeke &amp;#8211; 1776 &amp;#8211; L’année améric</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -4776,7 +4647,6 @@
           <t>Vous trouverez ci-dessous le programme des conférences 2026 de la Chaire Grands enjeux stratégiques contemporains, dirigée par le professeur Louis Gautier. Les inscriptions sont ouvertes sur le site de la Chaire : https://chairestrategique.pantheonsorbonne.fr. Les conférences pourront être suivies en présentiel ou à distance. Révolutions et changements en cours dans les affaires militaires 2026 26 janvierLeçon inauguraleGénéral Fabien Mandon, [&amp;#8230;] L’article Chaire Grands enjeux stratégiques</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4809,7 +4679,6 @@
           <t>Ce 8 décembre 2025 le comité directeur du Maitron a réuni les partenaires pour faire le point sur la remise en route de ce monumental dictionnaire biographique du mouvement ouvrier.Plusieurs évolutions ont été annoncées : l’édition mise en ligne entre 2006 et 2024, riche de 230 000 notices, est patrimonialisée ; de nouveaux corpus de notices sont [&amp;#8230;] L’article Comité directeur du Maitron : compte rendu et programme 2026 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -4842,7 +4711,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Simon Dufour autour du thème « Les environnements fluviaux au prisme de la géographie ». Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Simon Dufour &amp;#8211; Les environnements fluviaux au prisme de la géographie est app</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4875,7 +4743,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Sandrine Vaucelle consacrée au thème « Aménagement et/ou protection : les zones humides urbaines en contexte de changements climatiques [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Sandrine Vaucelle &amp;#8211; Aménagement et/ou protection : le</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4908,7 +4775,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Jean-François Dunyach autour du thème « Matérialités révolutionnaires : objets, vecteurs et agents de la circulation des idées et [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Jean-François Dunyach &amp;#8211; Matérialités révolutionnaires : obj</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4941,7 +4807,6 @@
           <t>Les membres de l’Association des professeurs d’histoire et de géographie, vigilants quant aux détournements des nouvelles technologies au service de projets autoritaires, conscients des risques portés par l’intelligence artificielle pour le travail des élèves, l’apprentissage de l’indépendance d’esprit et pour l’enseignement de l’histoire, de la géographie et de l’enseignement moral et civique, adoptent les cinq [&amp;#8230;] L’article Pour une approche critique de l’I.A en cours d’histoire-géograph</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4974,7 +4839,6 @@
           <t>Samedi 20 Septembre 2025 : Bureau National (10h-12h en présentiel)Conseil de Gestion (14h-16h30 en présentiel) Samedi 27 septembre 2025 : Demi-journée d’étude en Sorbonne « Marc Bloch : vie, combats, héritages » Du vendredi 3 au Dimanche 5 Octobre 2025 : FIG à Saint-Dié-des-Vosges Du Mercredi 8 octobre au Dimanche 12 Octobre 2025 : RDVH à Blois Samedi 18 octobre 2025 : Journée d’étude organisée pour les agrégatives [&amp;#8230;] L’article Calendrier 2025-2026 des réunions institutionnelles de l’APHG</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5007,7 +4871,6 @@
           <t>La note de service du 2 septembre 2025, parue au BOEN n°33 du 4 septembre de la même année, a établi les nouvelles modalités du diplôme national du brevet (DNB) à compter de la session 2026. Celles-ci introduisent quant à l’épreuve d’Histoire-Géographie et d’Enseignement Moral et Civique un certain nombre de changements : notes séparées pour [&amp;#8230;] L’article Pour une préparation sereine du DNB &amp;#8211; Motion de l’atelier collège de l’APHG est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5040,7 +4903,803 @@
           <t>Samedi 20 Septembre 2025 : Bureau National (10h-12h en présentiel)Conseil de Gestion (14h-16h30 en présentiel) Samedi 27 septembre 2025 : Demi-journée d’étude en Sorbonne « Marc Bloch : vie, combats, héritages » Du vendredi 3 au Dimanche 5 Octobre 2025 : FIG à Saint-Dié-des-Vosges Du Mercredi 8 octobre au Dimanche 12 Octobre 2025 : RDVH à Blois Samedi 18 octobre 2025 : Journée d’étude organisée pour les agrégatives [&amp;#8230;] L’article Calendrier 2025-2026 des réunions institutionnelles de l’APHG</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:05</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Comment le génie de George Sand a été minimisé par l'histoire littéraire</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-le-genie-de-george-sand-a-ete-minimise-par-lhistoire-litteraire-283164</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Cent cinquante ans après sa mort, quelle image de George Sand domine ? La scandaleuse ? La romantique défenseuse des paysans ? Son génie ne peut se réduire à ces clichés.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:24</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>En 1768, comment un roi paralysa l’État en se mettant en grève</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/en-1768-comment-un-roi-paralysa-letat-en-se-mettant-en-greve-285736</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Au XVIIIe siècle, la Suède expérimenta une forme de gouvernement proche du parlementarisme moderne. Lorsqu'un conflit institutionnel éclata en 1768, un roi décida de se mettre en grève, déclenchant une crise constitutionnelle qui interrogeait le rôle même de la monarchie.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:40</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Comment célèbre-t-on en Europe le jour le plus long de l’année ?</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-celebre-t-on-en-europe-le-jour-le-plus-long-de-lannee-285716</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Pourquoi allume-t-on de grands feux à la Saint-Jean ? Pourquoi danse-t-on autour d’un mât décoré de fleurs ? Derrière ces traditions festives se cache un héritage complexe où se croisent croyances ancestrales, folklore et identité culturelle.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-06-19 07:33</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Quarante ans après, faut-il encore célébrer la « Main de Dieu » de Maradona ?</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quarante-ans-apres-faut-il-encore-celebrer-la-main-de-dieu-de-maradona-285714</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Quarante ans après le quart de finale légendaire entre l’Argentine et l’Angleterre, la « Main de Dieu » continue de diviser. Peut-on célébrer un geste de tricherie tout en admirant le génie de Diego Maradona ?</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:40</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Les attaques de drones ukrainiens en Russie ont été multipliées par 13 depuis 2023</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/19/les-attaques-de-drones-ukrainiens-en-russie-ont-ete-multipliees-par-13-depuis-2023/</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Depuis le début de l’année, plus de 150 attaques de drones ukrainiens ont visé des cibles en Russie, soit deux fois plus que l’an dernier et quatre fois plus qu’en 2024. L’article Les attaques de drones ukrainiens en Russie ont été multipliées par 13 depuis 2023 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-06-19 04:44</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Le philosophe normalien du moment géopolitique</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/19/le-philosophe-normalien-du-moment-geopolitique/</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Pourquoi lire Pierre Hassner est plus urgent que jamais. L’article Le philosophe normalien du moment géopolitique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-06-19 04:30</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>La hausse des températures pourrait coûter à l’économie indienne jusqu’à 4,5 % de son PIB d’ici 2030</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/19/la-hausse-des-temperatures-pourrait-couter-a-leconomie-indienne-jusqua-45-de-son-pib-dici-2030/</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Depuis plusieurs semaines, New Delhi subit une vague de chaleur intense, avec des températures dépassant fréquemment les 40°C. L’article La hausse des températures pourrait coûter à l’économie indienne jusqu’à 4,5&amp;#160;% de son PIB d’ici 2030 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:19</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Opération Coup de pouce! pour le capes interne</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/operation-coup-de-pouce-pour-le-capes-interne/</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Le premier rendez-vous de la saison 2026-2027 est prévu le 29 juin 2026 à 20h30, avec Marie Digout, Thomas Gosselin et Marine Sorano. &amp;#160; &amp;#160; &amp;#160; L’article Opération Coup de pouce! pour le capes interne est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:59</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Victor Delaporte – Le militantisme pro-Algérie française de 1944 à 1962</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-victor-delaporte-le-militantisme-pro-algerie-francaise-de-1944-a-1962/</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Victor Delaporte consacrée au thème « Le militantisme pro-Algérie française de 1944 à 1962 ». Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Victor Delaporte &amp;#8211; Le militantisme pro-Algérie française de 1944 à 1962 </t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:01</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Catherine Denys – L’âge des révolutions : les anciens Pays-Bas</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-catherine-denys-lage-des-revolutions-les-anciens-pays-bas/</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Catherine Denys consacrée au thème « L’âge des révolutions : les anciens Pays-Bas ». Le podcast est proposé en version [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Catherine Denys &amp;#8211; L’âge des révolutions : les anciens Pays-Bas est app</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:55</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Glossaire bilingue sur les centres de données / Bilingual Glossary About Data Centers</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/dnl/dnl-hg-anglais/glossaire-bilingue-sur-les-centres-de-donnees-bilingual-glossary-about-data-centers</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-06-19 08:56</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Ressources de Géoconfluences pour traiter les programmes de géographie en CE2</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2/ressources-de-geoconfluences-pour-traiter-les-programmes-de-geographie-en-ce2</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:40</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Sujets de spécialité HGGSP 2026</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/concours-examens-programmes/sujets-de-specialite-hggsp-2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:05</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Ressources de Géoconfluences pour traiter les programmes de géographie en CE1</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2/ressources-de-geoconfluences-pour-traiter-les-programmes-de-geographie-en-ce1</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-06-17 07:45</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Irak: Wassermangel in einem Land nach dem Konflikt</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/dnl/dnl-hg-allemand/irak-wassermangel-in-einem-land-nach-dem-konflikt</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Im Irak hat der Wassermangel sich zu einer Wasserkrise entwickelt, welche durch den Klimawandel ausgelöst, sich dann aber durch den desolaten Zustand des Landes nach der Beilegung des Konflikts verstärkt hat, begleitet von einer ungenügenden Wasserwirtschaft sowie dem Bau von Stauanlagen in den Nachbarländern stromaufwärts. Der gesamte Irak ist davon betroffen, und zwar auch der Norden, die Weizenkammer des Landes, welchem bisher solche Engpässe erspart geblieben sind. Die Auswirkungen der Wasse</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-06-15 08:30</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Risque sismique et résilience dans l’espace urbain de Malatya (Turquie)</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/risques-et-societes/risque-sismique-et-resilience-malatya-turquie</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>En 2025, deux ans après les séismes du 6 février 2023 en Turquie, les conséquences sont encore visibles dans le paysage urbain de la ville de Malatya. Outre la vulnérabilité de ces territoires au risque sismique, cette situation reflète aussi une préparation insuffisante des pouvoirs publics face à la catastrophe et à la reconstruction. La résilience s'opère néanmoins sur le temps long, et s'accompagne localement de la construction d'une nouvelle culture du risque.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-06-12 12:35</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Les photographies lauréates du concours Géophoto Guyane 2026</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/evenements/photographies-laureates-du-concours-geophoto-guyane-2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Les élèves avaient pour consigne de transmettre une photographie accompagnée d'un commentaire mobilisant du vocabulaire géographique. Ces photographies sont susceptibles d'illustrer de nombreuses thématiques des programmes scolaires de géographie. Les versions originales de ces photographies ont été versées dans la banque d’images de Géoconfluences.</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:45</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Ressources de Géoconfluences pour traiter les programmes de géographie en CP</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2/selection-de-ressources-de-geoconfluences-pour-le-programme-de-geographie-en-cp</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:40</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Ressources pour le cycle 2</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:12</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Étude de cas</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/france-espaces-ruraux-periurbains/etude-de-cas</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:13</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Géographie intime des capitales. Rêves d'Etat, vie des citoyens</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/ageoda/geographie-intime-des-capitales-reves-detat-vie-des-citoyens</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Exposition photo</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-06-09 06:55</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Les Glorieuses (Îles éparses) et Diego Garcia (archipel des Chagos) : des aires marines protégées au service des ZEE</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/geographie-du-politique/articles/glorieuses-iles-eparses-et-diego-garcia-archipel-des-chagos-des-amp-au-service-des-zee</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>En droit international, la "terre commande la mer" : c'est la possession des terres qui justifie le contrôle des eaux. Deux puissances maritimes, la France et le Royaume-Uni, tentent d'inverser la logique. En plaçant les espaces maritimes sous protection environnementale, ils espèrent consolider leur contrôle sur des archipels contestés. Mais dans les Îles Glorieuses comme dans les Chagos, cette stratégie du fait accompli se heurte aux réactions des États voisins, et peut crisper les tensions au</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:35</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Coupe du monde de football 2026 : les États-Unis et la géopolitique du sport</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/breves/coupe-du-monde-de-football-2026-les-etats-unis-et-la-geopolitique-du-sport</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Organisée du 11 juin au 19 juillet entre Canada, Mexique et États-Unis, la 23e Coupe du monde de football est un évènement majeur. Comme toutes les grandes compétitions sportives, le Mondial possède une forte dimension géopolitique, liée à sa médiatisation, voire à son instrumentalisation, dans un contexte complexe marqué par tensions internes et externes liées à la présidence de Donald Trump et la poursuite de la guerre au Moyen-Orient.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-06-08 11:25</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Les régions transfrontalières en Europe, laboratoires de recompositions territoriales</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/territoires-europeens-regions-etats-union/articles-scientifiques/les-regions-transfrontalieres-en-europe-laboratoires-de-recompositions-territoriales</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Au cœur de la construction européenne et d’intégration régionale, les régions transfrontalières sont des laboratoires de transformation territoriale. Entre recomposition de la région, retour des frontières, et politique européenne spécifique (INTERREG), elles participent de la création de nouvelles formes d'espaces transfrontaliers. Cet article est une proposition de synthèse sur les différentes formes de régions transfrontalières et leur évolution en Europe, menée en suivant deux exemples, la G</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:43</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:50</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Le prix du livre de géographie 2026 est attribué à Pascal Clerc (Émanciper ou contrôler ? Les élèves et l’école au XXIe siècle)</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/evenements/pascal-clerc-laureat-du-prix-du-livre-de-geographie-des-lyceens-et-etudiants-les-commentaires-des-eleves-et-etudiants</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Le Prix du livre de géographie des lycéens et étudiants 2026 a été décerné à Pascal Clerc pour "Émanciper ou contrôler ? Les élèves et l’école au XXIe siècle" (éditions Autrement). Les collégiens, lycéens et étudiants exposent leurs arguments en faveur de cet ouvrage.</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5182,6 +5841,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4935,7 +4935,6 @@
           <t>Cent cinquante ans après sa mort, quelle image de George Sand domine ? La scandaleuse ? La romantique défenseuse des paysans ? Son génie ne peut se réduire à ces clichés.</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4968,7 +4967,6 @@
           <t>Au XVIIIe siècle, la Suède expérimenta une forme de gouvernement proche du parlementarisme moderne. Lorsqu'un conflit institutionnel éclata en 1768, un roi décida de se mettre en grève, déclenchant une crise constitutionnelle qui interrogeait le rôle même de la monarchie.</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5001,7 +4999,6 @@
           <t>Pourquoi allume-t-on de grands feux à la Saint-Jean ? Pourquoi danse-t-on autour d’un mât décoré de fleurs ? Derrière ces traditions festives se cache un héritage complexe où se croisent croyances ancestrales, folklore et identité culturelle.</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5034,7 +5031,6 @@
           <t>Quarante ans après le quart de finale légendaire entre l’Argentine et l’Angleterre, la « Main de Dieu » continue de diviser. Peut-on célébrer un geste de tricherie tout en admirant le génie de Diego Maradona ?</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5067,7 +5063,6 @@
           <t>Depuis le début de l’année, plus de 150 attaques de drones ukrainiens ont visé des cibles en Russie, soit deux fois plus que l’an dernier et quatre fois plus qu’en 2024. L’article Les attaques de drones ukrainiens en Russie ont été multipliées par 13 depuis 2023 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5100,7 +5095,6 @@
           <t>Pourquoi lire Pierre Hassner est plus urgent que jamais. L’article Le philosophe normalien du moment géopolitique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5133,7 +5127,6 @@
           <t>Depuis plusieurs semaines, New Delhi subit une vague de chaleur intense, avec des températures dépassant fréquemment les 40°C. L’article La hausse des températures pourrait coûter à l’économie indienne jusqu’à 4,5&amp;#160;% de son PIB d’ici 2030 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -5166,7 +5159,6 @@
           <t>Le premier rendez-vous de la saison 2026-2027 est prévu le 29 juin 2026 à 20h30, avec Marie Digout, Thomas Gosselin et Marine Sorano. &amp;#160; &amp;#160; &amp;#160; L’article Opération Coup de pouce! pour le capes interne est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -5199,7 +5191,6 @@
           <t xml:space="preserve">Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Victor Delaporte consacrée au thème « Le militantisme pro-Algérie française de 1944 à 1962 ». Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Victor Delaporte &amp;#8211; Le militantisme pro-Algérie française de 1944 à 1962 </t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -5232,7 +5223,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2025-2026 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Catherine Denys consacrée au thème « L’âge des révolutions : les anciens Pays-Bas ». Le podcast est proposé en version [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Catherine Denys &amp;#8211; L’âge des révolutions : les anciens Pays-Bas est app</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -5260,8 +5250,6 @@
           <t>https://geoconfluences.ens-lyon.fr/programmes/dnl/dnl-hg-anglais/glossaire-bilingue-sur-les-centres-de-donnees-bilingual-glossary-about-data-centers</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -5289,8 +5277,6 @@
           <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2/ressources-de-geoconfluences-pour-traiter-les-programmes-de-geographie-en-ce2</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -5318,8 +5304,6 @@
           <t>https://geoconfluences.ens-lyon.fr/actualites/veille/concours-examens-programmes/sujets-de-specialite-hggsp-2026</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -5347,8 +5331,6 @@
           <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2/ressources-de-geoconfluences-pour-traiter-les-programmes-de-geographie-en-ce1</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -5381,7 +5363,6 @@
           <t>Im Irak hat der Wassermangel sich zu einer Wasserkrise entwickelt, welche durch den Klimawandel ausgelöst, sich dann aber durch den desolaten Zustand des Landes nach der Beilegung des Konflikts verstärkt hat, begleitet von einer ungenügenden Wasserwirtschaft sowie dem Bau von Stauanlagen in den Nachbarländern stromaufwärts. Der gesamte Irak ist davon betroffen, und zwar auch der Norden, die Weizenkammer des Landes, welchem bisher solche Engpässe erspart geblieben sind. Die Auswirkungen der Wasse</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -5414,7 +5395,6 @@
           <t>En 2025, deux ans après les séismes du 6 février 2023 en Turquie, les conséquences sont encore visibles dans le paysage urbain de la ville de Malatya. Outre la vulnérabilité de ces territoires au risque sismique, cette situation reflète aussi une préparation insuffisante des pouvoirs publics face à la catastrophe et à la reconstruction. La résilience s'opère néanmoins sur le temps long, et s'accompagne localement de la construction d'une nouvelle culture du risque.</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -5447,7 +5427,6 @@
           <t>Les élèves avaient pour consigne de transmettre une photographie accompagnée d'un commentaire mobilisant du vocabulaire géographique. Ces photographies sont susceptibles d'illustrer de nombreuses thématiques des programmes scolaires de géographie. Les versions originales de ces photographies ont été versées dans la banque d’images de Géoconfluences.</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -5475,8 +5454,6 @@
           <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2/selection-de-ressources-de-geoconfluences-pour-le-programme-de-geographie-en-cp</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -5504,8 +5481,6 @@
           <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-pour-le-cycle-2</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -5533,8 +5508,6 @@
           <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/france-espaces-ruraux-periurbains/etude-de-cas</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -5567,7 +5540,6 @@
           <t>Exposition photo</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -5600,7 +5572,6 @@
           <t>En droit international, la "terre commande la mer" : c'est la possession des terres qui justifie le contrôle des eaux. Deux puissances maritimes, la France et le Royaume-Uni, tentent d'inverser la logique. En plaçant les espaces maritimes sous protection environnementale, ils espèrent consolider leur contrôle sur des archipels contestés. Mais dans les Îles Glorieuses comme dans les Chagos, cette stratégie du fait accompli se heurte aux réactions des États voisins, et peut crisper les tensions au</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -5633,7 +5604,6 @@
           <t>Organisée du 11 juin au 19 juillet entre Canada, Mexique et États-Unis, la 23e Coupe du monde de football est un évènement majeur. Comme toutes les grandes compétitions sportives, le Mondial possède une forte dimension géopolitique, liée à sa médiatisation, voire à son instrumentalisation, dans un contexte complexe marqué par tensions internes et externes liées à la présidence de Donald Trump et la poursuite de la guerre au Moyen-Orient.</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5666,7 +5636,6 @@
           <t>Au cœur de la construction européenne et d’intégration régionale, les régions transfrontalières sont des laboratoires de transformation territoriale. Entre recomposition de la région, retour des frontières, et politique européenne spécifique (INTERREG), elles participent de la création de nouvelles formes d'espaces transfrontaliers. Cet article est une proposition de synthèse sur les différentes formes de régions transfrontalières et leur évolution en Europe, menée en suivant deux exemples, la G</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -5699,7 +5668,204 @@
           <t>Le Prix du livre de géographie des lycéens et étudiants 2026 a été décerné à Pascal Clerc pour "Émanciper ou contrôler ? Les élèves et l’école au XXIe siècle" (éditions Autrement). Les collégiens, lycéens et étudiants exposent leurs arguments en faveur de cet ouvrage.</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-06-20 06:46</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>À quoi sert la géopolitique ?</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/20/a-quoi-sert-la-geopolitique/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Le fondateur de la revue Hérodote retrace l’histoire d’une discipline longtemps marginalisée, aujourd’hui centrale. L’article À quoi sert la géopolitique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-06-20 04:30</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : au cours de la prochaine décennie, Moscou va consacrer 15 % de son PIB au paiement des intérêts de sa dette</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/20/economie-russe-au-cours-de-la-prochaine-decennie-moscou-va-consacrer-15-de-son-pib-au-paiement-des-interets-de-sa-dette/</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Sur les cinq premiers mois de l'année, le déficit budgétaire russe a atteint 6 000 milliards de roubles, soit 2,6&amp;#160;% du produit intérieur brut. L’article Économie russe&amp;#160;: au cours de la prochaine décennie, Moscou va consacrer 15&amp;#160;% de son PIB au paiement des intérêts de sa dette est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:19</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>En Iran, un changement de régime a eu lieu</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/19/en-iran-un-changement-de-regime-a-eu-lieu/</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Le régime des mollahs est-il en passe de prendre fin au profit d'un tournant brutalement pragmatique des Gardiens de la Révolution&amp;#160;? L’article En Iran, un changement de régime a eu lieu est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-06-19 16:58</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Le tableau des 16e de finale commence déjà à se remplir</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/19/le-tableau-des-16e-de-finale-commence-deja-a-se-remplir/</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Le Canada pourrait bientôt rejoindre le Mexique parmi les équipes déjà qualifiées pour la phase à élimination directe. Neuvième épisode de notre rendez-vous quotidien avec la Coupe du monde. Consultez ici les épisodes précédents. L’article Le tableau des 16e de finale commence déjà à se remplir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-06-19 14:58</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Le Brexit, dix ans après : 10 points pour chiffrer l’addition</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/19/le-brexit-dix-ans-apres/</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Le Brexit raconte une histoire paradoxale&amp;#160;: le Royaume-Uni a quitté l'Union sans vraiment s'en détacher. L’article Le Brexit, dix ans après&amp;#160;: 10 points pour chiffrer l’addition est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:20</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Alexandre Joly – Les hommes en noir du football</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/alexandre-joly-les-hommes-en-noir-du-football/</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#160; &amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1202785555?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#82</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5866,6 +6032,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5700,7 +5700,6 @@
           <t>Le fondateur de la revue Hérodote retrace l’histoire d’une discipline longtemps marginalisée, aujourd’hui centrale. L’article À quoi sert la géopolitique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -5733,7 +5732,6 @@
           <t>Sur les cinq premiers mois de l'année, le déficit budgétaire russe a atteint 6 000 milliards de roubles, soit 2,6&amp;#160;% du produit intérieur brut. L’article Économie russe&amp;#160;: au cours de la prochaine décennie, Moscou va consacrer 15&amp;#160;% de son PIB au paiement des intérêts de sa dette est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -5766,7 +5764,6 @@
           <t>Le régime des mollahs est-il en passe de prendre fin au profit d'un tournant brutalement pragmatique des Gardiens de la Révolution&amp;#160;? L’article En Iran, un changement de régime a eu lieu est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5799,7 +5796,6 @@
           <t>Le Canada pourrait bientôt rejoindre le Mexique parmi les équipes déjà qualifiées pour la phase à élimination directe. Neuvième épisode de notre rendez-vous quotidien avec la Coupe du monde. Consultez ici les épisodes précédents. L’article Le tableau des 16e de finale commence déjà à se remplir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -5832,7 +5828,6 @@
           <t>Le Brexit raconte une histoire paradoxale&amp;#160;: le Royaume-Uni a quitté l'Union sans vraiment s'en détacher. L’article Le Brexit, dix ans après&amp;#160;: 10 points pour chiffrer l’addition est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5865,7 +5860,270 @@
           <t>Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#160; &amp;#60;div style= »padding:75% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1202785555?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#82</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:42</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Oui, le football a une histoire aux États-Unis. Le « soccer » est devenu un sport populaire</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/oui-le-football-a-une-histoire-aux-etats-unis-le-soccer-est-devenu-un-sport-populaire-284594</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, le football n’est pas né avec l’arrivée de Lionel Messi en 2023 à la Major League Soccer (MLS), mais en 1913. Depuis, le soccer a trouvé son public et son modèle économique.</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:44</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Quelle éducation au vivant à l’heure de l’anthropocène ?</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quelle-education-au-vivant-a-lheure-de-lanthropocene-281654</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>À l’école, on tend à découper le savoir en disciplines afin d’en faciliter l’appropriation par les élèves. Mais cette décomposition en objets d’étude peut transmettre une vision fragmentée du vivant.</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-06-21 07:25</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Un tiers de l’humanité doit s’endetter pour vivre</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/un-tiers-de-lhumanite-doit-sendetter-pour-vivre-284126</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Emprunter pour manger, se loger ou se soigner&amp;nbsp;: pour plus de 2,5&amp;nbsp;milliards de personnes, la dette est un outil ordinaire de survie.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:00</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Votre cerveau pourrait être le dernier mot de passe impossible à hacker</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/21/votre-cerveau-pourrait-etre-le-dernier-mot-de-passe-que-lon-ne-peut-pas-hacker/</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Face au développement vertigineux de la cybercriminalité, des scientifiques travaillent à une nouvelle forme d'authentification continue basée sur la bio-cryptographie et utilisant les ondes cérébrales. L’article Votre cerveau pourrait être le dernier mot de passe impossible à hacker est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-06-21 04:00</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi les élites gagnent toujours</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/21/pourquoi-les-elites-gagnent-toujours/</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Un siècle après, l’école italienne de l’élitisme reste extraordinairement pertinente pour analyser le Brexit, Trump et la crise de la démocratie. L’article Pourquoi les élites gagnent toujours est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-06-20 17:50</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>En Coupe du monde, les États-Unis commencent à rêver</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/20/en-coupe-du-monde-les-etats-unis-commencent-a-rever/</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Deux matchs, deux victoires&amp;#160;: pour la première fois depuis 1930, les États-Unis enchaînent en Coupe du monde. Mais le plus difficile reste à venir. L’article En Coupe du monde, les États-Unis commencent à rêver est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-06-20 15:44</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Qui est Andy Burnham, le travailliste qui pourrait devenir le prochain Premier ministre du Royaume-Uni ?</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/20/qui-est-andy-burnham-le-travailliste-qui-pourrait-devenir-le-prochain-premier-ministre-du-royaume-uni/</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Après avoir remporté l’élection du 19 juin à Makerfield, Andy Burnham se prépare à défier le Premier ministre, Keir Starmer. L’article Qui est Andy Burnham, le travailliste qui pourrait devenir le prochain Premier ministre du Royaume-Uni&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:43</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-06-20 06:46</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>À quoi sert la géopolitique ?</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/20/quoi-sert-la-geopolitique/</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Le fondateur de la revue Hérodote retrace l’histoire d’une discipline longtemps marginalisée, aujourd’hui centrale. L’article À quoi sert la géopolitique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6038,6 +6296,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId177"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5892,7 +5892,6 @@
           <t>Aux États-Unis, le football n’est pas né avec l’arrivée de Lionel Messi en 2023 à la Major League Soccer (MLS), mais en 1913. Depuis, le soccer a trouvé son public et son modèle économique.</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5925,7 +5924,6 @@
           <t>À l’école, on tend à découper le savoir en disciplines afin d’en faciliter l’appropriation par les élèves. Mais cette décomposition en objets d’étude peut transmettre une vision fragmentée du vivant.</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5958,7 +5956,6 @@
           <t>Emprunter pour manger, se loger ou se soigner&amp;nbsp;: pour plus de 2,5&amp;nbsp;milliards de personnes, la dette est un outil ordinaire de survie.</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5991,7 +5988,6 @@
           <t>Face au développement vertigineux de la cybercriminalité, des scientifiques travaillent à une nouvelle forme d'authentification continue basée sur la bio-cryptographie et utilisant les ondes cérébrales. L’article Votre cerveau pourrait être le dernier mot de passe impossible à hacker est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -6024,7 +6020,6 @@
           <t>Un siècle après, l’école italienne de l’élitisme reste extraordinairement pertinente pour analyser le Brexit, Trump et la crise de la démocratie. L’article Pourquoi les élites gagnent toujours est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -6057,7 +6052,6 @@
           <t>Deux matchs, deux victoires&amp;#160;: pour la première fois depuis 1930, les États-Unis enchaînent en Coupe du monde. Mais le plus difficile reste à venir. L’article En Coupe du monde, les États-Unis commencent à rêver est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -6090,7 +6084,6 @@
           <t>Après avoir remporté l’élection du 19 juin à Makerfield, Andy Burnham se prépare à défier le Premier ministre, Keir Starmer. L’article Qui est Andy Burnham, le travailliste qui pourrait devenir le prochain Premier ministre du Royaume-Uni&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -6123,7 +6116,336 @@
           <t>Le fondateur de la revue Hérodote retrace l’histoire d’une discipline longtemps marginalisée, aujourd’hui centrale. L’article À quoi sert la géopolitique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-06-21 18:45</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>« This is a final chance to change » : vers un tournant politique majeur au Royaume-Uni ?</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/this-is-a-final-chance-to-change-vers-un-tournant-politique-majeur-au-royaume-uni-285723</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Andy Burnham vient d’être élu député à la Chambre des Communes. Il va pouvoir défier, et possiblement vaincre, Keir Starmer, pour prendre la tête du parti travailliste et du pays entier.</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:04</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>La France dispose-t-elle d’assez d’électricité pour équiper tous les logements de climatiseurs ?</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/la-france-dispose-t-elle-dassez-delectricite-pour-equiper-tous-les-logements-de-climatiseurs/</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Équiper tous les logements de climatisation conduirait à une hausse de 15 TWh de la consommation d’électricité. L’article La France dispose-t-elle d&amp;rsquo;assez d&amp;rsquo;électricité pour équiper tous les logements de climatiseurs&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:02</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Comment Yves Lacoste a libéré la géographie</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/comment-yves-lacoste-a-libere-la-geographie/</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Polémiste et savant rebelle, le fondateur de Hérodote a fait de la géopolitique une discipline critique et un champ de bataille intellectuel. L’article Comment Yves Lacoste a libéré la géographie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-06-22 05:04</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Yves Lacoste (1929 – 2026) : père refondateur de la géopolitique française</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/yves-lacoste-1929-2026-pere-refondateur-de-la-geopolitique-francaise/</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>La trajectoire exceptionnelle du plus important géopoliticien de sa génération, expliquée par sa plus grande élève, aujourd'hui directrice de la revue Hérodote . L’article Yves Lacoste (1929 &amp;#8211; 2026)&amp;#160;: père refondateur de la géopolitique française est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-06-22 04:47</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Le régime iranien a-t-il encore besoin de haïr l’Amérique ?</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/le-regime-iranien-a-t-il-toujours-besoin-de-faire-la-guerre-a-lamerique/</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>La décapitation de la génération révolutionnaire a ouvert un conflit profond entre une faction qui veut venger ses martyrs et une qui veut reconstruire le pays. L’article Le régime iranien a-t-il encore besoin de haïr l’Amérique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-06-22 04:30</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>À deux semaines du 4 juillet, près de 40 % des Américains doutent que le pays existe encore dans 250 ans</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/a-deux-semaines-de-4-juillet-pres-de-40-des-americains-doutent-que-le-pays-existe-encore-dans-250-ans/</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>De plus, ils sont 64&amp;#160;% à estimer que la démocratie américaine risque de s'effondrer et 77&amp;#160;% à anticiper une hausse de la violence politique. L’article À deux semaines du 4 juillet, près de 40&amp;#160;% des Américains doutent que le pays existe encore dans 250 ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-06-21 17:18</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Après de nouvelles menaces de Donald Trump, l’Iran se serait retiré des négociations en cours en Suisse</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/21/liran-se-serait-retire-des-negociations-en-cours-en-suisse/</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Les discussions commencées ce dimanche, 21 juin, en Suisse ont déjà été interrompues après que le président américain a averti qu’il pourrait frapper à nouveau l’Iran si le Hezbollah poursuivait ses opérations au Liban. L’article Après de nouvelles menaces de Donald Trump, l’Iran se serait retiré des négociations en cours en Suisse est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:57</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>À la Coupe du monde, la crise des pauses fraîcheur</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/21/a-la-coupe-du-monde-la-crise-des-pauses-fraicheurs/</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Quelques heures après l’exploit historique de Curaçao, les pauses hydratation s’imposent comme l’un des sujets les plus débattus. L’article À la Coupe du monde, la crise des pauses fraîcheur est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-06-21 16:50</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Elon Musk et le coup d’État futuriste de SpaceX</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/21/elon-musk-et-le-coup-detat-futuriste-de-spacex/</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Pour résister aux cauchemars du Muskverse , il faut déchiffrer sa stratégie narrative. L’article Elon Musk et le coup d&amp;rsquo;État futuriste de SpaceX est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:34</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:15</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Image à la une. La perception ambivalente de l’éolien en Nouvelle-Aquitaine</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/a-la-une/image-a-la-une/la-perception-ambivalente-de-l-eolien-en-nouvelle-aquitaine</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Dans les plaines agricoles du nord de la Nouvelle-Aquitaine (ancienne région Poitou-Charentes), un nouveau paysage s’impose : une verticalité marquée par l’alignement d’éoliennes qui pointent à l’horizon des territoires ruraux. Les deux Charentes, la Vienne, la Haute-Vienne et les Deux-Sèvres sont à l’avant-garde de ces territoires en recomposition, où se redéfinissent les rapports à l’espace, mais aussi les représentations qui leur sont associées.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6304,6 +6626,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6148,7 +6148,6 @@
           <t>Andy Burnham vient d’être élu député à la Chambre des Communes. Il va pouvoir défier, et possiblement vaincre, Keir Starmer, pour prendre la tête du parti travailliste et du pays entier.</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -6181,7 +6180,6 @@
           <t>Équiper tous les logements de climatisation conduirait à une hausse de 15 TWh de la consommation d’électricité. L’article La France dispose-t-elle d&amp;rsquo;assez d&amp;rsquo;électricité pour équiper tous les logements de climatiseurs&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -6214,7 +6212,6 @@
           <t>Polémiste et savant rebelle, le fondateur de Hérodote a fait de la géopolitique une discipline critique et un champ de bataille intellectuel. L’article Comment Yves Lacoste a libéré la géographie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -6247,7 +6244,6 @@
           <t>La trajectoire exceptionnelle du plus important géopoliticien de sa génération, expliquée par sa plus grande élève, aujourd'hui directrice de la revue Hérodote . L’article Yves Lacoste (1929 &amp;#8211; 2026)&amp;#160;: père refondateur de la géopolitique française est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -6280,7 +6276,6 @@
           <t>La décapitation de la génération révolutionnaire a ouvert un conflit profond entre une faction qui veut venger ses martyrs et une qui veut reconstruire le pays. L’article Le régime iranien a-t-il encore besoin de haïr l’Amérique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -6313,7 +6308,6 @@
           <t>De plus, ils sont 64&amp;#160;% à estimer que la démocratie américaine risque de s'effondrer et 77&amp;#160;% à anticiper une hausse de la violence politique. L’article À deux semaines du 4 juillet, près de 40&amp;#160;% des Américains doutent que le pays existe encore dans 250 ans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -6346,7 +6340,6 @@
           <t>Les discussions commencées ce dimanche, 21 juin, en Suisse ont déjà été interrompues après que le président américain a averti qu’il pourrait frapper à nouveau l’Iran si le Hezbollah poursuivait ses opérations au Liban. L’article Après de nouvelles menaces de Donald Trump, l’Iran se serait retiré des négociations en cours en Suisse est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -6379,7 +6372,6 @@
           <t>Quelques heures après l’exploit historique de Curaçao, les pauses hydratation s’imposent comme l’un des sujets les plus débattus. L’article À la Coupe du monde, la crise des pauses fraîcheur est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -6412,7 +6404,6 @@
           <t>Pour résister aux cauchemars du Muskverse , il faut déchiffrer sa stratégie narrative. L’article Elon Musk et le coup d&amp;rsquo;État futuriste de SpaceX est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -6445,7 +6436,299 @@
           <t>Dans les plaines agricoles du nord de la Nouvelle-Aquitaine (ancienne région Poitou-Charentes), un nouveau paysage s’impose : une verticalité marquée par l’alignement d’éoliennes qui pointent à l’horizon des territoires ruraux. Les deux Charentes, la Vienne, la Haute-Vienne et les Deux-Sèvres sont à l’avant-garde de ces territoires en recomposition, où se redéfinissent les rapports à l’espace, mais aussi les représentations qui leur sont associées.</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:43</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Comment Marc Bloch a révolutionné le métier d’historien</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-marc-bloch-a-revolutionne-le-metier-dhistorien-285757</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Marc Bloch (1886-1944), historien et résistant, entre au Panthéon ce 23&amp;nbsp;juin. Il fit dialoguer histoire et sciences sociales en refusant de s’enfermer dans une histoire nationale.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:43</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Supporters, joueurs, stades, territoires : la géographie cachée du football</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/supporters-joueurs-stades-territoires-la-geographie-cachee-du-football-285202</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Le football mobilise bien des enjeux géographiques&amp;nbsp;: territoires, mobilités, identités et usages de l’espace&amp;nbsp;– du stade aux foules mondialisées.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:59</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Colombie : l’élection d’Abelardo De la Espriella marque une nouvelle victoire pour Trump en Amérique latine</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/23/colombie-lelection-dabelardo-de-la-espriella-marque-une-nouvelle-victoire-pour-trump-en-amerique-latine/</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Abelardo De la Espriella, candidat d’extrême droite soutenu par Trump, a remporté dimanche le second tour de l’élection présidentielle en Colombie. L’article Colombie&amp;#160;: l’élection d’Abelardo De la Espriella marque une nouvelle victoire pour Trump en Amérique latine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-06-23 04:30</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>La géo-ingénierie est une idée dangereuse que nous ne pouvons plus éluder</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/23/geo-ingenierie-une-idee-dangereuse-que-nous-ne-pouvons-plus-eluder/</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Pour lutter contre les risques existentiels du réchauffement climatique, faut-il atténuer la lumière du soleil&amp;#160;? L’article La géo-ingénierie est une idée dangereuse que nous ne pouvons plus éluder est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-06-23 04:30</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Avec GLM-5.2, la Chine a-t-elle ouvert un nouveau « moment DeepSeek » ?</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/23/avec-glm-5-2-la-chine-a-t-elle-ouvert-un-nouveau-moment-deepseek/</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Le nouveau modèle de Zhipu IA affiche de meilleures performances que les derniers modèles d’Anthropic et d'OpenAI. L’article Avec GLM-5.2, la Chine a-t-elle ouvert un nouveau «&amp;#160;moment DeepSeek&amp;#160;»&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-06-22 17:30</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Messi ou Mbappé : quel joueur sera le meilleur buteur de la Coupe du monde ?</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/messi-ou-mbappe-quel-joueur-sera-le-meilleur-buteur-de-la-coupe-du-monde/</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Kylian Mbappé, âgé de 27 ans, a déjà inscrit 14 buts en Coupe du monde durant sa carrière. L’article Messi ou Mbappé&amp;#160;: quel joueur sera le meilleur buteur de la Coupe du monde&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-06-22 16:47</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Jusqu’à 6 navires chinois sont déployés en permanence autour de Taïwan</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/22/jusqua-6-navires-chinois-sont-deployes-en-permanence-autour-de-taiwan/</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>C’est deux fois plus qu’en 2020, et six fois plus par rapport à la fin des années 2010. L’article Jusqu’à 6 navires chinois sont déployés en permanence autour de Taïwan est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:05</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Yves Lacoste est mort le 20 juin 2026 – revue de presse</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/revues-de-presse/yves-lacoste-est-mort-le-20-juin-2026-revue-de-presse</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Yves Lacoste a réhabilité la géopolitique, en particulier avec sa thèse sur la guerre du Vietnam et son ouvrage de 1976, "La géographie, ça sert, d'abord, à faire la guerre". Entouré à l'université de Vincennes puis de Paris VIII par une équipe composée notamment de Béatrice Giblin, il a fondé la revue Hérodote en 1976.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:57</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-06-22 06:00</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Lettre d'information n° 223</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/a-propos/lettres-dinformation/lettre-information-223</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6636,6 +6919,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId196"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6468,7 +6468,6 @@
           <t>Marc Bloch (1886-1944), historien et résistant, entre au Panthéon ce 23&amp;nbsp;juin. Il fit dialoguer histoire et sciences sociales en refusant de s’enfermer dans une histoire nationale.</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -6501,7 +6500,6 @@
           <t>Le football mobilise bien des enjeux géographiques&amp;nbsp;: territoires, mobilités, identités et usages de l’espace&amp;nbsp;– du stade aux foules mondialisées.</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -6534,7 +6532,6 @@
           <t>Abelardo De la Espriella, candidat d’extrême droite soutenu par Trump, a remporté dimanche le second tour de l’élection présidentielle en Colombie. L’article Colombie&amp;#160;: l’élection d’Abelardo De la Espriella marque une nouvelle victoire pour Trump en Amérique latine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -6567,7 +6564,6 @@
           <t>Pour lutter contre les risques existentiels du réchauffement climatique, faut-il atténuer la lumière du soleil&amp;#160;? L’article La géo-ingénierie est une idée dangereuse que nous ne pouvons plus éluder est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -6600,7 +6596,6 @@
           <t>Le nouveau modèle de Zhipu IA affiche de meilleures performances que les derniers modèles d’Anthropic et d'OpenAI. L’article Avec GLM-5.2, la Chine a-t-elle ouvert un nouveau «&amp;#160;moment DeepSeek&amp;#160;»&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -6633,7 +6628,6 @@
           <t>Kylian Mbappé, âgé de 27 ans, a déjà inscrit 14 buts en Coupe du monde durant sa carrière. L’article Messi ou Mbappé&amp;#160;: quel joueur sera le meilleur buteur de la Coupe du monde&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -6666,7 +6660,6 @@
           <t>C’est deux fois plus qu’en 2020, et six fois plus par rapport à la fin des années 2010. L’article Jusqu’à 6 navires chinois sont déployés en permanence autour de Taïwan est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -6699,7 +6692,6 @@
           <t>Yves Lacoste a réhabilité la géopolitique, en particulier avec sa thèse sur la guerre du Vietnam et son ouvrage de 1976, "La géographie, ça sert, d'abord, à faire la guerre". Entouré à l'université de Vincennes puis de Paris VIII par une équipe composée notamment de Béatrice Giblin, il a fondé la revue Hérodote en 1976.</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -6727,8 +6719,336 @@
           <t>https://geoconfluences.ens-lyon.fr/a-propos/lettres-dinformation/lettre-information-223</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:17</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Violences sexuelles sur mineurs : deux siècles de bruit médiatique et d’inertie</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/violences-sexuelles-sur-mineurs-deux-siecles-de-bruit-mediatique-et-dinertie-285500</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Malgré les révélations qui éclatent régulièrement dans l’actualité à leur sujet, les violences sexuelles sur mineurs restent invisibilisées dans la société.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:15</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Alliances d’universités européennes : porter des projets communs, un défi linguistique ?</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/alliances-duniversites-europeennes-porter-des-projets-communs-un-defi-linguistique-282630</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Comment coordonner des formations et des projets de recherche issus d’environnements linguistiques différents&amp;nbsp;? La question recoupe des enjeux à la fois pragmatiques et stratégiques.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:25</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>« L’arc de Trump » : une glorification des États-Unis… et surtout de leur président actuel</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/larc-de-trump-une-glorification-des-etats-unis-et-surtout-de-leur-president-actuel-285682</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>À l’occasion des 250&amp;nbsp;ans des États-Unis, Donald Trump veut bâtir un arc de triomphe géant à Washington. Un monument qui sera avant tout à sa propre gloire…</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-06-23 14:16</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Comment la diaspora iranienne vit la guerre à distance</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-la-diaspora-iranienne-vit-la-guerre-a-distance-283713</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Les Iraniens de l’étranger, obnubilés par la situation dans leur pays, traversent une période très compliquée sur le plan psychologique.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:48</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Dans les villes européennes, seulement 47 % de la population voit au moins 3 arbres depuis sa fenêtre</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/24/dans-les-villes-europeennes-seulement-47-de-la-population-voit-au-moins-3-arbres-depuis-sa-fenetre/</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>En plus d’avoir un impact positif sur la santé mentale et de contribuer à une meilleure forme physique, la couverture arborée en ville contribue à la réduction des îlots de chaleur. L’article Dans les villes européennes, seulement 47&amp;#160;% de la population voit au moins 3 arbres depuis sa fenêtre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-06-24 04:30</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>La Chine américanise sa puissance</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/24/la-chine-americanise-sa-puissance/</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>En se dotant d'un nouvel arsenal juridique pour transformer l'interdépendance en levier, le Parti communiste s'inspire de plus en plus des doctrines de Washington. L’article La Chine américanise sa puissance est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-06-24 04:30</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Malgré une reprise du trafic, l’incertitude persiste dans le détroit d’Ormuz</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/24/malgre-une-reprise-du-trafic-lincertitude-persiste-dans-le-detroit-dormuz/</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Les armateurs, qui perçoivent l’accord signé entre Téhéran et Washington comme un signal positif, font toujours l’objet d’instructions contradictoires. L’article Malgré une reprise du trafic, l’incertitude persiste dans le détroit d’Ormuz est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:35</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>L’Afrique est le continent qui a le plus profité de l’élargissement de la compétition à 48 équipes</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/23/lafrique-est-le-continent-qui-a-le-plus-profite-de-lelargissement-de-la-competition-a-48-equipes/</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Le Ghana et la République démocratique du Congo jouent ce soir leur qualification pour la phase éliminatoire. L’article L’Afrique est le continent qui a le plus profité de l’élargissement de la compétition à 48 équipes est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-06-23 15:54</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Le Testament de Marc Bloch lu par Carlo Ginzburg</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/23/le-testament-de-marc-bloch-lu-par-carlo-ginzburg/</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>À l'occasion de sa panthéonisation, nous republions ce texte étincelant, accompagné d'une note introductive du grand historien italien récemment disparu. L’article Le Testament de Marc Bloch lu par Carlo Ginzburg est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:43</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-06-23 15:25</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Il fait plus chaud en France que sur 99 % de la planète : pourquoi la vague de chaleur qui frappe le pays est historique</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/23/il-fait-plus-chaud-aujourdhui-en-france-que-sur-99-de-la-planete-pourquoi-la-vague-de-chaleur-qui-frappe-le-pays-est-historique/</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Après avoir connu la nuit la plus chaude depuis 1947, du 22 au 23 juin, la France a connu la journée la plus chaude de son histoire récente. L’article Il fait plus chaud en France que sur 99&amp;#160;% de la planète&amp;#160;: pourquoi la vague de chaleur qui frappe le pays est historique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6928,6 +7248,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId206"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6751,7 +6751,6 @@
           <t>Malgré les révélations qui éclatent régulièrement dans l’actualité à leur sujet, les violences sexuelles sur mineurs restent invisibilisées dans la société.</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -6784,7 +6783,6 @@
           <t>Comment coordonner des formations et des projets de recherche issus d’environnements linguistiques différents&amp;nbsp;? La question recoupe des enjeux à la fois pragmatiques et stratégiques.</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -6817,7 +6815,6 @@
           <t>À l’occasion des 250&amp;nbsp;ans des États-Unis, Donald Trump veut bâtir un arc de triomphe géant à Washington. Un monument qui sera avant tout à sa propre gloire…</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -6850,7 +6847,6 @@
           <t>Les Iraniens de l’étranger, obnubilés par la situation dans leur pays, traversent une période très compliquée sur le plan psychologique.</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -6883,7 +6879,6 @@
           <t>En plus d’avoir un impact positif sur la santé mentale et de contribuer à une meilleure forme physique, la couverture arborée en ville contribue à la réduction des îlots de chaleur. L’article Dans les villes européennes, seulement 47&amp;#160;% de la population voit au moins 3 arbres depuis sa fenêtre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -6916,7 +6911,6 @@
           <t>En se dotant d'un nouvel arsenal juridique pour transformer l'interdépendance en levier, le Parti communiste s'inspire de plus en plus des doctrines de Washington. L’article La Chine américanise sa puissance est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6949,7 +6943,6 @@
           <t>Les armateurs, qui perçoivent l’accord signé entre Téhéran et Washington comme un signal positif, font toujours l’objet d’instructions contradictoires. L’article Malgré une reprise du trafic, l’incertitude persiste dans le détroit d’Ormuz est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -6982,7 +6975,6 @@
           <t>Le Ghana et la République démocratique du Congo jouent ce soir leur qualification pour la phase éliminatoire. L’article L’Afrique est le continent qui a le plus profité de l’élargissement de la compétition à 48 équipes est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7015,7 +7007,6 @@
           <t>À l'occasion de sa panthéonisation, nous republions ce texte étincelant, accompagné d'une note introductive du grand historien italien récemment disparu. L’article Le Testament de Marc Bloch lu par Carlo Ginzburg est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -7048,7 +7039,303 @@
           <t>Après avoir connu la nuit la plus chaude depuis 1947, du 22 au 23 juin, la France a connu la journée la plus chaude de son histoire récente. L’article Il fait plus chaud en France que sur 99&amp;#160;% de la planète&amp;#160;: pourquoi la vague de chaleur qui frappe le pays est historique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:53</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Le boycott académique contre Israël est minoritaire et traduit l’émergence de nouvelles normes académiques</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-boycott-academique-contre-israel-est-minoritaire-et-traduit-lemergence-de-nouvelles-normes-academiques-284203</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>De l’Allemagne de l’après-Première Guerre mondiale à l’Afrique du Sud de l’apartheid, les boycotts académiques ont jalonné l’histoire contemporaine. Le cas israélien ravive aujourd’hui les interrogations sur leur légitimité et leur efficacité.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:52</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>La démocratie en recul face à la poussée des autoritarismes</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-democratie-en-recul-face-a-la-poussee-des-autoritarismes-285091</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Partout ou presque, l’autoritarisme gagne du terrain, sous une forme spécifique mêlant nationalisme sourcilleux et capitalisme débridé. Enquête sur un modèle qui défie ouvertement les démocraties libérales.</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:52</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Coupe du monde de football 2026 : faut-il craindre une hausse des violences envers les femmes ?</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/coupe-du-monde-de-football-2026-faut-il-craindre-une-hausse-des-violences-envers-les-femmes-285265</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Les violences domestiques augmentent souvent les jours de match. Dans plusieurs pays, associations et autorités tentent d’endiguer le phénomène.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-06-25 09:39</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Les classements des premiers groupes laissent apparaître quelques surprises</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/25/les-classements-des-premiers-groupes-laissent-apparaitre-quelques-surprises/</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L'Afrique du Sud a notamment décroché sa première qualification pour la phase à élimination directe de son histoire. L’article Les classements des premiers groupes laissent apparaître quelques surprises est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-06-25 05:12</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Résoudre l’énigme Trump</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/25/resoudre-lenigme-trump/</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Si l'erratique est devenu une méthode, c’est que dans le nouveau paradigme du capitalisme politique américain, la géopolitique, ça sert, d’abord, à faire des actifs. L’article Résoudre l&amp;rsquo;énigme Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-06-25 04:30</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Après El Fasher, le risque de nouveaux massacres commis par les FSR pèse sur El Obeid</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/25/apres-el-fasher-le-risque-de-nouveaux-massacres-commis-par-les-fsr-pese-sur-el-obeid/</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Les Forces de soutien rapide auraient reçu d’importants renforts autour d’El Obeid, dans le cadre du siège maintenu autour de la ville depuis 2023. L’article Après El Fasher, le risque de nouveaux massacres commis par les FSR pèse sur El Obeid est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:07</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : le marché boursier est à son niveau le plus faible depuis mars 2023</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/24/economie-russe-le-marche-boursier-est-a-son-niveau-le-plus-faible-depuis-mars-2023/</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>La dégradation de la situation financière du pays et l'intensification des frappes ukrainiennes sur les infrastructures énergétiques ont provoqué de vives inquiétudes chez les investisseurs. L’article Économie russe&amp;#160;: le marché boursier est à son niveau le plus faible depuis mars 2023 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-06-24 13:24</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo marque l’histoire, alors que Haïti fait ses adieux à la Coupe du monde</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/24/cristiano-ronaldo-marque-lhistoire-alors-que-haiti-fait-ses-adieux-a-la-coupe-du-monde/</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Critiqué après son premier match, Ronaldo a répondu par un doublé face à l'Ouzbékistan. À l’approche de la phase à éliminations directes, le débat se concentre désormais sur la modification des règles des tirs au but. L’article Cristiano Ronaldo marque l’histoire, alors que Haïti fait ses adieux à la Coupe du monde est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:38</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-06-24 12:26</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>L’État islamique est en train de s’étendre en Afrique de l’Ouest</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/24/letat-islamique-est-en-train-de-setendre-en-afrique-de-louest/</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Entretien fleuve avec l’un des meilleurs spécialistes du terrain sahélien. L’article L’État islamique est en train de s’étendre en Afrique de l’Ouest est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7258,6 +7545,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId215"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7071,7 +7071,6 @@
           <t>De l’Allemagne de l’après-Première Guerre mondiale à l’Afrique du Sud de l’apartheid, les boycotts académiques ont jalonné l’histoire contemporaine. Le cas israélien ravive aujourd’hui les interrogations sur leur légitimité et leur efficacité.</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -7104,7 +7103,6 @@
           <t>Partout ou presque, l’autoritarisme gagne du terrain, sous une forme spécifique mêlant nationalisme sourcilleux et capitalisme débridé. Enquête sur un modèle qui défie ouvertement les démocraties libérales.</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -7137,7 +7135,6 @@
           <t>Les violences domestiques augmentent souvent les jours de match. Dans plusieurs pays, associations et autorités tentent d’endiguer le phénomène.</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -7170,7 +7167,6 @@
           <t>L'Afrique du Sud a notamment décroché sa première qualification pour la phase à élimination directe de son histoire. L’article Les classements des premiers groupes laissent apparaître quelques surprises est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -7203,7 +7199,6 @@
           <t>Si l'erratique est devenu une méthode, c’est que dans le nouveau paradigme du capitalisme politique américain, la géopolitique, ça sert, d’abord, à faire des actifs. L’article Résoudre l&amp;rsquo;énigme Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -7236,7 +7231,6 @@
           <t>Les Forces de soutien rapide auraient reçu d’importants renforts autour d’El Obeid, dans le cadre du siège maintenu autour de la ville depuis 2023. L’article Après El Fasher, le risque de nouveaux massacres commis par les FSR pèse sur El Obeid est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7269,7 +7263,6 @@
           <t>La dégradation de la situation financière du pays et l'intensification des frappes ukrainiennes sur les infrastructures énergétiques ont provoqué de vives inquiétudes chez les investisseurs. L’article Économie russe&amp;#160;: le marché boursier est à son niveau le plus faible depuis mars 2023 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -7302,7 +7295,6 @@
           <t>Critiqué après son premier match, Ronaldo a répondu par un doublé face à l'Ouzbékistan. À l’approche de la phase à éliminations directes, le débat se concentre désormais sur la modification des règles des tirs au but. L’article Cristiano Ronaldo marque l’histoire, alors que Haïti fait ses adieux à la Coupe du monde est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -7335,7 +7327,270 @@
           <t>Entretien fleuve avec l’un des meilleurs spécialistes du terrain sahélien. L’article L’État islamique est en train de s’étendre en Afrique de l’Ouest est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:25</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Céline Dion, la superstar qui rapproche le Québec et la France</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/celine-dion-la-superstar-qui-rapproche-le-quebec-et-la-france-285777</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Plus qu’une chanteuse, Céline Dion est devenue en trente&amp;nbsp;ans la figure emblématique des relations culturelles entre la France et le Québec.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:29</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Quand l’IA s’invite dans nos relations, la véritable intimité tend à disparaître</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-lia-sinvite-dans-nos-relations-la-veritable-intimite-tend-a-disparaitre-285287</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>La banalisation de l’IA sape la curiosité de soi et l’envie de prendre des risques, nécessaires à la construction d’une véritable intimité et de relations qui ont du sens.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:28</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>De Southampton à Belfast : comment Nigel Farage fait entrer les thèmes de l’extrême droite dans le débat public britannique</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/de-southampton-a-belfast-comment-nigel-farage-fait-entrer-les-themes-de-lextreme-droite-dans-le-debat-public-britannique-285823</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Nigel Farage, à la tête du parti donné favori pour remporter les prochaines législatives au Royaume-Uni, banalise volontairement des slogans jusqu’ici cantonnés aux groupuscules d’extrême droite.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:08</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>La Norvège peut-elle mettre en difficulté la France pour la suite de la compétition ?</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/26/la-norvege-peut-elle-mettre-en-difficulte-la-france-pour-la-suite-de-la-competition/</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>La victoire de ce soir est clef, car elle déterminera le parcours de chaque équipe en phase éliminatoire. L’article La Norvège peut-elle mettre en difficulté la France pour la suite de la compétition&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-06-26 04:30</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>L’IA est l’une des technologies qui suscite le plus d’hostilité depuis l’essor d’Internet</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/26/lia-est-lune-des-technologies-qui-suscite-le-plus-dhostilite-depuis-lessor-dinternet/</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, seulement 16&amp;#160;% de la population considère que l’intelligence artificielle va avoir un impact positif sur la société. L’article L&amp;rsquo;IA est l’une des technologies qui suscite le plus d’hostilité depuis l&amp;rsquo;essor d&amp;rsquo;Internet est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-06-25 16:32</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Qui est le général Donahue, purgé par le secrétaire à la Défense de Trump ?</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/25/qui-est-le-general-donahue-purge-par-le-secretaire-a-la-defense-de-trump/</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Donahue est la dernière cible de la purge menée par Pete Hegseth parmi les hauts gradés de l’armée. L’article Qui est le général Donahue, purgé par le secrétaire à la Défense de Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:18</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi les Chinois ne dépensent pas ?</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/25/pourquoi-les-chinois-ne-depensent-pas/</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Une enquête à hauteur de citoyen, signée par l’un des meilleurs sociologues spécialistes de la Chine. L’article Pourquoi les Chinois ne dépensent pas&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26 11:43</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:04</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Il a fait plus chaud en France que dans presque un tiers du désert du Sahara (carte inédite)</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/25/mercredi-il-faisait-plus-chaud-en-france-que-dans-presque-un-tiers-du-desert-du-sahara/</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Avec une température moyenne de 30°C, la France a connu mercredi des températures supérieures à celles relevées dans 30,8&amp;#160;% du Sahara. L’article Il a fait plus chaud en France que dans presque un tiers du désert du Sahara (carte inédite) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7554,6 +7809,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId223"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7359,7 +7359,6 @@
           <t>Plus qu’une chanteuse, Céline Dion est devenue en trente&amp;nbsp;ans la figure emblématique des relations culturelles entre la France et le Québec.</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -7392,7 +7391,6 @@
           <t>La banalisation de l’IA sape la curiosité de soi et l’envie de prendre des risques, nécessaires à la construction d’une véritable intimité et de relations qui ont du sens.</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -7425,7 +7423,6 @@
           <t>Nigel Farage, à la tête du parti donné favori pour remporter les prochaines législatives au Royaume-Uni, banalise volontairement des slogans jusqu’ici cantonnés aux groupuscules d’extrême droite.</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -7458,7 +7455,6 @@
           <t>La victoire de ce soir est clef, car elle déterminera le parcours de chaque équipe en phase éliminatoire. L’article La Norvège peut-elle mettre en difficulté la France pour la suite de la compétition&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -7491,7 +7487,6 @@
           <t>Aux États-Unis, seulement 16&amp;#160;% de la population considère que l’intelligence artificielle va avoir un impact positif sur la société. L’article L&amp;rsquo;IA est l’une des technologies qui suscite le plus d’hostilité depuis l&amp;rsquo;essor d&amp;rsquo;Internet est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -7524,7 +7519,6 @@
           <t>Donahue est la dernière cible de la purge menée par Pete Hegseth parmi les hauts gradés de l’armée. L’article Qui est le général Donahue, purgé par le secrétaire à la Défense de Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -7557,7 +7551,6 @@
           <t>Une enquête à hauteur de citoyen, signée par l’un des meilleurs sociologues spécialistes de la Chine. L’article Pourquoi les Chinois ne dépensent pas&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -7590,7 +7583,237 @@
           <t>Avec une température moyenne de 30°C, la France a connu mercredi des températures supérieures à celles relevées dans 30,8&amp;#160;% du Sahara. L’article Il a fait plus chaud en France que dans presque un tiers du désert du Sahara (carte inédite) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:53</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Quand les religieuses prêtaient de l’argent : l’influence méconnue des couvents sur l’économie viennoise</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-les-religieuses-pretaient-de-largent-linfluence-meconnue-des-couvents-sur-leconomie-viennoise-285715</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Bien avant l’apparition des banques modernes, la Vienne médiévale reposait sur un vaste marché du crédit. Et parmi ses acteurs les plus fiables figuraient des communautés de religieuses, devenues des prêteuses incontournables.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:51</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Un portrait de Pocahontas daté de 1616 révèle le regard des colons anglais sur les peuples autochtones américains</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/un-portrait-de-pocahontas-date-de-1616-revele-le-regard-des-colons-anglais-sur-les-peuples-autochtones-americains-284216</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Bien loin de l'image popularisée par Disney, l'unique portrait réalisé du vivant de Pocahontas éclaire la manière dont les Anglais voyaient les peuples autochtones et justifiaient leur projet colonial.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-06-27 06:14</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Le populisme IA est en train d’arriver. Nous ne sommes pas prêts</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/27/le-populisme-ia-est-en-train-darriver-nous-ne-sommes-pas-prets/</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L'anthropologie sauvage d’une des nouvelles voix les plus influentes de la Silicon Valley. L’article Le populisme IA est en train d’arriver. Nous ne sommes pas prêts est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-06-27 04:30</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>En Russie, l’intérêt pour l’achat de systèmes anti-drones sur Internet est au plus haut depuis 2023</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/27/en-russie-linteret-pour-lachat-de-systemes-anti-drones-sur-internet-est-au-plus-haut-depuis-2023/</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Sur Yandex, les recherches concernant l’achat de systèmes anti-drones ont dépassé les 8 000 par semaine à la mi-juin, soit une hausse de 35&amp;#160;% par rapport à la fin du mois de mai. L’article En Russie, l’intérêt pour l’achat de systèmes anti-drones sur Internet est au plus haut depuis 2023 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:18</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Une voiture électrique sur dix vendue en Europe est désormais chinoise</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/26/une-voiture-electrique-sur-dix-vendue-en-europe-est-desormais-chinoise/</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Près d’un quart des voitures hybrides et 11&amp;#160;% des voitures électriques vendues le mois dernier en Europe étaient de marque chinoise, soit presque deux fois plus qu’il y a un an. L’article Une voiture électrique sur dix vendue en Europe est désormais chinoise est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:41</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Ce que l’État le plus numérique du continent a compris de l’IA</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/26/ce-que-lestonie-a-compris-de-lia/</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Une conversation fleuve avec la ministre de l’Éducation de l’Estonie. L’article Ce que l’État le plus numérique du continent a compris de l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27 10:56</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-06-26 12:31</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Comment le réchauffement climatique a rendu possible la vague de chaleur qui frappe l’Europe</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/26/comment-le-rechauffement-climatique-rend-possible-la-vague-de-chaleur-qui-frappe-leurope/</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Selon une étude, la vague de chaleur que traverse l’Europe occidentale serait impossible sans le réchauffement climatique causé par les émissions de gaz à effet de serre. L’article Comment le réchauffement climatique a rendu possible la vague de chaleur qui frappe l’Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7817,6 +8040,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId230"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7615,7 +7615,6 @@
           <t>Bien avant l’apparition des banques modernes, la Vienne médiévale reposait sur un vaste marché du crédit. Et parmi ses acteurs les plus fiables figuraient des communautés de religieuses, devenues des prêteuses incontournables.</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -7648,7 +7647,6 @@
           <t>Bien loin de l'image popularisée par Disney, l'unique portrait réalisé du vivant de Pocahontas éclaire la manière dont les Anglais voyaient les peuples autochtones et justifiaient leur projet colonial.</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -7681,7 +7679,6 @@
           <t>L'anthropologie sauvage d’une des nouvelles voix les plus influentes de la Silicon Valley. L’article Le populisme IA est en train d’arriver. Nous ne sommes pas prêts est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -7714,7 +7711,6 @@
           <t>Sur Yandex, les recherches concernant l’achat de systèmes anti-drones ont dépassé les 8 000 par semaine à la mi-juin, soit une hausse de 35&amp;#160;% par rapport à la fin du mois de mai. L’article En Russie, l’intérêt pour l’achat de systèmes anti-drones sur Internet est au plus haut depuis 2023 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -7747,7 +7743,6 @@
           <t>Près d’un quart des voitures hybrides et 11&amp;#160;% des voitures électriques vendues le mois dernier en Europe étaient de marque chinoise, soit presque deux fois plus qu’il y a un an. L’article Une voiture électrique sur dix vendue en Europe est désormais chinoise est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -7780,7 +7775,6 @@
           <t>Une conversation fleuve avec la ministre de l’Éducation de l’Estonie. L’article Ce que l’État le plus numérique du continent a compris de l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -7813,7 +7807,303 @@
           <t>Selon une étude, la vague de chaleur que traverse l’Europe occidentale serait impossible sans le réchauffement climatique causé par les émissions de gaz à effet de serre. L’article Comment le réchauffement climatique a rendu possible la vague de chaleur qui frappe l’Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-06-28 08:59</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Robin des Bois était bien plus violent que la légende ne le raconte</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/robin-des-bois-etait-bien-plus-violent-que-la-legende-ne-le-raconte-286330</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Robin des Bois est devenu le hors-la-loi le plus célèbre de l'histoire. Pourtant, les récits médiévaux décrivent un personnage bien plus violent que celui de la légende, tandis que d'autres bandits, aujourd'hui oubliés, ont inspiré nombre de ses aventures.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-06-28 08:59</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Comment une dent de chèvre éclaire enfin les secrets de l'élevage dans la Grèce antique</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-une-dent-de-chevre-eclaire-enfin-les-secrets-de-lelevage-dans-la-grece-antique-286329</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Les grands banquets de la Grèce antique étaient-ils alimentés par des troupeaux nomades ou par les fermes locales ? L'analyse isotopique apporte une réponse à un débat vieux d'un siècle.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-06-27 14:46</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Chercheuse, mère et précaire : une équation impossible</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/chercheuse-mere-et-precaire-une-equation-impossible-285418</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Accéder à un poste de titulaire dans l’enseignement supérieur et la recherche, c’est un parcours d’obstacles. Pour les femmes qui deviennent mères, la route se complique d’autant plus.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-06-28 09:00</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Derrière la mignonnerie du panda, une diplomatie d’influence chinoise de l’émotion en ligne</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/derriere-la-mignonnerie-du-panda-une-diplomatie-dinfluence-chinoise-de-lemotion-en-ligne-285620</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L’exploitation tous azimuts de l’image sympathique du panda vise à transformer la réputation, souvent négative, de la République populaire de Chine.</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:00</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Au-delà du technoprophète : Albert Robida et la guerre comme milieu</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/28/au-dela-du-technoprophete-albert-robida-et-la-guerre-comme-milieu/</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Pourquoi un auteur oublié éclaire mieux nos conflits que bien des prophètes technologiques contemporains. L’article Au-delà du technoprophète&amp;#160;: Albert Robida et la guerre comme milieu est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-06-28 04:30</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>L’IA de frontière est devenue une crise géopolitique</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/28/lacces-a-lia-de-frontiere-est-devenu-un-privilege-strategique/</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Un nouveau régime de diffusion de l'IA de frontière est en train de s'installer. Victor Storchan détaille le scénario américain et chinois, ainsi que les trajectoires possibles de l'Europe. L’article L&amp;rsquo;IA de frontière est devenue une crise géopolitique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:58</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Le Cap-Vert déjoue les pronostics et se qualifie pour les seizièmes de finale</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/27/le-cap-vert-dejoue-les-pronostics-et-se-qualifie-pour-les-seiziemes-de-finale/</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Qualifié pour la première fois de son histoire pour la phase à élimination directe, le Cap-Vert offre la plus belle réponse aux critiques concernant l'élargissement du tournoi. L’article Le Cap-Vert déjoue les pronostics et se qualifie pour les seizièmes de finale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:15</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Touba (Sénégal), la croissance urbaine de la capitale de la confrérie mouride</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/fait-religieux-et-construction-de-l-espace/etudes-de-cas/touba-senegal-la-croissance-urbaine-de-la-capitale-de-la-confrerie-mouride</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Capitale de la confrérie soufie des mourides, Touba est la deuxième agglomération du Sénégal. Construite selon les vœux du fondateur de la confrérie, simple village il y a un siècle seulement, elle doit sa croissance démographique à la fois au contexte sénégalais (le pays a multiplié sa population par 3,6 en 50 ans) et à la politique volontariste des califes successifs de la confrérie. Le lotissement de parcelles gratuites, notamment, a fortement incité les Mourides à s’installer à Touba.</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28 11:04</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:15</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Le parc de Pignerolle à Saint-Barthélemy d'Anjou : un exemple de forêt périurbaine protégée</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/france-espaces-ruraux-periurbains/etude-de-cas/le-parc-de-pignerolle-a-saint-barthelemy-danjou-une-foret-periurbaine-protegee</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>À proximité d’Angers, le parc de Pignerolle est une forêt périurbaine à vocation récréative. À la fonction de loisirs s'ajoute une fonction mémorielle mettant en valeur le patrimoine historique du lieu, associé à la Seconde Guerre mondiale. Certaines activités génèrent des conflits d’usage, notamment les activités cynégétiques, considérées comme indispensables pour la régulation des grands herbivores mais peu compatibles avec les autres fonctions récréatives.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8047,6 +8337,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId239"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7839,7 +7839,6 @@
           <t>Robin des Bois est devenu le hors-la-loi le plus célèbre de l'histoire. Pourtant, les récits médiévaux décrivent un personnage bien plus violent que celui de la légende, tandis que d'autres bandits, aujourd'hui oubliés, ont inspiré nombre de ses aventures.</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -7872,7 +7871,6 @@
           <t>Les grands banquets de la Grèce antique étaient-ils alimentés par des troupeaux nomades ou par les fermes locales ? L'analyse isotopique apporte une réponse à un débat vieux d'un siècle.</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -7905,7 +7903,6 @@
           <t>Accéder à un poste de titulaire dans l’enseignement supérieur et la recherche, c’est un parcours d’obstacles. Pour les femmes qui deviennent mères, la route se complique d’autant plus.</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -7938,7 +7935,6 @@
           <t>L’exploitation tous azimuts de l’image sympathique du panda vise à transformer la réputation, souvent négative, de la République populaire de Chine.</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -7971,7 +7967,6 @@
           <t>Pourquoi un auteur oublié éclaire mieux nos conflits que bien des prophètes technologiques contemporains. L’article Au-delà du technoprophète&amp;#160;: Albert Robida et la guerre comme milieu est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -8004,7 +7999,6 @@
           <t>Un nouveau régime de diffusion de l'IA de frontière est en train de s'installer. Victor Storchan détaille le scénario américain et chinois, ainsi que les trajectoires possibles de l'Europe. L’article L&amp;rsquo;IA de frontière est devenue une crise géopolitique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -8037,7 +8031,6 @@
           <t>Qualifié pour la première fois de son histoire pour la phase à élimination directe, le Cap-Vert offre la plus belle réponse aux critiques concernant l'élargissement du tournoi. L’article Le Cap-Vert déjoue les pronostics et se qualifie pour les seizièmes de finale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -8070,7 +8063,6 @@
           <t>Capitale de la confrérie soufie des mourides, Touba est la deuxième agglomération du Sénégal. Construite selon les vœux du fondateur de la confrérie, simple village il y a un siècle seulement, elle doit sa croissance démographique à la fois au contexte sénégalais (le pays a multiplié sa population par 3,6 en 50 ans) et à la politique volontariste des califes successifs de la confrérie. Le lotissement de parcelles gratuites, notamment, a fortement incité les Mourides à s’installer à Touba.</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -8103,7 +8095,204 @@
           <t>À proximité d’Angers, le parc de Pignerolle est une forêt périurbaine à vocation récréative. À la fonction de loisirs s'ajoute une fonction mémorielle mettant en valeur le patrimoine historique du lieu, associé à la Seconde Guerre mondiale. Certaines activités génèrent des conflits d’usage, notamment les activités cynégétiques, considérées comme indispensables pour la régulation des grands herbivores mais peu compatibles avec les autres fonctions récréatives.</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:04</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-06-29 11:54</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Le Japon et le Maroc sont deux équipes à ne pas sous-estimer</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/29/le-japon-et-le-maroc-sont-deux-equipes-a-ne-pas-sous-estimer/</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Les deux sélections, considérées comme perdantes par la quasi-totalité des pronostics, pourraient créer la surprise lors de leurs matchs respectifs contre le Brésil et les Pays-Bas. L’article Le Japon et le Maroc sont deux équipes à ne pas sous-estimer est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:04</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-06-29 08:35</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>La vague de chaleur la plus intense jamais mesurée en Pologne ne provoque aucun débat politique</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/29/la-vague-de-chaleur-la-plus-intense-jamais-mesuree-en-pologne-ne-provoque-aucun-debat-politique/</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L’une des démocraties les plus polarisées d’Europe a-t-elle trouvé un sujet qui ne divise pas&amp;#160;? L’article La vague de chaleur la plus intense jamais mesurée en Pologne ne provoque aucun débat politique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:04</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-06-29 05:36</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>La sécurité écologique est la nouvelle frontière de la géopolitique</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/29/la-securite-ecologique-est-la-nouvelle-frontiere-de-la-geopolitique/</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Aux fondements de toute autonomie stratégique se trouvent l'énergie, l'eau, les minéraux critiques — et la capacité à les régénérer. L’article La sécurité écologique est la nouvelle frontière de la géopolitique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:04</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-06-29 04:30</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>« Projet 2026 » : les nouvelles méthodes de la désinformation russe</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/29/projet-2026-les-nouvelles-methodes-de-la-desinformation-russe/</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Selon une fuite révélée par Bloomberg, le Kremlin se donne de nouvelles ambitions et modalités d'action dans la guerre informationnelle&amp;#160;: s'infiltrer dans les moteurs de recherche et les grands modèles de langage afin d'inonder Internet de contenus reprenant les matériaux ou les argumentaires de la Russie. L’article «&amp;#160;Projet 2026&amp;#160;»&amp;#160;: les nouvelles méthodes de la désinformation russe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:04</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:49</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Étienne Davignon (1932-2026), un grand Européen à l’ombre des fantômes du Congo belge</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/28/etienne-davignon-1932-2026-un-grand-europeen-a-lombre-des-fantomes-du-congo-belge/</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Le bourgmestre de Charleroi retrace l'itinéraire extraordinaire d'un géant de la diplomatie européenne, disparu il y a un mois. L’article Étienne Davignon (1932-2026), un grand Européen à l’ombre des fantômes du Congo belge est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:04</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-06-28 15:36</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Avec le Canada contre l’Afrique du Sud, les éliminations directes commencent. L’Argentine de Messi a-t-elle le parcours le plus favorable ?</t>
+        </is>
+      </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/28/avec-le-canada-contre-lafrique-du-sud-les-eliminations-directes-commencent-largentine-de-messi-a-t-elle-le-parcours-le-plus-favorable/</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Il ne reste plus que 32 matchs jusqu’à la fin du tournoi. L’article Avec le Canada contre l’Afrique du Sud, les éliminations directes commencent. L&amp;rsquo;Argentine de Messi a-t-elle le parcours le plus favorable&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8346,6 +8535,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId237"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId245"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8127,7 +8127,6 @@
           <t>Les deux sélections, considérées comme perdantes par la quasi-totalité des pronostics, pourraient créer la surprise lors de leurs matchs respectifs contre le Brésil et les Pays-Bas. L’article Le Japon et le Maroc sont deux équipes à ne pas sous-estimer est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -8160,7 +8159,6 @@
           <t>L’une des démocraties les plus polarisées d’Europe a-t-elle trouvé un sujet qui ne divise pas&amp;#160;? L’article La vague de chaleur la plus intense jamais mesurée en Pologne ne provoque aucun débat politique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -8193,7 +8191,6 @@
           <t>Aux fondements de toute autonomie stratégique se trouvent l'énergie, l'eau, les minéraux critiques — et la capacité à les régénérer. L’article La sécurité écologique est la nouvelle frontière de la géopolitique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -8226,7 +8223,6 @@
           <t>Selon une fuite révélée par Bloomberg, le Kremlin se donne de nouvelles ambitions et modalités d'action dans la guerre informationnelle&amp;#160;: s'infiltrer dans les moteurs de recherche et les grands modèles de langage afin d'inonder Internet de contenus reprenant les matériaux ou les argumentaires de la Russie. L’article «&amp;#160;Projet 2026&amp;#160;»&amp;#160;: les nouvelles méthodes de la désinformation russe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -8259,7 +8255,6 @@
           <t>Le bourgmestre de Charleroi retrace l'itinéraire extraordinaire d'un géant de la diplomatie européenne, disparu il y a un mois. L’article Étienne Davignon (1932-2026), un grand Européen à l’ombre des fantômes du Congo belge est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -8292,7 +8287,204 @@
           <t>Il ne reste plus que 32 matchs jusqu’à la fin du tournoi. L’article Avec le Canada contre l’Afrique du Sud, les éliminations directes commencent. L&amp;rsquo;Argentine de Messi a-t-elle le parcours le plus favorable&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:43</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:57</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Petits-enfants d’immigrés : du diplôme à l’emploi, le modèle républicain tient-il ses promesses ?</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/petits-enfants-dimmigres-du-diplome-a-lemploi-le-modele-republicain-tient-il-ses-promesses-284677</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Si, dans les familles immigrées, l’ascension scolaire est réelle, la génération des petits-enfants se heurte sur le terrain de l’emploi à des inégalités persistantes.</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:43</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-06-29 14:03</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Sahel : pourquoi les massacres de civils par les forces officielles sont en recul</t>
+        </is>
+      </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/sahel-pourquoi-les-massacres-de-civils-par-les-forces-officielles-sont-en-recul-285449</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Au Sahel, les exactions des armées et des milices nourrissent les rébellions djihadistes. La baisse apparente de ces massacres doit être appréhendée avec une grande circonspection.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:43</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-06-30 05:29</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Le mensonge qui unit Lula et Bolsonaro</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/30/le-mensonge-qui-unit-lula-et-bolsonaro/</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L’extrême droite bolsonariste et le Parti des travailleurs tentent de dissimuler une réalité géoéconomique de plus en plus contraignante&amp;#160;: l'étreinte avec la Chine de Xi Jinping. L’article Le mensonge qui unit Lula et Bolsonaro est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:43</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-06-30 04:30</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Les manifestations anti-migrants en Afrique du Sud pourraient provoquer le pire épisode de violences depuis 2021</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/30/les-manifestations-anti-migrants-en-afrique-du-sud-pourraient-provoquer-le-pire-episode-de-violences-depuis-2021/</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Des manifestants anti-immigration ont fixé un ultimatum&amp;#160;: tous les migrants en situation irrégulière doivent quitter le pays d'ici 30 juin. L’article Les manifestations anti-migrants en Afrique du Sud pourraient provoquer le pire épisode de violences depuis 2021 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:43</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-06-29 18:00</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Pax Silica : l’Europe s’aligne-t-elle sur Washington dans la guerre technologique avec Pékin ?</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/29/pax-silica-leurope-saligne-t-elle-sur-washington-dans-la-guerre-technologique-avec-pekin/</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L’initiative américaine compte désormais 24 pays, dont cinq États membres de l’Union ainsi que la Commission européenne. L’article Pax Silica&amp;#160;: l&amp;rsquo;Europe s&amp;rsquo;aligne-t-elle sur Washington dans la guerre technologique avec Pékin&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 11:43</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-06-29 13:00</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe marche comme un somnambule vers le nouveau choc chinois</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/29/leurope-marche-comme-un-somnambule-vers-le-nouveau-choc-chinois/</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Les conséquences de la stratégie du parti sur le modèle industriel européen sont tout simplement trop massives pour continuer à faire semblant. L’article L’Europe marche comme un somnambule vers le nouveau choc chinois est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8541,6 +8733,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId251"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8319,7 +8319,6 @@
           <t>Si, dans les familles immigrées, l’ascension scolaire est réelle, la génération des petits-enfants se heurte sur le terrain de l’emploi à des inégalités persistantes.</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -8352,7 +8351,6 @@
           <t>Au Sahel, les exactions des armées et des milices nourrissent les rébellions djihadistes. La baisse apparente de ces massacres doit être appréhendée avec une grande circonspection.</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -8385,7 +8383,6 @@
           <t>L’extrême droite bolsonariste et le Parti des travailleurs tentent de dissimuler une réalité géoéconomique de plus en plus contraignante&amp;#160;: l'étreinte avec la Chine de Xi Jinping. L’article Le mensonge qui unit Lula et Bolsonaro est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -8418,7 +8415,6 @@
           <t>Des manifestants anti-immigration ont fixé un ultimatum&amp;#160;: tous les migrants en situation irrégulière doivent quitter le pays d'ici 30 juin. L’article Les manifestations anti-migrants en Afrique du Sud pourraient provoquer le pire épisode de violences depuis 2021 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -8451,7 +8447,6 @@
           <t>L’initiative américaine compte désormais 24 pays, dont cinq États membres de l’Union ainsi que la Commission européenne. L’article Pax Silica&amp;#160;: l&amp;rsquo;Europe s&amp;rsquo;aligne-t-elle sur Washington dans la guerre technologique avec Pékin&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -8484,7 +8479,435 @@
           <t>Les conséquences de la stratégie du parti sur le modèle industriel européen sont tout simplement trop massives pour continuer à faire semblant. L’article L’Europe marche comme un somnambule vers le nouveau choc chinois est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:36</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Le 4-Juillet : une date inventée, un mythe construit, un récit disputé</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-4-juillet-une-date-inventee-un-mythe-construit-un-recit-dispute-286386</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Le 4-Juillet est le grand rite de la religion civile états-unienne. Et comme bien des rites, il est soumis, selon les périodes, à bien des interprétations différentes…</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:35</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>250 ans après, les griefs de la Déclaration d’indépendance des États-Unis restent étonnamment actuels</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/250-ans-apres-les-griefs-de-la-declaration-dindependance-des-etats-unis-restent-etonnamment-actuels-286322</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Au-delà de ses grandes formules sur la liberté et l’égalité, la Déclaration d’indépendance est un acte d’accusation contre le pouvoir britannique. Ses 27&amp;nbsp;doléances éclairent les origines concrètes de la révolution américaine.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:35</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>« Juneteenth Independence Day » : le long combat des Afro-Américains pour l’accès à l’éducation après l’abolition de l’esclavage</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/juneteenth-independence-day-le-long-combat-des-afro-americains-pour-lacces-a-leducation-apres-labolition-de-lesclavage-285961</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Contraction des mots «&amp;nbsp;June&amp;nbsp;» (juin) et «&amp;nbsp;nineteenth&amp;nbsp;» (dix-neuvième), le Juneteenth, qui marque l’émancipation des esclaves, est devenu un jour férié en 2021 aux États-Unis.</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:34</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>La Fayette a aidé les Américains à renverser le cours de la guerre d’indépendance – et à forger un sentiment d’identité nationale</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-fayette-a-aide-les-americains-a-renverser-le-cours-de-la-guerre-dindependance-et-a-forger-un-sentiment-didentite-nationale-285953</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Accueilli comme un héros de retour au pays, le marquis de La&amp;nbsp;Fayette effectua une grande tournée aux États-Unis en 1824-1825, juste avant le 50ᵉ&amp;nbsp;anniversaire de l’indépendance.</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:49</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Savoir nager est essentiel, mais ne suffit pas à prévenir les noyades</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/savoir-nager-est-essentiel-mais-ne-suffit-pas-a-prevenir-les-noyades-286377</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Le regain de baignades pendant la canicule s’est accompagné d’une hausse marquée des noyades. Comment intégrer à l’apprentissage de la natation les réflexes de prévention nécessaires à tous les âges&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:51</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>Le Viêt Nam a franchi le cap des 100 millions d’habitants. Et demain ?</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-viet-nam-a-franchi-le-cap-des-100-millions-dhabitants-et-demain-286280</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>La hausse de la population devrait ralentir dans les prochaines décennies, et une baisse pourrait survenir dans la seconde moitié du siècle.</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:21</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>L’équipe de France peut-elle être battue ?</t>
+        </is>
+      </c>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/lequipe-de-france-peut-elle-etre-battue/</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>La sélection française a dominé la Suède sur tous les plans livrant l’une de ses meilleures prestations depuis des années. L’article L’équipe de France peut-elle être battue&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-07-01 08:49</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>La stratégie de l’État connecteur est en train de faire gagner le Maroc</t>
+        </is>
+      </c>
+      <c r="E260" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/la-strategie-de-letat-connecteur-est-en-train-de-faire-gagner-le-maroc/</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Dans les bouleversements de la nouvelle mondialisation, Rabat transforme sa position d’interface entre l’Europe, l’Afrique et la Chine en levier de croissance. L’article La stratégie de l&amp;rsquo;État connecteur est en train de faire gagner le Maroc est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-07-01 04:30</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : malgré une hausse des volumes d’exportations de pétrole, les revenus diminuent</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/economie-russe-malgre-une-hausse-des-volumes-dexportations-de-petrole-les-revenus-diminuent/</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>L’accord signé entre les États-Unis et l’Iran pour mettre fin à la guerre a conduit à une baisse de 62&amp;#160;% du prix du baril d’Oural. L’article Économie russe&amp;#160;: malgré une hausse des volumes d’exportations de pétrole, les revenus diminuent est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:50</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>Après la défaite de l’Allemagne, la France doit redoubler de vigilance face à la Suède</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/30/apres-la-defaite-de-lallemagne-la-france-doit-redoubler-de-vigilance-face-a-la-suede/</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Si la France a tous les atouts pour s'imposer ce soir, mardi 30 juin, elle affrontera un adversaire imprévisible dont le parcours dans la compétition reste difficile à cerner. L’article Après la défaite de l’Allemagne, la France doit redoubler de vigilance face à la Suède est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:07</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>En 2025, la hausse des émissions de CO₂ a été quatre fois plus forte aux États-Unis qu’en Chine</t>
+        </is>
+      </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/30/en-2025-la-hausse-des-emissions-de-co%e2%82%82-a-ete-quatre-fois-plus-forte-aux-etats-unis-quen-chine/</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>La production américaine d’électricité à partir de charbon a bondi de 13&amp;#160;% l’an dernier pour répondre à la hausse de la demande créée par les centres de données. L’article En 2025, la hausse des émissions de CO₂ a été quatre fois plus forte aux États-Unis qu&amp;rsquo;en Chine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-06-30 13:02</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Les négociations avec les États-Unis sont en train de diviser le régime iranien</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/06/30/les-negociations-avec-les-etats-unis-sont-en-train-de-diviser-le-regime-iranien/</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>L’Assemblée des experts a publié une déclaration rare et critique à l'égard des négociations menées avec Washington. L’article Les négociations avec les États-Unis sont en train de diviser le régime iranien est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:58</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-06-30 08:00</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Préparer l’agrégation interne d’histoire-géographie avec l’opération Coup de pouce!</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/preparer-l-agregation-interne-d-histoire-geographie-avec-l-operation-coup-de/</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>En 2022-2023, Joëlle Alazard a initié l&amp;#8217;opération « Coup pouce Agrégation interne » de l&amp;#8217;Association des Professeurs d&amp;#8217;Histoire et de Géographie pour venir en aide aux candidats adhérents à l&amp;#8217;association. Pour faire vivre l&amp;#8217;association, les actions « coup de pouce » sont réservées aux adhérents 2026-2027 (adhésion + abonnement à la revue). Pour ce faire, il vous suffit de cliquer [&amp;#8230;] L’article Préparer l&amp;rsquo;agrégation interne d&amp;rsquo;histoire-géographie ave</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8739,6 +9162,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId264"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8511,7 +8511,6 @@
           <t>Le 4-Juillet est le grand rite de la religion civile états-unienne. Et comme bien des rites, il est soumis, selon les périodes, à bien des interprétations différentes…</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -8544,7 +8543,6 @@
           <t>Au-delà de ses grandes formules sur la liberté et l’égalité, la Déclaration d’indépendance est un acte d’accusation contre le pouvoir britannique. Ses 27&amp;nbsp;doléances éclairent les origines concrètes de la révolution américaine.</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -8577,7 +8575,6 @@
           <t>Contraction des mots «&amp;nbsp;June&amp;nbsp;» (juin) et «&amp;nbsp;nineteenth&amp;nbsp;» (dix-neuvième), le Juneteenth, qui marque l’émancipation des esclaves, est devenu un jour férié en 2021 aux États-Unis.</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -8610,7 +8607,6 @@
           <t>Accueilli comme un héros de retour au pays, le marquis de La&amp;nbsp;Fayette effectua une grande tournée aux États-Unis en 1824-1825, juste avant le 50ᵉ&amp;nbsp;anniversaire de l’indépendance.</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -8643,7 +8639,6 @@
           <t>Le regain de baignades pendant la canicule s’est accompagné d’une hausse marquée des noyades. Comment intégrer à l’apprentissage de la natation les réflexes de prévention nécessaires à tous les âges&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -8676,7 +8671,6 @@
           <t>La hausse de la population devrait ralentir dans les prochaines décennies, et une baisse pourrait survenir dans la seconde moitié du siècle.</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -8709,7 +8703,6 @@
           <t>La sélection française a dominé la Suède sur tous les plans livrant l’une de ses meilleures prestations depuis des années. L’article L’équipe de France peut-elle être battue&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -8742,7 +8735,6 @@
           <t>Dans les bouleversements de la nouvelle mondialisation, Rabat transforme sa position d’interface entre l’Europe, l’Afrique et la Chine en levier de croissance. L’article La stratégie de l&amp;rsquo;État connecteur est en train de faire gagner le Maroc est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -8775,7 +8767,6 @@
           <t>L’accord signé entre les États-Unis et l’Iran pour mettre fin à la guerre a conduit à une baisse de 62&amp;#160;% du prix du baril d’Oural. L’article Économie russe&amp;#160;: malgré une hausse des volumes d’exportations de pétrole, les revenus diminuent est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -8808,7 +8799,6 @@
           <t>Si la France a tous les atouts pour s'imposer ce soir, mardi 30 juin, elle affrontera un adversaire imprévisible dont le parcours dans la compétition reste difficile à cerner. L’article Après la défaite de l’Allemagne, la France doit redoubler de vigilance face à la Suède est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -8841,7 +8831,6 @@
           <t>La production américaine d’électricité à partir de charbon a bondi de 13&amp;#160;% l’an dernier pour répondre à la hausse de la demande créée par les centres de données. L’article En 2025, la hausse des émissions de CO₂ a été quatre fois plus forte aux États-Unis qu&amp;rsquo;en Chine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -8874,7 +8863,6 @@
           <t>L’Assemblée des experts a publié une déclaration rare et critique à l'égard des négociations menées avec Washington. L’article Les négociations avec les États-Unis sont en train de diviser le régime iranien est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -8907,7 +8895,270 @@
           <t>En 2022-2023, Joëlle Alazard a initié l&amp;#8217;opération « Coup pouce Agrégation interne » de l&amp;#8217;Association des Professeurs d&amp;#8217;Histoire et de Géographie pour venir en aide aux candidats adhérents à l&amp;#8217;association. Pour faire vivre l&amp;#8217;association, les actions « coup de pouce » sont réservées aux adhérents 2026-2027 (adhésion + abonnement à la revue). Pour ce faire, il vous suffit de cliquer [&amp;#8230;] L’article Préparer l&amp;rsquo;agrégation interne d&amp;rsquo;histoire-géographie ave</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:18</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>« Je vais partir » plutôt que « je partirai » : comment le français parle de l’avenir</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/je-vais-partir-plutot-que-je-partirai-comment-le-francais-parle-de-lavenir-285779</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Pourquoi dit-on plus souvent «&amp;nbsp;je vais partir&amp;nbsp;» que «&amp;nbsp;je partirai&amp;nbsp;»&amp;nbsp;? Les recherches expliquent comment le français à l’oral transforme l’expression du futur.</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:22</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Comment les jeux vidéo sont devenus un outil de soft power pour l’Ukraine</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-les-jeux-video-sont-devenus-un-outil-de-soft-power-pour-lukraine-285858</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Les jeux vidéo ukrainiens racontent la guerre, mettent en valeur le patrimoine, mobilisent des soutiens et renforcent le rayonnement culturel du pays.</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:29</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>Erdoğan, le Janus d’Ankara</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/02/erdogan-le-janus-dankara/</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>La Turquie n'a jamais été aussi indispensable, ni son régime aussi crépusculaire. L’article Erdoğan, le Janus d&amp;rsquo;Ankara est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-07-02 04:30</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Plus de 90 % des modèles d’IA les plus utilisés dans le monde sont américains ou chinois</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/02/plus-de-90-des-modeles-dia-les-plus-utilises-dans-le-monde-sont-americains-ou-chinois/</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Sur les 50 modèles d'intelligence artificielle les plus utilisés chaque jour en juin, 28 étaient américains et 19 étaient chinois. L’article Plus de 90&amp;#160;% des modèles d&amp;rsquo;IA les plus utilisés dans le monde sont américains ou chinois est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-07-01 16:14</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>L’armée russe a conquis 770 km² de territoire ukrainien au premier semestre, soit 2,5 fois moins qu’en 2025</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/larmee-russe-a-conquis-770-km%c2%b2-de-territoire-ukrainien-au-premier-semestre-soit-25-fois-moins-quen-2025/</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Les chiffres de la progression russe en juin sont largement en deçà des objectifs du Kremlin. L’article L’armée russe a conquis 770 km² de territoire ukrainien au premier semestre, soit 2,5 fois moins qu’en 2025 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-07-01 14:13</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>L’âge de la slopagande</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/lage-de-la-slopagande/</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Pour comprendre le nouveau régime informationnel, il faut élaborer une nouvelle théorie de la propagande à l'ère de l'IA. L’article L’âge de la slopagande est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-07-01 12:30</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Effet domino : en Amérique latine, 7 présidents proches ou alignés sur Trump ont été élus depuis 2025</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/effet-domino-en-amerique-latine-7-presidents-proches-ou-alignes-sur-trump-ont-ete-elus-depuis-2025/</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>La nouvelle présidente du Pérou, Keiko Fujimori, est la septième dirigeante qui affiche ou revendique une proximité avec Trump à accéder au pouvoir dans la région depuis 2025. L’article Effet domino&amp;#160;: en Amérique latine, 7 présidents proches ou alignés sur Trump ont été élus depuis 2025 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:31</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:21</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>L’équipe de France peut-elle être battue ?</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/01/equipe-de-france-peut-elle-etre-battue/</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>La sélection française a dominé la Suède sur tous les plans livrant l’une de ses meilleures prestations depuis des années. L’article L’équipe de France peut-elle être battue&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9175,6 +9426,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId263"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId272"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G273"/>
+  <dimension ref="A1:G285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8927,7 +8927,6 @@
           <t>Pourquoi dit-on plus souvent «&amp;nbsp;je vais partir&amp;nbsp;» que «&amp;nbsp;je partirai&amp;nbsp;»&amp;nbsp;? Les recherches expliquent comment le français à l’oral transforme l’expression du futur.</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -8960,7 +8959,6 @@
           <t>Les jeux vidéo ukrainiens racontent la guerre, mettent en valeur le patrimoine, mobilisent des soutiens et renforcent le rayonnement culturel du pays.</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -8993,7 +8991,6 @@
           <t>La Turquie n'a jamais été aussi indispensable, ni son régime aussi crépusculaire. L’article Erdoğan, le Janus d&amp;rsquo;Ankara est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -9026,7 +9023,6 @@
           <t>Sur les 50 modèles d'intelligence artificielle les plus utilisés chaque jour en juin, 28 étaient américains et 19 étaient chinois. L’article Plus de 90&amp;#160;% des modèles d&amp;rsquo;IA les plus utilisés dans le monde sont américains ou chinois est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -9059,7 +9055,6 @@
           <t>Les chiffres de la progression russe en juin sont largement en deçà des objectifs du Kremlin. L’article L’armée russe a conquis 770 km² de territoire ukrainien au premier semestre, soit 2,5 fois moins qu’en 2025 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -9092,7 +9087,6 @@
           <t>Pour comprendre le nouveau régime informationnel, il faut élaborer une nouvelle théorie de la propagande à l'ère de l'IA. L’article L’âge de la slopagande est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -9125,7 +9119,6 @@
           <t>La nouvelle présidente du Pérou, Keiko Fujimori, est la septième dirigeante qui affiche ou revendique une proximité avec Trump à accéder au pouvoir dans la région depuis 2025. L’article Effet domino&amp;#160;: en Amérique latine, 7 présidents proches ou alignés sur Trump ont été élus depuis 2025 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -9158,7 +9151,402 @@
           <t>La sélection française a dominé la Suède sur tous les plans livrant l’une de ses meilleures prestations depuis des années. L’article L’équipe de France peut-elle être battue&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-07-02 15:16</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>Les 250 ans des États-Unis : comment Trump cherche à s’approprier les Pères fondateurs</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-250-ans-des-etats-unis-comment-trump-cherche-a-sapproprier-les-peres-fondateurs-286667</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Le 250ᵉ&amp;nbsp;anniversaire de l’indépendance ravive la bataille autour du récit national états-unien, devenu un enjeu politique central à l’ère Trump.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:49</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>Après sa victoire contre l’Autriche, l’Espagne met en garde la France et l’Argentine : les meilleures équipes du tournoi sont désormais au nombre de trois</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/03/apres-sa-victoire-contre-autriche-espagne-met-en-garde-la-france-argentine/</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>La Roja se qualifie pour les huitièmes de finale, où elle affrontera le Portugal de Cristiano Ronaldo, lundi 6 juillet. L’article Après sa victoire contre l’Autriche, l’Espagne met en garde la France et l’Argentine&amp;#160;: les meilleures équipes du tournoi sont désormais au nombre de trois est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:40</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>Palantir et l’illusion de la souveraineté (texte commenté)</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/03/palantir-et-lillusion-de-la-souverainete-texte-commente/</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Confronté à des contestations de plus en plus profondes, le géant IA de Karp et Thiel élabore une nouvelle doctrine ésotérique de vassalisation. L’article Palantir et l’illusion de la souveraineté (texte commenté) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-07-03 04:30</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>Sam Altman proposerait une participation de 5 % du gouvernement américain au capital d’OpenAI : qu’est-ce que cela signifie ?</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/03/sam-altman-proposerait-une-participation-de-5-du-gouvernement-americain-au-capital-dopenai-quest-ce-que-cela-signifie/</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Sur fond de crise populiste larvée, l'IA reconfigure la politique et l'État américains. L’article Sam Altman proposerait une participation de 5&amp;#160;% du gouvernement américain au capital d&amp;rsquo;OpenAI&amp;#160;: qu’est-ce que cela signifie&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-07-02 17:14</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : une majorité estime que les conditions locales se détériorent</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/02/economie-russe-une-majorite-estime-que-les-conditions-locales-se-deteriorent/</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Selon une nouvelle enquête Gallup, le pessimisme économique atteint en Russie son niveau le plus élevé depuis au moins vingt ans. L’article Économie russe&amp;#160;: une majorité estime que les conditions locales se détériorent est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-07-02 12:50</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>Angleterre, Belgique, Allemagne : dans cette Coupe du monde, les favoris ne dominent plus</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/02/angleterre-belgique-allemagne-dans-cette-coupe-du-monde-les-favoris-ne-dominent-plus/</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>L'Angleterre sauvée par Kane face à la RDC, la Belgique ressuscitée à la 120e minute contre le Sénégal&amp;#160;: les grandes équipes européennes se qualifient, mais en frôlant l'élimination. L’article Angleterre, Belgique, Allemagne&amp;#160;: dans cette Coupe du monde, les favoris ne dominent plus est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-07-02 21:14</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>Plutarque</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/plutarque/</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;#160; &amp;#160; &amp;#60;iframe src= »https://player.vimeo.com/video/1206545604?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; width= »1920&amp;#8243; height= »1080&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » title= »FSC-C_Rideau_Kikuchi »&amp;#62;&amp;#60;/iframe&amp;#62; L’article Plutarque est apparu en </t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-07-02 21:09</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>Quels rôles pour les femmes dans la construction et la circulation des savoirs scientifiques au XVIIIe siècle ?</t>
+        </is>
+      </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/quels-roles-pour-les-femmes-dans-la-construction-et-la-circulation-des-savoirs-scientifiques-au-xviiie-siecle/</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>&amp;#160; &amp;#60;iframe src= »https://player.vimeo.com/video/1206545607?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; width= »1280&amp;#8243; height= »480&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » title= »FSC-Isabelle Lémonon-Waxin &amp;#8211; HD 720p »&amp;#62;&amp;#60;/iframe&amp;#62; L’article Quels rôle</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-07-02 21:03</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>La découverte du Polonium et du Radium</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/decouverte-polonium-radium/</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;#160; &amp;#160; &amp;#60;iframe src= »https://player.vimeo.com/video/1206545603?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; width= »1920&amp;#8243; height= »1080&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » title= »FSC-C_Maiani »&amp;#62;&amp;#60;/iframe&amp;#62; L’article La découverte du Polonium et du </t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-07-02 18:45</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>Starter Pack Agrégation interne 2 – les sujets et rapports du jury</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/starter-pack-agregation-interne-2-les-sujets-et-rapports-du-jury/</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>La lettre de cadrage de la session 2027 Lettre de cadrage &amp;#8211; agrégation interne d&amp;#8217;histoire-géographie &amp;#160; &amp;#160; Sujets de la session 2026 Sujet de dissertation &amp;#8211; Histoire Sujet de dissertation &amp;#8211; Géographie Épreuve 3 &amp;#8211; sujets d&amp;#8217;histoire et de géographie &amp;#160; Rapport du jury et sujets de la session 2025 Sujet de dissertation &amp;#8211; Histoire [&amp;#8230;] L’article Starter Pack Agrégation interne 2 &amp;#8211; les sujets et rapports du jury est apparu en premier su</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-07-01 19:27</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce CAPES interne – Présentation des épreuves et méthodologie du dossier RAEP</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-capes-interne-presentation-des-epreuves-et-methodologie-du-dossier-raep/</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Pour cette première séance, Marie Digout, Thomas Gosselin et Marine Sorano vous proposent une présentation du concours et des attentes du jury ainsi qu&amp;#8217;une méthodologie du dossier RAEP. Vous pouvez également télécharger les supports de la séance: Bien choisir son sujet &amp;#8211; 29 juin 2026 Objectif réussite CAPES interne &amp;#8211; 29 juin 2026 Le dossier [&amp;#8230;] L’article Coup de pouce CAPES interne &amp;#8211; Présentation des épreuves et méthodologie du dossier RAEP est apparu en premier sur</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:29</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-07-01 18:42</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>Starter Pack Agrégation interne 1 – BO et fiches Eduscol</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/starter-pack-agregation-interne-1-bo-et-fiches-eduscol/</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Sur cette page, vous trouverez les programmes scolaires en vigueur pour la session 2027 (année scolaire 2026/2027) ainsi que les fiches Eduscol par niveaux d&amp;#8217;enseignement. &amp;#160; NB: les ressources et liens présents sur cette page ont pour objectif de vous donner une vue d&amp;#8217;ensemble des programmes en vigueur. Pour la place de l&amp;#8217;EMC et de [&amp;#8230;] L’article Starter Pack Agrégation interne 1 &amp;#8211; BO et fiches Eduscol est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9434,6 +9822,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId271"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId284"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G285"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9183,7 +9183,6 @@
           <t>Le 250ᵉ&amp;nbsp;anniversaire de l’indépendance ravive la bataille autour du récit national états-unien, devenu un enjeu politique central à l’ère Trump.</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -9216,7 +9215,6 @@
           <t>La Roja se qualifie pour les huitièmes de finale, où elle affrontera le Portugal de Cristiano Ronaldo, lundi 6 juillet. L’article Après sa victoire contre l’Autriche, l’Espagne met en garde la France et l’Argentine&amp;#160;: les meilleures équipes du tournoi sont désormais au nombre de trois est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -9249,7 +9247,6 @@
           <t>Confronté à des contestations de plus en plus profondes, le géant IA de Karp et Thiel élabore une nouvelle doctrine ésotérique de vassalisation. L’article Palantir et l’illusion de la souveraineté (texte commenté) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -9282,7 +9279,6 @@
           <t>Sur fond de crise populiste larvée, l'IA reconfigure la politique et l'État américains. L’article Sam Altman proposerait une participation de 5&amp;#160;% du gouvernement américain au capital d&amp;rsquo;OpenAI&amp;#160;: qu’est-ce que cela signifie&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -9315,7 +9311,6 @@
           <t>Selon une nouvelle enquête Gallup, le pessimisme économique atteint en Russie son niveau le plus élevé depuis au moins vingt ans. L’article Économie russe&amp;#160;: une majorité estime que les conditions locales se détériorent est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -9348,7 +9343,6 @@
           <t>L'Angleterre sauvée par Kane face à la RDC, la Belgique ressuscitée à la 120e minute contre le Sénégal&amp;#160;: les grandes équipes européennes se qualifient, mais en frôlant l'élimination. L’article Angleterre, Belgique, Allemagne&amp;#160;: dans cette Coupe du monde, les favoris ne dominent plus est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -9381,7 +9375,6 @@
           <t xml:space="preserve">&amp;#160; &amp;#160; &amp;#60;iframe src= »https://player.vimeo.com/video/1206545604?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; width= »1920&amp;#8243; height= »1080&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » title= »FSC-C_Rideau_Kikuchi »&amp;#62;&amp;#60;/iframe&amp;#62; L’article Plutarque est apparu en </t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -9414,7 +9407,6 @@
           <t>&amp;#160; &amp;#60;iframe src= »https://player.vimeo.com/video/1206545607?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; width= »1280&amp;#8243; height= »480&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » title= »FSC-Isabelle Lémonon-Waxin &amp;#8211; HD 720p »&amp;#62;&amp;#60;/iframe&amp;#62; L’article Quels rôle</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -9447,7 +9439,6 @@
           <t xml:space="preserve">&amp;#160; &amp;#160; &amp;#60;iframe src= »https://player.vimeo.com/video/1206545603?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; width= »1920&amp;#8243; height= »1080&amp;#8243; frameborder= »0&amp;#8243; allow= »autoplay; fullscreen; picture-in-picture; clipboard-write; encrypted-media; web-share » referrerpolicy= »strict-origin-when-cross-origin » title= »FSC-C_Maiani »&amp;#62;&amp;#60;/iframe&amp;#62; L’article La découverte du Polonium et du </t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -9480,7 +9471,6 @@
           <t>La lettre de cadrage de la session 2027 Lettre de cadrage &amp;#8211; agrégation interne d&amp;#8217;histoire-géographie &amp;#160; &amp;#160; Sujets de la session 2026 Sujet de dissertation &amp;#8211; Histoire Sujet de dissertation &amp;#8211; Géographie Épreuve 3 &amp;#8211; sujets d&amp;#8217;histoire et de géographie &amp;#160; Rapport du jury et sujets de la session 2025 Sujet de dissertation &amp;#8211; Histoire [&amp;#8230;] L’article Starter Pack Agrégation interne 2 &amp;#8211; les sujets et rapports du jury est apparu en premier su</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -9513,7 +9503,6 @@
           <t>Pour cette première séance, Marie Digout, Thomas Gosselin et Marine Sorano vous proposent une présentation du concours et des attentes du jury ainsi qu&amp;#8217;une méthodologie du dossier RAEP. Vous pouvez également télécharger les supports de la séance: Bien choisir son sujet &amp;#8211; 29 juin 2026 Objectif réussite CAPES interne &amp;#8211; 29 juin 2026 Le dossier [&amp;#8230;] L’article Coup de pouce CAPES interne &amp;#8211; Présentation des épreuves et méthodologie du dossier RAEP est apparu en premier sur</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -9546,7 +9535,435 @@
           <t>Sur cette page, vous trouverez les programmes scolaires en vigueur pour la session 2027 (année scolaire 2026/2027) ainsi que les fiches Eduscol par niveaux d&amp;#8217;enseignement. &amp;#160; NB: les ressources et liens présents sur cette page ont pour objectif de vous donner une vue d&amp;#8217;ensemble des programmes en vigueur. Pour la place de l&amp;#8217;EMC et de [&amp;#8230;] L’article Starter Pack Agrégation interne 1 &amp;#8211; BO et fiches Eduscol est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-07-04 11:11</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>Comment une minuscule île des Caraïbes a rendu possible l'indépendance des États-Unis</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-une-minuscule-ile-des-cara-bes-a-rendu-possible-lindependance-des-etats-unis-286670</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>L'histoire de l'indépendance américaine ne s'est pas jouée uniquement sur les champs de bataille. Elle s'est aussi écrite dans les entrepôts et sur les quais d'une minuscule île des Caraïbes, au cœur des réseaux du commerce mondial.</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:32</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>Quand Hollywood a changé d’ennemi : comment les films de la guerre froide ont transformé les Allemands en alliés</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-hollywood-a-change-dennemi-comment-les-films-de-la-guerre-froide-ont-transforme-les-allemands-en-allies-285212</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Pendant la guerre froide, l’ancien ennemi allemand devient un partenaire indispensable pour les États-Unis, face à l’Union soviétique. Le cinéma témoigne de cette bascule symbolique.</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:33</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>À quoi sert l’éducation ? Pourquoi la nouvelle série coréenne « Que ça vous serve de leçon » fait un carton</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-quoi-sert-leducation-pourquoi-la-nouvelle-serie-coreenne-que-ca-vous-serve-de-lecon-fait-un-carton-286084</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>À la fois populaire et controversée, une nouvelle série coréenne ancrée dans le monde scolaire attire des spectateurs du monde entier. Comment expliquer un tel succès&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-07-03 14:33</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>Zimbabwe, Venezuela, Philippines : les banques centrales aussi peuvent faire faillite !</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/zimbabwe-venezuela-philippines-les-banques-centrales-aussi-peuvent-faire-faillite-283182</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Une banque centrale a un pouvoir de seigneuriage, hérité du Moyen&amp;nbsp;Âge. Elle peut créer de façon illimitée de la monnaie. Comment est-il alors possible qu’elle fasse éventuellement faillite&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-07-04 04:32</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis fêtent-ils aujourd’hui leur pire anniversaire ?</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/04/les-etats-unis-fetent-ils-aujourdhui-leur-pire-anniversaire/</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Graphiques et données pour scruter dans les tréfonds de la société américaine en ce 4 juillet 2026. L’article Les États-Unis fêtent-ils aujourd’hui leur pire anniversaire&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-07-04 04:00</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>La fin du récit atlantique est une chance historique</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/04/la-fin-du-recit-atlantique-et-nouveau-recit-europeen/</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Face au «&amp;#160;grand estrangement&amp;#160;» étatsunien, le moment est venu de construire un nouveau récit européen. L’article La fin du récit atlantique est une chance historique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:03</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>Vladimir Poutine vante des conquêtes sur des territoires qui n’existent pas réellement</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/03/vladimir-poutine-vante-des-conquetes-sur-des-territoires-qui-nexistent-pas-reellement/</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Erreurs géographiques, encerclements inexistants, vidéos produites par l’IA, face à un bilan humain catastrophique et à un front qui se fige, le récit du Kremlin s'éloigne de plus en plus du territoire pour entrer dans une carte imaginaire. L’article Vladimir Poutine vante des conquêtes sur des territoires qui n’existent pas réellement est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:15</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>Le fantasme de l’efficacité fasciste</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/03/le-fantasme-de-lefficacite-fasciste/</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Une grammaire critique de la nostalgie autoritaire en sept mythes particulièrement influents. L’article Le fantasme de l’efficacité fasciste est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:03</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>Le plan de Friedrich Merz pour faire repartir l’Allemagne</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/03/le-plan-de-friedrich-merz-pour-faire-repartir-lallemagne/</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Pour répondre au défi chinois et à la politique interne, Berlin abandonne plusieurs tabous de son modèle économique. L’article Le plan de Friedrich Merz pour faire repartir l&amp;rsquo;Allemagne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:22</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Retours d’expérience et conseils de préparation avec des lauréats de la session 2026</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-retours-dexperience-et-conseils-de-preparation-avec-des-laureats-de-la-session-2026/</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance organisée avec des lauréats de la session 2026 qui ont participé à la précédente saison de l&amp;#8217;opération Coup [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Retours d&amp;rsquo;expérience et conseils de préparation avec des lauréats de la sessio</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:22</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Alexandra Monot – Présentation de la question de géographie « le Pacifique »</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-alexandra-monot-presentation-de-la-question-de-geographie-le-pacifique/</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance d&amp;#8217;Alexandra Monot qui présente la nouvelle question de géographie intitulée « le Pacifique ». Le podcast est proposé en version [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Alexandra Monot &amp;#8211; Présentation de la question de géographi</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:22</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Guillaume Debat – Présentation de la question d’histoire moderne « l’âge des révolutions »</t>
+        </is>
+      </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-guillaume-debat-presentation-de-la-question-dhistoire-moderne-lage-des-revolutions/</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Guillaume Debat qui présente la question d&amp;#8217;histoire moderne « l&amp;#8217;âge des révolutions ». Le podcast est proposé en version [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Guillaume Debat &amp;#8211; Présentation de la question d&amp;rsquo;hi</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:52</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-03-26 08:46</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>Elven Le Goff – Le phénomène urbain à l’époque gauloise, les exemples de l’ouest de la France</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/elven-le-goff-le-phenomene-urbain-a-lepoque-gauloise-les-exemples-de-louest-de-la-france/</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200227377?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= </t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9834,6 +10251,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId283"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId297"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G298"/>
+  <dimension ref="A1:G305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9567,7 +9567,6 @@
           <t>L'histoire de l'indépendance américaine ne s'est pas jouée uniquement sur les champs de bataille. Elle s'est aussi écrite dans les entrepôts et sur les quais d'une minuscule île des Caraïbes, au cœur des réseaux du commerce mondial.</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -9600,7 +9599,6 @@
           <t>Pendant la guerre froide, l’ancien ennemi allemand devient un partenaire indispensable pour les États-Unis, face à l’Union soviétique. Le cinéma témoigne de cette bascule symbolique.</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -9633,7 +9631,6 @@
           <t>À la fois populaire et controversée, une nouvelle série coréenne ancrée dans le monde scolaire attire des spectateurs du monde entier. Comment expliquer un tel succès&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -9666,7 +9663,6 @@
           <t>Une banque centrale a un pouvoir de seigneuriage, hérité du Moyen&amp;nbsp;Âge. Elle peut créer de façon illimitée de la monnaie. Comment est-il alors possible qu’elle fasse éventuellement faillite&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -9699,7 +9695,6 @@
           <t>Graphiques et données pour scruter dans les tréfonds de la société américaine en ce 4 juillet 2026. L’article Les États-Unis fêtent-ils aujourd’hui leur pire anniversaire&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -9732,7 +9727,6 @@
           <t>Face au «&amp;#160;grand estrangement&amp;#160;» étatsunien, le moment est venu de construire un nouveau récit européen. L’article La fin du récit atlantique est une chance historique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -9765,7 +9759,6 @@
           <t>Erreurs géographiques, encerclements inexistants, vidéos produites par l’IA, face à un bilan humain catastrophique et à un front qui se fige, le récit du Kremlin s'éloigne de plus en plus du territoire pour entrer dans une carte imaginaire. L’article Vladimir Poutine vante des conquêtes sur des territoires qui n’existent pas réellement est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -9798,7 +9791,6 @@
           <t>Une grammaire critique de la nostalgie autoritaire en sept mythes particulièrement influents. L’article Le fantasme de l’efficacité fasciste est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -9831,7 +9823,6 @@
           <t>Pour répondre au défi chinois et à la politique interne, Berlin abandonne plusieurs tabous de son modèle économique. L’article Le plan de Friedrich Merz pour faire repartir l&amp;rsquo;Allemagne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -9864,7 +9855,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance organisée avec des lauréats de la session 2026 qui ont participé à la précédente saison de l&amp;#8217;opération Coup [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Retours d&amp;rsquo;expérience et conseils de préparation avec des lauréats de la sessio</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -9897,7 +9887,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance d&amp;#8217;Alexandra Monot qui présente la nouvelle question de géographie intitulée « le Pacifique ». Le podcast est proposé en version [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Alexandra Monot &amp;#8211; Présentation de la question de géographi</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -9930,7 +9919,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance de Guillaume Debat qui présente la question d&amp;#8217;histoire moderne « l&amp;#8217;âge des révolutions ». Le podcast est proposé en version [&amp;#8230;] L’article Coup de pouce Agrégation interne &amp;#8211; Guillaume Debat &amp;#8211; Présentation de la question d&amp;rsquo;hi</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -9963,7 +9951,237 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1200227377?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; allow= </t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:33</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>Mobiliser la justice face aux épidémies : en Italie, six ans après le covid, le succès d’une association de parents de victimes</t>
+        </is>
+      </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/mobiliser-la-justice-face-aux-epidemies-en-italie-six-ans-apres-le-covid-le-succes-dune-association-de-parents-de-victimes-286181</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Six ans après le covid, le combat d’une association de parents de victimes, à Bergame, en Italie, là où cette pandémie a débuté en Europe, montre l’impact de l’action juridique face aux épidémies.</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:31</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>Au Liban, Israël se heurte aux limites de sa stratégie régionale</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-liban-israel-se-heurte-aux-limites-de-sa-strategie-regionale-286279</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>L’armée israélienne s’enfonce dans le Sud-Liban face à un Hezbollah réorganisé. Une stratégie fondée sur des analyses erronées qui ébranle aujourd’hui l’alliance avec les États-Unis.</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-07-05 05:00</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>L’accord Nakamal avec le Vanuatu : les ambitions australiennes revues à la baisse</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/05/laccord-nakamal-avec-le-vanuatu-les-ambitions-australiennes-revues-a-la-baisse/</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Entre la volonté de sanctuariser ses frontières et la dépendance accrue vis-à-vis de Washington, Canberra tente de transformer une souveraineté régionale contestée par la Chine en un bouclier stratégique résilient. L’article L’accord Nakamal avec le Vanuatu&amp;#160;: les ambitions australiennes revues à la baisse est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-07-04 13:30</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>Dans cette Coupe du monde, rien n’est écrit d’avance</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/04/dans-cette-coupe-du-monde-rien-nest-ecrit-davance/</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Le Cap-Vert crée la surprise et tient l'Argentine en échec jusqu'à la prolongation&amp;#160;; les huitièmes de finale débutent ce soir avec Maroc-Canada et France-Paraguay. L’article Dans cette Coupe du monde, rien n’est écrit d’avance est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-07-04 13:20</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>Qu’aurait pensé Tocqueville de l’Amérique de Trump ?</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/04/tocqueville-trump-melonio/</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Pour comprendre ce qui reste de La Démocratie en Amérique , nous avons posé des questions à l’une de ses meilleures spécialistes. L’article Qu’aurait pensé Tocqueville de l’Amérique de Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-07-04 11:52</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>Les funérailles d’Ali Khamenei : un moment de vérité pour l’avenir du régime iranien ?</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/04/les-funerailles-dali-khamenei-un-moment-de-verite-pour-lavenir-du-regime-iranien/</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Les funérailles nationales d'Ali Khamenei commencent aujourd'hui, 4 juillet, plus de trois mois après sa mort. Il s'agit d'un test clef pour la République islamique. L’article Les funérailles d&amp;rsquo;Ali Khamenei&amp;#160;: un moment de vérité pour l&amp;rsquo;avenir du régime iranien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 11:02</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:40</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>Charte de déontologie de l’APHG</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/charte-de-deontologie-de-laphg/</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Charte de déontologie de l&amp;#8217;APHG Préambule L&amp;#8217;Association des Professeurs d&amp;#8217;Histoire et de Géographie (APHG) rassemble des enseignants, chercheurs et passionnés engagés dans la promotion de l&amp;#8217;histoire, de la géographie et de l’enseignement moral et civique. La présente charte définit les principes éthiques et déontologiques qui guident l&amp;#8217;action collective et individuelle de ses membres, en complément [&amp;#8230;] L’article Charte de déontologie de l&amp;rsquo;APHG est apparu</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10264,6 +10482,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId304"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G305"/>
+  <dimension ref="A1:G310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9983,7 +9983,6 @@
           <t>Six ans après le covid, le combat d’une association de parents de victimes, à Bergame, en Italie, là où cette pandémie a débuté en Europe, montre l’impact de l’action juridique face aux épidémies.</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -10016,7 +10015,6 @@
           <t>L’armée israélienne s’enfonce dans le Sud-Liban face à un Hezbollah réorganisé. Une stratégie fondée sur des analyses erronées qui ébranle aujourd’hui l’alliance avec les États-Unis.</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -10049,7 +10047,6 @@
           <t>Entre la volonté de sanctuariser ses frontières et la dépendance accrue vis-à-vis de Washington, Canberra tente de transformer une souveraineté régionale contestée par la Chine en un bouclier stratégique résilient. L’article L’accord Nakamal avec le Vanuatu&amp;#160;: les ambitions australiennes revues à la baisse est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -10082,7 +10079,6 @@
           <t>Le Cap-Vert crée la surprise et tient l'Argentine en échec jusqu'à la prolongation&amp;#160;; les huitièmes de finale débutent ce soir avec Maroc-Canada et France-Paraguay. L’article Dans cette Coupe du monde, rien n’est écrit d’avance est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -10115,7 +10111,6 @@
           <t>Pour comprendre ce qui reste de La Démocratie en Amérique , nous avons posé des questions à l’une de ses meilleures spécialistes. L’article Qu’aurait pensé Tocqueville de l’Amérique de Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -10148,7 +10143,6 @@
           <t>Les funérailles nationales d'Ali Khamenei commencent aujourd'hui, 4 juillet, plus de trois mois après sa mort. Il s'agit d'un test clef pour la République islamique. L’article Les funérailles d&amp;rsquo;Ali Khamenei&amp;#160;: un moment de vérité pour l&amp;rsquo;avenir du régime iranien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -10181,7 +10175,171 @@
           <t>Charte de déontologie de l&amp;#8217;APHG Préambule L&amp;#8217;Association des Professeurs d&amp;#8217;Histoire et de Géographie (APHG) rassemble des enseignants, chercheurs et passionnés engagés dans la promotion de l&amp;#8217;histoire, de la géographie et de l’enseignement moral et civique. La présente charte définit les principes éthiques et déontologiques qui guident l&amp;#8217;action collective et individuelle de ses membres, en complément [&amp;#8230;] L’article Charte de déontologie de l&amp;rsquo;APHG est apparu</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:43</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-07-06 11:23</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>La Norvège a éliminé le Brésil. L’Espagne affronte le Portugal, dans ce qui est devenu un classique du football européen</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/06/la-norvege-a-elimine-le-bresil-lespagne-affronte-le-portugal-dans-ce-qui-est-devenu-un-classique-du-football-europeen/</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>La suite ce soir avec le match Portugal-Espagne et Belgique-États-Unis, une rencontre ouverte après la «&amp;#160;grâce&amp;#160;» accordée par la FIFA à l'attaquant américain Folarin Balogun. L’article La Norvège a éliminé le Brésil. L&amp;rsquo;Espagne affronte le Portugal, dans ce qui est devenu un classique du football européen est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:43</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-07-06 05:41</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>Comment le chef de la Marine prépare la guerre de demain</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/06/comment-le-chef-de-la-marine-prepare-la-guerre-de-demain/</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Pour l'amiral Vaujour, les conflits se jouent désormais sur les mers, les flux et la vitesse d'adaptation. L’article Comment le chef de la Marine prépare la guerre de demain est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:43</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-07-06 05:39</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la jeunesse chinoise rêve-t-elle de retourner en 2008 ?</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/06/la-jeunesse-chinoise-reve-de-retourner-en-2008/</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>En Chine, le mème le plus populaire de la génération Z est aussi le symptôme d’une crise qui semble échapper au contrôle du Parti. L’article Pourquoi la jeunesse chinoise rêve-t-elle de retourner en 2008&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:43</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-07-05 15:00</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>Donald Trump a transformé la liberté d’expression en arme de vassalisation</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/05/donald-trump-a-transforme-la-liberte-dexpression-en-arme-de-vassalisation/</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Une enquête historique particulièrement fouillée sur la naissance d'une nouvelle doctrine américaine. L’article Donald Trump a transformé la liberté d’expression en arme de vassalisation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 12:43</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-07-05 13:12</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>La France se qualifie au terme d’un match étouffant contre le Paraguay. Le Canada, premier pays hôte éliminé du tournoi</t>
+        </is>
+      </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/05/la-france-se-qualifie-au-terme-dun-match-etouffant-contre-le-paraguay-le-canada-premier-pays-hote-elimine-du-tournoi/</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Les Bleus rencontreront le Maroc en quart de finale, le 9 juillet. Ce soir et cette nuit, deux autres huitièmes de finale au charme incontestable se disputeront&amp;#160;: Brésil-Norvège à 22h, suivi de Mexique-Angleterre à 2h. L’article La France se qualifie au terme d&amp;rsquo;un match étouffant contre le Paraguay. Le Canada, premier pays hôte éliminé du tournoi est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10489,6 +10647,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId303"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId309"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G310"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10207,7 +10207,6 @@
           <t>La suite ce soir avec le match Portugal-Espagne et Belgique-États-Unis, une rencontre ouverte après la «&amp;#160;grâce&amp;#160;» accordée par la FIFA à l'attaquant américain Folarin Balogun. L’article La Norvège a éliminé le Brésil. L&amp;rsquo;Espagne affronte le Portugal, dans ce qui est devenu un classique du football européen est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -10240,7 +10239,6 @@
           <t>Pour l'amiral Vaujour, les conflits se jouent désormais sur les mers, les flux et la vitesse d'adaptation. L’article Comment le chef de la Marine prépare la guerre de demain est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -10273,7 +10271,6 @@
           <t>En Chine, le mème le plus populaire de la génération Z est aussi le symptôme d’une crise qui semble échapper au contrôle du Parti. L’article Pourquoi la jeunesse chinoise rêve-t-elle de retourner en 2008&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -10306,7 +10303,6 @@
           <t>Une enquête historique particulièrement fouillée sur la naissance d'une nouvelle doctrine américaine. L’article Donald Trump a transformé la liberté d’expression en arme de vassalisation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -10339,7 +10335,237 @@
           <t>Les Bleus rencontreront le Maroc en quart de finale, le 9 juillet. Ce soir et cette nuit, deux autres huitièmes de finale au charme incontestable se disputeront&amp;#160;: Brésil-Norvège à 22h, suivi de Mexique-Angleterre à 2h. L’article La France se qualifie au terme d&amp;rsquo;un match étouffant contre le Paraguay. Le Canada, premier pays hôte éliminé du tournoi est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-07-06 13:44</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>Qu’est-ce que « l’affichage parental d’images de mineurs » ?</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quest-ce-que-laffichage-parental-dimages-de-mineurs-286722</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Publier une photo de famille sur les réseaux sociaux, est-ce partager un souvenir ou exposer son enfant&amp;nbsp;? L’expression «&amp;nbsp;affichage parental d’images de mineurs&amp;nbsp;» invite à se poser la question.</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-07-06 13:45</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi l’Iran ne parviendra pas à instaurer un péage dans le détroit d’Ormuz</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-liran-ne-parviendra-pas-a-instaurer-un-peage-dans-le-detroit-dormuz-286573</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>L’instauration par l’Iran d’un péage permanent sur le détroit d’Ormuz ne serait ni légale ni réalisable.</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-07-06 13:43</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi est-ce si difficile d’estimer les bénéfices et les coûts du Brexit ?</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-est-ce-si-difficile-destimer-les-benefices-et-les-couts-du-brexit-279281</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Les effets du Brexit, économiques et managériaux, divisent. Nous proposons de l’analyser comme un «&amp;nbsp;risque&amp;nbsp;» à l’aide des outils du «&amp;nbsp;risk management&amp;nbsp;».</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-07-07 07:16</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>Le sommet de l’OTAN s’ouvre à Ankara. Quels sont les points à suivre ?</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/07/le-sommet-de-lotan-souvre-a-ankara-quels-sont-les-points-a-suivre/</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Le sommet annuel de l'OTAN, qui réunira les chefs d'État et de gouvernement des 32 États membres, s'ouvre aujourd'hui, 7 juillet, à Ankara. Avec des discussions qui se concentreront principalement sur la hausse des dépenses de défense, et en s'appuyant sur la proximité d'Erdoğan avec le président américain, les alliés ont un objectif principal&amp;#160;: éviter un affrontement direct avec Donald Trump. L’article Le sommet de l’OTAN s’ouvre à Ankara. Quels sont les points à suivre&amp;#160;? est apparu e</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:58</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>À Erfurt, Alice Weidel renforce son pouvoir lors du congrès de l’AfD</t>
+        </is>
+      </c>
+      <c r="E315" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/06/a-erfurt-alice-weidel-renforce-son-pouvoir-lors-du-congres-de-lafd/</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Le parti de droite radicale Alternative für Deutschland (AfD) a tenu son congrès annuel ce week-end dans la capitale de la Thuringe, malgré la contestation de la société civile. Plus qu’une occasion de présenter un nouveau programme, s'il s’agit surtout d’une mise en scène comme une force de gouvernement possible. L’article À Erfurt, Alice Weidel renforce son pouvoir lors du congrès de l’AfD est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:33</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>Ce que révèle la mise en scène des funérailles du Khamenei</t>
+        </is>
+      </c>
+      <c r="E316" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/06/ce-que-revele-la-mise-en-scene-des-funerailles-du-khamenei/</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Pourquoi le régime iranien organise-t-il les plus grandes funérailles du XXIᵉ siècle&amp;#160;? L’article Ce que révèle la mise en scène des funérailles du Khamenei est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:45</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-07-06 04:39</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>Le réalisme européen commence par l’exemplarité</t>
+        </is>
+      </c>
+      <c r="E317" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/06/le-realisme-europeen-commence-par-lexemplarite/</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Pour définir sa puissance, l’Europe doit comprendre que sa force tient d'abord à la crédibilité de ses principes. L’article Le réalisme européen commence par l&amp;rsquo;exemplarité est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10652,6 +10878,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId307"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId316"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G317"/>
+  <dimension ref="A1:G324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10367,7 +10367,6 @@
           <t>Publier une photo de famille sur les réseaux sociaux, est-ce partager un souvenir ou exposer son enfant&amp;nbsp;? L’expression «&amp;nbsp;affichage parental d’images de mineurs&amp;nbsp;» invite à se poser la question.</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -10400,7 +10399,6 @@
           <t>L’instauration par l’Iran d’un péage permanent sur le détroit d’Ormuz ne serait ni légale ni réalisable.</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -10433,7 +10431,6 @@
           <t>Les effets du Brexit, économiques et managériaux, divisent. Nous proposons de l’analyser comme un «&amp;nbsp;risque&amp;nbsp;» à l’aide des outils du «&amp;nbsp;risk management&amp;nbsp;».</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -10466,7 +10463,6 @@
           <t>Le sommet annuel de l'OTAN, qui réunira les chefs d'État et de gouvernement des 32 États membres, s'ouvre aujourd'hui, 7 juillet, à Ankara. Avec des discussions qui se concentreront principalement sur la hausse des dépenses de défense, et en s'appuyant sur la proximité d'Erdoğan avec le président américain, les alliés ont un objectif principal&amp;#160;: éviter un affrontement direct avec Donald Trump. L’article Le sommet de l’OTAN s’ouvre à Ankara. Quels sont les points à suivre&amp;#160;? est apparu e</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -10499,7 +10495,6 @@
           <t>Le parti de droite radicale Alternative für Deutschland (AfD) a tenu son congrès annuel ce week-end dans la capitale de la Thuringe, malgré la contestation de la société civile. Plus qu’une occasion de présenter un nouveau programme, s'il s’agit surtout d’une mise en scène comme une force de gouvernement possible. L’article À Erfurt, Alice Weidel renforce son pouvoir lors du congrès de l’AfD est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -10532,7 +10527,6 @@
           <t>Pourquoi le régime iranien organise-t-il les plus grandes funérailles du XXIᵉ siècle&amp;#160;? L’article Ce que révèle la mise en scène des funérailles du Khamenei est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -10565,7 +10559,237 @@
           <t>Pour définir sa puissance, l’Europe doit comprendre que sa force tient d'abord à la crédibilité de ses principes. L’article Le réalisme européen commence par l&amp;rsquo;exemplarité est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-07-07 13:53</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>Retour sur le Covid-19 : d’une crise globale à des réponses nationales, les enseignements de la France, du Brésil et du Portugal</t>
+        </is>
+      </c>
+      <c r="E318" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/retour-sur-le-covid-19-dune-crise-globale-a-des-reponses-nationales-les-enseignements-de-la-france-du-bresil-et-du-portugal-286204</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Une analyse de la France, du Portugal et du Brésil montre comment l’organisation des soins et la gouvernance de chaque pays ont influencé la réponse nationale face au Covid-19.</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-07-07 13:52</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>Des drones à quelques milliers de dollars contre des bombardiers à 100 millions : les grandes puissances sont-elles encore à l’abri ?</t>
+        </is>
+      </c>
+      <c r="E319" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/des-drones-a-quelques-milliers-de-dollars-contre-des-bombardiers-a-100-millions-les-grandes-puissances-sont-elles-encore-a-labri-286311</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Les drones bon marché font des équipements coûteux des grandes puissances des cibles privilégiées.</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:37</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>En continuant ses frappes contre l’Iran, les États-Unis marquent-ils un nouveau pivot vers le Moyen-Orient ?</t>
+        </is>
+      </c>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/08/en-continuant-ses-frappes-contre-liran-les-etats-unis-marquent-ils-un-nouveau-pivot-vers-le-moyen-orient/</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>En poursuivant la guerre contre l’Iran, les États-Unis pourraient mettre une limite matérielle à leurs possibilités d’intervention sur d’autres théâtres d'opérations, y compris dans l’Indo-Pacifique. L’article En continuant ses frappes contre l’Iran, les États-Unis marquent-ils un nouveau pivot vers le Moyen-Orient&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-07-08 05:32</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>Près d’une majorité d’Européens s’opposent à des coupes dans les dépenses publiques pour investir dans la défense</t>
+        </is>
+      </c>
+      <c r="E321" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/08/pres-dune-majorite-deuropeens-sopposent-a-des-coupes-dans-les-depenses-publiques-pour-investir-dans-la-defense/</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Depuis 2015, les dépenses militaires de l'Otan ont augmenté de 28&amp;#160;% en volume, avec un objectif d'atteindre 5&amp;#160;% du PIB d'ici 2035, un calendrier que le sommet d'Ankara pourrait encore accélérer. Dans un contexte budgétaire fragile, ce financement pourrait s'imposer comme un sujet clef du débat&amp;#160;: selon une récente enquête, près d'une majorité d'Européens s'opposent à des coupes dans les dépenses publiques pour investir dans la défense. L’article Près d’une majorité d&amp;rsquo;Européen</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-07-07 17:36</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>En amont du sommet de l’OTAN à Ankara, Trump menace à nouveau le Groenland</t>
+        </is>
+      </c>
+      <c r="E322" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/07/en-amont-du-sommet-de-lotan-a-ankara-trump-menace-a-nouveau-le-groenland/</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Trump a réitéré, aujourd’hui, 7 juillet, aux côtés d'Erdoğan, qu’«&amp;#160;il faut que le Groenland soit contrôlé par les États-Unis, et non par le Danemark&amp;#160;». L’article En amont du sommet de l’OTAN à Ankara, Trump menace à nouveau le Groenland est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-07-07 15:39</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>Comment Erdoğan a inventé le néo-royalisme</t>
+        </is>
+      </c>
+      <c r="E323" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/07/commet-erdogan-a-invente-le-neo-royalisme/</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Depuis deux décennies, le président turc travaille systématiquement à l’avènement d’un nouveau régime politique. L’article Comment Erdoğan a inventé le néo-royalisme est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-07-07 13:16</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo fait ses adieux à la dernière Coupe du monde de sa carrière</t>
+        </is>
+      </c>
+      <c r="E324" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/07/cristiano-ronaldo-fait-ses-adieux-a-la-derniere-coupe-du-monde-de-sa-carriere/</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>L’Espagne a éliminé le Portugal hier, 6 juin, dans un match marqué par la prudence. La Roja a toutefois une nouvelle fois prouvé qu’elle savait s’imposer, que ce soit en jouant de manière spectaculaire ou en gérant les moments difficiles, ce qui en fait une candidate sérieuse à la victoire finale. L’article Cristiano Ronaldo fait ses adieux à la dernière Coupe du monde de sa carrière est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10885,6 +11109,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId315"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId323"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G324"/>
+  <dimension ref="A1:G334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10591,7 +10591,6 @@
           <t>Une analyse de la France, du Portugal et du Brésil montre comment l’organisation des soins et la gouvernance de chaque pays ont influencé la réponse nationale face au Covid-19.</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -10624,7 +10623,6 @@
           <t>Les drones bon marché font des équipements coûteux des grandes puissances des cibles privilégiées.</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -10657,7 +10655,6 @@
           <t>En poursuivant la guerre contre l’Iran, les États-Unis pourraient mettre une limite matérielle à leurs possibilités d’intervention sur d’autres théâtres d'opérations, y compris dans l’Indo-Pacifique. L’article En continuant ses frappes contre l’Iran, les États-Unis marquent-ils un nouveau pivot vers le Moyen-Orient&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -10690,7 +10687,6 @@
           <t>Depuis 2015, les dépenses militaires de l'Otan ont augmenté de 28&amp;#160;% en volume, avec un objectif d'atteindre 5&amp;#160;% du PIB d'ici 2035, un calendrier que le sommet d'Ankara pourrait encore accélérer. Dans un contexte budgétaire fragile, ce financement pourrait s'imposer comme un sujet clef du débat&amp;#160;: selon une récente enquête, près d'une majorité d'Européens s'opposent à des coupes dans les dépenses publiques pour investir dans la défense. L’article Près d’une majorité d&amp;rsquo;Européen</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -10723,7 +10719,6 @@
           <t>Trump a réitéré, aujourd’hui, 7 juillet, aux côtés d'Erdoğan, qu’«&amp;#160;il faut que le Groenland soit contrôlé par les États-Unis, et non par le Danemark&amp;#160;». L’article En amont du sommet de l’OTAN à Ankara, Trump menace à nouveau le Groenland est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -10756,7 +10751,6 @@
           <t>Depuis deux décennies, le président turc travaille systématiquement à l’avènement d’un nouveau régime politique. L’article Comment Erdoğan a inventé le néo-royalisme est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -10789,7 +10783,336 @@
           <t>L’Espagne a éliminé le Portugal hier, 6 juin, dans un match marqué par la prudence. La Roja a toutefois une nouvelle fois prouvé qu’elle savait s’imposer, que ce soit en jouant de manière spectaculaire ou en gérant les moments difficiles, ce qui en fait une candidate sérieuse à la victoire finale. L’article Cristiano Ronaldo fait ses adieux à la dernière Coupe du monde de sa carrière est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:28</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>Peut-on apprendre la géographie française grâce aux jeux « Pokémon » ?</t>
+        </is>
+      </c>
+      <c r="E325" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/peut-on-apprendre-la-geographie-francaise-grace-aux-jeux-pokemon-286912</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Les jeux «&amp;nbsp;Pokémon&amp;nbsp;» mobilisent en toile de fond la géographie, l’histoire et la culture des lieux dont ils sont inspirés, avec un savant dosage de clichés et de réalisme.</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:29</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>En supprimant le garant et le dépôt de garantie, le Brésil facilite la location des logements. Qui en profite vraiment ?</t>
+        </is>
+      </c>
+      <c r="E326" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/en-supprimant-le-garant-et-le-depot-de-garantie-le-bresil-facilite-la-location-des-logements-qui-en-profite-vraiment-281809</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Au Brésil, la plateforme Quintoandar se charge du recouvrement judiciaire auprès des propriétaires en cas d’impayés des locataires. Une garantie locative privée qui arrange tout le monde.</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:54</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>L’équipe marocaine que la France va affronter ce soir sera un adversaire plus redoutable qu’en 2022</t>
+        </is>
+      </c>
+      <c r="E327" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/09/lequipe-marocaine-que-la-france-va-affronter-ce-soir-sera-un-adversaire-plus-redoutable-que-en-2022/</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Le Maroc s’est considérablement amélioré depuis la Coupe du monde au Qatar. L’article L’équipe marocaine que la France va affronter ce soir sera un adversaire plus redoutable qu’en 2022 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-07-09 04:30</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : plus de 80 % des capacités de raffinage du pays ont été prises pour cible par l’Ukraine cette année</t>
+        </is>
+      </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/09/economie-russe-plus-de-80-des-capacites-de-raffinage-du-pays-ont-ete-prises-pour-cible-par-lukraine-cette-annee/</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Depuis le 1er janvier, 16 raffineries de pétrole russes représentant une capacité de raffinage de 161 millions de tonnes par an ont été ciblées à plusieurs reprises par des drones ukrainiens. L’article Économie russe&amp;#160;: plus de 80&amp;#160;% des capacités de raffinage du pays ont été prises pour cible par l’Ukraine cette année est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-07-09 04:30</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>Le nouveau choc chinois oblige l’Europe à se réinventer plus qu’à se protéger</t>
+        </is>
+      </c>
+      <c r="E329" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/09/le-nouveau-choc-chinois-oblige-leurope-a-se-reinventer-plus-qua-se-proteger/</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Le maximalisme industriel de Pékin est en train de faire changer le modèle européen. L’article Le nouveau choc chinois oblige l&amp;rsquo;Europe à se réinventer plus qu&amp;rsquo;à se protéger est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-07-08 15:44</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>La Coupe du monde est-elle sous l’influence de Trump ?</t>
+        </is>
+      </c>
+      <c r="E330" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/08/la-coupe-du-monde-est-elle-sous-linfluence-de-trump/</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>L'opportunisme politique de Gianni Infantino est bien connu, mais sa proximité avec Trump a atteint des proportions troublantes. L’article La Coupe du monde est-elle sous l&amp;rsquo;influence de Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-07-08 15:31</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>Opération Prométhée : la France peut gagner la course à l’IA. Quel en serait le prix ?</t>
+        </is>
+      </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/08/operation-promethee-la-france-peut-gagner-la-course-a-lia-quel-en-serait-le-prix/</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Une pièce de doctrine à l'attention du prochain président de la République et de ses électeurs. L’article Opération Prométhée&amp;#160;: la France peut gagner la course à l&amp;rsquo;IA. Quel en serait le prix&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:47</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>Pékin s’apprête à durcir l’accès étranger à ses modèles d’IA de pointe</t>
+        </is>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/08/pekin-sapprete-a-durcir-lacces-etranger-a-ses-modeles-dia-de-pointe/</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Le renforcement du contrôle chinois sur les flux technologiques liés à l’IA s’inscrit dans un contexte de symétrisation avec les États-Unis. L’article Pékin s’apprête à durcir l’accès étranger à ses modèles d’IA de pointe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:40</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Méthodologie de la dissertation de géographie</t>
+        </is>
+      </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-methodologie-de-la-dissertation-de-geographie/</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Zoé Lambert et consacrée à la méthodologie de la dissertation de géographie. Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne – Méthodologie de la dissertation de géographie est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 11:53</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:40</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Préparer le concours avec méthode</t>
+        </is>
+      </c>
+      <c r="E334" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-preparer-le-concours-avec-methode-2/</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Marie Laulan, Nathalie Maquoi et Sandrine Romy la méthodologie et l&amp;#8217;organisation générales du concours. Le podcast [&amp;#8230;] L’article Coup de pouce Agrégation interne – Préparer le concours avec méthode est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11116,6 +11439,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId321"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId333"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G334"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10815,7 +10815,6 @@
           <t>Les jeux «&amp;nbsp;Pokémon&amp;nbsp;» mobilisent en toile de fond la géographie, l’histoire et la culture des lieux dont ils sont inspirés, avec un savant dosage de clichés et de réalisme.</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -10848,7 +10847,6 @@
           <t>Au Brésil, la plateforme Quintoandar se charge du recouvrement judiciaire auprès des propriétaires en cas d’impayés des locataires. Une garantie locative privée qui arrange tout le monde.</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -10881,7 +10879,6 @@
           <t>Le Maroc s’est considérablement amélioré depuis la Coupe du monde au Qatar. L’article L’équipe marocaine que la France va affronter ce soir sera un adversaire plus redoutable qu’en 2022 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -10914,7 +10911,6 @@
           <t>Depuis le 1er janvier, 16 raffineries de pétrole russes représentant une capacité de raffinage de 161 millions de tonnes par an ont été ciblées à plusieurs reprises par des drones ukrainiens. L’article Économie russe&amp;#160;: plus de 80&amp;#160;% des capacités de raffinage du pays ont été prises pour cible par l’Ukraine cette année est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -10947,7 +10943,6 @@
           <t>Le maximalisme industriel de Pékin est en train de faire changer le modèle européen. L’article Le nouveau choc chinois oblige l&amp;rsquo;Europe à se réinventer plus qu&amp;rsquo;à se protéger est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -10980,7 +10975,6 @@
           <t>L'opportunisme politique de Gianni Infantino est bien connu, mais sa proximité avec Trump a atteint des proportions troublantes. L’article La Coupe du monde est-elle sous l&amp;rsquo;influence de Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -11013,7 +11007,6 @@
           <t>Une pièce de doctrine à l'attention du prochain président de la République et de ses électeurs. L’article Opération Prométhée&amp;#160;: la France peut gagner la course à l&amp;rsquo;IA. Quel en serait le prix&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -11046,7 +11039,6 @@
           <t>Le renforcement du contrôle chinois sur les flux technologiques liés à l’IA s’inscrit dans un contexte de symétrisation avec les États-Unis. L’article Pékin s’apprête à durcir l’accès étranger à ses modèles d’IA de pointe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -11079,7 +11071,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Zoé Lambert et consacrée à la méthodologie de la dissertation de géographie. Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne – Méthodologie de la dissertation de géographie est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -11112,7 +11103,303 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Marie Laulan, Nathalie Maquoi et Sandrine Romy la méthodologie et l&amp;#8217;organisation générales du concours. Le podcast [&amp;#8230;] L’article Coup de pouce Agrégation interne – Préparer le concours avec méthode est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:46</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>Les Vikings étaient bien plus que des pillards barbus : pourquoi les musées scandinaves entretiennent encore cette image ?</t>
+        </is>
+      </c>
+      <c r="E335" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-vikings-etaient-bien-plus-que-des-pillards-barbus-pourquoi-les-musees-scandinaves-entretiennent-encore-cette-image-287196</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Les musées nationaux de Scandinavie ne racontent pas seulement le passé : ils contribuent aussi à façonner l’identité contemporaine. Quitte à entretenir certains mythes sur les Vikings, toujours très présents dans l’imaginaire collectif.</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-07-10 08:59</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>La « malédiction » du « Titanic » et la vie oubliée de la fille du capitaine</t>
+        </is>
+      </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-malediction-du-titanic-et-la-vie-oubliee-de-la-fille-du-capitaine-286331</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Après le naufrage du « Titanic », Helen Melville Smith hérite d’une identité publique qu’elle n’a pas choisie. Son parcours montre comment les récits historiques peuvent enfermer des vies complexes dans des histoires de fatalité.</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-07-10 08:59</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>Avant Epstein, le scandale sexuel qui a forcé la Grande-Bretagne à changer sa loi</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/avant-epstein-le-scandale-sexuel-qui-a-force-la-grande-bretagne-a-changer-sa-loi-281457</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>En 1885, des journalistes et des militantes dénoncent un réseau impliquant de riches notables dans l'exploitation sexuelle de jeunes filles. Leur enquête fait évoluer la législation britannique, mais laisse les principaux responsables à l'abri des poursuites.</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:23</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>Écoles en surchauffe : un problème qui se joue avant tout à l’échelle des salles de classe</t>
+        </is>
+      </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ecoles-en-surchauffe-un-probleme-qui-se-joue-avant-tout-a-lechelle-des-salles-de-classe-286878</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Comment aider l’école à s’adapter aux canicules&amp;nbsp;? Il ne faut pas oublier que, au sein d’un même établissement, l’étage et l’exposition des salles jouent beaucoup.</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:24</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis à l’heure des christianismes concurrents</t>
+        </is>
+      </c>
+      <c r="E339" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-etats-unis-a-lheure-des-christianismes-concurrents-285305</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, la religion pèse de longue date sur la politique. Mais sous Trump, son influence s’étend sans cesse davantage.</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:18</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le nucléaire fait-il un retour ?</t>
+        </is>
+      </c>
+      <c r="E340" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/10/pourquoi-le-nucleaire-fait-il-un-retour/</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>La demande croissante d’électricité, la décarbonation des mix et la multiplication des centres de données alimentent un intérêt croissant pour l’énergie nucléaire. L’article Pourquoi le nucléaire fait-il un retour&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-07-10 04:30</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>À quatre mois des élections de mi-mandat, le Parti républicain se divise sur la construction de centres de données</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/10/a-quatre-mois-des-elections-de-mi-mandat-le-parti-republicain-se-divise-sur-la-construction-de-centres-de-donnees/</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>L’opposition de plusieurs élus et candidats républicains à la construction d’infrastructures liées à l’IA constitue un rare cas de rupture d’une partie du GOP avec la Maison-Blanche. L’article À quatre mois des élections de mi-mandat, le Parti républicain se divise sur la construction de centres de données est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-07-10 04:30</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>Ce que pensent vraiment les Ukrainiens de la guerre et de Trump (sondage exclusif)</t>
+        </is>
+      </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/10/ce-que-pensent-vraiment-les-ukrainiens-sondage-exclusif/</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Une plongée dans les grandes tendances de la société ukrainienne grâce à une série de données inédites. L’article Ce que pensent vraiment les Ukrainiens de la guerre et de Trump (sondage exclusif) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:48</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:06</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>Dans les rues de la capitale de la Corée du Nord il y a de plus en plus de voitures</t>
+        </is>
+      </c>
+      <c r="E343" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/09/pourquoi-les-voitures-se-multiplient-dans-les-rues-de-pyongyang/</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>La hausse du nombre de véhicules en circulation dans la capitale nord-coréenne reflète les efforts de Kim Jong-Un visant à stimuler la consommation. L’article Dans les rues de la capitale de la Corée du Nord il y a de plus en plus de voitures est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11449,6 +11736,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E332" r:id="rId331"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E333" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId342"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G343"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11135,7 +11135,6 @@
           <t>Les musées nationaux de Scandinavie ne racontent pas seulement le passé : ils contribuent aussi à façonner l’identité contemporaine. Quitte à entretenir certains mythes sur les Vikings, toujours très présents dans l’imaginaire collectif.</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -11168,7 +11167,6 @@
           <t>Après le naufrage du « Titanic », Helen Melville Smith hérite d’une identité publique qu’elle n’a pas choisie. Son parcours montre comment les récits historiques peuvent enfermer des vies complexes dans des histoires de fatalité.</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -11201,7 +11199,6 @@
           <t>En 1885, des journalistes et des militantes dénoncent un réseau impliquant de riches notables dans l'exploitation sexuelle de jeunes filles. Leur enquête fait évoluer la législation britannique, mais laisse les principaux responsables à l'abri des poursuites.</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -11234,7 +11231,6 @@
           <t>Comment aider l’école à s’adapter aux canicules&amp;nbsp;? Il ne faut pas oublier que, au sein d’un même établissement, l’étage et l’exposition des salles jouent beaucoup.</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -11267,7 +11263,6 @@
           <t>Aux États-Unis, la religion pèse de longue date sur la politique. Mais sous Trump, son influence s’étend sans cesse davantage.</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -11300,7 +11295,6 @@
           <t>La demande croissante d’électricité, la décarbonation des mix et la multiplication des centres de données alimentent un intérêt croissant pour l’énergie nucléaire. L’article Pourquoi le nucléaire fait-il un retour&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -11333,7 +11327,6 @@
           <t>L’opposition de plusieurs élus et candidats républicains à la construction d’infrastructures liées à l’IA constitue un rare cas de rupture d’une partie du GOP avec la Maison-Blanche. L’article À quatre mois des élections de mi-mandat, le Parti républicain se divise sur la construction de centres de données est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -11366,7 +11359,6 @@
           <t>Une plongée dans les grandes tendances de la société ukrainienne grâce à une série de données inédites. L’article Ce que pensent vraiment les Ukrainiens de la guerre et de Trump (sondage exclusif) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -11399,7 +11391,171 @@
           <t>La hausse du nombre de véhicules en circulation dans la capitale nord-coréenne reflète les efforts de Kim Jong-Un visant à stimuler la consommation. L’article Dans les rues de la capitale de la Corée du Nord il y a de plus en plus de voitures est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 10:11</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-07-11 09:04</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>Pays pauvres : comment les institutions financières internationales leur permettent de se financer à moindre coût ?</t>
+        </is>
+      </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pays-pauvres-comment-les-institutions-financieres-internationales-leur-permettent-de-se-financer-a-moindre-cout-280837</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Pourquoi les banques multilatérales de développement prêtent-elles aux pays pauvres&amp;nbsp;? Leur secret tient au statut de créancier privilégié.</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 10:11</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-07-11 05:36</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>La leçon de Jean Monnet</t>
+        </is>
+      </c>
+      <c r="E345" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/11/la-lecon-de-jean-monnet/</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>«&amp;#160;Le drame de l’Europe, c’est d’avoir rendu Jean Monnet ennuyeux.&amp;#160;» L’article La leçon de Jean Monnet est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 10:11</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-07-11 04:30</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>Comment Pékin investit la gouvernance environnementale mondiale</t>
+        </is>
+      </c>
+      <c r="E346" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/11/comment-pekin-investit-la-gouvernance-environnementale-mondiale/</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Avec la multiplication des partenariats climatiques et des réseaux de recherche adossés aux Nouvelles routes de la soie, Pékin investit méthodiquement le champ de la gouvernance environnementale mondiale. La présidence de Donald Trump pourrait lui offrir l'occasion de combler le vide laissé par Washington. L’article Comment Pékin investit la gouvernance environnementale mondiale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 10:11</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:06</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>La Russie consolide sa présence en Syrie</t>
+        </is>
+      </c>
+      <c r="E347" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/10/la-russie-consolide-sa-presence-en-syrie/</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Le pouvoir syrien, tout en se rapprochant des pays occidentaux et du Golfe, devrait permettre à Moscou de conserver une présence à Tartous et à Hmeimim. L’article La Russie consolide sa présence en Syrie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 10:11</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-07-10 14:43</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>Le Maroc a eu la malchance de tomber sur la France trop tôt</t>
+        </is>
+      </c>
+      <c r="E348" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/10/le-maroc-a-eu-la-malchance-de-tomber-sur-la-france-trop-tot/</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>En trois matchs à élimination directe, la France n'a pas encaissé le moindre but. Et en comptant la phase de groupes, elle n'a jamais été menée au score. L’article Le Maroc a eu la malchance de tomber sur la France trop tôt est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11745,6 +11901,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId341"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId347"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11423,7 +11423,6 @@
           <t>Pourquoi les banques multilatérales de développement prêtent-elles aux pays pauvres&amp;nbsp;? Leur secret tient au statut de créancier privilégié.</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -11456,7 +11455,6 @@
           <t>«&amp;#160;Le drame de l’Europe, c’est d’avoir rendu Jean Monnet ennuyeux.&amp;#160;» L’article La leçon de Jean Monnet est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -11489,7 +11487,6 @@
           <t>Avec la multiplication des partenariats climatiques et des réseaux de recherche adossés aux Nouvelles routes de la soie, Pékin investit méthodiquement le champ de la gouvernance environnementale mondiale. La présidence de Donald Trump pourrait lui offrir l'occasion de combler le vide laissé par Washington. L’article Comment Pékin investit la gouvernance environnementale mondiale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -11522,7 +11519,6 @@
           <t>Le pouvoir syrien, tout en se rapprochant des pays occidentaux et du Golfe, devrait permettre à Moscou de conserver une présence à Tartous et à Hmeimim. L’article La Russie consolide sa présence en Syrie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -11555,7 +11551,270 @@
           <t>En trois matchs à élimination directe, la France n'a pas encaissé le moindre but. Et en comptant la phase de groupes, elle n'a jamais été menée au score. L’article Le Maroc a eu la malchance de tomber sur la France trop tôt est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:35</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>Peut-on cartographier l'Odyssée ? Comment géographes antiques et chercheurs d'aujourd'hui ont retracé le voyage d'Ulysse</t>
+        </is>
+      </c>
+      <c r="E349" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/peut-on-cartographier-lodyssee-comment-geographes-antiques-et-chercheurs-daujourdhui-ont-retrace-le-voyage-dulysse-287354</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Et si l’Odyssée était aussi un atlas ? Pendant des siècles, des érudits ont tenté d'identifier les escales d'Ulysse sur les rivages de la Méditerranée, brouillant sans cesse la frontière entre histoire, géographie et mythologie.</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-07-12 08:38</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>Marianne : pourquoi la République a-t-elle choisi une femme désincarnée comme symbole d’unité nationale ?</t>
+        </is>
+      </c>
+      <c r="E350" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/marianne-pourquoi-la-republique-a-t-elle-choisi-une-femme-desincarnee-comme-symbole-dunite-nationale-281777</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Allégorie convoquée par tous les camps politiques, Marianne est insaisissable dès qu’il s’agit de lui donner une incarnation. Mais que représente-t-elle vraiment&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-07-12 08:39</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>Quand la Légion d’honneur fait monter les cours de Bourse : les décorations d’État, signaux de proximité politique ?</t>
+        </is>
+      </c>
+      <c r="E351" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-la-legion-dhonneur-fait-monter-les-cours-de-bourse-les-decorations-detat-signaux-de-proximite-politique-286866</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Les distinctions comme la Légion d’honneur ne sont-elles que des «&amp;nbsp;hochets avec lesquels on mène les hommes&amp;nbsp;», selon le mot de Napoléon&amp;nbsp;? Non, répond une recherche autour de leur impact économique.</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-07-12 08:37</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>Allons-nous vers une « corridorisation » du monde ?</t>
+        </is>
+      </c>
+      <c r="E352" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/allons-nous-vers-une-corridorisation-du-monde-286179</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>De l’Europe à la Chine, les grandes puissances souhaitent construire davantage de corridors, nouvelles voies stratégiques de la mondialisation.</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-07-12 05:00</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, l’utilisation de médicaments amaigrissants tels qu’Ozempic ou Wegovy a presque quadruplé en deux ans</t>
+        </is>
+      </c>
+      <c r="E353" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/12/aux-etats-unis-lutilisation-de-medicaments-amaigrissants-tels-quozempic-ou-wegovy-a-presque-quadruple-en-deux-ans/</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Environ 25 millions d'Américains pourraient suivre un traitement à base de GLP-1 d'ici 2030, soit près de 10&amp;#160;% de la population adulte, contre 10 millions en 2025. L’article Aux États-Unis, l&amp;rsquo;utilisation de médicaments amaigrissants tels qu’Ozempic ou Wegovy a presque quadruplé en deux ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-07-11 15:00</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>Vladimir Poutine a un problème avec l’intelligence artificielle</t>
+        </is>
+      </c>
+      <c r="E354" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/11/vladimir-poutine-a-un-probleme-avec-lintelligence-artificielle/</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Incapable de rivaliser avec les États-Unis ou la Chine au cœur de la révolution technologique, le Kremlin investit ses marges. L’article Vladimir Poutine a un problème avec l’intelligence artificielle est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-07-11 14:55</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>Demi-finale : France-Espagne, le rendez-vous devenu rituel</t>
+        </is>
+      </c>
+      <c r="E355" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/11/demi-finale-france-espagne-le-rendez-vous-devenu-rituel/</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Vainqueure de la Belgique (2-1), l'Espagne retrouvera les Bleus en demi-finale, comme à l'Euro 2024 et en Ligue des nations en 2025. L’article Demi-finale&amp;#160;: France-Espagne, le rendez-vous devenu rituel est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12 10:23</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-07-11 12:25</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>Donald Tusk tente d’apaiser les tensions mémorielles avec l’Ukraine</t>
+        </is>
+      </c>
+      <c r="E356" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/11/346025/</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Ce 11 juillet marque la 83ᵉ commémoration du «&amp;#160;dimanche sanglant&amp;#160;» de Volhynie, point culminant d'un massacre de 1943 que la Pologne qualifie de génocide, mais que Kiev refuse toujours de reconnaître comme tel. Le Premier ministre, Donald Tusk, a profité de l'occasion pour appeler à la vérité historique, tout en plaidant pour l'apaisement des relations avec l'Ukraine, après une séquence diplomatique tendue. L’article Donald Tusk tente d’apaiser les tensions mémorielles avec l’Ukraine e</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11906,6 +12165,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId345"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId355"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G356"/>
+  <dimension ref="A1:G361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11583,7 +11583,6 @@
           <t>Et si l’Odyssée était aussi un atlas ? Pendant des siècles, des érudits ont tenté d'identifier les escales d'Ulysse sur les rivages de la Méditerranée, brouillant sans cesse la frontière entre histoire, géographie et mythologie.</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -11616,7 +11615,6 @@
           <t>Allégorie convoquée par tous les camps politiques, Marianne est insaisissable dès qu’il s’agit de lui donner une incarnation. Mais que représente-t-elle vraiment&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -11649,7 +11647,6 @@
           <t>Les distinctions comme la Légion d’honneur ne sont-elles que des «&amp;nbsp;hochets avec lesquels on mène les hommes&amp;nbsp;», selon le mot de Napoléon&amp;nbsp;? Non, répond une recherche autour de leur impact économique.</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -11682,7 +11679,6 @@
           <t>De l’Europe à la Chine, les grandes puissances souhaitent construire davantage de corridors, nouvelles voies stratégiques de la mondialisation.</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -11715,7 +11711,6 @@
           <t>Environ 25 millions d'Américains pourraient suivre un traitement à base de GLP-1 d'ici 2030, soit près de 10&amp;#160;% de la population adulte, contre 10 millions en 2025. L’article Aux États-Unis, l&amp;rsquo;utilisation de médicaments amaigrissants tels qu’Ozempic ou Wegovy a presque quadruplé en deux ans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -11748,7 +11743,6 @@
           <t>Incapable de rivaliser avec les États-Unis ou la Chine au cœur de la révolution technologique, le Kremlin investit ses marges. L’article Vladimir Poutine a un problème avec l’intelligence artificielle est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -11781,7 +11775,6 @@
           <t>Vainqueure de la Belgique (2-1), l'Espagne retrouvera les Bleus en demi-finale, comme à l'Euro 2024 et en Ligue des nations en 2025. L’article Demi-finale&amp;#160;: France-Espagne, le rendez-vous devenu rituel est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -11814,7 +11807,171 @@
           <t>Ce 11 juillet marque la 83ᵉ commémoration du «&amp;#160;dimanche sanglant&amp;#160;» de Volhynie, point culminant d'un massacre de 1943 que la Pologne qualifie de génocide, mais que Kiev refuse toujours de reconnaître comme tel. Le Premier ministre, Donald Tusk, a profité de l'occasion pour appeler à la vérité historique, tout en plaidant pour l'apaisement des relations avec l'Ukraine, après une séquence diplomatique tendue. L’article Donald Tusk tente d’apaiser les tensions mémorielles avec l’Ukraine e</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:58</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-07-13 09:16</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>Le vrai mystère de « Vaiana » : qu’est-ce qui a bien pu pousser les Polynésiens à repartir vers l’est après 1 700 ans de pause ?</t>
+        </is>
+      </c>
+      <c r="E357" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-vrai-mystere-de-vaiana-quest-ce-qui-a-bien-pu-pousser-les-polynesiens-a-repartir-vers-lest-apres-1-700-ans-de-pause-287387</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>« Vaiana » s’inspire de l’une des plus grandes épopées de navigation de l’histoire humaine. En analysant d’anciens sédiments, des chercheurs apportent un nouvel éclairage sur la période.</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:58</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-07-13 05:32</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>Bataille d’Ormuz : la guerre entre les États-Unis et l’Iran a repris</t>
+        </is>
+      </c>
+      <c r="E358" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/13/bataille-dormuz-la-guerre-entre-les-etats-unis-et-liran-a-repris/</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Près d’un mois après la signature d’un protocole d’accord entre Téhéran et Washington, les deux pays s’affrontent toujours autour du trafic dans le détroit. L’article Bataille d’Ormuz&amp;#160;: la guerre entre les États-Unis et l’Iran a repris est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:58</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-07-13 04:00</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>Le 14 Juillet qui pourrait changer l’Europe</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/13/le-14-juillet-qui-pourrait-changer-leurope/</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>De la Place Rouge aux Champs-Élysées, les défilés militaires donnent à voir le nouvel ordre mondial. Encore faut-il savoir où regarder. L’article Le 14 Juillet qui pourrait changer l&amp;rsquo;Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:58</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-07-12 14:44</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>Brésil : l’évangélisme a-t-il appauvri le football de la Seleção ?</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/12/bresil-levangelisme-a-t-il-appauvri-le-football-de-la-selecao/</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Les demi-finales de cette Coupe du monde débutent mardi 14 juillet avec le match opposant la France à l'Espagne. En attendant, pour les 44 équipes éliminées, c'est le moment du bilan. Et au Brésil, cinq fois champion du monde, une théorie devient de plus en plus virale&amp;#160;: l'essor de l'évangélisme aurait appauvri le football de la Seleção. L’article Brésil&amp;#160;: l&amp;rsquo;évangélisme a-t-il appauvri le football de la Seleção&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:58</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-07-12 13:46</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>Nous assistons à la fin du monde de Kissinger</t>
+        </is>
+      </c>
+      <c r="E361" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/12/la-grande-bifurcation-fin-du-monde-de-kissinger/</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Selon l’un des principaux arpenteurs de la géopolitique, la grande bifurcation en cours signifie qu'il y a plus de fil diplomatique qui relie les grandes puissances. L’article Nous assistons à la fin du monde de Kissinger est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12173,6 +12330,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId353"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId360"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G361"/>
+  <dimension ref="A1:G368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11839,7 +11839,6 @@
           <t>« Vaiana » s’inspire de l’une des plus grandes épopées de navigation de l’histoire humaine. En analysant d’anciens sédiments, des chercheurs apportent un nouvel éclairage sur la période.</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -11872,7 +11871,6 @@
           <t>Près d’un mois après la signature d’un protocole d’accord entre Téhéran et Washington, les deux pays s’affrontent toujours autour du trafic dans le détroit. L’article Bataille d’Ormuz&amp;#160;: la guerre entre les États-Unis et l’Iran a repris est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -11905,7 +11903,6 @@
           <t>De la Place Rouge aux Champs-Élysées, les défilés militaires donnent à voir le nouvel ordre mondial. Encore faut-il savoir où regarder. L’article Le 14 Juillet qui pourrait changer l&amp;rsquo;Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -11938,7 +11935,6 @@
           <t>Les demi-finales de cette Coupe du monde débutent mardi 14 juillet avec le match opposant la France à l'Espagne. En attendant, pour les 44 équipes éliminées, c'est le moment du bilan. Et au Brésil, cinq fois champion du monde, une théorie devient de plus en plus virale&amp;#160;: l'essor de l'évangélisme aurait appauvri le football de la Seleção. L’article Brésil&amp;#160;: l&amp;rsquo;évangélisme a-t-il appauvri le football de la Seleção&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -11971,7 +11967,237 @@
           <t>Selon l’un des principaux arpenteurs de la géopolitique, la grande bifurcation en cours signifie qu'il y a plus de fil diplomatique qui relie les grandes puissances. L’article Nous assistons à la fin du monde de Kissinger est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-07-14 08:00</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>Les origines infrastructurelles de la Révolution française</t>
+        </is>
+      </c>
+      <c r="E362" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/14/origines-infrastructurelles-de-la-revolution-francaise/</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Grâce à de nouvelles données, deux jeunes chercheurs révèlent un paradoxe&amp;#160;: les infrastructures développées par la monarchie pour mieux gouverner la France ont aussi préparé les conditions de sa chute. L’article Les origines infrastructurelles de la Révolution française est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2026-07-14 04:30</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>14 juillet : deux fois plus de véhicules et d’aéronefs défileront à Paris qu’en 2025 à Washington</t>
+        </is>
+      </c>
+      <c r="E363" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/14/14-juillet-deux-fois-plus-de-vehicules-et-daeronefs-defileront-a-paris-quen-2025-a-washington/</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Le nombre de troupes au sol qui fouleront aujourd’hui les Champs-Élysées a été multiplié par deux depuis 2017. L’article 14 juillet&amp;#160;: deux fois plus de véhicules et d’aéronefs défileront à Paris qu’en 2025 à Washington est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-07-14 04:00</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>Donald Trump rêve-t-il d’être un président français ?</t>
+        </is>
+      </c>
+      <c r="E364" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/14/donald-trump-reve-t-il-detre-un-president-francais/</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Du 14 Juillet à Versailles, le président américain exacerbe les symboles du pouvoir français pour inventer une présidence impériale aux États-Unis. L’article Donald Trump rêve-t-il d’être un président français&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:03</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>Les robots humanoïdes ressemblent de plus en plus à des humains</t>
+        </is>
+      </c>
+      <c r="E365" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/13/les-robots-humanoides-ressemblent-de-plus-en-plus-a-des-humains/</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Bien qu’ils soient de plus en plus performants et accessibles, la demande réelle reste incertaine. L’article Les robots humanoïdes ressemblent de plus en plus à des humains est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-07-13 12:31</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>Que nous dit le rapport de forces autour de Komar sur le cours de la guerre en Ukraine ?</t>
+        </is>
+      </c>
+      <c r="E366" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/13/que-nous-dit-le-rapport-de-forces-autour-de-komar-sur-le-cours-de-la-guerre-en-ukraine/</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>La réussite ukrainienne dans le secteur de Komar est l’une des raisons qui expliquent comment Kiev est parvenu à diviser par 7 en un an le rythme de progression de l’armée russe. L’article Que nous dit le rapport de forces autour de Komar sur le cours de la guerre en Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:55</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>Éditorial Historiens &amp; Géographes 474</t>
+        </is>
+      </c>
+      <c r="E367" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/editorial-historiens-geographes-474/</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>ÉDITORIAL : LE TEMPS DES SENTINELLES Le monde continue de gronder, et le débat public national s&amp;#8217;électrise chaque jour un peu plus dans une surenchère de polémiques stériles qui dévitalisent la démocratie. Pendant ce temps, les professeurs continuent à faire face avec des moyens toujours plus contraints. Travailler dans le service public de l&amp;#8217;Éducation nationale [&amp;#8230;] L’article Éditorial Historiens &amp;#038; Géographes 474 est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:42</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:40</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>Sommaire H&amp;G 474</t>
+        </is>
+      </c>
+      <c r="E368" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/sommaire-hg-474/</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>SOMMAIRE 474 ÉDITORIAL : Le temps des sentinelles. Joëlle ALAZARD ACTUALITÉS HOMMAGE à Michel Bée, Jean LASPOUGEAS ENTRETIEN : “Les mémoires de Tchernobyl ont encore du mal à franchir les frontières en Europe…”Laurent COUMEL Tatiana KASPERSKI La loi Taubira du 21 mai 2001 : une loi pour quoi ? Pierre-Yves BOCQUET Europe : comment être puissant sans [&amp;#8230;] L’article Sommaire H&amp;#038;G 474 est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12335,6 +12561,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId359"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId367"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G368"/>
+  <dimension ref="A1:G377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11999,7 +11999,6 @@
           <t>Grâce à de nouvelles données, deux jeunes chercheurs révèlent un paradoxe&amp;#160;: les infrastructures développées par la monarchie pour mieux gouverner la France ont aussi préparé les conditions de sa chute. L’article Les origines infrastructurelles de la Révolution française est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -12032,7 +12031,6 @@
           <t>Le nombre de troupes au sol qui fouleront aujourd’hui les Champs-Élysées a été multiplié par deux depuis 2017. L’article 14 juillet&amp;#160;: deux fois plus de véhicules et d’aéronefs défileront à Paris qu’en 2025 à Washington est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -12065,7 +12063,6 @@
           <t>Du 14 Juillet à Versailles, le président américain exacerbe les symboles du pouvoir français pour inventer une présidence impériale aux États-Unis. L’article Donald Trump rêve-t-il d’être un président français&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -12098,7 +12095,6 @@
           <t>Bien qu’ils soient de plus en plus performants et accessibles, la demande réelle reste incertaine. L’article Les robots humanoïdes ressemblent de plus en plus à des humains est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -12131,7 +12127,6 @@
           <t>La réussite ukrainienne dans le secteur de Komar est l’une des raisons qui expliquent comment Kiev est parvenu à diviser par 7 en un an le rythme de progression de l’armée russe. L’article Que nous dit le rapport de forces autour de Komar sur le cours de la guerre en Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -12164,7 +12159,6 @@
           <t>ÉDITORIAL : LE TEMPS DES SENTINELLES Le monde continue de gronder, et le débat public national s&amp;#8217;électrise chaque jour un peu plus dans une surenchère de polémiques stériles qui dévitalisent la démocratie. Pendant ce temps, les professeurs continuent à faire face avec des moyens toujours plus contraints. Travailler dans le service public de l&amp;#8217;Éducation nationale [&amp;#8230;] L’article Éditorial Historiens &amp;#038; Géographes 474 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -12197,7 +12191,303 @@
           <t>SOMMAIRE 474 ÉDITORIAL : Le temps des sentinelles. Joëlle ALAZARD ACTUALITÉS HOMMAGE à Michel Bée, Jean LASPOUGEAS ENTRETIEN : “Les mémoires de Tchernobyl ont encore du mal à franchir les frontières en Europe…”Laurent COUMEL Tatiana KASPERSKI La loi Taubira du 21 mai 2001 : une loi pour quoi ? Pierre-Yves BOCQUET Europe : comment être puissant sans [&amp;#8230;] L’article Sommaire H&amp;#038;G 474 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:59</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>Non, « L’Odyssée » de Christopher Nolan ne trahit pas l'oeuvre d’Homère</t>
+        </is>
+      </c>
+      <c r="E369" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/non-lodyssee-de-christopher-nolan-ne-trahit-pas-loeuvre-dhomere-287225</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Le film de Christopher Nolan, loin de trahir l’épopée homérique, est fidèle à l’esprit d’un texte qui a toujours été interprété et capté par d’autres auteurs.</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-07-15 07:49</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>Comment Londres, Paris et New York faisaient face aux canicules avant la climatisation</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-londres-paris-et-new-york-faisaient-face-aux-canicules-avant-la-climatisation-287599</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Bien avant que le changement climatique ne place les canicules au cœur des politiques publiques, les habitants de Londres, Paris et New York avaient déjà appris à composer avec la chaleur.</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-07-15 06:55</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>Regards croisés sur l’histoire des Kalmouks, peuple mongol de Russie</t>
+        </is>
+      </c>
+      <c r="E371" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/regards-croises-sur-lhistoire-des-kalmouks-peuple-mongol-de-russie-285398</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>L’étude de trois textes des XVIIIᵉ et XIXᵉ siècles permet de mieux comprendre l’histoire des Kalmouks, présents en Russie depuis près de 400 ans.</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:46</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>L’Odyssée : voyage d’un mythe au cinéma</t>
+        </is>
+      </c>
+      <c r="E372" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lodyssee-voyage-dun-mythe-au-cinema-285778</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Si l’adaptation de Christopher Nolan est très attendue, l’épopée grecque a déjà inspiré de nombreux cinéastes depuis les années 1970.</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:51</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>Vous écoutez de la musique pour vous concentrer sur votre travail ? Ce n’est pas toujours la bonne stratégie</t>
+        </is>
+      </c>
+      <c r="E373" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vous-ecoutez-de-la-musique-pour-vous-concentrer-sur-votre-travail-ce-nest-pas-toujours-la-bonne-strategie-286709</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>L’idée que la musique classique pourrait aider à mémoriser et traiter de nouvelles informations a longtemps circulé. Qu’en penser ? Cela ne dépend-il pas en fait d’un ensemble de circonstances plus large ?</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:50</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="inlineStr">
+        <is>
+          <t>Face aux marchés, Andy Burnham aura-t-il les moyens de ses ambitions ?</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/face-aux-marches-andy-burnham-aura-t-il-les-moyens-de-ses-ambitions-286889</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Andy Burnham devrait succéder à Keir Starmer à la tête d’un pays où le Brexit n’a fait qu’amplifier les incertitudes politiques et économiques.</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-07-15 05:35</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="inlineStr">
+        <is>
+          <t>« La Russie de Poutine est en difficulté parce que notre stratégie fonctionne », entretien avec le Premier ministre estonien</t>
+        </is>
+      </c>
+      <c r="E375" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/15/la-russie-de-poutine-est-en-difficulte-parce-que-notre-strategie-fonctionne-entretien-avec-le-premier-ministre-estonien/</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Kristen Michal met en garde contre le triplement des cyberattaques russes et définit l'architecture de sécurité que nous devons bâtir pour rester «&amp;#160;un projet de paix, mais avec des armes&amp;#160;». L’article «&amp;#160;La Russie de Poutine est en difficulté parce que notre stratégie fonctionne&amp;#160;», entretien avec le Premier ministre estonien est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-07-15 04:30</t>
+        </is>
+      </c>
+      <c r="D376" s="3" t="inlineStr">
+        <is>
+          <t>La Chine engage la lutte contre la dépendance affective vis-à-vis de l’IA</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/15/la-chine-engage-la-lutte-contre-la-dependance-affective-vis-a-vis-de-lia/</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>À partir d’aujourd’hui, 15 juillet, de nouvelles réglementations visant à encadrer strictement les services de personnalisation des compagnons IA entrent en vigueur en Chine. L’article La Chine engage la lutte contre la dépendance affective vis-à-vis de l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 10:45</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:00</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>France-Espagne a été l’archétype de la demi-finale parfaite : tactique et contexte</t>
+        </is>
+      </c>
+      <c r="E377" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/14/france-espagne-est-larchetype-de-la-demi-finale-parfaite-tactique-et-contexte-pour-sy-preparer/</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Ce soir, à 21h, la Coupe du monde nous a offert le meilleur match que le football européen puisse proposer (et le racisme ne pourra pas gâcher ce moment). L’article France-Espagne a été l&amp;rsquo;archétype de la demi-finale parfaite&amp;#160;: tactique et contexte est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12568,6 +12858,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E366" r:id="rId365"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E367" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId376"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G377"/>
+  <dimension ref="A1:G386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12223,7 +12223,6 @@
           <t>Le film de Christopher Nolan, loin de trahir l’épopée homérique, est fidèle à l’esprit d’un texte qui a toujours été interprété et capté par d’autres auteurs.</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -12256,7 +12255,6 @@
           <t>Bien avant que le changement climatique ne place les canicules au cœur des politiques publiques, les habitants de Londres, Paris et New York avaient déjà appris à composer avec la chaleur.</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -12289,7 +12287,6 @@
           <t>L’étude de trois textes des XVIIIᵉ et XIXᵉ siècles permet de mieux comprendre l’histoire des Kalmouks, présents en Russie depuis près de 400 ans.</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -12322,7 +12319,6 @@
           <t>Si l’adaptation de Christopher Nolan est très attendue, l’épopée grecque a déjà inspiré de nombreux cinéastes depuis les années 1970.</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -12355,7 +12351,6 @@
           <t>L’idée que la musique classique pourrait aider à mémoriser et traiter de nouvelles informations a longtemps circulé. Qu’en penser ? Cela ne dépend-il pas en fait d’un ensemble de circonstances plus large ?</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -12388,7 +12383,6 @@
           <t>Andy Burnham devrait succéder à Keir Starmer à la tête d’un pays où le Brexit n’a fait qu’amplifier les incertitudes politiques et économiques.</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -12421,7 +12415,6 @@
           <t>Kristen Michal met en garde contre le triplement des cyberattaques russes et définit l'architecture de sécurité que nous devons bâtir pour rester «&amp;#160;un projet de paix, mais avec des armes&amp;#160;». L’article «&amp;#160;La Russie de Poutine est en difficulté parce que notre stratégie fonctionne&amp;#160;», entretien avec le Premier ministre estonien est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -12454,7 +12447,6 @@
           <t>À partir d’aujourd’hui, 15 juillet, de nouvelles réglementations visant à encadrer strictement les services de personnalisation des compagnons IA entrent en vigueur en Chine. L’article La Chine engage la lutte contre la dépendance affective vis-à-vis de l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -12487,7 +12479,303 @@
           <t>Ce soir, à 21h, la Coupe du monde nous a offert le meilleur match que le football européen puisse proposer (et le racisme ne pourra pas gâcher ce moment). L’article France-Espagne a été l&amp;rsquo;archétype de la demi-finale parfaite&amp;#160;: tactique et contexte est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:18</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>À quoi ressemblaient les premiers congés payés, en 1936, pour les ouvriers bretons ?</t>
+        </is>
+      </c>
+      <c r="E378" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-quoi-ressemblaient-les-premiers-conges-payes-en-1936-pour-les-ouvriers-bretons-285127</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Dans l’imaginaire collectif, les premiers congés payés ont le visage des vacanciers tout sourire dans le train, sur les plages ou en tandem. Mais pour les ouvriers bretons, l’été 1936 n’eut pas grand-chose à voir avec ces clichés.</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:19</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>Faire les saisons en camion : « devenir adulte » autrement ?</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/faire-les-saisons-en-camion-devenir-adulte-autrement-285491</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Que signifie grandir quand on choisit de ne pas se fixer ? Aussi particulière l’expérience des jeunes saisonniers nomades soit-elle, elle éclaire le passage à l’âge adulte dans un monde incertain.</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:20</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>Le Canada à l’Eurovision : le choix de la langue, une question politique cruciale</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-canada-a-leurovision-le-choix-de-la-langue-une-question-politique-cruciale-286815</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Le Canada participera à l’Eurovision en 2027, mais sera-ce en anglais, en français, dans les deux langues ou encore en langue autochtone&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:18</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>Depuis le traumatisme de la crise grecque, les agences de notation souveraine influencent-elles encore les marchés financiers ?</t>
+        </is>
+      </c>
+      <c r="E381" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/depuis-le-traumatisme-de-la-crise-grecque-les-agences-de-notation-souveraine-influencent-elles-encore-les-marches-financiers-277888</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Souvent critiquées mais toujours incontournables, les agences de notation souveraine influencent moins par l’information qu’elles détiennent que par le jugement qu’elles produisent.</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-07-16 04:30</t>
+        </is>
+      </c>
+      <c r="D382" s="3" t="inlineStr">
+        <is>
+          <t>Depuis 2022 et le début de la guerre en Ukraine, l’électrification de l’Union n’a que très peu évolué</t>
+        </is>
+      </c>
+      <c r="E382" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/16/depuis-2022-et-le-debut-de-la-guerre-en-ukraine-lelectrification-de-lunion-na-que-tres-peu-evolue/</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Le taux d’électrification de l’Union s’élève à seulement 23&amp;#160;%, soit un chiffre similaire à celui des pays autosuffisants en hydrocarbures. L’article Depuis 2022 et le début de la guerre en Ukraine, l’électrification de l’Union n’a que très peu évolué est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-07-16 04:30</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>Le Pentagone s’en prend aux puissances moyennes</t>
+        </is>
+      </c>
+      <c r="E383" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/16/le-pentagone-sen-prend-aux-puissances-moyennes/</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Ce que révèle un texte largement commenté d’Elbridge Colby sur l'avenir de l'ordre de sécurité américain. L’article Le Pentagone s’en prend aux puissances moyennes est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-07-15 17:54</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>Comprendre l’échec de la grande armée de Mbappé</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/15/comprendre-lechec-de-la-grande-armee-de-mbappe/</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>L’un des meilleurs tacticiens italiens analyse la campagne des Bleus, un manuel stratégique pour se remettre ou se relancer. L’article Comprendre l&amp;rsquo;échec de la grande armée de Mbappé est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-07-15 17:08</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>« Pour les Malouines, pour Diego et pour la dernière de Leo » : pourquoi le match Argentine-Angleterre s’annonce historique</t>
+        </is>
+      </c>
+      <c r="E385" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/15/pour-les-malouines-pour-diego-et-pour-la-derniere-de-leo-pourquoi-le-match-argentine-angleterre-sannonce-historique/</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Angleterre-Argentine est l'un des chocs les plus explosifs qu'une Coupe du monde puisse offrir. L’article «&amp;#160;Pour les Malouines, pour Diego et pour la dernière de Leo&amp;#160;»&amp;#160;: pourquoi le match Argentine-Angleterre s’annonce historique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:55</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-07-15 12:33</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>Les frappes ukrainiennes de drones pourraient rendre l’Arctique russe invivable</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/15/les-frappes-ukrainiennes-de-drones-pourraient-rendre-larctique-russe-invivable/</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Le territoire potentiellement concerné serait largement supérieur au territoire ukrainien occupé depuis 2014. L’article Les frappes ukrainiennes de drones pourraient rendre l’Arctique russe invivable est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -12867,6 +13155,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E375" r:id="rId374"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E376" r:id="rId375"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E386" r:id="rId385"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G386"/>
+  <dimension ref="A1:G393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12511,7 +12511,6 @@
           <t>Dans l’imaginaire collectif, les premiers congés payés ont le visage des vacanciers tout sourire dans le train, sur les plages ou en tandem. Mais pour les ouvriers bretons, l’été 1936 n’eut pas grand-chose à voir avec ces clichés.</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -12544,7 +12543,6 @@
           <t>Que signifie grandir quand on choisit de ne pas se fixer ? Aussi particulière l’expérience des jeunes saisonniers nomades soit-elle, elle éclaire le passage à l’âge adulte dans un monde incertain.</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -12577,7 +12575,6 @@
           <t>Le Canada participera à l’Eurovision en 2027, mais sera-ce en anglais, en français, dans les deux langues ou encore en langue autochtone&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -12610,7 +12607,6 @@
           <t>Souvent critiquées mais toujours incontournables, les agences de notation souveraine influencent moins par l’information qu’elles détiennent que par le jugement qu’elles produisent.</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -12643,7 +12639,6 @@
           <t>Le taux d’électrification de l’Union s’élève à seulement 23&amp;#160;%, soit un chiffre similaire à celui des pays autosuffisants en hydrocarbures. L’article Depuis 2022 et le début de la guerre en Ukraine, l’électrification de l’Union n’a que très peu évolué est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -12676,7 +12671,6 @@
           <t>Ce que révèle un texte largement commenté d’Elbridge Colby sur l'avenir de l'ordre de sécurité américain. L’article Le Pentagone s’en prend aux puissances moyennes est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -12709,7 +12703,6 @@
           <t>L’un des meilleurs tacticiens italiens analyse la campagne des Bleus, un manuel stratégique pour se remettre ou se relancer. L’article Comprendre l&amp;rsquo;échec de la grande armée de Mbappé est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -12742,7 +12735,6 @@
           <t>Angleterre-Argentine est l'un des chocs les plus explosifs qu'une Coupe du monde puisse offrir. L’article «&amp;#160;Pour les Malouines, pour Diego et pour la dernière de Leo&amp;#160;»&amp;#160;: pourquoi le match Argentine-Angleterre s’annonce historique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -12775,7 +12767,237 @@
           <t>Le territoire potentiellement concerné serait largement supérieur au territoire ukrainien occupé depuis 2014. L’article Les frappes ukrainiennes de drones pourraient rendre l’Arctique russe invivable est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-07-17 08:59</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>Botticelli : une nouvelle étude relance le mystère de la mort de son célèbre modèle</t>
+        </is>
+      </c>
+      <c r="E387" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/botticelli-une-nouvelle-etude-relance-le-mystere-de-la-mort-de-son-celebre-modele-287697</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Simonetta Vespucci, souvent considérée comme la muse de Botticelli, est morte à seulement 23 ans. Une équipe d’endocrinologues avance aujourd’hui qu’elle n’aurait pas succombé à la tuberculose…</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-07-17 08:57</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>« En tout cas, ce n’était pas une licorne… » Des sociologues ont interrogé 130 chasseurs de Bigfoot</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/en-tout-cas-ce-netait-pas-une-licorne-des-sociologues-ont-interroge-130-chasseurs-de-bigfoot-287204</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Ils passent leurs week-ends dans les forêts, analysent des sons mystérieux et débattent de la validité des empreintes. Une enquête sociologique explore de l’intérieur l’univers méconnu des chasseurs de Bigfoot et leur rapport à la preuve.</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:11</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>Peut-on réussir en politique sans charisme ? Quelques pistes de réflexion tirées de la situation outre-Manche</t>
+        </is>
+      </c>
+      <c r="E389" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/peut-on-reussir-en-politique-sans-charisme-quelques-pistes-de-reflexion-tirees-de-la-situation-outre-manche-287086</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Keir Starmer manque-t-il vraiment de charisme&amp;nbsp;? À partir d’une analyse de ses discours, la recherche montre que cette qualité relève moins d’un don inné que de techniques rhétoriques et scéniques qui peuvent s’apprendre.</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-07-17 06:00</t>
+        </is>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>En visant la Chine, Donald Trump prépare-t-il la disruption des midterms ? (Texte intégral)</t>
+        </is>
+      </c>
+      <c r="E390" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/17/donald-trump-prepare-t-il-le-terrain-a-la-disruption-des-elections-de-mi-mandat-texte-integral/</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Traduction et commentaire du discours à la nation prononcé dans la nuit par le président des États-Unis. L’article En visant la Chine, Donald Trump prépare-t-il la disruption des midterms&amp;#160;? (Texte intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2026-07-17 04:30</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>Offensive MAGA contre l’Europe : les États-Unis lancent un programme de financement d’organisations alignées</t>
+        </is>
+      </c>
+      <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/17/offensive-maga-contre-leurope-les-etats-unis-lancent-un-programme-de-financement-dorganisations-alignees/</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Il s’agit de la première fois depuis 2025 que l’administration Trump cherche à faire porter son agenda idéologique en Europe via un soutien financier direct. L’article Offensive MAGA contre l’Europe&amp;#160;: les États-Unis lancent un programme de financement d’organisations alignées est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:13</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la guerre des Malouines resurgit à la Coupe du monde ?</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/16/pourquoi-la-guerre-des-malouines-resurgit-dans-le-football-argentin/</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>L’équipe d’Argentine pourrait être sanctionnée par la FIFA pour avoir fêté sa victoire contre l’Angleterre en brandissant une banderole portant l'inscription&amp;#160;: «&amp;#160;Les Malouines sont argentines&amp;#160;». L’article Pourquoi la guerre des Malouines resurgit à la Coupe du monde&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 10:43</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:22</t>
+        </is>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : 14 % des pétroliers de la flotte fantôme russe auraient été frappés par des drones ukrainiens en 10 jours</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/16/economie-russe-14-des-petroliers-de-la-flotte-fantome-russe-auraient-ete-frappes-par-des-drones-ukrainiens-en-10-jours/</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Kiev affirme avoir frappé 136 navires appartenant à la flotte fantôme russe en mer Noire et d’Azov au cours des 10 derniers jours, dont 97 pétroliers. L’article Économie russe&amp;#160;: 14&amp;#160;% des pétroliers de la flotte fantôme russe auraient été frappés par des drones ukrainiens en 10 jours est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13164,6 +13386,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E384" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E385" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E393" r:id="rId392"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G393"/>
+  <dimension ref="A1:G399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12799,7 +12799,6 @@
           <t>Simonetta Vespucci, souvent considérée comme la muse de Botticelli, est morte à seulement 23 ans. Une équipe d’endocrinologues avance aujourd’hui qu’elle n’aurait pas succombé à la tuberculose…</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -12832,7 +12831,6 @@
           <t>Ils passent leurs week-ends dans les forêts, analysent des sons mystérieux et débattent de la validité des empreintes. Une enquête sociologique explore de l’intérieur l’univers méconnu des chasseurs de Bigfoot et leur rapport à la preuve.</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -12865,7 +12863,6 @@
           <t>Keir Starmer manque-t-il vraiment de charisme&amp;nbsp;? À partir d’une analyse de ses discours, la recherche montre que cette qualité relève moins d’un don inné que de techniques rhétoriques et scéniques qui peuvent s’apprendre.</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -12898,7 +12895,6 @@
           <t>Traduction et commentaire du discours à la nation prononcé dans la nuit par le président des États-Unis. L’article En visant la Chine, Donald Trump prépare-t-il la disruption des midterms&amp;#160;? (Texte intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -12931,7 +12927,6 @@
           <t>Il s’agit de la première fois depuis 2025 que l’administration Trump cherche à faire porter son agenda idéologique en Europe via un soutien financier direct. L’article Offensive MAGA contre l’Europe&amp;#160;: les États-Unis lancent un programme de financement d’organisations alignées est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -12964,7 +12959,6 @@
           <t>L’équipe d’Argentine pourrait être sanctionnée par la FIFA pour avoir fêté sa victoire contre l’Angleterre en brandissant une banderole portant l'inscription&amp;#160;: «&amp;#160;Les Malouines sont argentines&amp;#160;». L’article Pourquoi la guerre des Malouines resurgit à la Coupe du monde&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -12997,7 +12991,204 @@
           <t>Kiev affirme avoir frappé 136 navires appartenant à la flotte fantôme russe en mer Noire et d’Azov au cours des 10 derniers jours, dont 97 pétroliers. L’article Économie russe&amp;#160;: 14&amp;#160;% des pétroliers de la flotte fantôme russe auraient été frappés par des drones ukrainiens en 10 jours est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:16</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-07-18 05:37</t>
+        </is>
+      </c>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>Se faire attacher pour résister aux Sirènes : ce que le choix d’Ulysse révèle du droit</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/se-faire-attacher-pour-resister-aux-sirenes-ce-que-le-choix-dulysse-revele-du-droit-287612</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Lorsqu’Ulysse parie sur sa faiblesse face au chant des Sirènes et se fait attacher au mât de son navire, il démontre en réalité la force du contrat, en droit.</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:16</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:03</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>La nationalisation qui vient</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/18/la-nationalisation-qui-vient/</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Ce n'est pas Marx, ce n'est pas Trump. Généalogie historique du nouveau paradigme géo-économique. L’article La nationalisation qui vient est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:16</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-07-18 04:30</t>
+        </is>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>Effet Trump : pour la première fois depuis 20 ans, la Chine est perçue plus positivement dans le monde que les États-Unis</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/18/effet-trump-pour-la-premiere-fois-depuis-20-ans-la-chine-est-percue-plus-positivement-dans-le-monde-que-les-etats-unis/</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>La première année de la deuxième présidence Trump a été marquée par un effondrement de l’image des États-Unis à l’international – au profit de la Chine. L’article Effet Trump&amp;#160;: pour la première fois depuis 20 ans, la Chine est perçue plus positivement dans le monde que les États-Unis est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:16</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-07-17 13:36</t>
+        </is>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>Kimi K3 : le nouveau modèle d’IA chinois à la frontière de l’open source</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/17/kimi-k3-le-nouveau-modele-dia-chinois-a-la-frontiere-de-lopen-source/</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Après DeepSeek et Zhipu AI, l'entreprise chinoise Moonshot publie à son tour un modèle d'IA dont les capacités rivalisent avec celles de ses concurrents américains. L’article Kimi K3&amp;#160;: le nouveau modèle d’IA chinois à la frontière de l’open source est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:16</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-07-17 11:52</t>
+        </is>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>La doctrine AI+ : le plan de Xi Jinping pour ruiner la Silicon Valley</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/17/la-doctrine-ai-le-plan-de-xi-jinping-pour-ruiner-la-silicon-valley/</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Traduction commentée du discours du président chinois à la Conférence mondiale sur l'IA de Shanghai. L’article La doctrine AI+&amp;#160;: le plan de Xi Jinping pour ruiner la Silicon Valley est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 10:16</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-07-17 11:48</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>En Ukraine, le limogeage du ministre de la Défense Fedorov pourrait avoir des conséquences sur la trajectoire de la guerre</t>
+        </is>
+      </c>
+      <c r="E399" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/17/en-ukraine-le-limogeage-du-ministre-de-la-defense-fedorov-pourrait-avoir-des-consequences-sur-la-trajectoire-de-la-guerre/</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Le limogeage de Mykhaïlo Fedorov a provoqué la crise politique la plus importante en Ukraine depuis le remplacement de l’ancien commandant en chef de l’armée, Valery Zaloujny, par Oleksandr Syrsky en 2024. L’article En Ukraine, le limogeage du ministre de la Défense Fedorov pourrait avoir des conséquences sur la trajectoire de la guerre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13393,6 +13584,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E391" r:id="rId390"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E392" r:id="rId391"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E399" r:id="rId398"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G399"/>
+  <dimension ref="A1:G421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13023,7 +13023,6 @@
           <t>Lorsqu’Ulysse parie sur sa faiblesse face au chant des Sirènes et se fait attacher au mât de son navire, il démontre en réalité la force du contrat, en droit.</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -13056,7 +13055,6 @@
           <t>Ce n'est pas Marx, ce n'est pas Trump. Généalogie historique du nouveau paradigme géo-économique. L’article La nationalisation qui vient est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -13089,7 +13087,6 @@
           <t>La première année de la deuxième présidence Trump a été marquée par un effondrement de l’image des États-Unis à l’international – au profit de la Chine. L’article Effet Trump&amp;#160;: pour la première fois depuis 20 ans, la Chine est perçue plus positivement dans le monde que les États-Unis est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -13122,7 +13119,6 @@
           <t>Après DeepSeek et Zhipu AI, l'entreprise chinoise Moonshot publie à son tour un modèle d'IA dont les capacités rivalisent avec celles de ses concurrents américains. L’article Kimi K3&amp;#160;: le nouveau modèle d’IA chinois à la frontière de l’open source est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -13155,7 +13151,6 @@
           <t>Traduction commentée du discours du président chinois à la Conférence mondiale sur l'IA de Shanghai. L’article La doctrine AI+&amp;#160;: le plan de Xi Jinping pour ruiner la Silicon Valley est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -13188,7 +13183,712 @@
           <t>Le limogeage de Mykhaïlo Fedorov a provoqué la crise politique la plus importante en Ukraine depuis le remplacement de l’ancien commandant en chef de l’armée, Valery Zaloujny, par Oleksandr Syrsky en 2024. L’article En Ukraine, le limogeage du ministre de la Défense Fedorov pourrait avoir des conséquences sur la trajectoire de la guerre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:23</t>
+        </is>
+      </c>
+      <c r="D400" s="3" t="inlineStr">
+        <is>
+          <t>Taylor au pays des Soviets : quand Lénine s'inspirait de l'organisation scientifique du travail</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/taylor-au-pays-des-soviets-quand-lenine-sinspirait-de-lorganisation-scientifique-du-travail-278683</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Contrairement à une idée reçue, le taylorisme et le management n’ont pas seulement concerné les capitalistes. L’URSS a également repris ces principes pour rationaliser le travail.</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:23</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>Santé des étudiants : plus d’un sur deux entre à l’université avec une fragilité physique ou mentale</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/sante-des-etudiants-plus-dun-sur-deux-entre-a-luniversite-avec-une-fragilite-physique-ou-mentale-286054</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Plus d’un étudiant sur deux arrive à l’université avec une vulnérabilité physique ou mentale : la meilleure solution pourrait être l’activité physique individualisée.</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:22</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>Quand l’État vacille, qui gouverne encore ?</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-letat-vacille-qui-gouverne-encore-286368</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Quand l’État s’effondre, l’action publique ne disparaît pas toujours. À Haïti comme ailleurs, d’autres acteurs prennent le relais, redéfinissant la frontière entre gouvernance-légitimité-pouvoir.</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-07-19 04:30</t>
+        </is>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>Les bananes pourraient-elles disparaître ?</t>
+        </is>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/19/les-bananes-pourraient-elles-disparaitre/</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>En raison des maladies et du réchauffement climatique, les bananes Cavendish, les plus consommées au monde, pourraient connaître le même sort que la Gros Michel. L’article Les bananes pourraient-elles disparaître&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-07-19 04:00</t>
+        </is>
+      </c>
+      <c r="D404" s="3" t="inlineStr">
+        <is>
+          <t>Ce que l’IA apprend (et n’apprend pas) aux enfants</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/19/ia-enseignement/</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>L'école peut fermer en juillet, la transmission, elle, ne s'arrête jamais — et les géants de la tech l'ont parfaitement compris. L’article Ce que l’IA apprend (et n’apprend pas) aux enfants est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-07-18 12:30</t>
+        </is>
+      </c>
+      <c r="D405" s="3" t="inlineStr">
+        <is>
+          <t>France-Angleterre : la petite finale de la Coupe du monde verra s’affronter deux grandes équipes déçues</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/18/france-angleterre-la-petite-finale-de-la-coupe-du-monde-verra-saffronter-deux-grandes-equipes-decues/</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>France et Angleterre n'ont plus grand-chose à se dire dans cette finale pour la troisième place. L’article France-Angleterre&amp;#160;: la petite finale de la Coupe du monde verra s’affronter deux grandes équipes déçues est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-07-18 11:30</t>
+        </is>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : l’indice de la bourse de Moscou a chuté de 27 % depuis le début de l’année</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/18/economie-russe-lindice-de-la-bourse-de-moscou-a-chute-de-27-depuis-le-debut-de-lannee/</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>La dégradation de la situation économique russe inquiète jusque dans les cercles les plus proches de Vladimir Poutine. L’article Économie russe&amp;#160;: l’indice de la bourse de Moscou a chuté de 27&amp;#160;% depuis le début de l’année est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:10</t>
+        </is>
+      </c>
+      <c r="D407" s="3" t="inlineStr">
+        <is>
+          <t>Géographie au CAPES d'histoire-géographie à bac+3 : bibliographie indicative</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/concours/capes-hg-bibliographie-indicative-geo</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Des pistes bibliographiques pour préparer le CAPES bac+3.</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:30</t>
+        </is>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>Parutions papier en géographie, printemps 2026</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/parutions/parutions-papier-en-geographie-printemps-2026</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Parmi les thèmes abordés dans les livres en français parus ce printemps : Amérique, États-Unis, Hérault, Sfax, feu, catastrophe, destruction du patrimoine, photo de paysage, géographie sensible, quantitative, économique, géopolitique, transitions, projets alimentaires territoriaux, matériaux, mers et océans, Antoine Bailly, Camille Vallaux...</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-07-15 12:30</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>Frontières : ressources sur Géoconfluences</t>
+        </is>
+      </c>
+      <c r="E409" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/concours/anciens-prog-concours/frontieres-ressources-sur-geoconfluences</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Les ressources de Géoconfluences sur le thème des frontières.</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-07-15 06:35</t>
+        </is>
+      </c>
+      <c r="D410" s="3" t="inlineStr">
+        <is>
+          <t>Image à la une. Tomates et mondialisation en Martinique</t>
+        </is>
+      </c>
+      <c r="E410" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/a-la-une/image-a-la-une/image-a-la-une-tomates-et-mondialisation-en-martinique</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>La photographie d’un rayon de fruits et légumes en Martinique illustre tout autant le coût de la vie très élevé dans les DROM que plusieurs aspects de la mondialisation : une mondialisation économique qui, grâce à des transports internationaux bon marché, broie une économie locale de petite taille, une mondialisation culturelle (de l’alimentation et des goûts) illustrée par la préférence pour certains types de produits, voire une mondialisation des techniques de production.</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-07-15 06:00</t>
+        </is>
+      </c>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>Lettre d'information n° 224</t>
+        </is>
+      </c>
+      <c r="E411" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/a-propos/lettres-dinformation/lettre-information-224</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:15</t>
+        </is>
+      </c>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>Après la victoire de Péter Magyar en Hongrie, une transition libérale très scrutée</t>
+        </is>
+      </c>
+      <c r="E412" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/eclairage/apres-la-victoire-de-peter-magyar-en-hongrie-une-transition-liberale-tres-scrutee</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Au terme d’un scrutin particulièrement suivi dans le monde entier, le dirigeant hongrois souverainiste et anti-européen, Viktor Orbán, a été largement battu par son opposant Péter Magyar. Cette victoire met fin à seize ans d’un gouvernement illibéral, marqué par un ralentissement économique, un rapprochement avec la Russie et de nombreuses affaires de corruption. Le système Orbán pourrait cependant survivre à une élection qui bouleverse déjà les équilibres européens.</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:15</t>
+        </is>
+      </c>
+      <c r="D413" s="3" t="inlineStr">
+        <is>
+          <t>Géohistoire d’une catégorie spatiale située : l’outre-mer</t>
+        </is>
+      </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/epistemo/articles/geohistoire-d-une-categorie-spatiale-situee-l-outre-mer</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>L'outre-mer a d'abord désigné en français les régions situées au-delà de la Méditerranée, correspondant à ce qu'on appellerait aujourd'hui le Proche-Orient. Le mot a ensuite servi à nommer l'ensemble des terres situées au-delà des océans, et plus particulièrement les possessions françaises. C'est alors qu'il a pris une connotation coloniale. L'expression a survécu à la décolonisation et à la départementalisation, incarnée par les DOM-TOM puis les DROM, mais la connotation demeure et pose questio</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:50</t>
+        </is>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>Nouveautés en géographie sur les sites académiques — d'avril à juillet 2026</t>
+        </is>
+      </c>
+      <c r="E414" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/actualites/veille/revues-de-presse/nouveautes-en-geographie-sur-les-sites-academiques-avril-a-juillet-2026</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>De nombreux scénarios pédagogiques, des inspirations, des analyses de gestes professionnels, des formations, des concours ou des prix pour les élèves, des communications officielles, des conférences scientifiques, des outils numériques... Les portails histoire-géographie des sites académiques offrent un large éventail d'informations et de ressources pour l'enseignement.</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:20</t>
+        </is>
+      </c>
+      <c r="D415" s="3" t="inlineStr">
+        <is>
+          <t>[Bibliographie] Mobilités et transports urbains dans le monde (ENS de Lyon 2027)</t>
+        </is>
+      </c>
+      <c r="E415" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/concours/bibliographie-mobilites-et-transports-urbains-dans-le-monde-ens-de-lyon-2027</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Des indications bibliographiques pour préparer la question au programme du concours d'entrée à l'ENS de Lyon pour la session 2027. Cette bibliographie, pas plus qu'aucune autre, ne saurait être exhaustive : n'hésitez pas à nous communiquer vos suggestions.</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:20</t>
+        </is>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>[Bibliographie] Les territoires d'Outre-mer français (ENS de Paris 2027)</t>
+        </is>
+      </c>
+      <c r="E416" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/concours/bibliographie-les-territoires-doutre-mer-francais-ens-de-paris-2027</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Des indications bibliographiques pour préparer la question au programme du concours d'entrée à l'ENS de Paris pour la session 2027. Cette bibliographie, pas plus qu'aucune autre, ne saurait être exhaustive : n'hésitez pas à nous communiquer vos suggestions.</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-07-06 07:05</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>Ressources de Géoconfluences pour traiter les programmes de géographie en CM1</t>
+        </is>
+      </c>
+      <c r="E417" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/programmes/classes/ressources-cycle-3/selection-ressources-cm1</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>(Nouveaux programmes 2026)</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-07-02 14:40</t>
+        </is>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>Atlas et bibliographies</t>
+        </is>
+      </c>
+      <c r="E418" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/arctique/outils-et-ressources</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-07-02 14:40</t>
+        </is>
+      </c>
+      <c r="D419" s="3" t="inlineStr">
+        <is>
+          <t>Atlas et bibliographies</t>
+        </is>
+      </c>
+      <c r="E419" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/arctique/outils-et-ressources/bibliographies</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-07-02 14:23</t>
+        </is>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>Bibliographies</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/geographie-critique-des-ressources/bibliographies-1/bibliographies</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>OpenEdition - Géoconfluences</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-07-02 14:23</t>
+        </is>
+      </c>
+      <c r="D421" s="3" t="inlineStr">
+        <is>
+          <t>Bibliographies</t>
+        </is>
+      </c>
+      <c r="E421" s="4" t="inlineStr">
+        <is>
+          <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/geographie-critique-des-ressources/bibliographies-1</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13590,6 +14290,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E397" r:id="rId396"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E398" r:id="rId397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E421" r:id="rId420"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G421"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13215,7 +13215,6 @@
           <t>Contrairement à une idée reçue, le taylorisme et le management n’ont pas seulement concerné les capitalistes. L’URSS a également repris ces principes pour rationaliser le travail.</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -13248,7 +13247,6 @@
           <t>Plus d’un étudiant sur deux arrive à l’université avec une vulnérabilité physique ou mentale : la meilleure solution pourrait être l’activité physique individualisée.</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -13281,7 +13279,6 @@
           <t>Quand l’État s’effondre, l’action publique ne disparaît pas toujours. À Haïti comme ailleurs, d’autres acteurs prennent le relais, redéfinissant la frontière entre gouvernance-légitimité-pouvoir.</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -13314,7 +13311,6 @@
           <t>En raison des maladies et du réchauffement climatique, les bananes Cavendish, les plus consommées au monde, pourraient connaître le même sort que la Gros Michel. L’article Les bananes pourraient-elles disparaître&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -13347,7 +13343,6 @@
           <t>L'école peut fermer en juillet, la transmission, elle, ne s'arrête jamais — et les géants de la tech l'ont parfaitement compris. L’article Ce que l’IA apprend (et n’apprend pas) aux enfants est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -13380,7 +13375,6 @@
           <t>France et Angleterre n'ont plus grand-chose à se dire dans cette finale pour la troisième place. L’article France-Angleterre&amp;#160;: la petite finale de la Coupe du monde verra s’affronter deux grandes équipes déçues est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -13413,7 +13407,6 @@
           <t>La dégradation de la situation économique russe inquiète jusque dans les cercles les plus proches de Vladimir Poutine. L’article Économie russe&amp;#160;: l’indice de la bourse de Moscou a chuté de 27&amp;#160;% depuis le début de l’année est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -13446,7 +13439,6 @@
           <t>Des pistes bibliographiques pour préparer le CAPES bac+3.</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -13479,7 +13471,6 @@
           <t>Parmi les thèmes abordés dans les livres en français parus ce printemps : Amérique, États-Unis, Hérault, Sfax, feu, catastrophe, destruction du patrimoine, photo de paysage, géographie sensible, quantitative, économique, géopolitique, transitions, projets alimentaires territoriaux, matériaux, mers et océans, Antoine Bailly, Camille Vallaux...</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -13512,7 +13503,6 @@
           <t>Les ressources de Géoconfluences sur le thème des frontières.</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -13545,7 +13535,6 @@
           <t>La photographie d’un rayon de fruits et légumes en Martinique illustre tout autant le coût de la vie très élevé dans les DROM que plusieurs aspects de la mondialisation : une mondialisation économique qui, grâce à des transports internationaux bon marché, broie une économie locale de petite taille, une mondialisation culturelle (de l’alimentation et des goûts) illustrée par la préférence pour certains types de produits, voire une mondialisation des techniques de production.</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -13573,8 +13562,6 @@
           <t>https://geoconfluences.ens-lyon.fr/a-propos/lettres-dinformation/lettre-information-224</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -13607,7 +13594,6 @@
           <t>Au terme d’un scrutin particulièrement suivi dans le monde entier, le dirigeant hongrois souverainiste et anti-européen, Viktor Orbán, a été largement battu par son opposant Péter Magyar. Cette victoire met fin à seize ans d’un gouvernement illibéral, marqué par un ralentissement économique, un rapprochement avec la Russie et de nombreuses affaires de corruption. Le système Orbán pourrait cependant survivre à une élection qui bouleverse déjà les équilibres européens.</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -13640,7 +13626,6 @@
           <t>L'outre-mer a d'abord désigné en français les régions situées au-delà de la Méditerranée, correspondant à ce qu'on appellerait aujourd'hui le Proche-Orient. Le mot a ensuite servi à nommer l'ensemble des terres situées au-delà des océans, et plus particulièrement les possessions françaises. C'est alors qu'il a pris une connotation coloniale. L'expression a survécu à la décolonisation et à la départementalisation, incarnée par les DOM-TOM puis les DROM, mais la connotation demeure et pose questio</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -13673,7 +13658,6 @@
           <t>De nombreux scénarios pédagogiques, des inspirations, des analyses de gestes professionnels, des formations, des concours ou des prix pour les élèves, des communications officielles, des conférences scientifiques, des outils numériques... Les portails histoire-géographie des sites académiques offrent un large éventail d'informations et de ressources pour l'enseignement.</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -13706,7 +13690,6 @@
           <t>Des indications bibliographiques pour préparer la question au programme du concours d'entrée à l'ENS de Lyon pour la session 2027. Cette bibliographie, pas plus qu'aucune autre, ne saurait être exhaustive : n'hésitez pas à nous communiquer vos suggestions.</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -13739,7 +13722,6 @@
           <t>Des indications bibliographiques pour préparer la question au programme du concours d'entrée à l'ENS de Paris pour la session 2027. Cette bibliographie, pas plus qu'aucune autre, ne saurait être exhaustive : n'hésitez pas à nous communiquer vos suggestions.</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -13772,7 +13754,6 @@
           <t>(Nouveaux programmes 2026)</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -13800,8 +13781,6 @@
           <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/arctique/outils-et-ressources</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -13829,8 +13808,6 @@
           <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-regionaux/arctique/outils-et-ressources/bibliographies</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -13858,8 +13835,6 @@
           <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/geographie-critique-des-ressources/bibliographies-1/bibliographies</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -13887,8 +13862,171 @@
           <t>https://geoconfluences.ens-lyon.fr/informations-scientifiques/dossiers-thematiques/geographie-critique-des-ressources/bibliographies-1</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:41</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-07-19 17:08</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>Ukraine : un remaniement qui révèle les fractures au sein du premier cercle de Volodymyr Zelensky</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ukraine-un-remaniement-qui-revele-les-fractures-au-sein-du-premier-cercle-de-volodymyr-zelensky-287851</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Le remplacement du jeune ministre de la défense Mykhaïlo Fedorov, grand ordonnateur de la guerre des drones ukrainienne, reflète des conflits internes et suscite le mécontentement de la population.</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:41</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-07-20 08:45</t>
+        </is>
+      </c>
+      <c r="D423" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis se préparent-ils à une nouvelle escalade en Iran ?</t>
+        </is>
+      </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/20/les-etats-unis-se-preparent-ils-a-une-nouvelle-escalade-en-iran/</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Des dizaines d’avions supplémentaires sont déployés depuis les bases de l’armée américaine en Europe vers le Moyen-Orient. L’article Les États-Unis se préparent-ils à une nouvelle escalade en Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:41</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-07-20 03:30</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>La Chine a sauvé la junte birmane, et après ?</t>
+        </is>
+      </c>
+      <c r="E424" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/20/la-chine-a-sauve-la-junte-birmane-et-apres/</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>La Chine a établi un protectorat recalcitrant au Myanmar. Les généraux, ni capables, ni inféodés, rendent ce pari de plus en plus intenable. L’article La Chine a sauvé la junte birmane, et après&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:41</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:21</t>
+        </is>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>Derrière la finale Argentine-Espagne, un affrontement entre l’un des plus proches alliés et un pays ciblé par Donald Trump</t>
+        </is>
+      </c>
+      <c r="E425" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/19/derriere-la-finale-argentine-espagne-un-affrontement-entre-lun-des-plus-proches-allies-et-un-pays-cible-par-donald-trump/</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Ce soir, Trump se trouvera dans les tribunes du MetLife Stadium aux côtés du Premier ministre espagnol Sánchez, son principal adversaire au sein de l’OTAN. L’article Derrière la finale Argentine-Espagne, un affrontement entre l’un des plus proches alliés et un pays ciblé par Donald Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:41</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-07-19 04:00</t>
+        </is>
+      </c>
+      <c r="D426" s="3" t="inlineStr">
+        <is>
+          <t>Ce que l’IA apprend (et n’apprend pas) aux enfants</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/19/ia-enseignement-devillers/</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>L'école peut fermer en juillet, la transmission, elle, ne s'arrête jamais — et les géants de la tech l'ont parfaitement compris. L’article Ce que l’IA apprend (et n’apprend pas) aux enfants est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14312,6 +14450,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E419" r:id="rId418"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E420" r:id="rId419"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E426" r:id="rId425"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13894,7 +13894,6 @@
           <t>Le remplacement du jeune ministre de la défense Mykhaïlo Fedorov, grand ordonnateur de la guerre des drones ukrainienne, reflète des conflits internes et suscite le mécontentement de la population.</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -13927,7 +13926,6 @@
           <t>Des dizaines d’avions supplémentaires sont déployés depuis les bases de l’armée américaine en Europe vers le Moyen-Orient. L’article Les États-Unis se préparent-ils à une nouvelle escalade en Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -13960,7 +13958,6 @@
           <t>La Chine a établi un protectorat recalcitrant au Myanmar. Les généraux, ni capables, ni inféodés, rendent ce pari de plus en plus intenable. L’article La Chine a sauvé la junte birmane, et après&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -13993,7 +13990,6 @@
           <t>Ce soir, Trump se trouvera dans les tribunes du MetLife Stadium aux côtés du Premier ministre espagnol Sánchez, son principal adversaire au sein de l’OTAN. L’article Derrière la finale Argentine-Espagne, un affrontement entre l’un des plus proches alliés et un pays ciblé par Donald Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -14026,7 +14022,237 @@
           <t>L'école peut fermer en juillet, la transmission, elle, ne s'arrête jamais — et les géants de la tech l'ont parfaitement compris. L’article Ce que l’IA apprend (et n’apprend pas) aux enfants est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-07-20 15:18</t>
+        </is>
+      </c>
+      <c r="D427" s="3" t="inlineStr">
+        <is>
+          <t>Plus d’un adulte sur cinq est touché par le handicap dans sa famille</t>
+        </is>
+      </c>
+      <c r="E427" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/plus-dun-adulte-sur-cinq-est-touche-par-le-handicap-dans-sa-famille-286870</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Les inégalités sociales de santé sont très marquées dans les situations de handicap et le fait d’être parent d’un enfant handicapé a de fortes répercussions sur l’emploi.</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-07-20 15:17</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>Billes, cartes Pokémon… Pourquoi les enfants aiment faire du troc</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/billes-cartes-pokemon-pourquoi-les-enfants-aiment-faire-du-troc-287039</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Dans les groupes d’enfants, dans les cours de récréation, on s’échange des billes, des cartes à collectionner ou des goûters. C’est une façon de nouer des liens et d’apprendre la valeur des choses.</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-07-20 15:16</t>
+        </is>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>Les ONG à bout de souffle : comment réinventer un nouveau modèle d’organisation ?</t>
+        </is>
+      </c>
+      <c r="E429" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-ong-a-bout-de-souffle-comment-reinventer-un-nouveau-modele-dorganisation-287356</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Les coupes dans les aides publiques fragilisent les ONG. Pour rester efficaces malgré des moyens en baisse, elles doivent mieux coordonner leurs actions et innover.</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2026-07-21 04:30</t>
+        </is>
+      </c>
+      <c r="D430" s="3" t="inlineStr">
+        <is>
+          <t>Le gazoduc Nigeria-Maroc pourrait renforcer la position du Rabat – aux dépens de l’Algérie</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/21/le-gazoduc-nigeria-maroc-pourrait-renforcer-la-position-du-rabat-aux-depens-de-lalgerie/</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Estimé à 23 milliards d’euros et traversant 13 pays africains, le projet, approuvé le 19 juillet, fait toutefois face à plusieurs obstacles. L’article Le gazoduc Nigeria-Maroc pourrait renforcer la position du Rabat – aux dépens de l’Algérie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-07-21 04:00</t>
+        </is>
+      </c>
+      <c r="D431" s="3" t="inlineStr">
+        <is>
+          <t>Qu’est-ce que le manchesterisme ? Comprendre la doctrine Andy Burnham</t>
+        </is>
+      </c>
+      <c r="E431" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/21/quest-ce-que-le-manchesterisme-la-doctrine-andy-burnham/</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Fin du néolibéralisme, socialisme «&amp;#160;business-friendly&amp;#160;»… L'ancien maire du Grand Manchester promet de décentraliser le pouvoir, mais est-ce vraiment possible&amp;#160;? L’article Qu’est-ce que le manchesterisme&amp;#160;? Comprendre la doctrine Andy Burnham est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-07-20 15:30</t>
+        </is>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>Un soldat russe vit en moyenne 20 à 30 minutes sur le front ukrainien</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/20/un-soldat-russe-vit-en-moyenne-20-a-30-minutes-sur-le-front-ukrainien/</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>La difficulté à recruter des volontaires pour combattre en Ukraine pourrait conduire le Kremlin à procéder à une nouvelle mobilisation, après les élections de septembre. L’article Un soldat russe vit en moyenne 20 à 30 minutes sur le front ukrainien est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 11:04</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-07-20 12:56</t>
+        </is>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>Ingérence de Trump, slopification, changement climatique : quel bilan tirer de ce Mondial ?</t>
+        </is>
+      </c>
+      <c r="E433" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/20/ingerence-de-trump-slopification-changement-climatique-quel-bilan-tirer-de-ce-mondial/</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>La plus grande Coupe du monde de l’histoire a été marquée par le sacre de l'équipe d’Espagne – mais pas seulement. L’article Ingérence de Trump, slopification, changement climatique&amp;#160;: quel bilan tirer de ce Mondial&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14455,6 +14681,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E424" r:id="rId423"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E425" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E433" r:id="rId432"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G433"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14054,7 +14054,6 @@
           <t>Les inégalités sociales de santé sont très marquées dans les situations de handicap et le fait d’être parent d’un enfant handicapé a de fortes répercussions sur l’emploi.</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -14087,7 +14086,6 @@
           <t>Dans les groupes d’enfants, dans les cours de récréation, on s’échange des billes, des cartes à collectionner ou des goûters. C’est une façon de nouer des liens et d’apprendre la valeur des choses.</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -14120,7 +14118,6 @@
           <t>Les coupes dans les aides publiques fragilisent les ONG. Pour rester efficaces malgré des moyens en baisse, elles doivent mieux coordonner leurs actions et innover.</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -14153,7 +14150,6 @@
           <t>Estimé à 23 milliards d’euros et traversant 13 pays africains, le projet, approuvé le 19 juillet, fait toutefois face à plusieurs obstacles. L’article Le gazoduc Nigeria-Maroc pourrait renforcer la position du Rabat – aux dépens de l’Algérie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -14186,7 +14182,6 @@
           <t>Fin du néolibéralisme, socialisme «&amp;#160;business-friendly&amp;#160;»… L'ancien maire du Grand Manchester promet de décentraliser le pouvoir, mais est-ce vraiment possible&amp;#160;? L’article Qu’est-ce que le manchesterisme&amp;#160;? Comprendre la doctrine Andy Burnham est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -14219,7 +14214,6 @@
           <t>La difficulté à recruter des volontaires pour combattre en Ukraine pourrait conduire le Kremlin à procéder à une nouvelle mobilisation, après les élections de septembre. L’article Un soldat russe vit en moyenne 20 à 30 minutes sur le front ukrainien est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -14252,7 +14246,171 @@
           <t>La plus grande Coupe du monde de l’histoire a été marquée par le sacre de l'équipe d’Espagne – mais pas seulement. L’article Ingérence de Trump, slopification, changement climatique&amp;#160;: quel bilan tirer de ce Mondial&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:05</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:06</t>
+        </is>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>Le « SAVE America Act » : réforme de bon sens ou manœuvre partisane ?</t>
+        </is>
+      </c>
+      <c r="E434" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-save-america-act-reforme-de-bon-sens-ou-manoeuvre-partisane-287881</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Avec le projet de loi «&amp;nbsp;SAVE America Act&amp;nbsp;», Donald Trump affirme vouloir mettre fin à la fraude électorale. Selon ses adversaires, il veut surtout avantager son parti aux prochaines midterms.</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:05</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:05</t>
+        </is>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>Les enjeux politiques et religieux autour du bombardement de la cathédrale de la Dormition à Kiev</t>
+        </is>
+      </c>
+      <c r="E435" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-enjeux-politiques-et-religieux-autour-du-bombardement-de-la-cathedrale-de-la-dormition-a-kiev-287117</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>La frappe contre la cathédrale de la Dormition remet au premier plan un autre front de la guerre&amp;nbsp;: la bataille entre Moscou et Kiev pour l’héritage orthodoxe.</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:05</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-07-22 04:30</t>
+        </is>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>En lançant l’Organisation de coopération mondiale sur l’IA (WAICO), Pékin peut-il rivaliser avec la Pax Silica américaine ?</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/22/en-lancant-lorganisation-de-cooperation-mondiale-sur-lia-waico-pekin-peut-il-rivaliser-avec-la-pax-silica-americaine/</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>La course IA ne se joue plus seulement sur les modèles, mais aussi sur les alliances. L’article En lançant l’Organisation de coopération mondiale sur l’IA (WAICO), Pékin peut-il rivaliser avec la Pax Silica américaine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:05</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-07-21 18:53</t>
+        </is>
+      </c>
+      <c r="D437" s="3" t="inlineStr">
+        <is>
+          <t>Malgré l’imposition de tarifs sur la majeure partie du monde, les États-Unis ont perdu 75 000 emplois manufacturiers depuis l’investiture de Trump</t>
+        </is>
+      </c>
+      <c r="E437" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/21/malgre-limposition-de-tarifs-sur-la-majeure-partie-du-monde-les-etats-unis-ont-perdu-75-000-emplois-manufacturiers-depuis-linvestiture-de-trump/</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Après avoir de nouveau menacé le Canada de tarifs douaniers, l’administration américaine se préparerait à imposer de nouveaux droits de douane sur plusieurs dizaines de pays. L’article Malgré l’imposition de tarifs sur la majeure partie du monde, les États-Unis ont perdu 75 000 emplois manufacturiers depuis l’investiture de Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:05</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-07-21 12:11</t>
+        </is>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>La guerre des détroits s’étend : les Houthis annoncent bloquer les ports saoudiens de la mer Rouge</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/21/la-guerre-des-detroits-setend-les-houthis-annoncent-bloquer-les-ports-saoudiens-de-la-mer-rouge/</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Le détroit de Bab el-Mandeb représente désormais 7&amp;#160;% des approvisionnements mondiaux en pétrole. L’article La guerre des détroits s’étend&amp;#160;: les Houthis annoncent bloquer les ports saoudiens de la mer Rouge est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14688,6 +14846,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E431" r:id="rId430"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E432" r:id="rId431"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E438" r:id="rId437"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G438"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14278,7 +14278,6 @@
           <t>Avec le projet de loi «&amp;nbsp;SAVE America Act&amp;nbsp;», Donald Trump affirme vouloir mettre fin à la fraude électorale. Selon ses adversaires, il veut surtout avantager son parti aux prochaines midterms.</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -14311,7 +14310,6 @@
           <t>La frappe contre la cathédrale de la Dormition remet au premier plan un autre front de la guerre&amp;nbsp;: la bataille entre Moscou et Kiev pour l’héritage orthodoxe.</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -14344,7 +14342,6 @@
           <t>La course IA ne se joue plus seulement sur les modèles, mais aussi sur les alliances. L’article En lançant l’Organisation de coopération mondiale sur l’IA (WAICO), Pékin peut-il rivaliser avec la Pax Silica américaine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -14377,7 +14374,6 @@
           <t>Après avoir de nouveau menacé le Canada de tarifs douaniers, l’administration américaine se préparerait à imposer de nouveaux droits de douane sur plusieurs dizaines de pays. L’article Malgré l’imposition de tarifs sur la majeure partie du monde, les États-Unis ont perdu 75 000 emplois manufacturiers depuis l’investiture de Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -14410,7 +14406,270 @@
           <t>Le détroit de Bab el-Mandeb représente désormais 7&amp;#160;% des approvisionnements mondiaux en pétrole. L’article La guerre des détroits s’étend&amp;#160;: les Houthis annoncent bloquer les ports saoudiens de la mer Rouge est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-07-22 14:14</t>
+        </is>
+      </c>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>Bien avant Ormuz, Athènes a fait du contrôle d’un détroit près de Troie la clé de sa fortune</t>
+        </is>
+      </c>
+      <c r="E439" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/bien-avant-ormuz-athenes-a-fait-du-controle-dun-detroit-pres-de-troie-la-cle-de-sa-fortune-287981</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Dans «&amp;nbsp;L’Odyssée&amp;nbsp;-&amp;nbsp;», Christopher Nolan fait de la guerre de Troie un conflit pour le contrôle d’une route maritime. Si cette interprétation s’éloigne d’Homère, elle éclaire pourtant le rôle des Dardanelles.</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2026-07-22 14:11</t>
+        </is>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>Faut-il limiter le temps d’écran des enfants ? Les pédiatres américains revoient leur position</t>
+        </is>
+      </c>
+      <c r="E440" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/faut-il-limiter-le-temps-decran-des-enfants-les-pediatres-americains-revoient-leur-position-287983</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>À l’heure où la France choisit de limiter l’accès des adolescents aux réseaux sociaux, un changement de doctrine s’opère chez les pédiatres américains.</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2026-07-22 14:14</t>
+        </is>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>Écouter Phnom Penh : ce que les cultures urbaines disent du Cambodge contemporain</t>
+        </is>
+      </c>
+      <c r="E441" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ecouter-phnom-penh-ce-que-les-cultures-urbaines-disent-du-cambodge-contemporain-286369</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Dans les rues de Phnom Penh, le rap et le skateboard deviennent de nouveaux marqueurs sociaux.</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2026-07-23 04:30</t>
+        </is>
+      </c>
+      <c r="D442" s="3" t="inlineStr">
+        <is>
+          <t>En Chine, il y a trois fois plus d’offres d’emploi que d’ingénieurs en algorithmes d’IA</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/23/en-chine-il-y-a-trois-fois-plus-doffres-demploi-que-dingenieurs-en-algorithmes-dia/</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Le pays pourrait connaître un déficit de 4 millions de travailleurs spécialisés dans le secteur de l’IA d’ici 2030. L’article En Chine, il y a trois fois plus d&amp;rsquo;offres d&amp;#8217;emploi que d&amp;rsquo;ingénieurs en algorithmes d&amp;rsquo;IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:30</t>
+        </is>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>Le premier pas de l’extrême droite, c’est de normaliser des mots extrêmes</t>
+        </is>
+      </c>
+      <c r="E443" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/23/le-premier-pas-de-lextreme-droite-cest-de-normaliser-des-mots-extremes/</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Pour naviguer dans la politique de nos années Vingt, nous publions à partir de lundi un ambitieux Vocabulaire de l'extrême droite. Son directeur scientifique s'explique. L’article Le premier pas de l&amp;rsquo;extrême droite, c&amp;rsquo;est de normaliser des mots extrêmes est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>2026-07-22 14:25</t>
+        </is>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>En signant un accord sur le nucléaire civil avec l’Arabie saoudite, Trump ouvre-t-il la voie à une prolifération nucléaire au Moyen-Orient ?</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/22/en-signant-un-accord-sur-le-nucleaire-civil-avec-larabie-saoudite-trump-ouvre-t-il-la-voie-a-une-proliferation-nucleaire-au-moyen-orient/</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>La Maison-Blanche pourrait signer dès aujourd’hui, mercredi 22, un accord de 30 ans autorisant des entreprises américaines à développer un programme nucléaire civil en Arabie saoudite. L’article En signant un accord sur le nucléaire civil avec l&amp;rsquo;Arabie saoudite, Trump ouvre-t-il la voie à une prolifération nucléaire au Moyen-Orient&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>2026-07-22 13:25</t>
+        </is>
+      </c>
+      <c r="D445" s="3" t="inlineStr">
+        <is>
+          <t>L’IA est-elle en train de cannibaliser l’économie mondiale ?</t>
+        </is>
+      </c>
+      <c r="E445" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/22/lia-est-elle-en-train-de-cannibaliser-leconomie-mondiale/</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>L'explosion de l’intelligence artificielle et les risques d’une transition hors norme. L’article L&amp;rsquo;IA est-elle en train de cannibaliser l’économie mondiale&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:06</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2026-07-22 11:40</t>
+        </is>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>Qui est Mykhaïlo Drapatiy, le nouveau commandant en chef des armées ukrainiennes ?</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/22/qui-est-mykhailo-drapatiy-le-nouveau-commandant-en-chef-des-armees-ukrainiennes/</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Drapatiy est le 3e commandant en chef des armées ukrainiennes depuis 2022. L’article Qui est Mykhaïlo Drapatiy, le nouveau commandant en chef des armées ukrainiennes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14851,6 +15110,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E436" r:id="rId435"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E437" r:id="rId436"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E446" r:id="rId445"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14438,7 +14438,6 @@
           <t>Dans «&amp;nbsp;L’Odyssée&amp;nbsp;-&amp;nbsp;», Christopher Nolan fait de la guerre de Troie un conflit pour le contrôle d’une route maritime. Si cette interprétation s’éloigne d’Homère, elle éclaire pourtant le rôle des Dardanelles.</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -14471,7 +14470,6 @@
           <t>À l’heure où la France choisit de limiter l’accès des adolescents aux réseaux sociaux, un changement de doctrine s’opère chez les pédiatres américains.</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -14504,7 +14502,6 @@
           <t>Dans les rues de Phnom Penh, le rap et le skateboard deviennent de nouveaux marqueurs sociaux.</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -14537,7 +14534,6 @@
           <t>Le pays pourrait connaître un déficit de 4 millions de travailleurs spécialisés dans le secteur de l’IA d’ici 2030. L’article En Chine, il y a trois fois plus d&amp;rsquo;offres d&amp;#8217;emploi que d&amp;rsquo;ingénieurs en algorithmes d&amp;rsquo;IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -14570,7 +14566,6 @@
           <t>Pour naviguer dans la politique de nos années Vingt, nous publions à partir de lundi un ambitieux Vocabulaire de l'extrême droite. Son directeur scientifique s'explique. L’article Le premier pas de l&amp;rsquo;extrême droite, c&amp;rsquo;est de normaliser des mots extrêmes est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -14603,7 +14598,6 @@
           <t>La Maison-Blanche pourrait signer dès aujourd’hui, mercredi 22, un accord de 30 ans autorisant des entreprises américaines à développer un programme nucléaire civil en Arabie saoudite. L’article En signant un accord sur le nucléaire civil avec l&amp;rsquo;Arabie saoudite, Trump ouvre-t-il la voie à une prolifération nucléaire au Moyen-Orient&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -14636,7 +14630,6 @@
           <t>L'explosion de l’intelligence artificielle et les risques d’une transition hors norme. L’article L&amp;rsquo;IA est-elle en train de cannibaliser l’économie mondiale&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -14669,7 +14662,270 @@
           <t>Drapatiy est le 3e commandant en chef des armées ukrainiennes depuis 2022. L’article Qui est Mykhaïlo Drapatiy, le nouveau commandant en chef des armées ukrainiennes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:49</t>
+        </is>
+      </c>
+      <c r="D447" s="3" t="inlineStr">
+        <is>
+          <t>Arêtes de poisson, quarantaine et vaccination : les armes des Aborigènes contre la variole</t>
+        </is>
+      </c>
+      <c r="E447" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/aretes-de-poisson-quarantaine-et-vaccination-les-armes-des-aborigenes-contre-la-variole-287598</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Longtemps, les historiens ont surtout étudié les origines de l’épidémie de variole qui a ravagé le sud-est de l’Australie au début des années 1830. De nouvelles recherches montrent que les peuples aborigènes ne furent pas seulement des victimes…</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:48</t>
+        </is>
+      </c>
+      <c r="D448" s="3" t="inlineStr">
+        <is>
+          <t>Le Royaume-Uni face au scandale des adoptions forcées de l’après-guerre</t>
+        </is>
+      </c>
+      <c r="E448" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-royaume-uni-face-au-scandale-des-adoptions-forcees-de-lapres-guerre-287201</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Dans une société où la honte était profondément ancrée dans les traditions religieuses, jusqu’à un demi-million d’enfants ont été confiés à l’adoption au Royaume-Uni et en Irlande sans le consentement de leur mère.</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-07-23 14:33</t>
+        </is>
+      </c>
+      <c r="D449" s="3" t="inlineStr">
+        <is>
+          <t>En Australie, 85 % des enfants utilisent encore les réseaux sociaux malgré leur interdiction : est-ce déjà un échec ?</t>
+        </is>
+      </c>
+      <c r="E449" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/en-australie-85-des-enfants-utilisent-encore-les-reseaux-sociaux-malgre-leur-interdiction-est-ce-deja-un-echec-288152</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Interdire les réseaux sociaux aux moins de 15 ans est-il efficace&amp;nbsp;? Alors qu’une loi vient d’être votée en ce sens en France, l’Australie dispose déjà de six mois de recul sur la question.</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:47</t>
+        </is>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>Coupe du Monde 2026 : le football a-t-il gagné ?</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/coupe-du-monde-2026-le-football-a-t-il-gagne-288223</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Le football au sens large n’est pas sorti vainqueur d’une compétition démesurée, marquée par la personnalité de Donald Trump et l’inféodation à celui-ci de Gianni Infantino.</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-07-23 14:34</t>
+        </is>
+      </c>
+      <c r="D451" s="3" t="inlineStr">
+        <is>
+          <t>Ce que la crise politique en Ukraine dit de l’avenir de la défense européenne</t>
+        </is>
+      </c>
+      <c r="E451" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ce-que-la-crise-politique-en-ukraine-dit-de-lavenir-de-la-defense-europeenne-288007</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Le limogeage de Mykhaïlo Fedorov révèle un enjeu dépassant l’Ukraine : adapter les institutions au rythme de la guerre technologique.</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-07-24 04:30</t>
+        </is>
+      </c>
+      <c r="D452" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis s’apprêteraient à mener des opérations militaires au Mali</t>
+        </is>
+      </c>
+      <c r="E452" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/24/les-etats-unis-sappreteraient-a-mener-des-operations-militaires-au-mali/</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Il s’agirait du 8e pays visé par une intervention armée américaine depuis le retour au pouvoir de Donald Trump, il y a 18 mois. L’article Les États-Unis s’apprêteraient à mener des opérations militaires au Mali est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-07-23 16:20</t>
+        </is>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>Deux fois plus d’hectares ont brûlé en Europe depuis le 1er janvier par rapport à la moyenne des 20 dernières années</t>
+        </is>
+      </c>
+      <c r="E453" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/23/deux-fois-plus-dhectares-ont-brule-en-europe-depuis-le-1er-janvier-par-rapport-a-la-moyenne-des-20-dernieres-annees/</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Au mercredi 22 juillet, 275 000 hectares ont brûlé en Europe depuis le début de l’année, dont plus de la moitié en Espagne et en France. L’article Deux fois plus d&amp;rsquo;hectares ont brûlé en Europe depuis le 1er janvier par rapport à la moyenne des 20 dernières années est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-07-23 11:10</t>
+        </is>
+      </c>
+      <c r="D454" s="3" t="inlineStr">
+        <is>
+          <t>Le Pakistan veut mettre à profit sa proximité avec Trump pour obtenir une facilité de 10 milliards de dollars</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/23/le-pakistan-veut-mettre-a-profit-sa-proximite-avec-trump-pour-obtenir-une-facilite-de-10-milliards-de-dollars/</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>En raison de crises et de conflits successifs, les réserves de change du pays ne permettent plus de couvrir que trois mois d'importations. L’article Le Pakistan veut mettre à profit sa proximité avec Trump pour obtenir une facilité de 10 milliards de dollars est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15118,6 +15374,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E444" r:id="rId443"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E445" r:id="rId444"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E454" r:id="rId453"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G454"/>
+  <dimension ref="A1:G459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14694,7 +14694,6 @@
           <t>Longtemps, les historiens ont surtout étudié les origines de l’épidémie de variole qui a ravagé le sud-est de l’Australie au début des années 1830. De nouvelles recherches montrent que les peuples aborigènes ne furent pas seulement des victimes…</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -14727,7 +14726,6 @@
           <t>Dans une société où la honte était profondément ancrée dans les traditions religieuses, jusqu’à un demi-million d’enfants ont été confiés à l’adoption au Royaume-Uni et en Irlande sans le consentement de leur mère.</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -14760,7 +14758,6 @@
           <t>Interdire les réseaux sociaux aux moins de 15 ans est-il efficace&amp;nbsp;? Alors qu’une loi vient d’être votée en ce sens en France, l’Australie dispose déjà de six mois de recul sur la question.</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -14793,7 +14790,6 @@
           <t>Le football au sens large n’est pas sorti vainqueur d’une compétition démesurée, marquée par la personnalité de Donald Trump et l’inféodation à celui-ci de Gianni Infantino.</t>
         </is>
       </c>
-      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -14826,7 +14822,6 @@
           <t>Le limogeage de Mykhaïlo Fedorov révèle un enjeu dépassant l’Ukraine : adapter les institutions au rythme de la guerre technologique.</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -14859,7 +14854,6 @@
           <t>Il s’agirait du 8e pays visé par une intervention armée américaine depuis le retour au pouvoir de Donald Trump, il y a 18 mois. L’article Les États-Unis s’apprêteraient à mener des opérations militaires au Mali est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -14892,7 +14886,6 @@
           <t>Au mercredi 22 juillet, 275 000 hectares ont brûlé en Europe depuis le début de l’année, dont plus de la moitié en Espagne et en France. L’article Deux fois plus d&amp;rsquo;hectares ont brûlé en Europe depuis le 1er janvier par rapport à la moyenne des 20 dernières années est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -14925,7 +14918,171 @@
           <t>En raison de crises et de conflits successifs, les réserves de change du pays ne permettent plus de couvrir que trois mois d'importations. L’article Le Pakistan veut mettre à profit sa proximité avec Trump pour obtenir une facilité de 10 milliards de dollars est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 10:24</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-07-25 06:58</t>
+        </is>
+      </c>
+      <c r="D455" s="3" t="inlineStr">
+        <is>
+          <t>Alcool, tabac, cannabis : les jeunes se sont-ils vraiment détournés des drogues ?</t>
+        </is>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/alcool-tabac-cannabis-les-jeunes-se-sont-ils-vraiment-detournes-des-drogues-286189</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Si la consommation de drogues baisse à l’adolescence, elle va de pair avec un accroissement des inégalités et de nouvelles tendances comme le « binge drinking ».</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 10:24</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-07-25 04:30</t>
+        </is>
+      </c>
+      <c r="D456" s="3" t="inlineStr">
+        <is>
+          <t>Le canal de Panama : prochain goulot d’étranglement perturbé après le détroit d’Ormuz et de Bab-el-Mandeb ?</t>
+        </is>
+      </c>
+      <c r="E456" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/25/le-canal-de-panama-prochain-goulot-detranglement-perturbe-apres-le-detroit-dormuz-et-de-bab-el-mandeb/</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>En raison du niveau actuel du lac Gatún, l'Autorité du canal va réduire à partir d'aujourd'hui, samedi 25, le nombre de créneaux de réservation quotidiens pour les écluses Panamax du canal de Panama, qui relie les océans Pacifique et Atlantique. L’article Le canal de Panama&amp;#160;: prochain goulot d’étranglement perturbé après le détroit d’Ormuz et de Bab-el-Mandeb&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 10:24</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-07-24 18:44</t>
+        </is>
+      </c>
+      <c r="D457" s="3" t="inlineStr">
+        <is>
+          <t>Vers une nouvelle campagne israélo-américaine contre l’Iran ?</t>
+        </is>
+      </c>
+      <c r="E457" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/24/vers-une-nouvelle-campagne-israelo-americaine-contre-liran/</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Le Premier ministre israélien, Benyamin Netanyahou, est attendu à Washington mardi 28 juillet, alors que Donald Trump a menacé hier l’Iran d’une attaque de grande envergure «&amp;#160;plus importante que jamais&amp;#160;». L’article Vers une nouvelle campagne israélo-américaine contre l’Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 10:24</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-07-24 12:11</t>
+        </is>
+      </c>
+      <c r="D458" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : le nombre de pompes funèbres a augmenté de plus de 20 % au premier semestre</t>
+        </is>
+      </c>
+      <c r="E458" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/24/economie-russe-le-nombre-de-pompes-funebres-a-augmente-de-plus-de-20-au-premier-semestre/</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Les lourdes pertes subies par l’armée russe en Ukraine contribuent à l'essor d'une industrie de la mort en Russie. L’article Économie russe&amp;#160;: le nombre de pompes funèbres a augmenté de plus de 20&amp;#160;% au premier semestre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 10:24</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:50</t>
+        </is>
+      </c>
+      <c r="D459" s="3" t="inlineStr">
+        <is>
+          <t>La doctrine Kratsios et la nouvelle puissance scientifique américaine</t>
+        </is>
+      </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/24/la-doctrine-kratsios-et-la-nouvelle-puissance-scientifique-americaine/</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Traduction et commentaire du texte voulant faire de la science et de l’IA les fondements d’une domination américaine planétaire. L’article La doctrine Kratsios et la nouvelle puissance scientifique américaine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15382,6 +15539,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E452" r:id="rId451"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E453" r:id="rId452"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E459" r:id="rId458"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G459"/>
+  <dimension ref="A1:G463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14950,7 +14950,6 @@
           <t>Si la consommation de drogues baisse à l’adolescence, elle va de pair avec un accroissement des inégalités et de nouvelles tendances comme le « binge drinking ».</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -14983,7 +14982,6 @@
           <t>En raison du niveau actuel du lac Gatún, l'Autorité du canal va réduire à partir d'aujourd'hui, samedi 25, le nombre de créneaux de réservation quotidiens pour les écluses Panamax du canal de Panama, qui relie les océans Pacifique et Atlantique. L’article Le canal de Panama&amp;#160;: prochain goulot d’étranglement perturbé après le détroit d’Ormuz et de Bab-el-Mandeb&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -15016,7 +15014,6 @@
           <t>Le Premier ministre israélien, Benyamin Netanyahou, est attendu à Washington mardi 28 juillet, alors que Donald Trump a menacé hier l’Iran d’une attaque de grande envergure «&amp;#160;plus importante que jamais&amp;#160;». L’article Vers une nouvelle campagne israélo-américaine contre l’Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -15049,7 +15046,6 @@
           <t>Les lourdes pertes subies par l’armée russe en Ukraine contribuent à l'essor d'une industrie de la mort en Russie. L’article Économie russe&amp;#160;: le nombre de pompes funèbres a augmenté de plus de 20&amp;#160;% au premier semestre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -15082,7 +15078,138 @@
           <t>Traduction et commentaire du texte voulant faire de la science et de l’IA les fondements d’une domination américaine planétaire. L’article La doctrine Kratsios et la nouvelle puissance scientifique américaine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:42</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:37</t>
+        </is>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>Le totalitarisme numérique est-il inéluctable ?</t>
+        </is>
+      </c>
+      <c r="E460" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-totalitarisme-numerique-est-il-ineluctable-287104</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>L’essor de l’IA et des Big Tech favorise une surveillance accrue. Sans garde-fous démocratiques, le numérique peut mener au technofascisme et au totalitarisme.</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:42</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-07-26 04:30</t>
+        </is>
+      </c>
+      <c r="D461" s="3" t="inlineStr">
+        <is>
+          <t>Pour saisir l’ampleur du développement de la recherche pharmaceutique en Chine, il faut regarder le prix des singes</t>
+        </is>
+      </c>
+      <c r="E461" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/26/pour-saisir-lampleur-du-developpement-de-la-recherche-pharmaceutique-en-chine-il-faut-regarder-le-prix-des-singes/</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Une femelle macaque crabier adulte s'échange à près de 26 000 euros en Chine, soit 7,5 fois plus qu'en 2019, avant la pandémie de Covid-19. L’article Pour saisir l&amp;rsquo;ampleur du développement de la recherche pharmaceutique en Chine, il faut regarder le prix des singes est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:42</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-07-26 04:30</t>
+        </is>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>Tout ce que vous avez toujours voulu savoir sur l’Encyclique Magnifica humanitas</t>
+        </is>
+      </c>
+      <c r="E462" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/26/tout-ce-que-vous-avez-toujours-voulu-savoir-sur-lencyclique-magnifica-humanitas/</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Nous publions l’une des études les plus fouillées, critiques et ambitieuses de la première encyclique sur l’IA. L’article Tout ce que vous avez toujours voulu savoir sur l’Encyclique Magnifica humanitas est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 10:42</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-07-25 16:44</t>
+        </is>
+      </c>
+      <c r="D463" s="3" t="inlineStr">
+        <is>
+          <t>À Berlin, un remaniement ministériel chaotique en plein été</t>
+        </is>
+      </c>
+      <c r="E463" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/25/a-berlin-un-remaniement-ministeriel-chaotique-en-plein-ete/</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>En plein cœur de l'été, le gouvernement allemand a procédé à un remaniement difficile, à la veille de trois élections régionales clefs. L’article À Berlin, un remaniement ministériel chaotique en plein été est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15544,6 +15671,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E457" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E458" r:id="rId457"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E463" r:id="rId462"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G463"/>
+  <dimension ref="A1:G468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15110,7 +15110,6 @@
           <t>L’essor de l’IA et des Big Tech favorise une surveillance accrue. Sans garde-fous démocratiques, le numérique peut mener au technofascisme et au totalitarisme.</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -15143,7 +15142,6 @@
           <t>Une femelle macaque crabier adulte s'échange à près de 26 000 euros en Chine, soit 7,5 fois plus qu'en 2019, avant la pandémie de Covid-19. L’article Pour saisir l&amp;rsquo;ampleur du développement de la recherche pharmaceutique en Chine, il faut regarder le prix des singes est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -15176,7 +15174,6 @@
           <t>Nous publions l’une des études les plus fouillées, critiques et ambitieuses de la première encyclique sur l’IA. L’article Tout ce que vous avez toujours voulu savoir sur l’Encyclique Magnifica humanitas est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -15209,7 +15206,171 @@
           <t>En plein cœur de l'été, le gouvernement allemand a procédé à un remaniement difficile, à la veille de trois élections régionales clefs. L’article À Berlin, un remaniement ministériel chaotique en plein été est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:18</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-07-27 10:13</t>
+        </is>
+      </c>
+      <c r="D464" s="3" t="inlineStr">
+        <is>
+          <t>Peut-on s’inspirer du Japon pour repenser la durabilité de la filière textile en France ?</t>
+        </is>
+      </c>
+      <c r="E464" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/peut-on-sinspirer-du-japon-pour-repenser-la-durabilite-de-la-filiere-textile-en-france-281779</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Longtemps, le Japon a été le pays du textile reconditionné. Analyse d’un modèle économique peu connu pour éclairer les voies d’une mutation possible du secteur textile.</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:18</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:49</t>
+        </is>
+      </c>
+      <c r="D465" s="3" t="inlineStr">
+        <is>
+          <t>Comment Donald Trump s’enrichit, ainsi que ses proches, en monnayant sa présidence au profit d’autres pays</t>
+        </is>
+      </c>
+      <c r="E465" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/27/comment-donald-trump-senrichit-ainsi-que-ses-proches-en-monnayant-sa-presidence-au-profit-dautres-pays/</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Depuis sa victoire en 2024, le président américain met à profit son influence et les outils de la politique commerciale américaine pour faire avancer ses propres intérêts – et enrichir ses proches. L’article Comment Donald Trump s&amp;rsquo;enrichit, ainsi que ses proches, en monnayant sa présidence au profit d&amp;rsquo;autres pays est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:18</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-07-27 04:30</t>
+        </is>
+      </c>
+      <c r="D466" s="3" t="inlineStr">
+        <is>
+          <t>Le PiS polonais a implosé</t>
+        </is>
+      </c>
+      <c r="E466" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/27/le-pis-polonais-a-implose/</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Demain, mardi 28 juillet, le comité politique du parti Droit et justice (PiS) se réunira pour entériner le départ de plus d'une quarantaine de parlementaires, dont l'ancien Premier ministre, Mateusz Morawiecki. Le PiS penche ainsi pour une orientation plus radicale. Il s'agit de la plus importante scission qu'ait connue la droite nationale-conservatrice polonaise. L’article Le PiS polonais a implosé est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:18</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-07-27 04:30</t>
+        </is>
+      </c>
+      <c r="D467" s="3" t="inlineStr">
+        <is>
+          <t>Le défi existentiel de Kimi</t>
+        </is>
+      </c>
+      <c r="E467" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/27/le-defi-existentiel-de-kimi/</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Le plus grave danger pour la domination américaine est que la Silicon Valley cesse d'être le rêve du monde. L’article Le défi existentiel de Kimi est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 12:18</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-07-26 13:29</t>
+        </is>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>Milei lance la campagne de Flavio Bolsonaro (discours intégral)</t>
+        </is>
+      </c>
+      <c r="E468" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/26/milei-flavio-bolsonaro-discours-integral-sao-paulo/</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Dans un acte d'ingérence inédit, le président argentin révèle pourquoi le Brésil est devenu le principal champ de bataille de l'internationale réactionnaire. L’article Milei lance la campagne de Flavio Bolsonaro (discours intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15675,6 +15836,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E461" r:id="rId460"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E462" r:id="rId461"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E468" r:id="rId467"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G468"/>
+  <dimension ref="A1:G476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15238,7 +15238,6 @@
           <t>Longtemps, le Japon a été le pays du textile reconditionné. Analyse d’un modèle économique peu connu pour éclairer les voies d’une mutation possible du secteur textile.</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -15271,7 +15270,6 @@
           <t>Depuis sa victoire en 2024, le président américain met à profit son influence et les outils de la politique commerciale américaine pour faire avancer ses propres intérêts – et enrichir ses proches. L’article Comment Donald Trump s&amp;rsquo;enrichit, ainsi que ses proches, en monnayant sa présidence au profit d&amp;rsquo;autres pays est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -15304,7 +15302,6 @@
           <t>Demain, mardi 28 juillet, le comité politique du parti Droit et justice (PiS) se réunira pour entériner le départ de plus d'une quarantaine de parlementaires, dont l'ancien Premier ministre, Mateusz Morawiecki. Le PiS penche ainsi pour une orientation plus radicale. Il s'agit de la plus importante scission qu'ait connue la droite nationale-conservatrice polonaise. L’article Le PiS polonais a implosé est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -15337,7 +15334,6 @@
           <t>Le plus grave danger pour la domination américaine est que la Silicon Valley cesse d'être le rêve du monde. L’article Le défi existentiel de Kimi est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -15370,7 +15366,270 @@
           <t>Dans un acte d'ingérence inédit, le président argentin révèle pourquoi le Brésil est devenu le principal champ de bataille de l'internationale réactionnaire. L’article Milei lance la campagne de Flavio Bolsonaro (discours intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:16</t>
+        </is>
+      </c>
+      <c r="D469" s="3" t="inlineStr">
+        <is>
+          <t>Ulysse aux mille ruses était-il aussi un athlète ?</t>
+        </is>
+      </c>
+      <c r="E469" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ulysse-aux-mille-ruses-etait-il-aussi-un-athlete-288213</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Ulysse aux mille ruses était aussi un sportif accompli, même si l’on rencontre dans l’épopée homérique une multitude de héros et d’héroïnes encore plus athlétiques.</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:46</t>
+        </is>
+      </c>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>Les Vikings étaient bien plus que des pillards barbus : pourquoi les musées scandinaves entretiennent-ils encore cette image ?</t>
+        </is>
+      </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-vikings-etaient-bien-plus-que-des-pillards-barbus-pourquoi-les-musees-scandinaves-entretiennent-ils-encore-cette-image-287196</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Les musées nationaux de Scandinavie ne racontent pas seulement le passé&amp;nbsp;: ils contribuent aussi à façonner l’identité contemporaine. Quitte à entretenir certains mythes sur les Vikings, toujours très présents dans l’imaginaire collectif.</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:19</t>
+        </is>
+      </c>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>Peu importe ce que les enfants lisent, tant qu’ils lisent ? Dépasser les préjugés sur les « bonnes » et « mauvaises lectures »</t>
+        </is>
+      </c>
+      <c r="E471" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/peu-importe-ce-que-les-enfants-lisent-tant-quils-lisent-depasser-les-prejuges-sur-les-bonnes-et-mauvaises-lectures-287799</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Pour donner aux enfants le goût de la lecture, ne faut-il d’abord en finir avec les catégories figées de « bonnes » et « mauvaises lectures » pour partir des centres d’intérêts de chacun ?</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-07-27 13:20</t>
+        </is>
+      </c>
+      <c r="D472" s="3" t="inlineStr">
+        <is>
+          <t>Indonésie et Asie du Sud-Est : la France a une carte à jouer</t>
+        </is>
+      </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/indonesie-et-asie-du-sud-est-la-france-a-une-carte-a-jouer-287087</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Ni Washington, ni Pékin : les États d’Asie du Sud-Est, à commencer par l’Indonésie, cherchent à faire entendre leur voix. Une occasion à saisir pour la France et l’Europe.</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-07-28 10:17</t>
+        </is>
+      </c>
+      <c r="D473" s="3" t="inlineStr">
+        <is>
+          <t>La politique erratique de Trump constitue un frein à la réindustrialisation des États-Unis</t>
+        </is>
+      </c>
+      <c r="E473" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/28/la-politique-erratique-de-trump-constitue-un-frein-a-la-reindustrialisation-des-etats-unis/</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Plus de 500 000 emplois étaient à pourvoir dans le secteur manufacturier en mai aux États-Unis, soit plus qu’avant la pandémie de coronavirus. L’article La politique erratique de Trump constitue un frein à la réindustrialisation des États-Unis est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-07-28 04:30</t>
+        </is>
+      </c>
+      <c r="D474" s="3" t="inlineStr">
+        <is>
+          <t>Anti-nation</t>
+        </is>
+      </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/28/anti-nation/</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>De Maurras à Trump, la construction d’un ennemi intérieur est souvent la clef discursive de la conquête de l’espace national. L’article Anti-nation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-07-28 04:30</t>
+        </is>
+      </c>
+      <c r="D475" s="3" t="inlineStr">
+        <is>
+          <t>La guerre en Ukraine est-elle en train de se connecter avec la guerre en Iran ?</t>
+        </is>
+      </c>
+      <c r="E475" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/28/la-guerre-en-ukraine-est-elle-en-train-de-se-connecter-avec-la-guerre-en-iran/</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Le régime iranien qui fabrique des drones utilisés par la Russie pour ses frappes en Ukraine accuse Kiev d’avoir attaqué un navire iranien en mer Caspienne et menace de représailles. L’article La guerre en Ukraine est-elle en train de se connecter avec la guerre en Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:13</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:47</t>
+        </is>
+      </c>
+      <c r="D476" s="3" t="inlineStr">
+        <is>
+          <t>La surface brûlée en France depuis le 1er janvier représente près de la moitié du Luxembourg</t>
+        </is>
+      </c>
+      <c r="E476" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/27/la-surface-brulee-en-france-depuis-le-1er-janvier-represente-pres-de-la-moitie-du-luxembourg/</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Dans le sud-ouest, 46 000 hectares ont brûlé en seulement cinq jours. L’article La surface brûlée en France depuis le 1er janvier représente près de la moitié du Luxembourg est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15841,6 +16100,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E466" r:id="rId465"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E467" r:id="rId466"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E476" r:id="rId475"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G476"/>
+  <dimension ref="A1:G488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15398,7 +15398,6 @@
           <t>Ulysse aux mille ruses était aussi un sportif accompli, même si l’on rencontre dans l’épopée homérique une multitude de héros et d’héroïnes encore plus athlétiques.</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -15431,7 +15430,6 @@
           <t>Les musées nationaux de Scandinavie ne racontent pas seulement le passé&amp;nbsp;: ils contribuent aussi à façonner l’identité contemporaine. Quitte à entretenir certains mythes sur les Vikings, toujours très présents dans l’imaginaire collectif.</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -15464,7 +15462,6 @@
           <t>Pour donner aux enfants le goût de la lecture, ne faut-il d’abord en finir avec les catégories figées de « bonnes » et « mauvaises lectures » pour partir des centres d’intérêts de chacun ?</t>
         </is>
       </c>
-      <c r="G471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -15497,7 +15494,6 @@
           <t>Ni Washington, ni Pékin : les États d’Asie du Sud-Est, à commencer par l’Indonésie, cherchent à faire entendre leur voix. Une occasion à saisir pour la France et l’Europe.</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -15530,7 +15526,6 @@
           <t>Plus de 500 000 emplois étaient à pourvoir dans le secteur manufacturier en mai aux États-Unis, soit plus qu’avant la pandémie de coronavirus. L’article La politique erratique de Trump constitue un frein à la réindustrialisation des États-Unis est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -15563,7 +15558,6 @@
           <t>De Maurras à Trump, la construction d’un ennemi intérieur est souvent la clef discursive de la conquête de l’espace national. L’article Anti-nation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -15596,7 +15590,6 @@
           <t>Le régime iranien qui fabrique des drones utilisés par la Russie pour ses frappes en Ukraine accuse Kiev d’avoir attaqué un navire iranien en mer Caspienne et menace de représailles. L’article La guerre en Ukraine est-elle en train de se connecter avec la guerre en Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -15629,7 +15622,402 @@
           <t>Dans le sud-ouest, 46 000 hectares ont brûlé en seulement cinq jours. L’article La surface brûlée en France depuis le 1er janvier représente près de la moitié du Luxembourg est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:50</t>
+        </is>
+      </c>
+      <c r="D477" s="3" t="inlineStr">
+        <is>
+          <t>Une icône méconnue du marronnage : Selomoh del Castilho et le capitaine Broos</t>
+        </is>
+      </c>
+      <c r="E477" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/une-icone-meconnue-du-marronnage-selomoh-del-castilho-et-le-capitaine-broos-287419</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Au Suriname, Selomoh del Castilho a immortalisé le capitaine Broos, figure du marronnage au XIXᵉ siècle, dans un portrait devenu emblématique.</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:48</t>
+        </is>
+      </c>
+      <c r="D478" s="3" t="inlineStr">
+        <is>
+          <t>Forces de l’ordre et recours aux armes : comment la Révolution française a posé les termes du débat</t>
+        </is>
+      </c>
+      <c r="E478" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/forces-de-lordre-et-recours-aux-armes-comment-la-revolution-francaise-a-pose-les-termes-du-debat-287837</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>En créant la gendarmerie nationale le 16 février 1791, les révolutionnaires proposent une conception nouvelle de la force publique armée qui structure encore le droit aujourd’hui.</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:47</t>
+        </is>
+      </c>
+      <c r="D479" s="3" t="inlineStr">
+        <is>
+          <t>Des empereurs romains à Donald Trump : quand les dirigeants politiques se montrent dans les enceintes sportives</t>
+        </is>
+      </c>
+      <c r="E479" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/des-empereurs-romains-a-donald-trump-quand-les-dirigeants-politiques-se-montrent-dans-les-enceintes-sportives-288123</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Au MetLife Stadium pendant la finale de la Coupe du Monde, Donald Trump s’est-il comporté d’une façon semblable à celle des empereurs romains au Cirque Maximus&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-07-28 14:14</t>
+        </is>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>Être rejeté par les autres fait mal : aider enfants et ados à rebondir quand ils sont mis de côté</t>
+        </is>
+      </c>
+      <c r="E480" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/etre-rejete-par-les-autres-fait-mal-aider-enfants-et-ados-a-rebondir-quand-ils-sont-mis-de-cote-288361</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>En tant que parent, il peut être douloureux de voir son enfant souffrir d’être mis à l’écart par les autres. Mais il existe des moyens de les aider.</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-07-28 14:16</t>
+        </is>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>Comment X est devenu l’un des théâtres de la guerre en Ukraine</t>
+        </is>
+      </c>
+      <c r="E481" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-x-est-devenu-lun-des-theatres-de-la-guerre-en-ukraine-287462</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Depuis le début de la guerre en Ukraine, X est devenu un champ de bataille informationnel où diplomatie, OSINT, propagande et journalisme se croisent en temps réel.</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:30</t>
+        </is>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>L’AfD a une chance sur deux de gouverner seule pour la première fois en Allemagne [Simulation exclusive]</t>
+        </is>
+      </c>
+      <c r="E482" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/29/simulations-exclusives-lafd-a-une-chance-sur-deux-de-gouverner-la-saxe-anhalt/</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>L'extrême droite a une chance sur deux de gouverner seule la Saxe-Anhalt après le scrutin du 6 septembre. L’article L&amp;rsquo;AfD a une chance sur deux de gouverner seule pour la première fois en Allemagne [Simulation exclusive] est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-07-29 06:31</t>
+        </is>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>« Pour survivre, nous devons nous coordonner pour ralentir la course IA »</t>
+        </is>
+      </c>
+      <c r="E483" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/29/pour-survivre-nous-devons-nous-coordonner-pour-ralentir-la-course/</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Plus de mille ingénieurs demandent à Washington de réguler la frontière de l'IA avant qu’il ne soit trop tard. L’article «&amp;#160;Pour survivre, nous devons nous coordonner pour ralentir la course IA&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-07-29 05:23</t>
+        </is>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>L’Ukraine pourrait-elle amener Moscou à accepter un cessez-le-feu aérien ?</t>
+        </is>
+      </c>
+      <c r="E484" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/29/lukraine-pourrait-elle-amener-moscou-a-accepter-un-cessez-le-feu-aerien/</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Entre juin 2025 et juin 2026, l’armée ukrainienne aurait frappé plus de 350 000 cibles russes à l’aide de drones. L’article L’Ukraine pourrait-elle amener Moscou à accepter un cessez-le-feu aérien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-07-29 04:00</t>
+        </is>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>Profiler un agresseur en série</t>
+        </is>
+      </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/29/profiler-un-agresseur-en-serie/</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Quand les choses vont mal, Poutine surenchérit. Selon l’ancien ambassadeur français à Moscou, il serait imprudent de parier sur un changement de méthode. L’article Profiler un agresseur en série est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-07-28 14:48</t>
+        </is>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>Après un vote aux côtés de la Russie et de la Corée du Nord à l’ONU, les États-Unis accusent la France de complaisance à l’égard de régimes dictatoriaux</t>
+        </is>
+      </c>
+      <c r="E486" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/28/apres-un-vote-aux-cotes-de-la-russie-et-de-la-coree-du-nord-a-lonu-les-etats-unis-accusent-la-france-de-complaisance-a-legard-de-regimes-dictatoriaux/</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Washington a voté avec la Russie, la Corée du Nord et le Mali contre le renouvellement du mandat du Haut-commissaire aux droits de l’homme de l’ONU. L’article Après un vote aux côtés de la Russie et de la Corée du Nord à l’ONU, les États-Unis accusent la France de complaisance à l’égard de régimes dictatoriaux est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-07-28 14:39</t>
+        </is>
+      </c>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi l’IA c’est Thémis plutôt que Prométhée</t>
+        </is>
+      </c>
+      <c r="E487" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/28/pourquoi-lia-cest-themis-plutot-que-promethee/</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Face à l'incertitude, le prochain président devrait bâtir les actifs qui préserveront le droit des Français de choisir entre banalisation de l'IA et course à la frontière. L’article Pourquoi l’IA c’est Thémis plutôt que Prométhée est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:22</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-07-28 04:30</t>
+        </is>
+      </c>
+      <c r="D488" s="3" t="inlineStr">
+        <is>
+          <t>Anti-nation</t>
+        </is>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/28/l-anti-nation/</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>De Maurras à Trump, la construction d’un ennemi intérieur est souvent la clef discursive de la conquête de l’espace national. L’article Anti-nation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16108,6 +16496,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E474" r:id="rId473"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E475" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E488" r:id="rId487"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15654,7 +15654,6 @@
           <t>Au Suriname, Selomoh del Castilho a immortalisé le capitaine Broos, figure du marronnage au XIXᵉ siècle, dans un portrait devenu emblématique.</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -15687,7 +15686,6 @@
           <t>En créant la gendarmerie nationale le 16 février 1791, les révolutionnaires proposent une conception nouvelle de la force publique armée qui structure encore le droit aujourd’hui.</t>
         </is>
       </c>
-      <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -15720,7 +15718,6 @@
           <t>Au MetLife Stadium pendant la finale de la Coupe du Monde, Donald Trump s’est-il comporté d’une façon semblable à celle des empereurs romains au Cirque Maximus&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -15753,7 +15750,6 @@
           <t>En tant que parent, il peut être douloureux de voir son enfant souffrir d’être mis à l’écart par les autres. Mais il existe des moyens de les aider.</t>
         </is>
       </c>
-      <c r="G480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -15786,7 +15782,6 @@
           <t>Depuis le début de la guerre en Ukraine, X est devenu un champ de bataille informationnel où diplomatie, OSINT, propagande et journalisme se croisent en temps réel.</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -15819,7 +15814,6 @@
           <t>L'extrême droite a une chance sur deux de gouverner seule la Saxe-Anhalt après le scrutin du 6 septembre. L’article L&amp;rsquo;AfD a une chance sur deux de gouverner seule pour la première fois en Allemagne [Simulation exclusive] est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -15852,7 +15846,6 @@
           <t>Plus de mille ingénieurs demandent à Washington de réguler la frontière de l'IA avant qu’il ne soit trop tard. L’article «&amp;#160;Pour survivre, nous devons nous coordonner pour ralentir la course IA&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -15885,7 +15878,6 @@
           <t>Entre juin 2025 et juin 2026, l’armée ukrainienne aurait frappé plus de 350 000 cibles russes à l’aide de drones. L’article L’Ukraine pourrait-elle amener Moscou à accepter un cessez-le-feu aérien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -15918,7 +15910,6 @@
           <t>Quand les choses vont mal, Poutine surenchérit. Selon l’ancien ambassadeur français à Moscou, il serait imprudent de parier sur un changement de méthode. L’article Profiler un agresseur en série est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -15951,7 +15942,6 @@
           <t>Washington a voté avec la Russie, la Corée du Nord et le Mali contre le renouvellement du mandat du Haut-commissaire aux droits de l’homme de l’ONU. L’article Après un vote aux côtés de la Russie et de la Corée du Nord à l’ONU, les États-Unis accusent la France de complaisance à l’égard de régimes dictatoriaux est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -15984,7 +15974,6 @@
           <t>Face à l'incertitude, le prochain président devrait bâtir les actifs qui préserveront le droit des Français de choisir entre banalisation de l'IA et course à la frontière. L’article Pourquoi l’IA c’est Thémis plutôt que Prométhée est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -16017,7 +16006,204 @@
           <t>De Maurras à Trump, la construction d’un ennemi intérieur est souvent la clef discursive de la conquête de l’espace national. L’article Anti-nation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:04</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:20</t>
+        </is>
+      </c>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>L’Ukraine peut-elle gagner la guerre ?</t>
+        </is>
+      </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lukraine-peut-elle-gagner-la-guerre-288358</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Les frappes ukrainiennes sur le territoire russe représentent un changement d’approche porteur d’effets bénéfiques à Kiev, mais ne suffiront pas, à elles seules, à assurer une victoire militaire.</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:04</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-07-30 04:30</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>Ce que l’évasion de deux modèles d’OpenAI révèle de l’état de la cybersécurité</t>
+        </is>
+      </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/30/ce-que-levasion-de-modeles-dopenai-revele-de-letat-de-la-cybersecurite/</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Les modèles de frontière ont franchi un seuil offensif. Les capacités de cyberdéfense vont-elles suivre&amp;#160;? L’article Ce que l&amp;rsquo;évasion de deux modèles d&amp;rsquo;OpenAI révèle de l&amp;rsquo;état de la cybersécurité est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:04</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-07-30 04:00</t>
+        </is>
+      </c>
+      <c r="D491" s="3" t="inlineStr">
+        <is>
+          <t>Crise de la masculinité</t>
+        </is>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/30/crise-masculinite/</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>De la Rome antique à la manosphère, le récit d’une virilité menacée – aujourd’hui au cœur de la mobilisation de l’extrême droite – resurgit quand la position sociale des femmes change. L’article Crise de la masculinité est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:04</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:58</t>
+        </is>
+      </c>
+      <c r="D492" s="3" t="inlineStr">
+        <is>
+          <t>Qui décide vraiment à Téhéran aujourd’hui ?</t>
+        </is>
+      </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/29/qui-decide-vraiment-a-teheran-aujourdhui/</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Trois factions se disputent le contrôle du régime iranien. Une cartographie à chaud. L’article Qui décide vraiment à Téhéran aujourd&amp;rsquo;hui&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:04</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:30</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>L’AfD a une chance sur deux de gouverner seule pour la première fois en Allemagne [Simulation exclusive]</t>
+        </is>
+      </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/29/simulations-exclusives-lafd-a-une-chance-sur-deux-de-gouverner-saxe-anhalt/</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>L'extrême droite a une chance sur deux de gouverner seule la Saxe-Anhalt après le scrutin du 6 septembre. L’article L&amp;rsquo;AfD a une chance sur deux de gouverner seule pour la première fois en Allemagne [Simulation exclusive] est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:04</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:50</t>
+        </is>
+      </c>
+      <c r="D494" s="3" t="inlineStr">
+        <is>
+          <t>Calendrier 2026-2027 des réunions institutionnelles de l’APHG</t>
+        </is>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/calendrier-2026-2027-des-reunions-institutionnelles-de-laphg/</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Automne 2026 Samedi 12 septembre 2026 : Bureau national (10h-12h, en présentiel) Conseil de gestion (14h-16h30, en présentiel) Samedi 26 septembre 2026 : journée d’étude coorganisée par l’APHG Paris et le CNFG – Université de Paris-Cité : « Géographie du Pacifique, de l’environnement et de la santé : nouveaux regards, nouvelles problématiques ». Du vendredi 2 au dimanche 4 [&amp;#8230;] L’article Calendrier 2026-2027 des réunions institutionnelles de l&amp;rsquo;APHG est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16508,6 +16694,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E486" r:id="rId485"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E487" r:id="rId486"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E494" r:id="rId493"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G494"/>
+  <dimension ref="A1:G505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16038,7 +16038,6 @@
           <t>Les frappes ukrainiennes sur le territoire russe représentent un changement d’approche porteur d’effets bénéfiques à Kiev, mais ne suffiront pas, à elles seules, à assurer une victoire militaire.</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -16071,7 +16070,6 @@
           <t>Les modèles de frontière ont franchi un seuil offensif. Les capacités de cyberdéfense vont-elles suivre&amp;#160;? L’article Ce que l&amp;rsquo;évasion de deux modèles d&amp;rsquo;OpenAI révèle de l&amp;rsquo;état de la cybersécurité est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -16104,7 +16102,6 @@
           <t>De la Rome antique à la manosphère, le récit d’une virilité menacée – aujourd’hui au cœur de la mobilisation de l’extrême droite – resurgit quand la position sociale des femmes change. L’article Crise de la masculinité est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -16137,7 +16134,6 @@
           <t>Trois factions se disputent le contrôle du régime iranien. Une cartographie à chaud. L’article Qui décide vraiment à Téhéran aujourd&amp;rsquo;hui&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -16170,7 +16166,6 @@
           <t>L'extrême droite a une chance sur deux de gouverner seule la Saxe-Anhalt après le scrutin du 6 septembre. L’article L&amp;rsquo;AfD a une chance sur deux de gouverner seule pour la première fois en Allemagne [Simulation exclusive] est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -16203,7 +16198,369 @@
           <t>Automne 2026 Samedi 12 septembre 2026 : Bureau national (10h-12h, en présentiel) Conseil de gestion (14h-16h30, en présentiel) Samedi 26 septembre 2026 : journée d’étude coorganisée par l’APHG Paris et le CNFG – Université de Paris-Cité : « Géographie du Pacifique, de l’environnement et de la santé : nouveaux regards, nouvelles problématiques ». Du vendredi 2 au dimanche 4 [&amp;#8230;] L’article Calendrier 2026-2027 des réunions institutionnelles de l&amp;rsquo;APHG est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:19</t>
+        </is>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>Les tout premiers influenceurs au monde étaient français et sont nés après la Révolution</t>
+        </is>
+      </c>
+      <c r="E495" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-tout-premiers-influenceurs-au-monde-etaient-francais-et-sont-nes-apres-la-revolution-287797</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Comment s’habiller, recevoir, décorer son intérieur ou choisir un restaurant : après 1789, ces questions deviennent essentielles pour une société en pleine recomposition. C’est dans ce contexte qu’apparaissent les tout premiers influenceurs de l’histoire.</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:19</t>
+        </is>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>La fée Morgane : comment la sœur du roi Arthur est-elle devenue la plus célèbre des sorcières médiévales ?</t>
+        </is>
+      </c>
+      <c r="E496" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-fee-morgane-comment-la-soeur-du-roi-arthur-est-elle-devenue-la-plus-celebre-des-sorcieres-medievales-287708</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>La fée Morgane n’a pas toujours été l’ennemie du roi Arthur. Les premiers textes médiévaux en font une savante et une guérisseuse, avant que les romans de chevalerie ne la transforment en magicienne vindicative.</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:15</t>
+        </is>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>Qu’est-ce que la littérature « jeune adulte » ?</t>
+        </is>
+      </c>
+      <c r="E497" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quest-ce-que-la-litterature-jeune-adulte-288455</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Les romans de cette catégorie s’adressent à des jeunes gens en pleine construction, qui peuvent s’identifier aux héros et héroïnes.</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-07-31 08:17</t>
+        </is>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>Que peut nous apprendre l’Australie, référence mondiale en matière d’alerte, sur la gestion des incendies ?</t>
+        </is>
+      </c>
+      <c r="E498" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/que-peut-nous-apprendre-laustralie-reference-mondiale-en-matiere-dalerte-sur-la-gestion-des-incendies-288760</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Comment prévenir efficacement la population face aux feux de végétation ? L’exemple australien montre que des alertes claires et cohérentes sont indispensables, mais qu’elles ne suffisent pas toujours à faire changer les comportements.</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-07-30 15:28</t>
+        </is>
+      </c>
+      <c r="D499" s="3" t="inlineStr">
+        <is>
+          <t>Vente de la Coupe du monde : le bras de fer entre la FIFA et l’Europe</t>
+        </is>
+      </c>
+      <c r="E499" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vente-de-la-coupe-du-monde-le-bras-de-fer-entre-la-fifa-et-leurope-288759</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>En proposant de créer une filiale commerciale valorisée 20 milliards de dollars, Gianni Infantino a déclenché un affrontement inédit avec l’UEFA. Derrière ce conflit se joue l’avenir du football mondial.</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:16</t>
+        </is>
+      </c>
+      <c r="D500" s="3" t="inlineStr">
+        <is>
+          <t>La caméra au service de la recherche : l’expérience d’un documentaire à Madagascar</t>
+        </is>
+      </c>
+      <c r="E500" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-camera-au-service-de-la-recherche-lexperience-dun-documentaire-a-madagascar-287405</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Si la recherche en sciences sociales nous est souvent transmise par écrit, elle se prête aussi à l’image, comme le montre le récit entourant le tournage d’un documentaire.</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-07-31 10:08</t>
+        </is>
+      </c>
+      <c r="D501" s="3" t="inlineStr">
+        <is>
+          <t>Plus de 40 000 arrivées illégales de migrants et 19 morts : que se passe-t-il à Ceuta, l’exclave espagnole frontalière avec le Maroc ?</t>
+        </is>
+      </c>
+      <c r="E501" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/31/plus-de-40-000-arrivees-illegales-de-migrants-et-19-morts-que-se-passe-t-il-a-ceuta-lexclave-espagnole-frontaliere-avec-le-maroc/</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>L’afflux massif de migrants à Ceuta semble moins relever d’une faille de sécurité que d’une instrumentalisation par Rabat de sa population contre Madrid. L’article Plus de 40 000 arrivées illégales de migrants et 19 morts&amp;#160;: que se passe-t-il à Ceuta, l’exclave espagnole frontalière avec le Maroc&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-07-31 04:30</t>
+        </is>
+      </c>
+      <c r="D502" s="3" t="inlineStr">
+        <is>
+          <t>Les Russes se préparent à une nouvelle mobilisation – et cherchent à l’éviter</t>
+        </is>
+      </c>
+      <c r="E502" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/31/les-russes-se-preparent-a-une-nouvelle-mobilisation-et-cherchent-a-leviter/</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Sur Yandex, les recherches portant sur les moyens d'obtenir une exemption de conscription ont explosé ces dernières semaines. L’article Les Russes se préparent à une nouvelle mobilisation – et cherchent à l’éviter est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-07-31 04:00</t>
+        </is>
+      </c>
+      <c r="D503" s="3" t="inlineStr">
+        <is>
+          <t>La prochaine crise financière pourrait dégénérer en une spirale de destruction mutuelle</t>
+        </is>
+      </c>
+      <c r="E503" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/31/la-prochaine-crise-pourrait-degenerer-en-une-spirale-de-destruction-mutuelle/</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Le vrai risque économique est désormais géopolitique. L’article La prochaine crise financière pourrait dégénérer en une spirale de destruction mutuelle est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-07-30 15:42</t>
+        </is>
+      </c>
+      <c r="D504" s="3" t="inlineStr">
+        <is>
+          <t>La Russie peut-elle développer une alternative à Starlink ?</t>
+        </is>
+      </c>
+      <c r="E504" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/30/la-russie-peut-elle-developper-une-alternative-a-starlink/</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Le projet de constellation Rassvet, porté par le Bureau 1440, pourrait compter 250 satellites en orbite dès 2027. L’article La Russie peut-elle développer une alternative à Starlink&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31 11:27</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-07-30 12:19</t>
+        </is>
+      </c>
+      <c r="D505" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe doublera son réseau de bornes de recharge d’ici à 2030</t>
+        </is>
+      </c>
+      <c r="E505" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/30/le-nombre-de-bornes-de-recharge-de-voitures-electriques-devrait-presque-doubler-en-europe-dici-2030/</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Pour comprendre pourquoi, il faut se tourner vers la Chine. L’article L&amp;rsquo;Europe doublera son réseau de bornes de recharge d&amp;rsquo;ici à 2030 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16700,6 +17057,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E492" r:id="rId491"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E493" r:id="rId492"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E505" r:id="rId504"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G505"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16230,7 +16230,6 @@
           <t>Comment s’habiller, recevoir, décorer son intérieur ou choisir un restaurant : après 1789, ces questions deviennent essentielles pour une société en pleine recomposition. C’est dans ce contexte qu’apparaissent les tout premiers influenceurs de l’histoire.</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -16263,7 +16262,6 @@
           <t>La fée Morgane n’a pas toujours été l’ennemie du roi Arthur. Les premiers textes médiévaux en font une savante et une guérisseuse, avant que les romans de chevalerie ne la transforment en magicienne vindicative.</t>
         </is>
       </c>
-      <c r="G496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -16296,7 +16294,6 @@
           <t>Les romans de cette catégorie s’adressent à des jeunes gens en pleine construction, qui peuvent s’identifier aux héros et héroïnes.</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -16329,7 +16326,6 @@
           <t>Comment prévenir efficacement la population face aux feux de végétation ? L’exemple australien montre que des alertes claires et cohérentes sont indispensables, mais qu’elles ne suffisent pas toujours à faire changer les comportements.</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -16362,7 +16358,6 @@
           <t>En proposant de créer une filiale commerciale valorisée 20 milliards de dollars, Gianni Infantino a déclenché un affrontement inédit avec l’UEFA. Derrière ce conflit se joue l’avenir du football mondial.</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -16395,7 +16390,6 @@
           <t>Si la recherche en sciences sociales nous est souvent transmise par écrit, elle se prête aussi à l’image, comme le montre le récit entourant le tournage d’un documentaire.</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -16428,7 +16422,6 @@
           <t>L’afflux massif de migrants à Ceuta semble moins relever d’une faille de sécurité que d’une instrumentalisation par Rabat de sa population contre Madrid. L’article Plus de 40 000 arrivées illégales de migrants et 19 morts&amp;#160;: que se passe-t-il à Ceuta, l’exclave espagnole frontalière avec le Maroc&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -16461,7 +16454,6 @@
           <t>Sur Yandex, les recherches portant sur les moyens d'obtenir une exemption de conscription ont explosé ces dernières semaines. L’article Les Russes se préparent à une nouvelle mobilisation – et cherchent à l’éviter est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -16494,7 +16486,6 @@
           <t>Le vrai risque économique est désormais géopolitique. L’article La prochaine crise financière pourrait dégénérer en une spirale de destruction mutuelle est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -16527,7 +16518,6 @@
           <t>Le projet de constellation Rassvet, porté par le Bureau 1440, pourrait compter 250 satellites en orbite dès 2027. L’article La Russie peut-elle développer une alternative à Starlink&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -16560,7 +16550,204 @@
           <t>Pour comprendre pourquoi, il faut se tourner vers la Chine. L’article L&amp;rsquo;Europe doublera son réseau de bornes de recharge d&amp;rsquo;ici à 2030 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:38</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-08-01 08:11</t>
+        </is>
+      </c>
+      <c r="D506" s="3" t="inlineStr">
+        <is>
+          <t>Comment la crise à la frontière de Ceuta a immédiatement servi les intérêts de l’extrême droite espagnole</t>
+        </is>
+      </c>
+      <c r="E506" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-la-crise-a-la-frontiere-de-ceuta-a-immediatement-servi-les-interets-de-lextreme-droite-espagnole-288890</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>La crise migratoire de Ceuta ne se résume pas aux chiffres. En diffusant des images spectaculaires d’arrivées massives, elle a offert un terrain favorable aux discours les plus durs sur l’immigration en Espagne.</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:38</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-08-01 07:45</t>
+        </is>
+      </c>
+      <c r="D507" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Ceuta est au cœur d’une crise migratoire permanente</t>
+        </is>
+      </c>
+      <c r="E507" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-ceuta-est-au-coeur-dune-crise-migratoire-permanente-288888</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>La crise migratoire à Ceuta révèle comment la géopolitique, la dépendance de l’Europe à l’égard du Maroc et les limites des capacités institutionnelles transforment la frontière en un défi pour la démocratie et les droits humains.</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:38</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-08-01 05:00</t>
+        </is>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>L’armée russe a avancé de 1 km² par jour en moyenne en juillet</t>
+        </is>
+      </c>
+      <c r="E508" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/01/larmee-russe-a-avance-de-1-km%c2%b2-par-jour-en-moyenne-en-juillet/</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Cette année, l'offensive russe de printemps-été ne devrait donner lieu à aucune victoire majeure pour Moscou. L’article L’armée russe a avancé de 1 km² par jour en moyenne en juillet est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:38</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-08-01 04:09</t>
+        </is>
+      </c>
+      <c r="D509" s="3" t="inlineStr">
+        <is>
+          <t>Le corps illibéral de l’idéologie vécue</t>
+        </is>
+      </c>
+      <c r="E509" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/01/clavicular-looksmaxxing-corps-illiberal-lideologie-vecue/</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Le courant looksmaxxing de l'influencer Clavicular révèle le secret de l'accélération réactionnaire&amp;#160;: une idéologie qui se vit avant de se penser. L’article Le corps illibéral de l’idéologie vécue est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:38</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:33</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Ceuta n’est pas une crise migratoire pour l’Europe</t>
+        </is>
+      </c>
+      <c r="E510" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/31/pourquoi-ceuta-nest-pas-une-crise-migratoire-pour-leurope/</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Pour l’auteur de De l'immigration en France (Grasset, 2026), les images spectaculaires qui ont envahi nos écrans ne confirment aucunement le récit de la submersion. L’article Pourquoi Ceuta n’est pas une crise migratoire pour l’Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:38</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-07-31 16:19</t>
+        </is>
+      </c>
+      <c r="D511" s="3" t="inlineStr">
+        <is>
+          <t>Le Sahel pourrait être au seuil d’une nouvelle ère humide</t>
+        </is>
+      </c>
+      <c r="E511" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/07/31/le-sahel-pourrait-etre-au-seuil-dune-nouvelle-ere-humide/</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Le changement climatique, la plantation d'arbres et l'adoption de nouvelles habitudes de consommation d'eau pourraient mettre fin à des décennies de sécheresse. L’article Le Sahel pourrait être au seuil d’une nouvelle ère humide est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17068,6 +17255,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E503" r:id="rId502"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E504" r:id="rId503"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E511" r:id="rId510"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:G515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16582,7 +16582,6 @@
           <t>La crise migratoire de Ceuta ne se résume pas aux chiffres. En diffusant des images spectaculaires d’arrivées massives, elle a offert un terrain favorable aux discours les plus durs sur l’immigration en Espagne.</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -16615,7 +16614,6 @@
           <t>La crise migratoire à Ceuta révèle comment la géopolitique, la dépendance de l’Europe à l’égard du Maroc et les limites des capacités institutionnelles transforment la frontière en un défi pour la démocratie et les droits humains.</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -16648,7 +16646,6 @@
           <t>Cette année, l'offensive russe de printemps-été ne devrait donner lieu à aucune victoire majeure pour Moscou. L’article L’armée russe a avancé de 1 km² par jour en moyenne en juillet est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -16681,7 +16678,6 @@
           <t>Le courant looksmaxxing de l'influencer Clavicular révèle le secret de l'accélération réactionnaire&amp;#160;: une idéologie qui se vit avant de se penser. L’article Le corps illibéral de l’idéologie vécue est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -16714,7 +16710,6 @@
           <t>Pour l’auteur de De l'immigration en France (Grasset, 2026), les images spectaculaires qui ont envahi nos écrans ne confirment aucunement le récit de la submersion. L’article Pourquoi Ceuta n’est pas une crise migratoire pour l’Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -16747,7 +16742,138 @@
           <t>Le changement climatique, la plantation d'arbres et l'adoption de nouvelles habitudes de consommation d'eau pourraient mettre fin à des décennies de sécheresse. L’article Le Sahel pourrait être au seuil d’une nouvelle ère humide est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:37</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:57</t>
+        </is>
+      </c>
+      <c r="D512" s="3" t="inlineStr">
+        <is>
+          <t>Inde : la crise de la classe moyenne nourrit la colère étudiante</t>
+        </is>
+      </c>
+      <c r="E512" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/inde-la-crise-de-la-classe-moyenne-nourrit-la-colere-etudiante-288761</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>L’actuelle fronde des étudiants en Inde reflète les difficultés d’une classe moyenne dont l’essor a nettement ralenti au cours de ces dernières années.</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:37</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-08-02 05:00</t>
+        </is>
+      </c>
+      <c r="D513" s="3" t="inlineStr">
+        <is>
+          <t>La sécheresse a fait baisser le niveau des fleuves européens à leur plus bas niveau</t>
+        </is>
+      </c>
+      <c r="E513" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/02/la-secheresse-a-fait-baisser-le-niveau-des-fleuves-europeens-a-leur-plus-bas-niveau/</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>En Allemagne, la chute des débits du Rhin pourrait coûter jusqu’à 0,2&amp;#160;% du PIB au troisième trimestre. L’article La sécheresse a fait baisser le niveau des fleuves européens à leur plus bas niveau est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:37</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-08-02 04:00</t>
+        </is>
+      </c>
+      <c r="D514" s="3" t="inlineStr">
+        <is>
+          <t>Le déclin de l’Occident</t>
+        </is>
+      </c>
+      <c r="E514" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/02/le-declin-de-loccident/</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>De Weimar à Washington, la prophétie d'une civilisation condamnée à la décadence sert de socle idéologique à l'assaut contre la démocratie libérale. L’article Le déclin de l’Occident est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:37</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-08-01 17:18</t>
+        </is>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>Après Ceuta qui soutient Sanchez en Europe ?</t>
+        </is>
+      </c>
+      <c r="E515" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/01/comment-se-positionnent-les-pays-europeens-face-a-la-crise-de-ceuta/</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Des tensions avec l'Italie de Meloni au soutien de la France et du Portugal, nous cartographions les positions des 27 pays de l’Union. L’article Après Ceuta qui soutient Sanchez en Europe&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17261,6 +17387,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E509" r:id="rId508"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E510" r:id="rId509"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E515" r:id="rId514"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G515"/>
+  <dimension ref="A1:G521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16774,7 +16774,6 @@
           <t>L’actuelle fronde des étudiants en Inde reflète les difficultés d’une classe moyenne dont l’essor a nettement ralenti au cours de ces dernières années.</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -16807,7 +16806,6 @@
           <t>En Allemagne, la chute des débits du Rhin pourrait coûter jusqu’à 0,2&amp;#160;% du PIB au troisième trimestre. L’article La sécheresse a fait baisser le niveau des fleuves européens à leur plus bas niveau est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -16840,7 +16838,6 @@
           <t>De Weimar à Washington, la prophétie d'une civilisation condamnée à la décadence sert de socle idéologique à l'assaut contre la démocratie libérale. L’article Le déclin de l’Occident est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -16873,7 +16870,204 @@
           <t>Des tensions avec l'Italie de Meloni au soutien de la France et du Portugal, nous cartographions les positions des 27 pays de l’Union. L’article Après Ceuta qui soutient Sanchez en Europe&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-08-02 13:31</t>
+        </is>
+      </c>
+      <c r="D516" s="3" t="inlineStr">
+        <is>
+          <t>Que signifient les chevelures bouclées des Égyptiennes d’hier et d’aujourd’hui ?</t>
+        </is>
+      </c>
+      <c r="E516" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/que-signifient-les-chevelures-bouclees-des-egyptiennes-dhier-et-daujourdhui-285868</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Déjà dans l’Égypte ancienne, les chevelures bouclées revêtaient une symbolique forte.</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-08-02 13:33</t>
+        </is>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>Construire des cabanes : un jeu d’enfants qui interroge nos liens avec la nature</t>
+        </is>
+      </c>
+      <c r="E517" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/construire-des-cabanes-un-jeu-denfants-qui-interroge-nos-liens-avec-la-nature-286727</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Que nous disent les cabanes des imaginaires de l’enfance ? Et comment permettent-elles aux plus jeunes de se sentir petit à petit dans la nature comme chez eux ?</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-08-03 04:30</t>
+        </is>
+      </c>
+      <c r="D518" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : la crise des carburants s’approfondit et les exportations chutent</t>
+        </is>
+      </c>
+      <c r="E518" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/03/economie-russe-la-crise-des-carburants-sapprofondit-et-les-exportations-chutent/</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Parmi les premiers exportateurs mondiaux de produits pétroliers avant l'invasion de l'Ukraine, la Russie doit désormais acheter son essence à l'Inde et au Kazakhstan. L’article Économie russe&amp;#160;: la crise des carburants s’approfondit et les exportations chutent est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-08-03 04:30</t>
+        </is>
+      </c>
+      <c r="D519" s="3" t="inlineStr">
+        <is>
+          <t>L’administration Trump est en train de faire plier l’Université américaine</t>
+        </is>
+      </c>
+      <c r="E519" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/03/ladministration-trump-est-en-train-de-faire-plier-luniversite-americaine/</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Selon l’ancien directeur de la Yale Law School, un règlement passé inaperçu en Europe donne à la Maison-Blanche un levier sur la science américaine. L’article L&amp;rsquo;administration Trump est en train de faire plier l’Université américaine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-08-02 14:27</t>
+        </is>
+      </c>
+      <c r="D520" s="3" t="inlineStr">
+        <is>
+          <t>La crise de Ceuta est-elle la première ruée algorithmique de l’histoire ?</t>
+        </is>
+      </c>
+      <c r="E520" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/02/la-crise-de-ceuta-est-elle-la-premiere-ruee-algorithmique-de-lhistoire/</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Tout ce que l'on sait du rôle des réseaux sociaux dans le pic migratoire historique du 30 juillet qui est maintenant presque entièrement résorbé. L’article La crise de Ceuta est-elle la première ruée algorithmique de l’histoire&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-08-02 14:05</t>
+        </is>
+      </c>
+      <c r="D521" s="3" t="inlineStr">
+        <is>
+          <t>La plus grande victoire de la mafia est d’avoir cessé de ressembler à la mafia</t>
+        </is>
+      </c>
+      <c r="E521" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/02/la-plus-grande-victoire-de-la-mafia-est-davoir-cesse-de-ressembler-a-la-mafia/</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Les révélations du grand écrivain italien, condamné à vivre sous escorte. L’article La plus grande victoire de la mafia est d&amp;rsquo;avoir cessé de ressembler à la mafia est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17391,6 +17585,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E513" r:id="rId512"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E514" r:id="rId513"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E521" r:id="rId520"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G521"/>
+  <dimension ref="A1:G527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16902,7 +16902,6 @@
           <t>Déjà dans l’Égypte ancienne, les chevelures bouclées revêtaient une symbolique forte.</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -16935,7 +16934,6 @@
           <t>Que nous disent les cabanes des imaginaires de l’enfance ? Et comment permettent-elles aux plus jeunes de se sentir petit à petit dans la nature comme chez eux ?</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -16968,7 +16966,6 @@
           <t>Parmi les premiers exportateurs mondiaux de produits pétroliers avant l'invasion de l'Ukraine, la Russie doit désormais acheter son essence à l'Inde et au Kazakhstan. L’article Économie russe&amp;#160;: la crise des carburants s’approfondit et les exportations chutent est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -17001,7 +16998,6 @@
           <t>Selon l’ancien directeur de la Yale Law School, un règlement passé inaperçu en Europe donne à la Maison-Blanche un levier sur la science américaine. L’article L&amp;rsquo;administration Trump est en train de faire plier l’Université américaine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -17034,7 +17030,6 @@
           <t>Tout ce que l'on sait du rôle des réseaux sociaux dans le pic migratoire historique du 30 juillet qui est maintenant presque entièrement résorbé. L’article La crise de Ceuta est-elle la première ruée algorithmique de l’histoire&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -17067,7 +17062,204 @@
           <t>Les révélations du grand écrivain italien, condamné à vivre sous escorte. L’article La plus grande victoire de la mafia est d&amp;rsquo;avoir cessé de ressembler à la mafia est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:20</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:02</t>
+        </is>
+      </c>
+      <c r="D522" s="3" t="inlineStr">
+        <is>
+          <t>Route 66 : cent ans d’un mythe qui ne raconte pas toute l’histoire</t>
+        </is>
+      </c>
+      <c r="E522" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/route-66-cent-ans-dun-mythe-qui-ne-raconte-pas-toute-lhistoire-287643</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Symbole du rêve américain, de l’aventure et de la liberté, la Route 66 n’a pourtant jamais offert la même expérience à tous. Son histoire raconte aussi l’exclusion des voyageurs noirs et le déclin des petites villes qu’elle faisait vivre.</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:20</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:03</t>
+        </is>
+      </c>
+      <c r="D523" s="3" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, les universités peinent à enrayer le recul de la lecture</t>
+        </is>
+      </c>
+      <c r="E523" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/aux-etats-unis-les-universites-peinent-a-enrayer-le-recul-de-la-lecture-288421</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Aux États-Unis, les enseignants du supérieur voient leurs étudiants lire de moins en moins. Face à ce recul, certains réduisent leurs exigences.</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:20</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:04</t>
+        </is>
+      </c>
+      <c r="D524" s="3" t="inlineStr">
+        <is>
+          <t>« Ils sont parmi nous » : la nouvelle plateforme de la Maison-Blanche et la déshumanisation des sans-papiers</t>
+        </is>
+      </c>
+      <c r="E524" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ils-sont-parmi-nous-la-nouvelle-plateforme-de-la-maison-blanche-et-la-deshumanisation-des-sans-papiers-288434</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>La page «&amp;nbsp;Aliens.gov&amp;nbsp;», hébergée sur le site de la Maison-Blanche, joue sur le double sens en anglais du mot «&amp;nbsp;alien&amp;nbsp;» (étranger/extraterrestre) afin de déshumaniser les immigrés clandestins.</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:20</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-08-04 04:30</t>
+        </is>
+      </c>
+      <c r="D525" s="3" t="inlineStr">
+        <is>
+          <t>La monnaie est redevenue une arme, il faut armer l’euro</t>
+        </is>
+      </c>
+      <c r="E525" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/04/la-monnaie-est-redevenue-une-arme-il-faut-armer-leuro/</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Notre souveraineté dépend désormais de la capacité à faire de la monnaie commune un instrument de puissance géopolitique. L’article La monnaie est redevenue une arme, il faut armer l’euro est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:20</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-08-04 04:30</t>
+        </is>
+      </c>
+      <c r="D526" s="3" t="inlineStr">
+        <is>
+          <t>Combien de soldats russes combattent vraiment en Ukraine ?</t>
+        </is>
+      </c>
+      <c r="E526" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/04/combien-de-soldats-russes-combattent-vraiment-en-ukraine/</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>La lecture méticuleuse du budget de la Russie permet d’y voir plus clair dans le brouillard de guerre du Kremlin. L’article Combien de soldats russes combattent vraiment en Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:20</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-08-03 15:08</t>
+        </is>
+      </c>
+      <c r="D527" s="3" t="inlineStr">
+        <is>
+          <t>La doctrine Bessent fait du dollar la monnaie de la vassalisation heureuse</t>
+        </is>
+      </c>
+      <c r="E527" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/03/la-doctrine-bessent-fait-du-dollar-la-monnaie-de-la-vassalisation-heureuse/</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>En intervenant sur le yen après le peso, l'administration Trump inaugure une protection monétaire réservée à ses alliés les plus alignés, désormais intégrés à un système asymétrique de tribut. L’article La doctrine Bessent fait du dollar la monnaie de la vassalisation heureuse est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17591,6 +17783,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E519" r:id="rId518"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E520" r:id="rId519"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E527" r:id="rId526"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G527"/>
+  <dimension ref="A1:G535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17094,7 +17094,6 @@
           <t>Symbole du rêve américain, de l’aventure et de la liberté, la Route 66 n’a pourtant jamais offert la même expérience à tous. Son histoire raconte aussi l’exclusion des voyageurs noirs et le déclin des petites villes qu’elle faisait vivre.</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -17127,7 +17126,6 @@
           <t>Aux États-Unis, les enseignants du supérieur voient leurs étudiants lire de moins en moins. Face à ce recul, certains réduisent leurs exigences.</t>
         </is>
       </c>
-      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -17160,7 +17158,6 @@
           <t>La page «&amp;nbsp;Aliens.gov&amp;nbsp;», hébergée sur le site de la Maison-Blanche, joue sur le double sens en anglais du mot «&amp;nbsp;alien&amp;nbsp;» (étranger/extraterrestre) afin de déshumaniser les immigrés clandestins.</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -17193,7 +17190,6 @@
           <t>Notre souveraineté dépend désormais de la capacité à faire de la monnaie commune un instrument de puissance géopolitique. L’article La monnaie est redevenue une arme, il faut armer l’euro est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -17226,7 +17222,6 @@
           <t>La lecture méticuleuse du budget de la Russie permet d’y voir plus clair dans le brouillard de guerre du Kremlin. L’article Combien de soldats russes combattent vraiment en Ukraine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -17259,7 +17254,270 @@
           <t>En intervenant sur le yen après le peso, l'administration Trump inaugure une protection monétaire réservée à ses alliés les plus alignés, désormais intégrés à un système asymétrique de tribut. L’article La doctrine Bessent fait du dollar la monnaie de la vassalisation heureuse est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-08-04 14:07</t>
+        </is>
+      </c>
+      <c r="D528" s="3" t="inlineStr">
+        <is>
+          <t>Le pouvoir politique face aux incendies : depuis la Rome de Néron, un exercice de mise en scène ?</t>
+        </is>
+      </c>
+      <c r="E528" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-pouvoir-politique-face-aux-incendies-depuis-la-rome-de-neron-un-exercice-de-mise-en-scene-288896</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Comment les textes antiques peuvent-ils nous aider à remettre en perspective les rouages de la communication politique en situation de crise&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-08-04 14:08</t>
+        </is>
+      </c>
+      <c r="D529" s="3" t="inlineStr">
+        <is>
+          <t>L’administration Trump veut priver les citoyens d’un puissant levier pour protéger l’environnement</t>
+        </is>
+      </c>
+      <c r="E529" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ladministration-trump-veut-priver-les-citoyens-dun-puissant-levier-pour-proteger-lenvironnement-289055</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Depuis des décennies, des citoyens et des associations utilisent les tribunaux pour contraindre les entreprises et l’État fédéral à respecter les lois environnementales. L’administration Trump cherche désormais à restreindre ce pouvoir.</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-08-04 14:07</t>
+        </is>
+      </c>
+      <c r="D530" s="3" t="inlineStr">
+        <is>
+          <t>La défaite de la Seleção peut-elle coûter une élection présidentielle au Brésil ?</t>
+        </is>
+      </c>
+      <c r="E530" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-defaite-de-la-selecao-peut-elle-couter-une-election-presidentielle-au-bresil-288655</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Le Brésil a l’image d’un pays fou de football, si bien qu’on peut se demander s’il y a un rapport entre les résultats de son équipe nationale et la perception qu’a la population du pouvoir en place.</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:29</t>
+        </is>
+      </c>
+      <c r="D531" s="3" t="inlineStr">
+        <is>
+          <t>Trump peut encore gagner les élections de mi-mandat</t>
+        </is>
+      </c>
+      <c r="E531" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/05/trump-peut-encore-gagner-les-elections-de-mi-mandat/</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Les sondages erronés et les divisions démocrates pourraient offrir une victoire inattendue en novembre au parti républicain. L’article Trump peut encore gagner les élections de mi-mandat est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-08-05 04:30</t>
+        </is>
+      </c>
+      <c r="D532" s="3" t="inlineStr">
+        <is>
+          <t>Avec V4-Flash, DeepSeek mise sur l’IA à faible coût plutôt que sur la course à la puissance</t>
+        </is>
+      </c>
+      <c r="E532" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/05/avec-v4-flash-deepseek-mise-sur-lia-a-faible-cout-plutot-que-sur-la-course-a-la-puissance/</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Fin juillet, le Chinois DeepSeek, leader de l'IA à bas coût, a publié la nouvelle version de son modèle «&amp;#160;Flash&amp;#160;»&amp;#160;: cent fois moins cher que Claude Fable 5, le modèle le plus avancé d'Anthropic, gratuit et librement réutilisable, il est déjà en tête des usages sur la plateforme OpenRouter. L’article Avec V4-Flash, DeepSeek mise sur l&amp;rsquo;IA à faible coût plutôt que sur la course à la puissance est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-08-05 04:00</t>
+        </is>
+      </c>
+      <c r="D533" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le Maroc n’a pas pu orchestrer la crise de Ceuta</t>
+        </is>
+      </c>
+      <c r="E533" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/05/pourquoi-le-maroc-na-pas-pu-orchestrer-la-crise-de-ceuta/</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Attribuer la crise à Rabat revient à méconnaître la dynamique sociale marocaine et la singularité de l’exclave. L’article Pourquoi le Maroc n’a pas pu orchestrer la crise de Ceuta est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-08-04 17:44</t>
+        </is>
+      </c>
+      <c r="D534" s="3" t="inlineStr">
+        <is>
+          <t>Les réseaux sociaux ont-ils organisé la ruée vers Ceuta ?</t>
+        </is>
+      </c>
+      <c r="E534" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/04/les-reseaux-sociaux-ont-ils-organise-la-ruee-vers-ceuta/</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Une enquête OSINT reconstitue le passage de 50 000 migrants dans l’exclave espagnole. L’article Les réseaux sociaux ont-ils organisé la ruée vers Ceuta&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:16</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-08-04 14:32</t>
+        </is>
+      </c>
+      <c r="D535" s="3" t="inlineStr">
+        <is>
+          <t>Après la crise de Ceuta l’Europe doit apprendre à sécuriser ses frontières numériques</t>
+        </is>
+      </c>
+      <c r="E535" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/04/apres-la-crise-de-ceuta-leurope-doit-apprendre-a-securiser-ses-frontieres-numeriques/</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>L’ancien commissaire européen indique les pistes étonnamment négligées à ce stade par la présidente Ursula von der Leyen. L’article Après la crise de Ceuta l&amp;rsquo;Europe doit apprendre à sécuriser ses frontières numériques est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17789,6 +18047,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E525" r:id="rId524"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E526" r:id="rId525"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E535" r:id="rId534"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G535"/>
+  <dimension ref="A1:G540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17286,7 +17286,6 @@
           <t>Comment les textes antiques peuvent-ils nous aider à remettre en perspective les rouages de la communication politique en situation de crise&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -17319,7 +17318,6 @@
           <t>Depuis des décennies, des citoyens et des associations utilisent les tribunaux pour contraindre les entreprises et l’État fédéral à respecter les lois environnementales. L’administration Trump cherche désormais à restreindre ce pouvoir.</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -17352,7 +17350,6 @@
           <t>Le Brésil a l’image d’un pays fou de football, si bien qu’on peut se demander s’il y a un rapport entre les résultats de son équipe nationale et la perception qu’a la population du pouvoir en place.</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -17385,7 +17382,6 @@
           <t>Les sondages erronés et les divisions démocrates pourraient offrir une victoire inattendue en novembre au parti républicain. L’article Trump peut encore gagner les élections de mi-mandat est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -17418,7 +17414,6 @@
           <t>Fin juillet, le Chinois DeepSeek, leader de l'IA à bas coût, a publié la nouvelle version de son modèle «&amp;#160;Flash&amp;#160;»&amp;#160;: cent fois moins cher que Claude Fable 5, le modèle le plus avancé d'Anthropic, gratuit et librement réutilisable, il est déjà en tête des usages sur la plateforme OpenRouter. L’article Avec V4-Flash, DeepSeek mise sur l&amp;rsquo;IA à faible coût plutôt que sur la course à la puissance est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -17451,7 +17446,6 @@
           <t>Attribuer la crise à Rabat revient à méconnaître la dynamique sociale marocaine et la singularité de l’exclave. L’article Pourquoi le Maroc n’a pas pu orchestrer la crise de Ceuta est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -17484,7 +17478,6 @@
           <t>Une enquête OSINT reconstitue le passage de 50 000 migrants dans l’exclave espagnole. L’article Les réseaux sociaux ont-ils organisé la ruée vers Ceuta&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -17517,7 +17510,171 @@
           <t>L’ancien commissaire européen indique les pistes étonnamment négligées à ce stade par la présidente Ursula von der Leyen. L’article Après la crise de Ceuta l&amp;rsquo;Europe doit apprendre à sécuriser ses frontières numériques est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:19</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-08-05 13:18</t>
+        </is>
+      </c>
+      <c r="D536" s="3" t="inlineStr">
+        <is>
+          <t>Dans l’Antiquité, les Grecs n’étaient pas tous bodybuildés !</t>
+        </is>
+      </c>
+      <c r="E536" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/dans-lantiquite-les-grecs-netaient-pas-tous-bodybuildes-285079</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Les travaux récents en histoire ancienne mettent au jour des figures masculines très éloignées des stéréotypes athlétiques qui peuplent les musées.</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:19</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-08-05 13:22</t>
+        </is>
+      </c>
+      <c r="D537" s="3" t="inlineStr">
+        <is>
+          <t>Donald Trump ou la contagion du mal ordinaire</t>
+        </is>
+      </c>
+      <c r="E537" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/donald-trump-ou-la-contagion-du-mal-ordinaire-288861</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Donald Trump incarne moins une rupture qu’une désinhibition du pouvoir&amp;nbsp;: en banalisant la brutalité, il légitime une grammaire du rapport de force à tous les niveaux.</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:19</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-08-06 04:30</t>
+        </is>
+      </c>
+      <c r="D538" s="3" t="inlineStr">
+        <is>
+          <t>La rougeole explose aux États-Unis de Donald Trump</t>
+        </is>
+      </c>
+      <c r="E538" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/06/la-rougeole-explose-aux-etats-unis-de-donald-trump/</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Face à la pire épidémie de rougeole depuis trente-cinq ans, Robert F. Kennedy Jr. a fait un choix radical&amp;#160;: ne rien faire, sans le dire. L’article La rougeole explose aux États-Unis de Donald Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:19</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-08-06 04:00</t>
+        </is>
+      </c>
+      <c r="D539" s="3" t="inlineStr">
+        <is>
+          <t>L’Ukraine peut-elle gagner la guerre aux entrepôts ?</t>
+        </is>
+      </c>
+      <c r="E539" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/06/lukraine-peut-elle-gagner-la-guerre-aux-entrepots/</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Pour mesurer le succès de la stratégie de profondeur de Kyiv, il faut comprendre l'importance de Wildberries dans la Russie de Poutine. L’article L’Ukraine peut-elle gagner la guerre aux entrepôts&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:19</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:16</t>
+        </is>
+      </c>
+      <c r="D540" s="3" t="inlineStr">
+        <is>
+          <t>L’attentat de Berlin et le tournant sahélien du djihad européen</t>
+        </is>
+      </c>
+      <c r="E540" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/05/attentat-de-berlin-tournant-sahelien-du-djihad-europeen/</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>De nouveaux documents sur le terroriste de la Marche des Fiertés pourraient signaler une nouvelle phase de l'État islamique. L’article L’attentat de Berlin et le tournant sahélien du djihad européen est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18055,6 +18212,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E533" r:id="rId532"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E534" r:id="rId533"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E540" r:id="rId539"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G540"/>
+  <dimension ref="A1:G544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17542,7 +17542,6 @@
           <t>Les travaux récents en histoire ancienne mettent au jour des figures masculines très éloignées des stéréotypes athlétiques qui peuplent les musées.</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -17575,7 +17574,6 @@
           <t>Donald Trump incarne moins une rupture qu’une désinhibition du pouvoir&amp;nbsp;: en banalisant la brutalité, il légitime une grammaire du rapport de force à tous les niveaux.</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -17608,7 +17606,6 @@
           <t>Face à la pire épidémie de rougeole depuis trente-cinq ans, Robert F. Kennedy Jr. a fait un choix radical&amp;#160;: ne rien faire, sans le dire. L’article La rougeole explose aux États-Unis de Donald Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -17641,7 +17638,6 @@
           <t>Pour mesurer le succès de la stratégie de profondeur de Kyiv, il faut comprendre l'importance de Wildberries dans la Russie de Poutine. L’article L’Ukraine peut-elle gagner la guerre aux entrepôts&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -17674,7 +17670,138 @@
           <t>De nouveaux documents sur le terroriste de la Marche des Fiertés pourraient signaler une nouvelle phase de l'État islamique. L’article L’attentat de Berlin et le tournant sahélien du djihad européen est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:57</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-08-06 13:11</t>
+        </is>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>La guerre contre les houthistes du Yémen peut-elle détourner Riyad du Soudan ?</t>
+        </is>
+      </c>
+      <c r="E541" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-guerre-contre-les-houthistes-du-yemen-peut-elle-detourner-riyad-du-soudan-288862</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Une reprise de la guerre contre les houthistes du Yémen pourrait contraindre Riyad à réduire son soutien aux Forces armées soudanaises&amp;nbsp;: les priorités extérieures font l’objet de rééquilibrages constants.</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:57</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-08-07 05:49</t>
+        </is>
+      </c>
+      <c r="D542" s="3" t="inlineStr">
+        <is>
+          <t>La Russie prépare-t-elle une opération sous faux drapeau sur le territoire de l’OTAN ?</t>
+        </is>
+      </c>
+      <c r="E542" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/07/la-russie-prepare-t-elle-une-operation-sous-faux-drapeau-sur-le-territoire-de-lotan/</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Selon le ministre lituanien de la Défense, Robertas Kaunas, Moscou pourrait viser des infrastructures critiques des pays baltes avec des drones ukrainiens. Si rien n'indique que la Russie ait pris la décision de passer à l'acte, cette déclaration s'inscrit dans une série d'autres prises de parole de dirigeants du flanc est de l'OTAN qui mettent en garde contre la possibilité d'une attaque russe. L’article La Russie prépare-t-elle une opération sous faux drapeau sur le territoire de l&amp;rsquo;OTAN&amp;</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:57</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:30</t>
+        </is>
+      </c>
+      <c r="D543" s="3" t="inlineStr">
+        <is>
+          <t>La nouvelle thalassocratie chinoise</t>
+        </is>
+      </c>
+      <c r="E543" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/07/la-nouvelle-thalassocratie-chinoise/</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Comment Xi Jinping fait de la «&amp;#160;Méditerranée asiatique&amp;#160;» le cœur de son projet impérial. L’article La nouvelle thalassocratie chinoise est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:57</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-08-06 15:46</t>
+        </is>
+      </c>
+      <c r="D544" s="3" t="inlineStr">
+        <is>
+          <t>Que contient l’accord que l’Iran et l’Oman seraient en train de finaliser pour le transit dans le détroit d’Ormuz ?</t>
+        </is>
+      </c>
+      <c r="E544" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/06/que-contient-laccord-que-liran-et-loman-seraient-en-train-de-finaliser-pour-le-transit-dans-le-detroit-dormuz/</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Selon le vice-ministre iranien des Affaires étrangères, l’accord avec Mascate ne garantirait toutefois pas la reprise du trafic. L’article Que contient l&amp;rsquo;accord que l&amp;rsquo;Iran et l&amp;rsquo;Oman seraient en train de finaliser pour le transit dans le détroit d&amp;rsquo;Ormuz&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18217,6 +18344,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E538" r:id="rId537"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E539" r:id="rId538"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E544" r:id="rId543"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G544"/>
+  <dimension ref="A1:G553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17702,7 +17702,6 @@
           <t>Une reprise de la guerre contre les houthistes du Yémen pourrait contraindre Riyad à réduire son soutien aux Forces armées soudanaises&amp;nbsp;: les priorités extérieures font l’objet de rééquilibrages constants.</t>
         </is>
       </c>
-      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -17735,7 +17734,6 @@
           <t>Selon le ministre lituanien de la Défense, Robertas Kaunas, Moscou pourrait viser des infrastructures critiques des pays baltes avec des drones ukrainiens. Si rien n'indique que la Russie ait pris la décision de passer à l'acte, cette déclaration s'inscrit dans une série d'autres prises de parole de dirigeants du flanc est de l'OTAN qui mettent en garde contre la possibilité d'une attaque russe. L’article La Russie prépare-t-elle une opération sous faux drapeau sur le territoire de l&amp;rsquo;OTAN&amp;</t>
         </is>
       </c>
-      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -17768,7 +17766,6 @@
           <t>Comment Xi Jinping fait de la «&amp;#160;Méditerranée asiatique&amp;#160;» le cœur de son projet impérial. L’article La nouvelle thalassocratie chinoise est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -17801,7 +17798,303 @@
           <t>Selon le vice-ministre iranien des Affaires étrangères, l’accord avec Mascate ne garantirait toutefois pas la reprise du trafic. L’article Que contient l&amp;rsquo;accord que l&amp;rsquo;Iran et l&amp;rsquo;Oman seraient en train de finaliser pour le transit dans le détroit d&amp;rsquo;Ormuz&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-08-08 06:49</t>
+        </is>
+      </c>
+      <c r="D545" s="3" t="inlineStr">
+        <is>
+          <t>Comment les éclipses ont ouvert la cour impériale chinoise aux sciences européennes</t>
+        </is>
+      </c>
+      <c r="E545" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-les-eclipses-ont-ouvert-la-cour-imperiale-chinoise-aux-sciences-europeennes-289241</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Pendant des siècles, les astronomes impériaux chinois ont tenté de prédire les éclipses, dont dépendait la légitimité de l’empereur. L’arrivée des jésuites et de leurs méthodes mathématiques européennes allait révolutionner cette science.</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-08-09 07:36</t>
+        </is>
+      </c>
+      <c r="D546" s="3" t="inlineStr">
+        <is>
+          <t>Le Maroc, futur leader continental africain des data centers et de l’IA</t>
+        </is>
+      </c>
+      <c r="E546" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-maroc-futur-leader-continental-africain-des-data-centers-et-de-lia-288658</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>À travers une série de projets de data centers, le Maroc cherche à prendre une longueur d’avance sur ses voisins dans le secteur du numérique.</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
+        </is>
+      </c>
+      <c r="D547" s="3" t="inlineStr">
+        <is>
+          <t>Le Royaume-Uni, le Japon et l’Italie peuvent-ils réussir leur avion de combat de sixième génération là où la France et ses partenaires ont échoué ?</t>
+        </is>
+      </c>
+      <c r="E547" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-royaume-uni-le-japon-et-litalie-peuvent-ils-reussir-leur-avion-de-combat-de-sixieme-generation-la-ou-la-france-et-ses-partenaires-ont-echoue-289056</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Après l’échec du programme franco-germano-espagnol, le Royaume-Uni, l’Italie et le Japon accélèrent le développement du Tempest. Gouvernance, technologies, coûts : les clés d’un projet qui veut faire décoller le chasseur du futur.</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-08-09 04:30</t>
+        </is>
+      </c>
+      <c r="D548" s="3" t="inlineStr">
+        <is>
+          <t>Vers un monde à +2 °C ? Les 30 données de l’été du basculement écologique</t>
+        </is>
+      </c>
+      <c r="E548" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/09/vers-un-monde-a-2-c-les-30-donnees-de-lete-du-basculement-ecologique/</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Des records absolus de température sur terre et en mer, des forêts en feu, des fleuves à sec, une surmortalité importante, et un seuil de + 2 °C qui pourrait être franchi pour la première fois dès le début de l'année 2027. L’article Vers un monde à +2 °C&amp;#160;? Les 30 données de l’été du basculement écologique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-08-09 04:00</t>
+        </is>
+      </c>
+      <c r="D549" s="3" t="inlineStr">
+        <is>
+          <t>Tucker Carlson : « Il est temps de sauver l’Amérique » (discours intégral)</t>
+        </is>
+      </c>
+      <c r="E549" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/09/tucker-carlson-il-est-temps-de-sauver-lamerique-discours-integral/</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>L’ancienne star de Fox News veut donner une doctrine à l’après-Trump L’article Tucker Carlson&amp;#160;: «&amp;#160;Il est temps de sauver l’Amérique&amp;#160;» (discours intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:04</t>
+        </is>
+      </c>
+      <c r="D550" s="3" t="inlineStr">
+        <is>
+          <t>Une entreprise pétrolière proche de Trump se prépare à forer le Groenland sans autorisation</t>
+        </is>
+      </c>
+      <c r="E550" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/08/groenland-energy-trump/</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Un fait accompli inédit place de nouveau Nuuk face aux menaces d’annexion territoriale de Washington. L’article Une entreprise pétrolière proche de Trump se prépare à forer le Groenland sans autorisation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-08-08 13:08</t>
+        </is>
+      </c>
+      <c r="D551" s="3" t="inlineStr">
+        <is>
+          <t>Faut-il avoir peur des virus conçus par l’IA ?</t>
+        </is>
+      </c>
+      <c r="E551" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/08/des-genomes-entiers-de-virus-crees-par-lia-danger-ou-opportunite/</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Cette percée scientifique pourrait transformer la lutte contre l’antibiorésistance, en ouvrant une nouvelle frontière pour la biosécurité. L’article Faut-il avoir peur des virus conçus par l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-08-08 05:39</t>
+        </is>
+      </c>
+      <c r="D552" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : les drones ukrainiens font flamber l’exportation de brut</t>
+        </is>
+      </c>
+      <c r="E552" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/08/economie-russe-les-drones-ukrainiens-font-flamber-lexportation-de-brut/</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Un paradoxe qui cache une mauvaise nouvelle pour le régime de Vladimir Poutine. L’article Économie russe&amp;#160;: les drones ukrainiens font flamber l’exportation de brut est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:35</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-08-08 04:00</t>
+        </is>
+      </c>
+      <c r="D553" s="3" t="inlineStr">
+        <is>
+          <t>Varsovie sous Varsovie</t>
+        </is>
+      </c>
+      <c r="E553" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/08/varsovie-sous-varsovie/</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>L’historienne de la littérature et directrice d’études à l’EHESS piste les traces d’un monde qui rayonne et qui saigne. L’article Varsovie sous Varsovie est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18348,6 +18641,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E542" r:id="rId541"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E543" r:id="rId542"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E553" r:id="rId552"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G553"/>
+  <dimension ref="A1:G556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17830,7 +17830,6 @@
           <t>Pendant des siècles, les astronomes impériaux chinois ont tenté de prédire les éclipses, dont dépendait la légitimité de l’empereur. L’arrivée des jésuites et de leurs méthodes mathématiques européennes allait révolutionner cette science.</t>
         </is>
       </c>
-      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -17863,7 +17862,6 @@
           <t>À travers une série de projets de data centers, le Maroc cherche à prendre une longueur d’avance sur ses voisins dans le secteur du numérique.</t>
         </is>
       </c>
-      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -17896,7 +17894,6 @@
           <t>Après l’échec du programme franco-germano-espagnol, le Royaume-Uni, l’Italie et le Japon accélèrent le développement du Tempest. Gouvernance, technologies, coûts : les clés d’un projet qui veut faire décoller le chasseur du futur.</t>
         </is>
       </c>
-      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -17929,7 +17926,6 @@
           <t>Des records absolus de température sur terre et en mer, des forêts en feu, des fleuves à sec, une surmortalité importante, et un seuil de + 2 °C qui pourrait être franchi pour la première fois dès le début de l'année 2027. L’article Vers un monde à +2 °C&amp;#160;? Les 30 données de l’été du basculement écologique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -17962,7 +17958,6 @@
           <t>L’ancienne star de Fox News veut donner une doctrine à l’après-Trump L’article Tucker Carlson&amp;#160;: «&amp;#160;Il est temps de sauver l’Amérique&amp;#160;» (discours intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -17995,7 +17990,6 @@
           <t>Un fait accompli inédit place de nouveau Nuuk face aux menaces d’annexion territoriale de Washington. L’article Une entreprise pétrolière proche de Trump se prépare à forer le Groenland sans autorisation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -18028,7 +18022,6 @@
           <t>Cette percée scientifique pourrait transformer la lutte contre l’antibiorésistance, en ouvrant une nouvelle frontière pour la biosécurité. L’article Faut-il avoir peur des virus conçus par l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -18061,7 +18054,6 @@
           <t>Un paradoxe qui cache une mauvaise nouvelle pour le régime de Vladimir Poutine. L’article Économie russe&amp;#160;: les drones ukrainiens font flamber l’exportation de brut est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -18094,7 +18086,105 @@
           <t>L’historienne de la littérature et directrice d’études à l’EHESS piste les traces d’un monde qui rayonne et qui saigne. L’article Varsovie sous Varsovie est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:12</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-08-10 04:30</t>
+        </is>
+      </c>
+      <c r="D554" s="3" t="inlineStr">
+        <is>
+          <t>La France et l’Europe deviendront-elles inassurables ?</t>
+        </is>
+      </c>
+      <c r="E554" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/10/la-france-et-leurope-deviendront-elles-inassurables/</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Les événements climatiques extrêmes, désormais récurrents et dont l'impact est croissant d'année en année, posent une question cruciale aux banques et aux assurances. L’article La France et l’Europe deviendront-elles inassurables&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:12</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-08-10 04:00</t>
+        </is>
+      </c>
+      <c r="D555" s="3" t="inlineStr">
+        <is>
+          <t>Et si la vraie révolution technologique n’était pas l’IA ?</t>
+        </is>
+      </c>
+      <c r="E555" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/10/la-vraie-revolution-technologique/</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>La course aux modèles pourrait masquer une transformation plus décisive de l’économie mondiale&amp;#160;: l’énergie verte. L’article Et si la vraie révolution technologique n’était pas l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:12</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-08-09 17:46</t>
+        </is>
+      </c>
+      <c r="D556" s="3" t="inlineStr">
+        <is>
+          <t>L’État profond</t>
+        </is>
+      </c>
+      <c r="E556" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/09/letat-profond/</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Comment la notion turque de derin devlet est devenue l'arme virale de nos années Vingt&amp;#160;? L’article L’État profond est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18650,6 +18740,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E551" r:id="rId550"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E552" r:id="rId551"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E556" r:id="rId555"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G556"/>
+  <dimension ref="A1:G564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18118,7 +18118,6 @@
           <t>Les événements climatiques extrêmes, désormais récurrents et dont l'impact est croissant d'année en année, posent une question cruciale aux banques et aux assurances. L’article La France et l’Europe deviendront-elles inassurables&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -18151,7 +18150,6 @@
           <t>La course aux modèles pourrait masquer une transformation plus décisive de l’économie mondiale&amp;#160;: l’énergie verte. L’article Et si la vraie révolution technologique n’était pas l’IA&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -18184,7 +18182,270 @@
           <t>Comment la notion turque de derin devlet est devenue l'arme virale de nos années Vingt&amp;#160;? L’article L’État profond est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:40</t>
+        </is>
+      </c>
+      <c r="D557" s="3" t="inlineStr">
+        <is>
+          <t>Que signifiaient les éclipses dans la Rome antique ?</t>
+        </is>
+      </c>
+      <c r="E557" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/que-signifiaient-les-eclipses-dans-la-rome-antique-289411</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Les Romains savaient déjà expliquer les éclipses, mais ils y voyaient des signes divins et les considéraient comme des présages. Science, religion et politique cohabitaient alors sous un même ciel.</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:24</t>
+        </is>
+      </c>
+      <c r="D558" s="3" t="inlineStr">
+        <is>
+          <t>Avant la haute couture : 400 000 ans d’histoire de la mode</t>
+        </is>
+      </c>
+      <c r="E558" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/avant-la-haute-couture-400-000-ans-dhistoire-de-la-mode-287399</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Bien avant la fast-fashion, les humains utilisaient déjà leur apparence pour communiquer. L’archéologie révèle l’origine sociale de la mode.</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:22</t>
+        </is>
+      </c>
+      <c r="D559" s="3" t="inlineStr">
+        <is>
+          <t>Informer sur les catastrophes à l’époque du Japon féodal : le rôle des « kawaraban »</t>
+        </is>
+      </c>
+      <c r="E559" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/informer-sur-les-catastrophes-a-lepoque-du-japon-feodal-le-role-des-kawaraban-288955</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Au Japon, le duo information et divertissement n’a pas attendu l’arrivée des journaux modernes. Les «&amp;nbsp;kawaraban&amp;nbsp;» ont longtemps permis de couvrir toutes sortes d’actualités et de divertir malgré la censure.</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:21</t>
+        </is>
+      </c>
+      <c r="D560" s="3" t="inlineStr">
+        <is>
+          <t>Faut-il s’inquiéter de la « starlinkisation » de l’accès à Internet en Afrique ?</t>
+        </is>
+      </c>
+      <c r="E560" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/faut-il-sinquieter-de-la-starlinkisation-de-lacces-a-internet-en-afrique-287464</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Si Starlink séduit nombre d’États africains confrontés aux déserts numériques, son implantation suscite également la méfiance face au risque de dépendance accrue à des opérateurs étrangers.</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:34</t>
+        </is>
+      </c>
+      <c r="D561" s="3" t="inlineStr">
+        <is>
+          <t>Le Pakistan a trouvé le mode d’emploi du clan Trump</t>
+        </is>
+      </c>
+      <c r="E561" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/11/le-pakistan-a-trouve-le-mode-demploi-du-clan-trump/</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Le maréchal Asim Munir et les autorités d’Islamabad ont parfaitement compris comment exploiter les obsessions de la Maison-Blanche. L’article Le Pakistan a trouvé le mode d’emploi du clan Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:30</t>
+        </is>
+      </c>
+      <c r="D562" s="3" t="inlineStr">
+        <is>
+          <t>La course à l’IA a un problème structurel</t>
+        </is>
+      </c>
+      <c r="E562" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/11/la-course-a-lia-a-un-probleme-structurel/</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>L'investissement dans l'IA a déjà dépassé, en trois ans, tous les grands booms depuis le XIXe siècle. L’article La course à l&amp;rsquo;IA a un problème structurel est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:27</t>
+        </is>
+      </c>
+      <c r="D563" s="3" t="inlineStr">
+        <is>
+          <t>L’Iran affirme qu’il ne négociera pas avec les États-Unis tant que Donald Trump sera président</t>
+        </is>
+      </c>
+      <c r="E563" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/10/liran-affirme-quil-ne-negociera-pas-avec-les-etats-unis-tant-que-donald-trump-sera-president/</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>La stratégie iranienne devient explicite&amp;#160;: «&amp;#160;La victoire n’est ni le combat, ni un accord, mais la gestion d’un processus qui n’est ni la guerre, ni la paix.&amp;#160;» L’article L’Iran affirme qu&amp;rsquo;il ne négociera pas avec les États-Unis tant que Donald Trump sera président est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:56</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:30</t>
+        </is>
+      </c>
+      <c r="D564" s="3" t="inlineStr">
+        <is>
+          <t>Écofascisme</t>
+        </is>
+      </c>
+      <c r="E564" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/10/ecofascisme/</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Utilisée par un pionnier de l’écologie politique, cette notion est devenue une catégorie clef et ambiguë du tournant vert des extrêmes droites. L’article Écofascisme est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18743,6 +19004,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E554" r:id="rId553"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E555" r:id="rId554"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E564" r:id="rId563"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G564"/>
+  <dimension ref="A1:G572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18214,7 +18214,6 @@
           <t>Les Romains savaient déjà expliquer les éclipses, mais ils y voyaient des signes divins et les considéraient comme des présages. Science, religion et politique cohabitaient alors sous un même ciel.</t>
         </is>
       </c>
-      <c r="G557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -18247,7 +18246,6 @@
           <t>Bien avant la fast-fashion, les humains utilisaient déjà leur apparence pour communiquer. L’archéologie révèle l’origine sociale de la mode.</t>
         </is>
       </c>
-      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -18280,7 +18278,6 @@
           <t>Au Japon, le duo information et divertissement n’a pas attendu l’arrivée des journaux modernes. Les «&amp;nbsp;kawaraban&amp;nbsp;» ont longtemps permis de couvrir toutes sortes d’actualités et de divertir malgré la censure.</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -18313,7 +18310,6 @@
           <t>Si Starlink séduit nombre d’États africains confrontés aux déserts numériques, son implantation suscite également la méfiance face au risque de dépendance accrue à des opérateurs étrangers.</t>
         </is>
       </c>
-      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -18346,7 +18342,6 @@
           <t>Le maréchal Asim Munir et les autorités d’Islamabad ont parfaitement compris comment exploiter les obsessions de la Maison-Blanche. L’article Le Pakistan a trouvé le mode d’emploi du clan Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -18379,7 +18374,6 @@
           <t>L'investissement dans l'IA a déjà dépassé, en trois ans, tous les grands booms depuis le XIXe siècle. L’article La course à l&amp;rsquo;IA a un problème structurel est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -18412,7 +18406,6 @@
           <t>La stratégie iranienne devient explicite&amp;#160;: «&amp;#160;La victoire n’est ni le combat, ni un accord, mais la gestion d’un processus qui n’est ni la guerre, ni la paix.&amp;#160;» L’article L’Iran affirme qu&amp;rsquo;il ne négociera pas avec les États-Unis tant que Donald Trump sera président est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -18445,7 +18438,270 @@
           <t>Utilisée par un pionnier de l’écologie politique, cette notion est devenue une catégorie clef et ambiguë du tournant vert des extrêmes droites. L’article Écofascisme est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:28</t>
+        </is>
+      </c>
+      <c r="D565" s="3" t="inlineStr">
+        <is>
+          <t>Durant la Renaissance, le retour des papes à Rome créa une ère de construction de palais sans précédent pour la « Ville éternelle »</t>
+        </is>
+      </c>
+      <c r="E565" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/durant-la-renaissance-le-retour-des-papes-a-rome-crea-une-ere-de-construction-de-palais-sans-precedent-pour-la-ville-eternelle-268262</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Près de 31&amp;nbsp;% des palais de Rome furent construits entre 1378 et 1599, après un siècle de stagnation économique. Comment expliquer un tel phénomène urbanistique&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:35</t>
+        </is>
+      </c>
+      <c r="D566" s="3" t="inlineStr">
+        <is>
+          <t>L’administration Trump veut sanctionner ceux qui jugent : un aveu de la force du droit international</t>
+        </is>
+      </c>
+      <c r="E566" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ladministration-trump-veut-sanctionner-ceux-qui-jugent-un-aveu-de-la-force-du-droit-international-288756</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>La volonté de Washington de «&amp;nbsp;démanteler&amp;nbsp;» la Cour pénale internationale masque aussi la crainte du pouvoir des mots du droit dans le temps.</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-08-12 05:52</t>
+        </is>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>Pour un changement de régime à la FIFA</t>
+        </is>
+      </c>
+      <c r="E567" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/12/pour-un-changement-de-regime-a-la-fifa/</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Trump et Infantino veulent s’accaparer le sport le plus populaire au monde. L’Union peut encore les en empêcher. L’article Pour un changement de régime à la FIFA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-08-12 04:30</t>
+        </is>
+      </c>
+      <c r="D568" s="3" t="inlineStr">
+        <is>
+          <t>Où en Europe a-t-on le plus de chance d’observer une éclipse solaire totale au cours de sa vie ? [Carte exclusive]</t>
+        </is>
+      </c>
+      <c r="E568" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/12/ou-en-europe-a-t-on-le-plus-de-chance-dobserver-une-eclipse-solaire-totale-au-cours-de-sa-vie-carte-exclusive/</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Selon des données de la NASA analysées par la revue, la probabilité de vivre une éclipse totale de son vivant varie entre 0 et 61&amp;#160;%. L’article Où en Europe a-t-on le plus de chance d’observer une éclipse solaire totale au cours de sa vie&amp;#160;? [Carte exclusive] est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:23</t>
+        </is>
+      </c>
+      <c r="D569" s="3" t="inlineStr">
+        <is>
+          <t>En un an et demi, Trump a créé 17 fois moins d’emplois que Joe Biden</t>
+        </is>
+      </c>
+      <c r="E569" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/11/en-un-an-et-demi-trump-a-cree-17-fois-moins-demplois-que-joe-biden/</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>En avril et en mai, l’inflation a augmenté plus vite que les salaires pour la première fois depuis mai 2023. L’article En un an et demi, Trump a créé 17 fois moins d’emplois que Joe Biden est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:00</t>
+        </is>
+      </c>
+      <c r="D570" s="3" t="inlineStr">
+        <is>
+          <t>Globalisme</t>
+        </is>
+      </c>
+      <c r="E570" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/11/globalisme/</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>De l’Amérique isolationniste à Donald Trump, itinéraire du mot-valise devenu la clef de voûte des récits antimondialistes des extrêmes droites. L’article Globalisme est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-08-11 13:00</t>
+        </is>
+      </c>
+      <c r="D571" s="3" t="inlineStr">
+        <is>
+          <t>L’île de Ré, côté marais</t>
+        </is>
+      </c>
+      <c r="E571" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/11/lile-de-re-cote-marais/</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Un portrait personnel d'un Ré plus intime. L’article L’île de Ré, côté marais est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 09:58</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-08-11 11:49</t>
+        </is>
+      </c>
+      <c r="D572" s="3" t="inlineStr">
+        <is>
+          <t>Pour reconnaître les textes écrits par l’IA, Claude laissera une trace invisible</t>
+        </is>
+      </c>
+      <c r="E572" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/11/pour-reconnaitre-les-textes-ecrits-par-lia-claude-laissera-une-trace-invisible/</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>La première application concrète de l’AI Act pourrait transformer radicalement les usages des LLM et avoir des effets géopolitiques profonds. L’article Pour reconnaître les textes écrits par l’IA, Claude laissera une trace invisible est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19012,6 +19268,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E562" r:id="rId561"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E563" r:id="rId562"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E572" r:id="rId571"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G572"/>
+  <dimension ref="A1:G578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18470,7 +18470,6 @@
           <t>Près de 31&amp;nbsp;% des palais de Rome furent construits entre 1378 et 1599, après un siècle de stagnation économique. Comment expliquer un tel phénomène urbanistique&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -18503,7 +18502,6 @@
           <t>La volonté de Washington de «&amp;nbsp;démanteler&amp;nbsp;» la Cour pénale internationale masque aussi la crainte du pouvoir des mots du droit dans le temps.</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -18536,7 +18534,6 @@
           <t>Trump et Infantino veulent s’accaparer le sport le plus populaire au monde. L’Union peut encore les en empêcher. L’article Pour un changement de régime à la FIFA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -18569,7 +18566,6 @@
           <t>Selon des données de la NASA analysées par la revue, la probabilité de vivre une éclipse totale de son vivant varie entre 0 et 61&amp;#160;%. L’article Où en Europe a-t-on le plus de chance d’observer une éclipse solaire totale au cours de sa vie&amp;#160;? [Carte exclusive] est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -18602,7 +18598,6 @@
           <t>En avril et en mai, l’inflation a augmenté plus vite que les salaires pour la première fois depuis mai 2023. L’article En un an et demi, Trump a créé 17 fois moins d’emplois que Joe Biden est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -18635,7 +18630,6 @@
           <t>De l’Amérique isolationniste à Donald Trump, itinéraire du mot-valise devenu la clef de voûte des récits antimondialistes des extrêmes droites. L’article Globalisme est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -18668,7 +18662,6 @@
           <t>Un portrait personnel d'un Ré plus intime. L’article L’île de Ré, côté marais est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -18701,7 +18694,204 @@
           <t>La première application concrète de l’AI Act pourrait transformer radicalement les usages des LLM et avoir des effets géopolitiques profonds. L’article Pour reconnaître les textes écrits par l’IA, Claude laissera une trace invisible est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:35</t>
+        </is>
+      </c>
+      <c r="D573" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la nouvelle « Petite Maison dans la prairie » est déjà une série politique</t>
+        </is>
+      </c>
+      <c r="E573" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-la-nouvelle-petite-maison-dans-la-prairie-est-deja-une-serie-politique-287645</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Depuis près d’un siècle, «&amp;nbsp;la Petite Maison dans la prairie&amp;nbsp;» façonne l’imaginaire de la conquête de l’Ouest. La version de Netflix ravive les débats sur le racisme, le récit national et la mémoire de la colonisation aux États-Unis.</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:34</t>
+        </is>
+      </c>
+      <c r="D574" s="3" t="inlineStr">
+        <is>
+          <t>Charles de Gaulle, héros de la France libre : une représentation qui a évolué dans la mémoire nationale ?</t>
+        </is>
+      </c>
+      <c r="E574" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/charles-de-gaulle-heros-de-la-france-libre-une-representation-qui-a-evolue-dans-la-memoire-nationale-287031</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Lorsque la France commémore entre juin et août les débarquements de 1944, ainsi que la libération progressive du territoire national, la figure du général de Gaulle n’est jamais loin.</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:27</t>
+        </is>
+      </c>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi nous n’avons pas encore bien compris l’AI Act</t>
+        </is>
+      </c>
+      <c r="E575" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/13/pourquoi-nous-navons-pas-encore-bien-compris-lai-act/</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Et pourquoi l’obligation de marquage n’est vraiment pas le sujet. L’article Pourquoi nous n’avons pas encore bien compris l’AI Act est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2026-08-13 04:30</t>
+        </is>
+      </c>
+      <c r="D576" s="3" t="inlineStr">
+        <is>
+          <t>En Ukraine et en Russie, la multiplication des attaques aériennes alourdit le bilan civil</t>
+        </is>
+      </c>
+      <c r="E576" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/13/en-ukraine-et-en-russie-la-multiplication-des-attaques-aeriennes-alourdit-le-bilan-civil/</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Malgré une ligne de front gelée, le nombre de victimes civiles continue d’augmenter. L’article En Ukraine et en Russie, la multiplication des attaques aériennes alourdit le bilan civil est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-08-12 15:55</t>
+        </is>
+      </c>
+      <c r="D577" s="3" t="inlineStr">
+        <is>
+          <t>Le Japon comme méthode</t>
+        </is>
+      </c>
+      <c r="E577" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/12/le-japon-comme-methode/</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>À Kyoto, le professeur de littératures comparées du Collège de France a découvert une nouvelle manière de lire le grand livre du monde. L’article Le Japon comme méthode est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2026-08-12 11:58</t>
+        </is>
+      </c>
+      <c r="D578" s="3" t="inlineStr">
+        <is>
+          <t>La Russie a représenté 100 % des importations de GNL de la Belgique en juillet</t>
+        </is>
+      </c>
+      <c r="E578" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/12/la-russie-a-represente-100-des-importations-de-gnl-de-la-belgique-en-juillet/</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Les volumes d’importations européennes de GNL russe ont augmenté de 16&amp;#160;% au premier semestre par rapport à 2025. L’article La Russie a représenté 100&amp;#160;% des importations de GNL de la Belgique en juillet est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19276,6 +19466,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E570" r:id="rId569"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E571" r:id="rId570"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E578" r:id="rId577"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G578"/>
+  <dimension ref="A1:G583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18726,7 +18726,6 @@
           <t>Depuis près d’un siècle, «&amp;nbsp;la Petite Maison dans la prairie&amp;nbsp;» façonne l’imaginaire de la conquête de l’Ouest. La version de Netflix ravive les débats sur le racisme, le récit national et la mémoire de la colonisation aux États-Unis.</t>
         </is>
       </c>
-      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -18759,7 +18758,6 @@
           <t>Lorsque la France commémore entre juin et août les débarquements de 1944, ainsi que la libération progressive du territoire national, la figure du général de Gaulle n’est jamais loin.</t>
         </is>
       </c>
-      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -18792,7 +18790,6 @@
           <t>Et pourquoi l’obligation de marquage n’est vraiment pas le sujet. L’article Pourquoi nous n’avons pas encore bien compris l’AI Act est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -18825,7 +18822,6 @@
           <t>Malgré une ligne de front gelée, le nombre de victimes civiles continue d’augmenter. L’article En Ukraine et en Russie, la multiplication des attaques aériennes alourdit le bilan civil est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -18858,7 +18854,6 @@
           <t>À Kyoto, le professeur de littératures comparées du Collège de France a découvert une nouvelle manière de lire le grand livre du monde. L’article Le Japon comme méthode est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -18891,7 +18886,171 @@
           <t>Les volumes d’importations européennes de GNL russe ont augmenté de 16&amp;#160;% au premier semestre par rapport à 2025. L’article La Russie a représenté 100&amp;#160;% des importations de GNL de la Belgique en juillet est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:56</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:17</t>
+        </is>
+      </c>
+      <c r="D579" s="3" t="inlineStr">
+        <is>
+          <t>L’histoire méconnue de la Vierge Marie, sainte patronne des États-Unis</t>
+        </is>
+      </c>
+      <c r="E579" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lhistoire-meconnue-de-la-vierge-marie-sainte-patronne-des-etats-unis-284472</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Pourquoi la Vierge Marie est-elle la patronne des États-Unis&amp;nbsp;? Cette tradition, née au XIXᵉ&amp;nbsp;siècle, révèle comment les catholiques américains ont cherché à concilier leur foi, leur patriotisme et leur place dans une société longtemps méfiante à leur égard.</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:56</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:00</t>
+        </is>
+      </c>
+      <c r="D580" s="3" t="inlineStr">
+        <is>
+          <t>Grand Remplacement</t>
+        </is>
+      </c>
+      <c r="E580" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/14/grand-remplacement/</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>De la prose de Renaud Camus aux organigrammes de l’État trumpiste, une fantasmagorie démographique est devenue en quinze ans une politique publique. L’article Grand Remplacement est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:56</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-08-14 04:30</t>
+        </is>
+      </c>
+      <c r="D581" s="3" t="inlineStr">
+        <is>
+          <t>Comment Taïwan se prépare à une invasion chinoise</t>
+        </is>
+      </c>
+      <c r="E581" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/14/comment-taiwan-se-prepare-a-une-invasion-chinoise/</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Décapitation du pouvoir, blocus naval, brouillage des communications et guerre urbaine figurent parmi les scénarios auxquels Taipei se prépare. L’article Comment Taïwan se prépare à une invasion chinoise est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:56</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:00</t>
+        </is>
+      </c>
+      <c r="D582" s="3" t="inlineStr">
+        <is>
+          <t>Où faut-il aller pour aimer l’Allemagne ?</t>
+        </is>
+      </c>
+      <c r="E582" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/13/ou-faut-il-aller-pour-aimer-lallemagne/</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>La philosophe et helléniste raconte son attachement à une nation condamnée à se méfier d’elle-même. L’article Où faut-il aller pour aimer l’Allemagne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:56</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:34</t>
+        </is>
+      </c>
+      <c r="D583" s="3" t="inlineStr">
+        <is>
+          <t>L’administration Trump a-t-elle recours à des corsaires au large de l’Amérique latine ?</t>
+        </is>
+      </c>
+      <c r="E583" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/13/administration-trump-a-t-elle-recours-a-des-corsaires-au-large-de-lamerique-latine/</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>L’administration américaine pourrait avoir autorisé l’émission de lettres de marque afin de permettre à des mercenaires de détruire des embarcations. L’article L’administration Trump a-t-elle recours à des corsaires au large de l’Amérique latine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19472,6 +19631,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E576" r:id="rId575"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E577" r:id="rId576"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E583" r:id="rId582"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G583"/>
+  <dimension ref="A1:G589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18918,7 +18918,6 @@
           <t>Pourquoi la Vierge Marie est-elle la patronne des États-Unis&amp;nbsp;? Cette tradition, née au XIXᵉ&amp;nbsp;siècle, révèle comment les catholiques américains ont cherché à concilier leur foi, leur patriotisme et leur place dans une société longtemps méfiante à leur égard.</t>
         </is>
       </c>
-      <c r="G579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -18951,7 +18950,6 @@
           <t>De la prose de Renaud Camus aux organigrammes de l’État trumpiste, une fantasmagorie démographique est devenue en quinze ans une politique publique. L’article Grand Remplacement est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -18984,7 +18982,6 @@
           <t>Décapitation du pouvoir, blocus naval, brouillage des communications et guerre urbaine figurent parmi les scénarios auxquels Taipei se prépare. L’article Comment Taïwan se prépare à une invasion chinoise est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -19017,7 +19014,6 @@
           <t>La philosophe et helléniste raconte son attachement à une nation condamnée à se méfier d’elle-même. L’article Où faut-il aller pour aimer l’Allemagne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
@@ -19050,7 +19046,204 @@
           <t>L’administration américaine pourrait avoir autorisé l’émission de lettres de marque afin de permettre à des mercenaires de détruire des embarcations. L’article L’administration Trump a-t-elle recours à des corsaires au large de l’Amérique latine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:21</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2026-08-15 05:34</t>
+        </is>
+      </c>
+      <c r="D584" s="3" t="inlineStr">
+        <is>
+          <t>Lanceurs d’alerte en exil : pourquoi les business schools ont une responsabilité à assumer</t>
+        </is>
+      </c>
+      <c r="E584" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lanceurs-dalerte-en-exil-pourquoi-les-business-schools-ont-une-responsabilite-a-assumer-284740</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Et si les business schools recrutaient des lanceurs d’alerte pour exposer les comportements non autorisés des entreprises. Un savoir pratique qui aurait sa place dans les cursus des futurs managers.</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:21</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:13</t>
+        </is>
+      </c>
+      <c r="D585" s="3" t="inlineStr">
+        <is>
+          <t>À la tête de l’ONU, l’heure d’une femme a-t-elle enfin sonné ?</t>
+        </is>
+      </c>
+      <c r="E585" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/a-la-tete-de-lonu-lheure-dune-femme-a-t-elle-enfin-sonne-288666</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>ONU cherche patron… ou patronne. Cette fois, une femme latino-américaine pourrait prendre la tête de l’institution. Réponse en décembre.</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:21</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-08-15 05:00</t>
+        </is>
+      </c>
+      <c r="D586" s="3" t="inlineStr">
+        <is>
+          <t>Combien de temps l’économie iranienne pourra-t-elle tenir ?</t>
+        </is>
+      </c>
+      <c r="E586" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/15/combien-de-temps-leconomie-iranienne-pourra-t-elle-tenir/</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Le blocus maritime imposé par Washington coûterait près de 380 millions d’euros par jour à Téhéran. L’article Combien de temps l&amp;rsquo;économie iranienne pourra-t-elle tenir&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:21</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-08-15 04:00</t>
+        </is>
+      </c>
+      <c r="D587" s="3" t="inlineStr">
+        <is>
+          <t>Heidegger aux îles Caïmans</t>
+        </is>
+      </c>
+      <c r="E587" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/15/heidegger-aux-iles-caimans/</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Pour comprendre la géopolitique de l’offshore, il faut penser un espace qui se dérobe. L’article Heidegger aux îles Caïmans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:21</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:53</t>
+        </is>
+      </c>
+      <c r="D588" s="3" t="inlineStr">
+        <is>
+          <t>L’administration Trump a soumis les membres de l’OTAN à un test de loyauté idéologique</t>
+        </is>
+      </c>
+      <c r="E588" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/14/ladministration-trump-a-soumis-les-membres-de-lotan-a-un-test-de-loyaute-ideologique/</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>La Maison-Blanche vise à conditionner sa protection militaire à des preuves explicites de vassalisation. L’article L’administration Trump a soumis les membres de l’OTAN à un test de loyauté idéologique est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:21</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:44</t>
+        </is>
+      </c>
+      <c r="D589" s="3" t="inlineStr">
+        <is>
+          <t>Poutine ouvre-t-il un front dans le Pacifique ?</t>
+        </is>
+      </c>
+      <c r="E589" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/14/poutine-ouvre-t-il-un-front-dans-le-pacifique/</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>La nouvelle agressivité du Kremlin contre le Japon ressemble moins à un pivot asiatique qu’à une diversion russe. L’article Poutine ouvre-t-il un front dans le Pacifique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19636,6 +19829,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E581" r:id="rId580"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E582" r:id="rId581"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E589" r:id="rId588"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G589"/>
+  <dimension ref="A1:G592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19078,7 +19078,6 @@
           <t>Et si les business schools recrutaient des lanceurs d’alerte pour exposer les comportements non autorisés des entreprises. Un savoir pratique qui aurait sa place dans les cursus des futurs managers.</t>
         </is>
       </c>
-      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -19111,7 +19110,6 @@
           <t>ONU cherche patron… ou patronne. Cette fois, une femme latino-américaine pourrait prendre la tête de l’institution. Réponse en décembre.</t>
         </is>
       </c>
-      <c r="G585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -19144,7 +19142,6 @@
           <t>Le blocus maritime imposé par Washington coûterait près de 380 millions d’euros par jour à Téhéran. L’article Combien de temps l&amp;rsquo;économie iranienne pourra-t-elle tenir&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -19177,7 +19174,6 @@
           <t>Pour comprendre la géopolitique de l’offshore, il faut penser un espace qui se dérobe. L’article Heidegger aux îles Caïmans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -19210,7 +19206,6 @@
           <t>La Maison-Blanche vise à conditionner sa protection militaire à des preuves explicites de vassalisation. L’article L’administration Trump a soumis les membres de l’OTAN à un test de loyauté idéologique est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -19243,7 +19238,105 @@
           <t>La nouvelle agressivité du Kremlin contre le Japon ressemble moins à un pivot asiatique qu’à une diversion russe. L’article Poutine ouvre-t-il un front dans le Pacifique&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 09:23</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:00</t>
+        </is>
+      </c>
+      <c r="D590" s="3" t="inlineStr">
+        <is>
+          <t>Trump peut-il faire basculer la campagne au Brésil ?</t>
+        </is>
+      </c>
+      <c r="E590" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/16/trump-peut-il-faire-basculer-la-campagne-au-bresil/</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Pour l'heure, les tarifs douaniers et les menaces de la Maison-Blanche semblent renforcer la campagne de Lula plutôt que de la fragiliser. L’article Trump peut-il faire basculer la campagne au Brésil&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 09:23</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2026-08-16 04:00</t>
+        </is>
+      </c>
+      <c r="D591" s="3" t="inlineStr">
+        <is>
+          <t>Vers l’Est, à Timișoara</t>
+        </is>
+      </c>
+      <c r="E591" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/16/timisoara-enigme-sentimentale/</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Pourquoi les pastèques du Banat poussent plus haut que les murs des empires&amp;#160;? L’article Vers l&amp;rsquo;Est, à Timișoara est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 09:23</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:00</t>
+        </is>
+      </c>
+      <c r="D592" s="3" t="inlineStr">
+        <is>
+          <t>La route au bord du monde</t>
+        </is>
+      </c>
+      <c r="E592" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/15/la-route-au-bord-du-monde/</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Sur la Highway 1 avec l’écrivain et éditeur français. L’article La route au bord du monde est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19835,6 +19928,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E587" r:id="rId586"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E588" r:id="rId587"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E592" r:id="rId591"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:G595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19270,7 +19270,6 @@
           <t>Pour l'heure, les tarifs douaniers et les menaces de la Maison-Blanche semblent renforcer la campagne de Lula plutôt que de la fragiliser. L’article Trump peut-il faire basculer la campagne au Brésil&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
@@ -19303,7 +19302,6 @@
           <t>Pourquoi les pastèques du Banat poussent plus haut que les murs des empires&amp;#160;? L’article Vers l&amp;rsquo;Est, à Timișoara est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -19336,7 +19334,105 @@
           <t>Sur la Highway 1 avec l’écrivain et éditeur français. L’article La route au bord du monde est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:36</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:00</t>
+        </is>
+      </c>
+      <c r="D593" s="3" t="inlineStr">
+        <is>
+          <t>26 livres à lire en septembre 2026</t>
+        </is>
+      </c>
+      <c r="E593" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/17/26-livres-a-lire-en-septembre-2026/</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>26 essais et ouvrages de non-fiction choisis parmi les parutions de toute l’Europe. L’article 26 livres à lire en septembre 2026 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:36</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-08-17 06:13</t>
+        </is>
+      </c>
+      <c r="D594" s="3" t="inlineStr">
+        <is>
+          <t>Donald Trump a ordonné de réduire drastiquement l’exercice militaire conjoint annuel avec la Corée du Sud</t>
+        </is>
+      </c>
+      <c r="E594" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/17/donald-trump-a-ordonne-de-reduire-drastiquement-lexercice-militaire-conjoint-annuel-avec-la-coree-du-sud/</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Cette annonce intervient alors que les États-Unis ne disposent plus de porte-avions dans le Pacifique. L’article Donald Trump a ordonné de réduire drastiquement l’exercice militaire conjoint annuel avec la Corée du Sud est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:36</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-08-16 16:00</t>
+        </is>
+      </c>
+      <c r="D595" s="3" t="inlineStr">
+        <is>
+          <t>L’exorcisme du pouvoir</t>
+        </is>
+      </c>
+      <c r="E595" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/16/exorcisme-du-pouvoir/</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Si tout le monde est d’accord avec Léon XIV, pourquoi Trump gagne-t-il les élections&amp;#160;? L’article L&amp;rsquo;exorcisme du pouvoir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19931,6 +20027,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E590" r:id="rId589"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E591" r:id="rId590"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E595" r:id="rId594"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G595"/>
+  <dimension ref="A1:G600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19366,7 +19366,6 @@
           <t>26 essais et ouvrages de non-fiction choisis parmi les parutions de toute l’Europe. L’article 26 livres à lire en septembre 2026 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -19399,7 +19398,6 @@
           <t>Cette annonce intervient alors que les États-Unis ne disposent plus de porte-avions dans le Pacifique. L’article Donald Trump a ordonné de réduire drastiquement l’exercice militaire conjoint annuel avec la Corée du Sud est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -19432,7 +19430,171 @@
           <t>Si tout le monde est d’accord avec Léon XIV, pourquoi Trump gagne-t-il les élections&amp;#160;? L’article L&amp;rsquo;exorcisme du pouvoir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:28</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2026-08-18 08:37</t>
+        </is>
+      </c>
+      <c r="D596" s="3" t="inlineStr">
+        <is>
+          <t>Allocation de rentrée scolaire : ce que les familles modestes font de cet argent</t>
+        </is>
+      </c>
+      <c r="E596" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/allocation-de-rentree-scolaire-ce-que-les-familles-modestes-font-de-cet-argent-289931</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Près de trois millions de familles modestes recevront l’allocation de rentrée scolaire (ARS). Que feront-elles de cet argent&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:28</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2026-08-18 04:30</t>
+        </is>
+      </c>
+      <c r="D597" s="3" t="inlineStr">
+        <is>
+          <t>La Russie construit des rampes de lancement de drones à portée des pays de l’OTAN</t>
+        </is>
+      </c>
+      <c r="E597" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/18/la-russie-construit-des-rampes-de-lancement-de-drones-a-portee-des-pays-de-lotan-2/</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Les territoires de 11 pays membres de l’OTAN seraient à portée de ces nouveaux sites. L’article La Russie construit des rampes de lancement de drones à portée des pays de l’OTAN est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:28</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:49</t>
+        </is>
+      </c>
+      <c r="D598" s="3" t="inlineStr">
+        <is>
+          <t>Trump menace de frapper Oman, le 10e pays ciblé depuis son retour au pouvoir</t>
+        </is>
+      </c>
+      <c r="E598" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/17/trump-menace-de-frapper-oman-le-10e-pays-cible-depuis-son-retour-au-pouvoir/</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>S’exprimant sur le blocage du détroit d’Ormuz, le président américain a menacé ce lundi 17 août «&amp;#160;d’écraser Oman sous les bombes&amp;#160;» si le pays «&amp;#160;se mettait en travers&amp;#160;» d’un accord. L’article Trump menace de frapper Oman, le 10e pays ciblé depuis son retour au pouvoir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:28</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2026-08-17 12:51</t>
+        </is>
+      </c>
+      <c r="D599" s="3" t="inlineStr">
+        <is>
+          <t>Comment l’Ukraine a discrètement repris le contrôle de plus de 700 km² de son territoire</t>
+        </is>
+      </c>
+      <c r="E599" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/17/comment-lukraine-a-discretement-repris-le-controle-de-plus-de-700-km%c2%b2-de-son-territoire/</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Au cours d’une opération largement entourée de secret, l’armée ukrainienne a réalisé en six mois son avancée la plus importante depuis l’été 2023. L’article Comment l’Ukraine a discrètement repris le contrôle de plus de 700 km² de son territoire est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:28</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2026-08-17 06:13</t>
+        </is>
+      </c>
+      <c r="D600" s="3" t="inlineStr">
+        <is>
+          <t>Donald Trump a ordonné de réduire drastiquement l’exercice militaire conjoint annuel avec la Corée du Sud</t>
+        </is>
+      </c>
+      <c r="E600" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/17/donald-trump-ordonne-de-reduire-drastiquement-lexercice-militaire-conjoint-annuel-avec-la-coree-du-sud/</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Cette annonce intervient alors que les États-Unis ne disposent plus de porte-avions dans le Pacifique. L’article Donald Trump a ordonné de réduire drastiquement l’exercice militaire conjoint annuel avec la Corée du Sud est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20030,6 +20192,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E593" r:id="rId592"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E594" r:id="rId593"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E600" r:id="rId599"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G600"/>
+  <dimension ref="A1:G607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19462,7 +19462,6 @@
           <t>Près de trois millions de familles modestes recevront l’allocation de rentrée scolaire (ARS). Que feront-elles de cet argent&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -19495,7 +19494,6 @@
           <t>Les territoires de 11 pays membres de l’OTAN seraient à portée de ces nouveaux sites. L’article La Russie construit des rampes de lancement de drones à portée des pays de l’OTAN est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -19528,7 +19526,6 @@
           <t>S’exprimant sur le blocage du détroit d’Ormuz, le président américain a menacé ce lundi 17 août «&amp;#160;d’écraser Oman sous les bombes&amp;#160;» si le pays «&amp;#160;se mettait en travers&amp;#160;» d’un accord. L’article Trump menace de frapper Oman, le 10e pays ciblé depuis son retour au pouvoir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -19561,7 +19558,6 @@
           <t>Au cours d’une opération largement entourée de secret, l’armée ukrainienne a réalisé en six mois son avancée la plus importante depuis l’été 2023. L’article Comment l’Ukraine a discrètement repris le contrôle de plus de 700 km² de son territoire est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -19594,7 +19590,237 @@
           <t>Cette annonce intervient alors que les États-Unis ne disposent plus de porte-avions dans le Pacifique. L’article Donald Trump a ordonné de réduire drastiquement l’exercice militaire conjoint annuel avec la Corée du Sud est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2026-08-18 13:09</t>
+        </is>
+      </c>
+      <c r="D601" s="3" t="inlineStr">
+        <is>
+          <t>Russie : les étudiants étrangers au cœur d’une nouvelle stratégie internationale</t>
+        </is>
+      </c>
+      <c r="E601" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/russie-les-etudiants-etrangers-au-coeur-dune-nouvelle-strategie-internationale-289510</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Loin de tourner le dos à l’internationalisation, la Russie fait des étudiants étrangers un levier de sa réorientation internationale et de la recomposition de ses réseaux scientifiques.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2026-08-19 04:30</t>
+        </is>
+      </c>
+      <c r="D602" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Xi Jinping ne craint plus l’Europe</t>
+        </is>
+      </c>
+      <c r="E602" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/19/pourquoi-xi-jinping-ne-craint-plus-leurope/</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Face au nouveau choc industriel chinois, l’Union dispose de leviers considérables. Le parti communiste chinois a pourtant cessé de croire qu'elle s'en servirait. L’article Pourquoi Xi Jinping ne craint plus l’Europe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2026-08-19 04:30</t>
+        </is>
+      </c>
+      <c r="D603" s="3" t="inlineStr">
+        <is>
+          <t>En Asie, Taïwan et la Corée du Sud ne sont pas les seuls à tirer profit du boom de l’IA</t>
+        </is>
+      </c>
+      <c r="E603" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/19/en-asie-taiwan-et-la-coree-du-sud-ne-sont-pas-les-seuls-a-tirer-profit-du-boom-de-lia/</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Grâce à l’explosion des exportations de semi-conducteurs, la Malaisie pourrait rejoindre le groupe des pays à revenu élevé dès 2030. L’article En Asie, Taïwan et la Corée du Sud ne sont pas les seuls à tirer profit du boom de l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:49</t>
+        </is>
+      </c>
+      <c r="D604" s="3" t="inlineStr">
+        <is>
+          <t>Qui est Dan Bilzerian, l’influenceur masculiniste qui fait campagne en Floride sur une plateforme antisémite et anti-Trump ?</t>
+        </is>
+      </c>
+      <c r="E604" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/18/qui-est-dan-bilzerian-linfluenceur-masculiniste-qui-fait-campagne-en-floride-sur-une-plateforme-antisemite-et-anti-trump/</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>La candidature de Dan Bilzerian est symptomatique de la radicalisation d’une frange de la droite américaine qui s’est accélérée depuis le début de la guerre en Iran. L’article Qui est Dan Bilzerian, l’influenceur masculiniste qui fait campagne en Floride sur une plateforme antisémite et anti-Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:29</t>
+        </is>
+      </c>
+      <c r="D605" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe doit recommencer à construire</t>
+        </is>
+      </c>
+      <c r="E605" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/18/leurope-doit-recommencer-a-construire/</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Pendant quinze ans, nous avons cherché à réguler la puissance technologique américaine plutôt que bâtir la nôtre. Il est temps de changer de doctrine. L’article L’Europe doit recommencer à construire est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2026-08-18 12:30</t>
+        </is>
+      </c>
+      <c r="D606" s="3" t="inlineStr">
+        <is>
+          <t>Les entreprises qui résistent à Trump ne sont pas pénalisées par les marchés</t>
+        </is>
+      </c>
+      <c r="E606" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/18/les-entreprises-qui-resistent-a-trump-ne-sont-pas-penalisees-par-les-marches/</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Les bonnes performances des entreprises qui n’ont pas mis fin à leurs politiques de diversité après le retour de Trump montrent les limites de son influence sur le secteur privé. L’article Les entreprises qui résistent à Trump ne sont pas pénalisées par les marchés est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:29</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:49</t>
+        </is>
+      </c>
+      <c r="D607" s="3" t="inlineStr">
+        <is>
+          <t>Trump menace de frapper Oman, le 10e pays ciblé depuis son retour au pouvoir</t>
+        </is>
+      </c>
+      <c r="E607" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/17/trump-menace-de-frapper-oman-10e-pays-cible-depuis-son-retour-au-pouvoir/</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>S’exprimant sur le blocage du détroit d’Ormuz, le président américain a menacé ce lundi 17 août «&amp;#160;d’écraser Oman sous les bombes&amp;#160;» si le pays «&amp;#160;se mettait en travers&amp;#160;» d’un accord. L’article Trump menace de frapper Oman, le 10e pays ciblé depuis son retour au pouvoir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20197,6 +20423,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E598" r:id="rId597"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E599" r:id="rId598"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E607" r:id="rId606"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G607"/>
+  <dimension ref="A1:G615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19622,7 +19622,6 @@
           <t>Loin de tourner le dos à l’internationalisation, la Russie fait des étudiants étrangers un levier de sa réorientation internationale et de la recomposition de ses réseaux scientifiques.</t>
         </is>
       </c>
-      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -19655,7 +19654,6 @@
           <t>Face au nouveau choc industriel chinois, l’Union dispose de leviers considérables. Le parti communiste chinois a pourtant cessé de croire qu'elle s'en servirait. L’article Pourquoi Xi Jinping ne craint plus l’Europe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
@@ -19688,7 +19686,6 @@
           <t>Grâce à l’explosion des exportations de semi-conducteurs, la Malaisie pourrait rejoindre le groupe des pays à revenu élevé dès 2030. L’article En Asie, Taïwan et la Corée du Sud ne sont pas les seuls à tirer profit du boom de l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -19721,7 +19718,6 @@
           <t>La candidature de Dan Bilzerian est symptomatique de la radicalisation d’une frange de la droite américaine qui s’est accélérée depuis le début de la guerre en Iran. L’article Qui est Dan Bilzerian, l’influenceur masculiniste qui fait campagne en Floride sur une plateforme antisémite et anti-Trump&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -19754,7 +19750,6 @@
           <t>Pendant quinze ans, nous avons cherché à réguler la puissance technologique américaine plutôt que bâtir la nôtre. Il est temps de changer de doctrine. L’article L’Europe doit recommencer à construire est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -19787,7 +19782,6 @@
           <t>Les bonnes performances des entreprises qui n’ont pas mis fin à leurs politiques de diversité après le retour de Trump montrent les limites de son influence sur le secteur privé. L’article Les entreprises qui résistent à Trump ne sont pas pénalisées par les marchés est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -19820,7 +19814,270 @@
           <t>S’exprimant sur le blocage du détroit d’Ormuz, le président américain a menacé ce lundi 17 août «&amp;#160;d’écraser Oman sous les bombes&amp;#160;» si le pays «&amp;#160;se mettait en travers&amp;#160;» d’un accord. L’article Trump menace de frapper Oman, le 10e pays ciblé depuis son retour au pouvoir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2026-08-19 13:34</t>
+        </is>
+      </c>
+      <c r="D608" s="3" t="inlineStr">
+        <is>
+          <t>Patrimoine : faut-il faire contribuer ceux qui exploitent son image ?</t>
+        </is>
+      </c>
+      <c r="E608" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/patrimoine-faut-il-faire-contribuer-ceux-qui-exploitent-son-image-286911</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Dans un contexte de baisse des financements publics, les utilisateurs commerciaux du patrimoine peuvent-ils en devenir les contributeurs&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2026-08-19 13:30</t>
+        </is>
+      </c>
+      <c r="D609" s="3" t="inlineStr">
+        <is>
+          <t>Un oligarque russe à l’honneur dans « The Economist » : quand les médias prêtent leur crédibilité aux acteurs des conflits</t>
+        </is>
+      </c>
+      <c r="E609" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/un-oligarque-russe-a-lhonneur-dans-the-economist-quand-les-medias-pretent-leur-credibilite-aux-acteurs-des-conflits-288365</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>En donnant une large tribune à l’oligarque russe sanctionné Andreï&amp;nbsp;Melnitchenko, «&amp;nbsp;The Economist&amp;nbsp;» interroge la responsabilité des médias face à la guerre en Ukraine.</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2026-08-19 13:26</t>
+        </is>
+      </c>
+      <c r="D610" s="3" t="inlineStr">
+        <is>
+          <t>États-Unis : le Parti démocrate a-t-il pris un virage progressiste ?</t>
+        </is>
+      </c>
+      <c r="E610" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/etats-unis-le-parti-democrate-a-t-il-pris-un-virage-progressiste-289512</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Dans le Michigan, la victoire surprise d’Abdul&amp;nbsp;El Sayed aux primaires du Parti démocrate renforce un peu plus l’ancrage de la tendance progressiste au sein du parti.</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-08-20 04:30</t>
+        </is>
+      </c>
+      <c r="D611" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : deux tiers de la population estime que les moments les plus difficiles pour le pays sont encore à venir</t>
+        </is>
+      </c>
+      <c r="E611" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/20/economie-russe-deux-tiers-de-la-population-estime-que-les-moments-les-plus-difficiles-pour-le-pays-sont-encore-a-venir/</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>La hausse du pessimisme quant à la situation du pays coïncide avec l’intensification des frappes ukrainiennes. L’article Économie russe&amp;#160;: deux tiers de la population estime que les moments les plus difficiles pour le pays sont encore à venir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-08-20 04:00</t>
+        </is>
+      </c>
+      <c r="D612" s="3" t="inlineStr">
+        <is>
+          <t>Le monde est-il vraiment redevenu impérial ?</t>
+        </is>
+      </c>
+      <c r="E612" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/20/le-monde-est-il-vraiment-redevenu-imperial/</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Deux siècles d’histoire mondiale pour comprendre le désir et le déni d’empire. L’article Le monde est-il vraiment redevenu impérial&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-08-19 17:07</t>
+        </is>
+      </c>
+      <c r="D613" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Israël a-t-il interdit les ventes d’armes au Qatar ?</t>
+        </is>
+      </c>
+      <c r="E613" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/19/pourquoi-israel-a-t-il-interdit-les-ventes-darmes-au-qatar/</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Les relations entre Israël et le Qatar, accusé de soutenir le Hamas, sont devenues un sujet central à l'approche des élections législatives d'octobre. L’article Pourquoi Israël a-t-il interdit les ventes d’armes au Qatar&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-08-19 14:29</t>
+        </is>
+      </c>
+      <c r="D614" s="3" t="inlineStr">
+        <is>
+          <t>L’humanité pourrait déjà être passée sous le seuil de renouvellement des générations</t>
+        </is>
+      </c>
+      <c r="E614" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/19/lhumanite-pourrait-etre-passee-sous-le-seuil-de-renouvellement-des-generations/</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>L'ampleur de l'effondrement démographique en cours dépasse les prévisions des démographes de ces dernières décennies. L’article L’humanité pourrait déjà être passée sous le seuil de renouvellement des générations est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-08-19 13:15</t>
+        </is>
+      </c>
+      <c r="D615" s="3" t="inlineStr">
+        <is>
+          <t>Dans un appel aux Ukrainiens, Fedorov défie Zelensky (texte intégral)</t>
+        </is>
+      </c>
+      <c r="E615" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/19/dans-un-appel-aux-ukrainiens-fedorov-defie-zelensky-texte-integral/</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>L’ancien ministre de la Défense vient-il de provoquer la plus grave crise politique depuis le limogeage de Zaloujny&amp;#160;? L’article Dans un appel aux Ukrainiens, Fedorov défie Zelensky (texte intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20430,6 +20687,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E605" r:id="rId604"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E606" r:id="rId605"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId614"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G615"/>
+  <dimension ref="A1:G623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19846,7 +19846,6 @@
           <t>Dans un contexte de baisse des financements publics, les utilisateurs commerciaux du patrimoine peuvent-ils en devenir les contributeurs&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
@@ -19879,7 +19878,6 @@
           <t>En donnant une large tribune à l’oligarque russe sanctionné Andreï&amp;nbsp;Melnitchenko, «&amp;nbsp;The Economist&amp;nbsp;» interroge la responsabilité des médias face à la guerre en Ukraine.</t>
         </is>
       </c>
-      <c r="G609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -19912,7 +19910,6 @@
           <t>Dans le Michigan, la victoire surprise d’Abdul&amp;nbsp;El Sayed aux primaires du Parti démocrate renforce un peu plus l’ancrage de la tendance progressiste au sein du parti.</t>
         </is>
       </c>
-      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
@@ -19945,7 +19942,6 @@
           <t>La hausse du pessimisme quant à la situation du pays coïncide avec l’intensification des frappes ukrainiennes. L’article Économie russe&amp;#160;: deux tiers de la population estime que les moments les plus difficiles pour le pays sont encore à venir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -19978,7 +19974,6 @@
           <t>Deux siècles d’histoire mondiale pour comprendre le désir et le déni d’empire. L’article Le monde est-il vraiment redevenu impérial&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -20011,7 +20006,6 @@
           <t>Les relations entre Israël et le Qatar, accusé de soutenir le Hamas, sont devenues un sujet central à l'approche des élections législatives d'octobre. L’article Pourquoi Israël a-t-il interdit les ventes d’armes au Qatar&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
@@ -20044,7 +20038,6 @@
           <t>L'ampleur de l'effondrement démographique en cours dépasse les prévisions des démographes de ces dernières décennies. L’article L’humanité pourrait déjà être passée sous le seuil de renouvellement des générations est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -20077,7 +20070,270 @@
           <t>L’ancien ministre de la Défense vient-il de provoquer la plus grave crise politique depuis le limogeage de Zaloujny&amp;#160;? L’article Dans un appel aux Ukrainiens, Fedorov défie Zelensky (texte intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:02</t>
+        </is>
+      </c>
+      <c r="D616" s="3" t="inlineStr">
+        <is>
+          <t>Vin, huile, profits : le véritable rôle des intendantes dans les fermes romaines</t>
+        </is>
+      </c>
+      <c r="E616" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vin-huile-profits-le-veritable-role-des-intendantes-dans-les-fermes-romaines-287595</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Qui produisait le vin de la Rome antique&amp;nbsp;? Les sources suggèrent que les «&amp;nbsp;vilicae&amp;nbsp;», les intendantes des domaines, étaient bien plus que des gestionnaires du foyer&amp;nbsp;: elles supervisaient les vendanges, la vinification, les rituels religieux et la transformation des récoltes.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:07</t>
+        </is>
+      </c>
+      <c r="D617" s="3" t="inlineStr">
+        <is>
+          <t>Loi sur l’interdiction des réseaux sociaux aux moins de 15 ans : où mène la censure du Conseil constitutionnel ?</t>
+        </is>
+      </c>
+      <c r="E617" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/loi-sur-linterdiction-des-reseaux-sociaux-aux-moins-de-15-ans-ou-mene-la-censure-du-conseil-constitutionnel-290011</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>La loi, qui sera réécrite en septembre, devrait s’attacher à neutraliser les fonctionnalités toxiques plutôt que d’interdire l’ensemble des réseaux aux enfants et aux adolescents.</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:05</t>
+        </is>
+      </c>
+      <c r="D618" s="3" t="inlineStr">
+        <is>
+          <t>Enquête de l’OSCE : dans les territoires ukrainiens occupés, la Russie endoctrine et militarise les enfants</t>
+        </is>
+      </c>
+      <c r="E618" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/enquete-de-losce-dans-les-territoires-ukrainiens-occupes-la-russie-endoctrine-et-militarise-les-enfants-288958</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Même si le droit international interdit l’endoctrinement et la militarisation des enfants dans les territoires occupés, la Russie se livre ouvertement à ces pratiques en Ukraine.</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-08-21 04:30</t>
+        </is>
+      </c>
+      <c r="D619" s="3" t="inlineStr">
+        <is>
+          <t>Pékin est en train de construire sa plus grande île artificielle de la mer de Chine du Sud</t>
+        </is>
+      </c>
+      <c r="E619" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/21/pekin-est-en-train-de-construire-sa-plus-grande-ile-artificielle-de-la-mer-de-chine-du-sud/</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Des images satellites montrent que les travaux en cours sur le récif d'Antelope pourraient considérablement renforcer la présence militaire chinoise dans la région. L’article Pékin est en train de construire sa plus grande île artificielle de la mer de Chine du Sud est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-08-21 04:00</t>
+        </is>
+      </c>
+      <c r="D620" s="3" t="inlineStr">
+        <is>
+          <t>Pouvons-nous encore marquer les machines ?</t>
+        </is>
+      </c>
+      <c r="E620" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/21/pouvons-nous-marquer-les-machines/</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Une conversation fleuve avec le mathématicien qui a inventé le watermarking des LLM. L’article Pouvons-nous encore marquer les machines&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:36</t>
+        </is>
+      </c>
+      <c r="D621" s="3" t="inlineStr">
+        <is>
+          <t>Idéologie du genre</t>
+        </is>
+      </c>
+      <c r="E621" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/20/ideologie-du-genre/</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Du Vatican à la Maison-Blanche, comment une guerre culturelle mondiale cherche à devenir une nouvelle croisade. L’article Idéologie du genre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-08-20 15:54</t>
+        </is>
+      </c>
+      <c r="D622" s="3" t="inlineStr">
+        <is>
+          <t>La robotique est-elle en train de vivre son « moment GPT-3 » ?</t>
+        </is>
+      </c>
+      <c r="E622" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/20/la-robotique-est-elle-en-train-de-vivre-son-moment-gpt-3/</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>En seulement huit mois, la start-up américaine Generalist AI a entraîné un modèle robotique capable de reproduire des tâches après une simple démonstration humaine. L’article La robotique est-elle en train de vivre son «&amp;#160;moment GPT-3&amp;#160;»&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:32</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-08-20 11:23</t>
+        </is>
+      </c>
+      <c r="D623" s="3" t="inlineStr">
+        <is>
+          <t>L’intelligence artificielle va-t-elle guérir le cancer ?</t>
+        </is>
+      </c>
+      <c r="E623" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/20/lia-va-t-elle-guerir-le-cancer/</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Merck et Moderna ont franchi hier une étape importante dans le traitement du mélanome. L'analyse précise de cette découverte révèle le véritable rôle de l'IA dans la révolution médicale en cours. L’article L’intelligence artificielle va-t-elle guérir le cancer&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20695,6 +20951,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E613" r:id="rId612"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E614" r:id="rId613"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E623" r:id="rId622"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G623"/>
+  <dimension ref="A1:G630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20102,7 +20102,6 @@
           <t>Qui produisait le vin de la Rome antique&amp;nbsp;? Les sources suggèrent que les «&amp;nbsp;vilicae&amp;nbsp;», les intendantes des domaines, étaient bien plus que des gestionnaires du foyer&amp;nbsp;: elles supervisaient les vendanges, la vinification, les rituels religieux et la transformation des récoltes.</t>
         </is>
       </c>
-      <c r="G616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
@@ -20135,7 +20134,6 @@
           <t>La loi, qui sera réécrite en septembre, devrait s’attacher à neutraliser les fonctionnalités toxiques plutôt que d’interdire l’ensemble des réseaux aux enfants et aux adolescents.</t>
         </is>
       </c>
-      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -20168,7 +20166,6 @@
           <t>Même si le droit international interdit l’endoctrinement et la militarisation des enfants dans les territoires occupés, la Russie se livre ouvertement à ces pratiques en Ukraine.</t>
         </is>
       </c>
-      <c r="G618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -20201,7 +20198,6 @@
           <t>Des images satellites montrent que les travaux en cours sur le récif d'Antelope pourraient considérablement renforcer la présence militaire chinoise dans la région. L’article Pékin est en train de construire sa plus grande île artificielle de la mer de Chine du Sud est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -20234,7 +20230,6 @@
           <t>Une conversation fleuve avec le mathématicien qui a inventé le watermarking des LLM. L’article Pouvons-nous encore marquer les machines&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -20267,7 +20262,6 @@
           <t>Du Vatican à la Maison-Blanche, comment une guerre culturelle mondiale cherche à devenir une nouvelle croisade. L’article Idéologie du genre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -20300,7 +20294,6 @@
           <t>En seulement huit mois, la start-up américaine Generalist AI a entraîné un modèle robotique capable de reproduire des tâches après une simple démonstration humaine. L’article La robotique est-elle en train de vivre son «&amp;#160;moment GPT-3&amp;#160;»&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -20333,7 +20326,237 @@
           <t>Merck et Moderna ont franchi hier une étape importante dans le traitement du mélanome. L'analyse précise de cette découverte révèle le véritable rôle de l'IA dans la révolution médicale en cours. L’article L’intelligence artificielle va-t-elle guérir le cancer&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:00</t>
+        </is>
+      </c>
+      <c r="D624" s="3" t="inlineStr">
+        <is>
+          <t>Réalité virtuelle, expositions, théâtre… comment la technologie perpétue la légende du « Titanic »</t>
+        </is>
+      </c>
+      <c r="E624" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/realite-virtuelle-expositions-theatre-comment-la-technologie-perpetue-la-legende-du-titanic-287646</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Plus d’un siècle après le naufrage du «&amp;nbsp;Titanic&amp;nbsp;», qui fit près de 1&amp;nbsp;500&amp;nbsp;victimes, le 15&amp;nbsp;avril 1912, la catastrophe reste un puissant objet culturel. Les technologies immersives lui offrent désormais une nouvelle vie, entre mémoire, spectacle et émotion.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:58</t>
+        </is>
+      </c>
+      <c r="D625" s="3" t="inlineStr">
+        <is>
+          <t>Sécheresses, incendies et famines… Comment une période de réchauffement a redessiné le Moyen Âge</t>
+        </is>
+      </c>
+      <c r="E625" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/secheresses-incendies-et-famines-comment-une-periode-de-rechauffement-a-redessine-le-moyen-age-288300</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Entre le Xᵉ et le XIIIᵉ&amp;nbsp;siècles, une grande partie du monde a connu un climat plus chaud qu’à l’accoutumée. Cette «&amp;nbsp;anomalie climatique médiévale&amp;nbsp;» a favorisé l’essor de l’agriculture dans certaines régions et provoqué famines et crises ailleurs.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:58</t>
+        </is>
+      </c>
+      <c r="D626" s="3" t="inlineStr">
+        <is>
+          <t>Ukraine : des élections pendant la guerre renforceraient-elles vraiment la démocratie ?</t>
+        </is>
+      </c>
+      <c r="E626" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ukraine-des-elections-pendant-la-guerre-renforceraient-elles-vraiment-la-democratie-290179</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Des millions de déplacés internes et de réfugiés, une partie du territoire sous occupation russe et des frappes quotidiennes&amp;nbsp;: malgré ce contexte, des responsables ukrainiens relancent le débat sur la tenue d’élections.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2026-08-22 04:30</t>
+        </is>
+      </c>
+      <c r="D627" s="3" t="inlineStr">
+        <is>
+          <t>Léon XIV à Saint-Marin : la diplomatie des micro-États, une stratégie vaticane ?</t>
+        </is>
+      </c>
+      <c r="E627" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/22/leon-xiv-a-saint-marin-la-diplomatie-des-micro-etats-une-strategie-vaticane/</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Au temps du retour des Empires, la stratégie du Saint-Siège offre une alternative à l’affirmation seule de la puissance brute. L’article Léon XIV à Saint-Marin&amp;#160;: la diplomatie des micro-États, une stratégie vaticane&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2026-08-21 18:16</t>
+        </is>
+      </c>
+      <c r="D628" s="3" t="inlineStr">
+        <is>
+          <t>Illibéralisme</t>
+        </is>
+      </c>
+      <c r="E628" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/21/illiberalisme/</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Des conservateurs de l’après-guerre aux néoréactionnaires de la Silicon Valley, une généalogie de la contre-révolution. L’article Illibéralisme est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:22</t>
+        </is>
+      </c>
+      <c r="D629" s="3" t="inlineStr">
+        <is>
+          <t>La politique migratoire européenne de Meloni se retourne contre elle</t>
+        </is>
+      </c>
+      <c r="E629" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/21/la-politique-migratoire-europeenne-de-meloni-se-retourne-contre-elle/</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Au moins six pays européens s’apprêtent à renvoyer des demandeurs d’asile vers l’Italie. L’article La politique migratoire européenne de Meloni se retourne contre elle est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22 09:22</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:13</t>
+        </is>
+      </c>
+      <c r="D630" s="3" t="inlineStr">
+        <is>
+          <t>Quels pays européens pourraient être pris pour cible par l’Iran ?</t>
+        </is>
+      </c>
+      <c r="E630" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/21/quels-pays-europeens-pourraient-etre-pris-pour-cible-par-liran/</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>L’arsenal de drones iraniens constitue une menace pour les bases utilisées par l’armée américaine en Europe. L’article Quels pays européens pourraient être pris pour cible par l’Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20959,6 +21182,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId620"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId621"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId629"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G630"/>
+  <dimension ref="A1:G632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20358,7 +20358,6 @@
           <t>Plus d’un siècle après le naufrage du «&amp;nbsp;Titanic&amp;nbsp;», qui fit près de 1&amp;nbsp;500&amp;nbsp;victimes, le 15&amp;nbsp;avril 1912, la catastrophe reste un puissant objet culturel. Les technologies immersives lui offrent désormais une nouvelle vie, entre mémoire, spectacle et émotion.</t>
         </is>
       </c>
-      <c r="G624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -20391,7 +20390,6 @@
           <t>Entre le Xᵉ et le XIIIᵉ&amp;nbsp;siècles, une grande partie du monde a connu un climat plus chaud qu’à l’accoutumée. Cette «&amp;nbsp;anomalie climatique médiévale&amp;nbsp;» a favorisé l’essor de l’agriculture dans certaines régions et provoqué famines et crises ailleurs.</t>
         </is>
       </c>
-      <c r="G625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -20424,7 +20422,6 @@
           <t>Des millions de déplacés internes et de réfugiés, une partie du territoire sous occupation russe et des frappes quotidiennes&amp;nbsp;: malgré ce contexte, des responsables ukrainiens relancent le débat sur la tenue d’élections.</t>
         </is>
       </c>
-      <c r="G626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -20457,7 +20454,6 @@
           <t>Au temps du retour des Empires, la stratégie du Saint-Siège offre une alternative à l’affirmation seule de la puissance brute. L’article Léon XIV à Saint-Marin&amp;#160;: la diplomatie des micro-États, une stratégie vaticane&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -20490,7 +20486,6 @@
           <t>Des conservateurs de l’après-guerre aux néoréactionnaires de la Silicon Valley, une généalogie de la contre-révolution. L’article Illibéralisme est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -20523,7 +20518,6 @@
           <t>Au moins six pays européens s’apprêtent à renvoyer des demandeurs d’asile vers l’Italie. L’article La politique migratoire européenne de Meloni se retourne contre elle est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -20556,7 +20550,72 @@
           <t>L’arsenal de drones iraniens constitue une menace pour les bases utilisées par l’armée américaine en Europe. L’article Quels pays européens pourraient être pris pour cible par l’Iran&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23 09:23</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2026-08-23 04:30</t>
+        </is>
+      </c>
+      <c r="D631" s="3" t="inlineStr">
+        <is>
+          <t>Les réserves européennes de gaz sont plus faibles qu’en 2022</t>
+        </is>
+      </c>
+      <c r="E631" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/23/les-reserves-europeennes-de-gaz-sont-plus-faibles-quen-2022/</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>À l’échelle de l’Union, le stockage de gaz se situe à 62&amp;#160;% au 21 août. Si le risque n’est pas tant celui d’une pénurie, les États européens pourraient voir les prix grimper durant les mois d’hiver, notamment si le conflit au Moyen-Orient se prolonge. L’article Les réserves européennes de gaz sont plus faibles qu’en 2022 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23 09:23</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2026-08-23 04:00</t>
+        </is>
+      </c>
+      <c r="D632" s="3" t="inlineStr">
+        <is>
+          <t>Le projet d’État de Donald Trump</t>
+        </is>
+      </c>
+      <c r="E632" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/23/le-projet-detat-de-donald-trump/</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>La guerre contre la bureaucratie cache une transformation radicale du pouvoir américain. L’article Le projet d’État de Donald Trump est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21189,6 +21248,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E628" r:id="rId627"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId628"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E632" r:id="rId631"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G632"/>
+  <dimension ref="A1:G636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20582,7 +20582,6 @@
           <t>À l’échelle de l’Union, le stockage de gaz se situe à 62&amp;#160;% au 21 août. Si le risque n’est pas tant celui d’une pénurie, les États européens pourraient voir les prix grimper durant les mois d’hiver, notamment si le conflit au Moyen-Orient se prolonge. L’article Les réserves européennes de gaz sont plus faibles qu’en 2022 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -20615,7 +20614,138 @@
           <t>La guerre contre la bureaucratie cache une transformation radicale du pouvoir américain. L’article Le projet d’État de Donald Trump est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:42</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2026-08-24 05:39</t>
+        </is>
+      </c>
+      <c r="D633" s="3" t="inlineStr">
+        <is>
+          <t>Un malentendu islandais ?</t>
+        </is>
+      </c>
+      <c r="E633" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/24/un-malentendu-islandais/</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Géopolitique du référendum du 29 août qui pourrait rouvrir l’Arctique à l’Union. L’article Un malentendu islandais&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:42</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2026-08-24 04:30</t>
+        </is>
+      </c>
+      <c r="D634" s="3" t="inlineStr">
+        <is>
+          <t>La dérive des comptes publics américains se poursuit</t>
+        </is>
+      </c>
+      <c r="E634" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/24/la-derive-des-comptes-publics-americains-se-poursuit/</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Si les taux d’intérêt auxquels l’État américain doit s’endetter se stabilisaient à 5&amp;#160;%, il devrait toutefois payer chaque année le double du budget annuel de la défense pour le paiement des intérêts. L’article La dérive des comptes publics américains se poursuit est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:42</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:46</t>
+        </is>
+      </c>
+      <c r="D635" s="3" t="inlineStr">
+        <is>
+          <t>Harvard a commencé à créer des avatars de ses professeurs à l’aide de l’IA</t>
+        </is>
+      </c>
+      <c r="E635" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/23/harvard-a-commence-a-creer-des-avatars-de-ses-professeurs-a-laide-de-lia/</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>L’accès à leurs conseils commence à 699 dollars. L’article Harvard a commencé à créer des avatars de ses professeurs à l&amp;rsquo;aide de l&amp;rsquo;IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:42</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:06</t>
+        </is>
+      </c>
+      <c r="D636" s="3" t="inlineStr">
+        <is>
+          <t>Le discours intégral de Mark Carney contre la vassalisation du Canada</t>
+        </is>
+      </c>
+      <c r="E636" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/23/le-discours-integral-de-mark-carney-contre-la-vassalisation-du-canada/</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Sous couvert de négociation commerciale, Trump voulait mettre le Canada sous tutelle. Le premier ministre a dit non. L’article Le discours intégral de Mark Carney contre la vassalisation du Canada est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21250,6 +21380,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId629"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E631" r:id="rId630"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E636" r:id="rId635"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G636"/>
+  <dimension ref="A1:G644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20646,7 +20646,6 @@
           <t>Géopolitique du référendum du 29 août qui pourrait rouvrir l’Arctique à l’Union. L’article Un malentendu islandais&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -20679,7 +20678,6 @@
           <t>Si les taux d’intérêt auxquels l’État américain doit s’endetter se stabilisaient à 5&amp;#160;%, il devrait toutefois payer chaque année le double du budget annuel de la défense pour le paiement des intérêts. L’article La dérive des comptes publics américains se poursuit est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -20712,7 +20710,6 @@
           <t>L’accès à leurs conseils commence à 699 dollars. L’article Harvard a commencé à créer des avatars de ses professeurs à l&amp;rsquo;aide de l&amp;rsquo;IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
@@ -20745,7 +20742,270 @@
           <t>Sous couvert de négociation commerciale, Trump voulait mettre le Canada sous tutelle. Le premier ministre a dit non. L’article Le discours intégral de Mark Carney contre la vassalisation du Canada est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:43</t>
+        </is>
+      </c>
+      <c r="D637" s="3" t="inlineStr">
+        <is>
+          <t>Comment est fabriqué un billet de banque ? Dans les coulisses de la Banque de France depuis Napoléon Bonaparte</t>
+        </is>
+      </c>
+      <c r="E637" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-est-fabrique-un-billet-de-banque-dans-les-coulisses-de-la-banque-de-france-depuis-napoleon-bonaparte-285174</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Retour historique et pratique sur l’art et l’industrie fiduciaires avec les billets émis par la Banque de France, du papier à l’illustration par les plus grands artistes, en passant par l’impression sur les presses à taille-douce.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:40</t>
+        </is>
+      </c>
+      <c r="D638" s="3" t="inlineStr">
+        <is>
+          <t>Langue populaire, langue savante : des différences à reconsidérer pour mieux lutter contre les inégalités scolaires</t>
+        </is>
+      </c>
+      <c r="E638" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/langue-populaire-langue-savante-des-differences-a-reconsiderer-pour-mieux-lutter-contre-les-inegalites-scolaires-287822</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Loin d’être la version sommaire de la langue savante, la langue populaire est tout aussi complexe et introduit un autre rapport à la parole. Le comprendre ne permettrait-il pas de mieux accueillir tous les élèves en classe&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:39</t>
+        </is>
+      </c>
+      <c r="D639" s="3" t="inlineStr">
+        <is>
+          <t>Entre conflits armés et El Niño, la dangereuse convergence des crises en mer Rouge</t>
+        </is>
+      </c>
+      <c r="E639" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/entre-conflits-armes-et-el-nino-la-dangereuse-convergence-des-crises-en-mer-rouge-290123</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Guerres régionales et El&amp;nbsp;Niño conjuguent leurs effets en mer Rouge, menaçant d’aggraver l’insécurité alimentaire de populations déjà fragilisées par les conflits.</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2026-08-24 15:38</t>
+        </is>
+      </c>
+      <c r="D640" s="3" t="inlineStr">
+        <is>
+          <t>Djen Djen : ce qu’un port algérien révèle des mutations des routes maritimes mondiales</t>
+        </is>
+      </c>
+      <c r="E640" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/djen-djen-ce-quun-port-algerien-revele-des-mutations-des-routes-maritimes-mondiales-289933</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>À Djen Djen, en Algérie, 200&amp;nbsp;conteneurs ont changé de navire sans passer par le marché algérien&amp;nbsp;: une première qui offre au port un nouveau rôle dans les flux maritimes internationaux.</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2026-08-25 05:55</t>
+        </is>
+      </c>
+      <c r="D641" s="3" t="inlineStr">
+        <is>
+          <t>L’Union peut-elle devenir une puissance sans capitalisme européen ?</t>
+        </is>
+      </c>
+      <c r="E641" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/25/lunion-peut-elle-devenir-une-puissance-sans-capitalisme-europeen/</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Entretien fleuve avec l’économiste pionnier de la théorie de la régulation. L’article L’Union peut-elle devenir une puissance sans capitalisme européen&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2026-08-25 04:30</t>
+        </is>
+      </c>
+      <c r="D642" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis peuvent-ils se défaire de leur dépendance aux terres rares en provenance de Chine ?</t>
+        </is>
+      </c>
+      <c r="E642" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/25/les-etats-unis-peuvent-ils-se-defaire-de-leur-dependance-aux-terres-rares-en-provenance-de-chine/</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Malgré des partenariats, des investissements et la prise de participations dans des entreprises privées, la stratégie de la Maison Blanche présente une faille&amp;#160;: les terres rares lourdes. L’article Les États-Unis peuvent-ils se défaire de leur dépendance aux terres rares en provenance de Chine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2026-08-24 16:06</t>
+        </is>
+      </c>
+      <c r="D643" s="3" t="inlineStr">
+        <is>
+          <t>Les océans ont atteint leur température la plus élevée jamais enregistrée</t>
+        </is>
+      </c>
+      <c r="E643" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/24/les-oceans-ont-atteint-leur-temperature-la-plus-elevee-jamais-enregistree/</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Le précédent record de 2024 a été battu samedi 22 août, lorsque les océans ont atteint une température moyenne globale de 21,1°C. L’article Les océans ont atteint leur température la plus élevée jamais enregistrée est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:31</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:08</t>
+        </is>
+      </c>
+      <c r="D644" s="3" t="inlineStr">
+        <is>
+          <t>Attaques russes : l’Europe est dans une paix hybride</t>
+        </is>
+      </c>
+      <c r="E644" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/24/attaques-russes-leurope-est-dans-une-paix-hybride/</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Plus de 150 attaques commanditées par Moscou ont été conduites en Europe depuis 2022. L’article Attaques russes&amp;#160;: l’Europe est dans une paix hybride est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21384,6 +21644,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId633"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId634"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId643"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G644"/>
+  <dimension ref="A1:G651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20774,7 +20774,6 @@
           <t>Retour historique et pratique sur l’art et l’industrie fiduciaires avec les billets émis par la Banque de France, du papier à l’illustration par les plus grands artistes, en passant par l’impression sur les presses à taille-douce.</t>
         </is>
       </c>
-      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -20807,7 +20806,6 @@
           <t>Loin d’être la version sommaire de la langue savante, la langue populaire est tout aussi complexe et introduit un autre rapport à la parole. Le comprendre ne permettrait-il pas de mieux accueillir tous les élèves en classe&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
@@ -20840,7 +20838,6 @@
           <t>Guerres régionales et El&amp;nbsp;Niño conjuguent leurs effets en mer Rouge, menaçant d’aggraver l’insécurité alimentaire de populations déjà fragilisées par les conflits.</t>
         </is>
       </c>
-      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -20873,7 +20870,6 @@
           <t>À Djen Djen, en Algérie, 200&amp;nbsp;conteneurs ont changé de navire sans passer par le marché algérien&amp;nbsp;: une première qui offre au port un nouveau rôle dans les flux maritimes internationaux.</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -20906,7 +20902,6 @@
           <t>Entretien fleuve avec l’économiste pionnier de la théorie de la régulation. L’article L’Union peut-elle devenir une puissance sans capitalisme européen&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -20939,7 +20934,6 @@
           <t>Malgré des partenariats, des investissements et la prise de participations dans des entreprises privées, la stratégie de la Maison Blanche présente une faille&amp;#160;: les terres rares lourdes. L’article Les États-Unis peuvent-ils se défaire de leur dépendance aux terres rares en provenance de Chine&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -20972,7 +20966,6 @@
           <t>Le précédent record de 2024 a été battu samedi 22 août, lorsque les océans ont atteint une température moyenne globale de 21,1°C. L’article Les océans ont atteint leur température la plus élevée jamais enregistrée est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -21005,7 +20998,237 @@
           <t>Plus de 150 attaques commanditées par Moscou ont été conduites en Europe depuis 2022. L’article Attaques russes&amp;#160;: l’Europe est dans une paix hybride est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:26</t>
+        </is>
+      </c>
+      <c r="D645" s="3" t="inlineStr">
+        <is>
+          <t>COP17 en Mongolie : la diplomatie de la terre à l’épreuve de la crise du multilatéralisme environnemental</t>
+        </is>
+      </c>
+      <c r="E645" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/cop17-en-mongolie-la-diplomatie-de-la-terre-a-lepreuve-de-la-crise-du-multilateralisme-environnemental-290199</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Sur fond de canicules et d’incendies, la COP sur la désertification se réunit pour lutter contre la dégradation des terres, qui accentue les pressions sur les écosystèmes et sur les populations.</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:26</t>
+        </is>
+      </c>
+      <c r="D646" s="3" t="inlineStr">
+        <is>
+          <t>Protéger les enfants en mobilité au Mali : l’angle mort des dispositifs actuels</t>
+        </is>
+      </c>
+      <c r="E646" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/proteger-les-enfants-en-mobilite-au-mali-langle-mort-des-dispositifs-actuels-289937</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Au Mali, des réseaux communautaires protègent les enfants confiés en ville, mais les failles des placements et des dispositifs publics accroissent leur vulnérabilité.</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2026-08-26 05:30</t>
+        </is>
+      </c>
+      <c r="D647" s="3" t="inlineStr">
+        <is>
+          <t>Le pouvoir de ceux qui critiquent le pouvoir</t>
+        </is>
+      </c>
+      <c r="E647" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/26/le-pouvoir-de-ceux-qui-critiquent-le-pouvoir/</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>La critique devait nous libérer des dogmes et des arguments d’autorité. Elle a fini par créer une élite qui peine à reconnaître sa propre responsabilité. L’article Le pouvoir de ceux qui critiquent le pouvoir est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2026-08-26 04:30</t>
+        </is>
+      </c>
+      <c r="D648" s="3" t="inlineStr">
+        <is>
+          <t>Près de la moitié de l’approvisionnement mondial en pétrole provient de pays engagés dans un conflit</t>
+        </is>
+      </c>
+      <c r="E648" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/26/pres-de-la-moitie-de-lapprovisionnement-mondial-en-petrole-provient-de-pays-engages-dans-un-conflit/</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Les États-Unis sont les principaux bénéficiaires des perturbations qui impactent les approvisionnements énergétiques mondiaux. L’article Près de la moitié de l’approvisionnement mondial en pétrole provient de pays engagés dans un conflit est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2026-08-25 16:30</t>
+        </is>
+      </c>
+      <c r="D649" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : le Kremlin tire profit des frappes de drones ukrainiens pour accélérer sa saisie d’actifs</t>
+        </is>
+      </c>
+      <c r="E649" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/25/economie-russe-le-kremlin-tire-profit-des-frappes-de-drones-ukrainiens-pour-accelerer-sa-saisie-dactifs/</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Le succès de la campagne ukrainienne pourrait produire un effet inattendu&amp;#160;: permettre au Kremlin de renflouer ses caisses. L’article Économie russe&amp;#160;: le Kremlin tire profit des frappes de drones ukrainiens pour accélérer sa saisie d’actifs est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:34</t>
+        </is>
+      </c>
+      <c r="D650" s="3" t="inlineStr">
+        <is>
+          <t>Palantir veut recruter Mykhaïlo Fedorov, l’homme fort de la tech ukrainienne</t>
+        </is>
+      </c>
+      <c r="E650" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/25/palantir-veut-recruter-mykhailo-fedorov-lhomme-fort-de-la-tech-ukrainienne/</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Le ministre de la Défense limogé par Zelensky est de plus en plus proche du géant fondé par Peter Thiel. L’article Palantir veut recruter Mykhaïlo Fedorov, l’homme fort de la tech ukrainienne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:36</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2026-08-25 12:08</t>
+        </is>
+      </c>
+      <c r="D651" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le Parti communiste chinois organise des jeux des robots de Pékin ?</t>
+        </is>
+      </c>
+      <c r="E651" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/25/pourquoi-le-parti-communiste-chinois-organise-des-jeux-des-robots-de-pekin/</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Le Colisée robotique des 2026 World Humanoid Robot Games décodé cliché par cliché. L’article Pourquoi le Parti communiste chinois organise des jeux des robots de Pékin&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21652,6 +21875,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E642" r:id="rId641"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId642"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E645" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E646" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E647" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E648" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E651" r:id="rId650"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G651"/>
+  <dimension ref="A1:G667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21030,7 +21030,6 @@
           <t>Sur fond de canicules et d’incendies, la COP sur la désertification se réunit pour lutter contre la dégradation des terres, qui accentue les pressions sur les écosystèmes et sur les populations.</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -21063,7 +21062,6 @@
           <t>Au Mali, des réseaux communautaires protègent les enfants confiés en ville, mais les failles des placements et des dispositifs publics accroissent leur vulnérabilité.</t>
         </is>
       </c>
-      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -21096,7 +21094,6 @@
           <t>La critique devait nous libérer des dogmes et des arguments d’autorité. Elle a fini par créer une élite qui peine à reconnaître sa propre responsabilité. L’article Le pouvoir de ceux qui critiquent le pouvoir est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -21129,7 +21126,6 @@
           <t>Les États-Unis sont les principaux bénéficiaires des perturbations qui impactent les approvisionnements énergétiques mondiaux. L’article Près de la moitié de l’approvisionnement mondial en pétrole provient de pays engagés dans un conflit est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -21162,7 +21158,6 @@
           <t>Le succès de la campagne ukrainienne pourrait produire un effet inattendu&amp;#160;: permettre au Kremlin de renflouer ses caisses. L’article Économie russe&amp;#160;: le Kremlin tire profit des frappes de drones ukrainiens pour accélérer sa saisie d’actifs est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
@@ -21195,7 +21190,6 @@
           <t>Le ministre de la Défense limogé par Zelensky est de plus en plus proche du géant fondé par Peter Thiel. L’article Palantir veut recruter Mykhaïlo Fedorov, l’homme fort de la tech ukrainienne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
@@ -21228,7 +21222,534 @@
           <t>Le Colisée robotique des 2026 World Humanoid Robot Games décodé cliché par cliché. L’article Pourquoi le Parti communiste chinois organise des jeux des robots de Pékin&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:25</t>
+        </is>
+      </c>
+      <c r="D652" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi Napoléon III a fait de l’archéologie une affaire d’État</t>
+        </is>
+      </c>
+      <c r="E652" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-napoleon-iii-a-fait-de-larcheologie-une-affaire-detat-286579</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>En lançant de grandes fouilles et de nouvelles institutions, Napoléon III fait de l’archéologie un instrument politique autant qu’un moteur de la recherche sur les origines de la France.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2026-08-26 12:56</t>
+        </is>
+      </c>
+      <c r="D653" s="3" t="inlineStr">
+        <is>
+          <t>Dioclétien, l’empereur romain qui abandonna le pouvoir pour cultiver des choux</t>
+        </is>
+      </c>
+      <c r="E653" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/diocletien-lempereur-romain-qui-abandonna-le-pouvoir-pour-cultiver-des-choux-287709</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Pourquoi un empereur au sommet de sa puissance abandonnerait-il volontairement le trône&amp;nbsp;? Entre maladie, réformes politiques et lassitude face aux complots, l’abdication de Dioclétien continue d’intriguer les historiens.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:28</t>
+        </is>
+      </c>
+      <c r="D654" s="3" t="inlineStr">
+        <is>
+          <t>Corsets, crinolines et maquillage au plomb… Quand la mode mettait la vie des femmes en péril</t>
+        </is>
+      </c>
+      <c r="E654" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/corsets-crinolines-et-maquillage-au-plomb-quand-la-mode-mettait-la-vie-des-femmes-en-peril-288942</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Bien avant les débats sur les gaines sculptantes ou les talons hauts, la mode exposait déjà ses adeptes à des poisons, des radiations ou des incendies. Une histoire de l’élégance à des périodes où celle-ci pouvait se payer au prix fort.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:27</t>
+        </is>
+      </c>
+      <c r="D655" s="3" t="inlineStr">
+        <is>
+          <t>Des cartes de scènes d’homicide dans trois villes anglaises bousculent nos idées reçues sur la violence au Moyen Âge</t>
+        </is>
+      </c>
+      <c r="E655" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/des-cartes-de-scenes-dhomicide-dans-trois-villes-anglaises-bousculent-nos-idees-recues-sur-la-violence-au-moyen-age-287093</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Où risquait-on le plus de mourir dans une ville médiévale&amp;nbsp;? En reconstituant 355 scènes d’homicides survenus entre 1296 et 1398, des historiens montrent que la violence suivait les flux de population, de commerce et de pouvoir.</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:27</t>
+        </is>
+      </c>
+      <c r="D656" s="3" t="inlineStr">
+        <is>
+          <t>Les archives orales, des sources comme les autres ? Comment les témoignages nourrissent le travail des historiens</t>
+        </is>
+      </c>
+      <c r="E656" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-archives-orales-des-sources-comme-les-autres-comment-les-temoignages-nourrissent-le-travail-des-historiens-287747</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Si les piliers de l’histoire orale ont été posés dès 1921 par Marc&amp;nbsp;Bloch, les sources orales ont mis près d’un siècle à être admises comme telles en histoire. Pourquoi tant de précautions&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:40</t>
+        </is>
+      </c>
+      <c r="D657" s="3" t="inlineStr">
+        <is>
+          <t>Quand la polarisation internationale s’invite dans la présidentielle brésilienne</t>
+        </is>
+      </c>
+      <c r="E657" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quand-la-polarisation-internationale-sinvite-dans-la-presidentielle-bresilienne-289957</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>À l’approche de la présidentielle brésilienne, le duel Lula&amp;nbsp;–&amp;nbsp;Flávio&amp;nbsp;Bolsonaro est marqué par une forte implication de leurs appuis respectifs au niveau international.</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2026-08-26 13:25</t>
+        </is>
+      </c>
+      <c r="D658" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le cas Natalie Harp révèle du système Trump</t>
+        </is>
+      </c>
+      <c r="E658" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ce-que-le-cas-natalie-harp-revele-du-systeme-trump-290073</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Une assistante de rang subalterne filtre-t-elle réellement les informations parvenant jusqu’au chef de l’État&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2026-08-27 16:00</t>
+        </is>
+      </c>
+      <c r="D659" s="3" t="inlineStr">
+        <is>
+          <t>Pour lancer des milliers de fusées par an, SpaceX va occuper près de 0,5 % de la Louisiane</t>
+        </is>
+      </c>
+      <c r="E659" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/27/pour-lancer-des-milliers-de-fusees-par-an-spacex-va-occuper-pres-de-05-de-la-louisiane/</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Le projet a été comparé par le gouverneur de l’État, un allié de Trump, à la vente de la Louisiane de 1803. L’article Pour lancer des milliers de fusées par an, SpaceX va occuper près de 0,5&amp;#160;% de la Louisiane est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:38</t>
+        </is>
+      </c>
+      <c r="D660" s="3" t="inlineStr">
+        <is>
+          <t>En prétendant renommer le lac Ontario, Trump s’inscrit dans la lignée de Mobutu</t>
+        </is>
+      </c>
+      <c r="E660" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/27/en-pretendant-renommer-le-lac-ontario-trump-sinscrit-dans-la-lignee-de-mobutu/</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Ce que révèle le nouvel épisode de la guerre des cartes du président américain. L’article En prétendant renommer le lac Ontario, Trump s’inscrit dans la lignée de Mobutu est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:16</t>
+        </is>
+      </c>
+      <c r="D661" s="3" t="inlineStr">
+        <is>
+          <t>Les huit scénarios de la guerre en Ukraine (texte intégral de la note Sberbank)</t>
+        </is>
+      </c>
+      <c r="E661" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/27/les-huit-scenarios-de-la-guerre-en-ukraine-texte-integral-de-la-note-sberbank/</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Une note interne attribuée à la plus grande banque russe révèle la logique et les impasses du conflit. L’article Les huit scénarios de la guerre en Ukraine (texte intégral de la note Sberbank) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2026-08-27 04:30</t>
+        </is>
+      </c>
+      <c r="D662" s="3" t="inlineStr">
+        <is>
+          <t>Plus d’un tiers des pages web publiées depuis le lancement de ChatGPT comportent des traces d’IA</t>
+        </is>
+      </c>
+      <c r="E662" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/27/plus-dun-tiers-des-pages-web-publiees-depuis-le-lancement-de-chatgpt-comportent-des-traces-dia/</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>La multiplication des contenus générés avec l’assistance de l’intelligence artificielle pourrait conduire à une baisse de la fiabilité et de la qualité des modèles. L’article Plus d&amp;rsquo;un tiers des pages web publiées depuis le lancement de ChatGPT comportent des traces d&amp;rsquo;IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2026-08-27 04:00</t>
+        </is>
+      </c>
+      <c r="D663" s="3" t="inlineStr">
+        <is>
+          <t>Dronophobie : enquête sur le mal du XXIe siècle</t>
+        </is>
+      </c>
+      <c r="E663" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/27/dronophobie-enquete-sur-le-mal-du-xxie-siecle/</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>En Ukraine, soldats et psychiatres découvrent le traumatisme d’une arme qui bouleverse les frontières de la guerre. L’article Dronophobie&amp;#160;: enquête sur le mal du XXIe siècle est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2026-08-26 16:51</t>
+        </is>
+      </c>
+      <c r="D664" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le directeur de la CIA s’est-il rendu à Moscou ?</t>
+        </is>
+      </c>
+      <c r="E664" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/26/pourquoi-le-directeur-de-la-cia-sest-il-rendu-a-moscou/</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>John Ratcliffe est le premier directeur de la CIA à se rendre en Russie depuis l'invasion de février 2022. L’article Pourquoi le directeur de la CIA s’est-il rendu à Moscou&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:28</t>
+        </is>
+      </c>
+      <c r="D665" s="3" t="inlineStr">
+        <is>
+          <t>La Russie n’a que 7 % de chances de remporter la guerre : les huit scénarios dressés par Sberbank</t>
+        </is>
+      </c>
+      <c r="E665" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/26/la-russie-na-que-7-de-chances-de-remporter-la-guerre-les-huit-scenarios-dresses-par-sberbank/</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Une fuite inédite présente les objectifs du Kremlin en Ukraine comme pratiquement inatteignables. L’article La Russie n’a que 7&amp;#160;% de chances de remporter la guerre&amp;#160;: les huit scénarios dressés par Sberbank est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2026-08-26 11:00</t>
+        </is>
+      </c>
+      <c r="D666" s="3" t="inlineStr">
+        <is>
+          <t>Le nouveau projet de Trump ? Des corsaires dans le cyberespace</t>
+        </is>
+      </c>
+      <c r="E666" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/26/le-nouveau-projet-de-trump-des-corsaires-dans-le-cyberespace/</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Nous traduisons et commentons un mémorandum passé trop inaperçu en Europe. L’article Le nouveau projet de Trump&amp;#160;? Des corsaires dans le cyberespace est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:24</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2026-08-26 10:23</t>
+        </is>
+      </c>
+      <c r="D667" s="3" t="inlineStr">
+        <is>
+          <t>Journée d’étude APHG-CNFG le 26 septembre : « Géographie du Pacifique, de l’environnement et de la santé »</t>
+        </is>
+      </c>
+      <c r="E667" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/journee-detude-aphg-cnfg-le-26-septembre-geographie-du-pacifique-de-lenvironnement-et-de-la-sante/</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Samedi 26 septembre 2026, 9h-16h30 Halle aux Farines, Salle 379F, Paris Cité, 75013 Paris (Entrer par le hall, monter au 2ᵉ étage, prendre l&amp;#8217;escalier F, monter un étage) Inscription obligatoire, au plus tard le 24 septembre : aphginscription75@gmail.com Au programme 9h-9h15 : Accueil 9h15-10h30 : Environnements – Les enjeux épistémologiques et didactiques, par Caroline Leininger-Frézal (PU Paris Cité, Présidente du CNFG) [&amp;#8230;] L’article Journée d&amp;rsquo;étude APHG-CNFG le 26 septembre :</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21882,6 +22403,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E649" r:id="rId648"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E650" r:id="rId649"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E667" r:id="rId666"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G667"/>
+  <dimension ref="A1:G674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21254,7 +21254,6 @@
           <t>En lançant de grandes fouilles et de nouvelles institutions, Napoléon III fait de l’archéologie un instrument politique autant qu’un moteur de la recherche sur les origines de la France.</t>
         </is>
       </c>
-      <c r="G652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
@@ -21287,7 +21286,6 @@
           <t>Pourquoi un empereur au sommet de sa puissance abandonnerait-il volontairement le trône&amp;nbsp;? Entre maladie, réformes politiques et lassitude face aux complots, l’abdication de Dioclétien continue d’intriguer les historiens.</t>
         </is>
       </c>
-      <c r="G653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -21320,7 +21318,6 @@
           <t>Bien avant les débats sur les gaines sculptantes ou les talons hauts, la mode exposait déjà ses adeptes à des poisons, des radiations ou des incendies. Une histoire de l’élégance à des périodes où celle-ci pouvait se payer au prix fort.</t>
         </is>
       </c>
-      <c r="G654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
@@ -21353,7 +21350,6 @@
           <t>Où risquait-on le plus de mourir dans une ville médiévale&amp;nbsp;? En reconstituant 355 scènes d’homicides survenus entre 1296 et 1398, des historiens montrent que la violence suivait les flux de population, de commerce et de pouvoir.</t>
         </is>
       </c>
-      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -21386,7 +21382,6 @@
           <t>Si les piliers de l’histoire orale ont été posés dès 1921 par Marc&amp;nbsp;Bloch, les sources orales ont mis près d’un siècle à être admises comme telles en histoire. Pourquoi tant de précautions&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -21419,7 +21414,6 @@
           <t>À l’approche de la présidentielle brésilienne, le duel Lula&amp;nbsp;–&amp;nbsp;Flávio&amp;nbsp;Bolsonaro est marqué par une forte implication de leurs appuis respectifs au niveau international.</t>
         </is>
       </c>
-      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -21452,7 +21446,6 @@
           <t>Une assistante de rang subalterne filtre-t-elle réellement les informations parvenant jusqu’au chef de l’État&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
@@ -21485,7 +21478,6 @@
           <t>Le projet a été comparé par le gouverneur de l’État, un allié de Trump, à la vente de la Louisiane de 1803. L’article Pour lancer des milliers de fusées par an, SpaceX va occuper près de 0,5&amp;#160;% de la Louisiane est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -21518,7 +21510,6 @@
           <t>Ce que révèle le nouvel épisode de la guerre des cartes du président américain. L’article En prétendant renommer le lac Ontario, Trump s’inscrit dans la lignée de Mobutu est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -21551,7 +21542,6 @@
           <t>Une note interne attribuée à la plus grande banque russe révèle la logique et les impasses du conflit. L’article Les huit scénarios de la guerre en Ukraine (texte intégral de la note Sberbank) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -21584,7 +21574,6 @@
           <t>La multiplication des contenus générés avec l’assistance de l’intelligence artificielle pourrait conduire à une baisse de la fiabilité et de la qualité des modèles. L’article Plus d&amp;rsquo;un tiers des pages web publiées depuis le lancement de ChatGPT comportent des traces d&amp;rsquo;IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
@@ -21617,7 +21606,6 @@
           <t>En Ukraine, soldats et psychiatres découvrent le traumatisme d’une arme qui bouleverse les frontières de la guerre. L’article Dronophobie&amp;#160;: enquête sur le mal du XXIe siècle est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -21650,7 +21638,6 @@
           <t>John Ratcliffe est le premier directeur de la CIA à se rendre en Russie depuis l'invasion de février 2022. L’article Pourquoi le directeur de la CIA s’est-il rendu à Moscou&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -21683,7 +21670,6 @@
           <t>Une fuite inédite présente les objectifs du Kremlin en Ukraine comme pratiquement inatteignables. L’article La Russie n’a que 7&amp;#160;% de chances de remporter la guerre&amp;#160;: les huit scénarios dressés par Sberbank est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -21716,7 +21702,6 @@
           <t>Nous traduisons et commentons un mémorandum passé trop inaperçu en Europe. L’article Le nouveau projet de Trump&amp;#160;? Des corsaires dans le cyberespace est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -21749,7 +21734,237 @@
           <t>Samedi 26 septembre 2026, 9h-16h30 Halle aux Farines, Salle 379F, Paris Cité, 75013 Paris (Entrer par le hall, monter au 2ᵉ étage, prendre l&amp;#8217;escalier F, monter un étage) Inscription obligatoire, au plus tard le 24 septembre : aphginscription75@gmail.com Au programme 9h-9h15 : Accueil 9h15-10h30 : Environnements – Les enjeux épistémologiques et didactiques, par Caroline Leininger-Frézal (PU Paris Cité, Présidente du CNFG) [&amp;#8230;] L’article Journée d&amp;rsquo;étude APHG-CNFG le 26 septembre :</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:47</t>
+        </is>
+      </c>
+      <c r="D668" s="3" t="inlineStr">
+        <is>
+          <t>Téléphone au lycée : comment transformer une interdiction en éducation ?</t>
+        </is>
+      </c>
+      <c r="E668" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/telephone-au-lycee-comment-transformer-une-interdiction-en-education-290377</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>À partir du 1er septembre, les téléphones portables seront interdits au lycée. Mais une interdiction ne peut suffire à une véritable éducation numérique.</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:31</t>
+        </is>
+      </c>
+      <c r="D669" s="3" t="inlineStr">
+        <is>
+          <t>Qu’est-ce qu’un « bon » prof à l’ère de l’IA ?</t>
+        </is>
+      </c>
+      <c r="E669" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/quest-ce-quun-bon-prof-a-lere-de-lia-288129</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>L’identité des enseignants s’est longtemps construite sur la maîtrise de disciplines. Mais être expert d’un domaine ne suffit pas à bien «&amp;nbsp;faire apprendre&amp;nbsp;» les élèves, et l’IA change la donne.</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:42</t>
+        </is>
+      </c>
+      <c r="D670" s="3" t="inlineStr">
+        <is>
+          <t>Que pensent vraiment les Israéliens et les Palestiniens ?</t>
+        </is>
+      </c>
+      <c r="E670" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/que-pensent-vraiment-les-israeliens-et-les-palestiniens-290490</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Un examen attentif de plusieurs sondages récents conduits auprès des Palestiniens comme des Israéliens donne un aperçu des craintes et des espoirs des deux populations.</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2026-08-28 16:20</t>
+        </is>
+      </c>
+      <c r="D671" s="3" t="inlineStr">
+        <is>
+          <t>Quelles sont les leçons de la guerre en Ukraine pour l’Armée populaire de libération ?</t>
+        </is>
+      </c>
+      <c r="E671" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/28/quelles-sont-les-lecons-de-la-guerre-en-ukraine-pour-larmee-populaire-de-liberation/</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Pour l’armée chinoise, la guerre en Ukraine n’est qu’une «&amp;#160;phase transitoire&amp;#160;» de la guerre moderne, avant l’utilisation à grande échelle de l’intelligence artificielle et des essaims de drones. L’article Quelles sont les leçons de la guerre en Ukraine pour l’Armée populaire de libération&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>2026-08-28 15:14</t>
+        </is>
+      </c>
+      <c r="D672" s="3" t="inlineStr">
+        <is>
+          <t>L’oligarque qui a déclaré la guerre aux oligarques</t>
+        </is>
+      </c>
+      <c r="E672" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/28/loligarque-qui-declare-la-guerre-aux-oligarques/</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>En Indonésie, Prabowo Subianto installe une nouvelle forme de capitalisme d’État clanique. L’article L’oligarque qui a déclaré la guerre aux oligarques est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2026-08-28 04:30</t>
+        </is>
+      </c>
+      <c r="D673" s="3" t="inlineStr">
+        <is>
+          <t>Les États-Unis gagnent plus souvent lorsque les guerres sont courtes</t>
+        </is>
+      </c>
+      <c r="E673" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/28/les-etats-unis-gagnent-plus-souvent-lorsque-les-guerres-sont-courtes/</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Les États-Unis ont remporté 50&amp;#160;% des guerres de plus de six mois depuis 1945, et 89&amp;#160;% des guerres de moins de six mois. L’article Les États-Unis gagnent plus souvent lorsque les guerres sont courtes est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 20:39</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2026-08-28 04:00</t>
+        </is>
+      </c>
+      <c r="D674" s="3" t="inlineStr">
+        <is>
+          <t>La Base idéologique du général Vannacci (texte intégral)</t>
+        </is>
+      </c>
+      <c r="E674" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/28/la-base-ideologique-du-general-vannacci-texte-integral/</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Nous avons traduit et annoté le programme de Futuro Nazionale, la force d’extrême droite qui fait trembler Meloni. L’article La Base idéologique du général Vannacci (texte intégral) est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -22419,6 +22634,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E665" r:id="rId664"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E666" r:id="rId665"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E674" r:id="rId673"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G674"/>
+  <dimension ref="A1:G677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21766,7 +21766,6 @@
           <t>À partir du 1er septembre, les téléphones portables seront interdits au lycée. Mais une interdiction ne peut suffire à une véritable éducation numérique.</t>
         </is>
       </c>
-      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="inlineStr">
@@ -21799,7 +21798,6 @@
           <t>L’identité des enseignants s’est longtemps construite sur la maîtrise de disciplines. Mais être expert d’un domaine ne suffit pas à bien «&amp;nbsp;faire apprendre&amp;nbsp;» les élèves, et l’IA change la donne.</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
@@ -21832,7 +21830,6 @@
           <t>Un examen attentif de plusieurs sondages récents conduits auprès des Palestiniens comme des Israéliens donne un aperçu des craintes et des espoirs des deux populations.</t>
         </is>
       </c>
-      <c r="G670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -21865,7 +21862,6 @@
           <t>Pour l’armée chinoise, la guerre en Ukraine n’est qu’une «&amp;#160;phase transitoire&amp;#160;» de la guerre moderne, avant l’utilisation à grande échelle de l’intelligence artificielle et des essaims de drones. L’article Quelles sont les leçons de la guerre en Ukraine pour l’Armée populaire de libération&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -21898,7 +21894,6 @@
           <t>En Indonésie, Prabowo Subianto installe une nouvelle forme de capitalisme d’État clanique. L’article L’oligarque qui a déclaré la guerre aux oligarques est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -21931,7 +21926,6 @@
           <t>Les États-Unis ont remporté 50&amp;#160;% des guerres de plus de six mois depuis 1945, et 89&amp;#160;% des guerres de moins de six mois. L’article Les États-Unis gagnent plus souvent lorsque les guerres sont courtes est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="inlineStr">
@@ -21964,7 +21958,105 @@
           <t>Nous avons traduit et annoté le programme de Futuro Nazionale, la force d’extrême droite qui fait trembler Meloni. L’article La Base idéologique du général Vannacci (texte intégral) est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29 14:08</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2026-08-29 12:12</t>
+        </is>
+      </c>
+      <c r="D675" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : la fortune des milliardaires a bondi de 20 % l’an dernier</t>
+        </is>
+      </c>
+      <c r="E675" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/29/economie-russe-la-fortune-des-milliardaires-a-bondi-de-20-lan-dernier/</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Le ratio entre la fortune des milliardaires russes et le PIB du pays atteint 27&amp;#160;%, soit plus que l’Inde et les États-Unis. L’article Économie russe&amp;#160;: la fortune des milliardaires a bondi de 20&amp;#160;% l’an dernier est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29 14:08</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>2026-08-29 05:32</t>
+        </is>
+      </c>
+      <c r="D676" s="3" t="inlineStr">
+        <is>
+          <t>L’Islande vote sur l’accession à l’Union européenne</t>
+        </is>
+      </c>
+      <c r="E676" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/29/lislande-vote-sur-laccession-a-lunion-europeenne/</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Aujourd’hui, 29 août, les Islandais votent lors d'un référendum sur la réouverture des négociations d’adhésion du pays à l’Union. L’article L’Islande vote sur l’accession à l’Union européenne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29 14:08</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>2026-08-29 04:00</t>
+        </is>
+      </c>
+      <c r="D677" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la Chine doit être autoritaire</t>
+        </is>
+      </c>
+      <c r="E677" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/29/pourquoi-la-chine-doit-etre-autoritaire/</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>L’un des articles les plus importants pour comprendre la Chine de Xi Jinping, pour la première fois en français. L’article Pourquoi la Chine doit être autoritaire est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -22641,6 +22733,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E672" r:id="rId671"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E673" r:id="rId672"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E677" r:id="rId676"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G677"/>
+  <dimension ref="A1:G680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21990,7 +21990,6 @@
           <t>Le ratio entre la fortune des milliardaires russes et le PIB du pays atteint 27&amp;#160;%, soit plus que l’Inde et les États-Unis. L’article Économie russe&amp;#160;: la fortune des milliardaires a bondi de 20&amp;#160;% l’an dernier est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="inlineStr">
@@ -22023,7 +22022,6 @@
           <t>Aujourd’hui, 29 août, les Islandais votent lors d'un référendum sur la réouverture des négociations d’adhésion du pays à l’Union. L’article L’Islande vote sur l’accession à l’Union européenne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -22056,7 +22054,105 @@
           <t>L’un des articles les plus importants pour comprendre la Chine de Xi Jinping, pour la première fois en français. L’article Pourquoi la Chine doit être autoritaire est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30 14:14</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>2026-08-30 04:30</t>
+        </is>
+      </c>
+      <c r="D678" s="3" t="inlineStr">
+        <is>
+          <t>[Simulations exclusives] Saxe-Anhalt : l’AfD gouvernerait dans plus de 6 scénarios sur 10 en cas d’abstention du BSW</t>
+        </is>
+      </c>
+      <c r="E678" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/30/simulations-exclusives-saxe-anhalt-lafd-gouvernerait-dans-plus-de-6-scenarios-sur-10-en-cas-dabstention-du-bsw/</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Les habitants de Saxe-Anhalt se rendront aux urnes dimanche prochain, le 6 septembre, pour élire les 83 députés du Landtag. Selon notre dernière simulation, l’AfD pourrait remporter l’immense majorité des circonscriptions de la région. L’article [Simulations exclusives] Saxe-Anhalt&amp;#160;: l’AfD gouvernerait dans plus de 6 scénarios sur 10 en cas d’abstention du BSW est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30 14:14</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>2026-08-30 04:00</t>
+        </is>
+      </c>
+      <c r="D679" s="3" t="inlineStr">
+        <is>
+          <t>La fabrique de l’individu occidental</t>
+        </is>
+      </c>
+      <c r="E679" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/30/la-fabrique-de-lindividu-occidental/</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>De la vie sobre aux fractures contemporaines de l’individualisation, la longue généalogie d'une émancipation paradoxale. L’article La fabrique de l’individu occidental est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30 14:14</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2026-08-29 14:58</t>
+        </is>
+      </c>
+      <c r="D680" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi le capitalisme n’arrive plus à penser un futur habitable ?</t>
+        </is>
+      </c>
+      <c r="E680" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/29/pourquoi-le-capitalisme-narrive-plus-a-penser-un-futur-habitable/</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Une conversation sur la crise d’un modèle civilisationnel par l’auteur de The Alibi of Capital . L’article Pourquoi le capitalisme n&amp;rsquo;arrive plus à penser un futur habitable&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -22736,6 +22832,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E675" r:id="rId674"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E676" r:id="rId675"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E680" r:id="rId679"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G680"/>
+  <dimension ref="A1:G691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22086,7 +22086,6 @@
           <t>Les habitants de Saxe-Anhalt se rendront aux urnes dimanche prochain, le 6 septembre, pour élire les 83 députés du Landtag. Selon notre dernière simulation, l’AfD pourrait remporter l’immense majorité des circonscriptions de la région. L’article [Simulations exclusives] Saxe-Anhalt&amp;#160;: l’AfD gouvernerait dans plus de 6 scénarios sur 10 en cas d’abstention du BSW est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
@@ -22119,7 +22118,6 @@
           <t>De la vie sobre aux fractures contemporaines de l’individualisation, la longue généalogie d'une émancipation paradoxale. L’article La fabrique de l’individu occidental est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
@@ -22152,7 +22150,369 @@
           <t>Une conversation sur la crise d’un modèle civilisationnel par l’auteur de The Alibi of Capital . L’article Pourquoi le capitalisme n&amp;rsquo;arrive plus à penser un futur habitable&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:30</t>
+        </is>
+      </c>
+      <c r="D681" s="3" t="inlineStr">
+        <is>
+          <t>Comment l’école maternelle s’est mise à évaluer les enfants : retour sur un siècle de transformations</t>
+        </is>
+      </c>
+      <c r="E681" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/comment-lecole-maternelle-sest-mise-a-evaluer-les-enfants-retour-sur-un-siecle-de-transformations-285793</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>En cette rentrée 2026-2027, un nouveau programme scolaire entre en vigueur en maternelle, et c’est la huitième&amp;nbsp;fois depuis&amp;nbsp;1977. Pourquoi une telle inflation de textes officiels&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:18</t>
+        </is>
+      </c>
+      <c r="D682" s="3" t="inlineStr">
+        <is>
+          <t>Réseaux sociaux : quand l’État contraint les jeunes plutôt que les plateformes</t>
+        </is>
+      </c>
+      <c r="E682" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/reseaux-sociaux-quand-letat-contraint-les-jeunes-plutot-que-les-plateformes-290383</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Sous l’impulsion d’Emmanuel Macron, l’État a multiplié les mesures contraignantes pour les jeunes utilisateurs de réseaux, tout en épargnant largement les plateformes.</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:28</t>
+        </is>
+      </c>
+      <c r="D683" s="3" t="inlineStr">
+        <is>
+          <t>Les « comptes Trump » : les angles morts d’une vaste opération de marketing politique</t>
+        </is>
+      </c>
+      <c r="E683" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-comptes-trump-les-angles-morts-dune-vaste-operation-de-marketing-politique-290456</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Les «&amp;nbsp;comptes Trump&amp;nbsp;» promettent d’aider les jeunes mineurs, citoyens des États-Unis, à se constituer un patrimoine. Mais le dispositif pourrait surtout profiter aux familles aisées.</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:42</t>
+        </is>
+      </c>
+      <c r="D684" s="3" t="inlineStr">
+        <is>
+          <t>Ceuta : ce qui se joue derrière le récit de la « crise migratoire »</t>
+        </is>
+      </c>
+      <c r="E684" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ceuta-ce-qui-se-joue-derriere-le-recit-de-la-crise-migratoire-290080</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Fin juillet, des dizaines de milliers de migrants ont pénétré à Ceuta. L’hypothèse d’un complot du gouvernement marocain a circulé, mais les sciences sociales décrivent plutôt un faisceau de mécanismes complexes.</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:05</t>
+        </is>
+      </c>
+      <c r="D685" s="3" t="inlineStr">
+        <is>
+          <t>Quelles sont les leçons du piratage de Hugging Face par les agents d’OpenAI ?</t>
+        </is>
+      </c>
+      <c r="E685" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/31/quelles-sont-les-lecons-du-piratage-de-hugging-face-par-les-agents-dopenai/</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Sans supervision, 700 agents d’OpenAI se sont ligués pour mener une opération de piratage sans précédent. L’article Quelles sont les leçons du piratage de Hugging Face par les agents d&amp;rsquo;OpenAI&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:28</t>
+        </is>
+      </c>
+      <c r="D686" s="3" t="inlineStr">
+        <is>
+          <t>Marine Le Pen peut-elle encore perdre l’élection présidentielle ?</t>
+        </is>
+      </c>
+      <c r="E686" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/31/marine-le-pen-peut-elle-encore-perdre-lelection-presidentielle/</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Cinq mécanismes peuvent empêcher le Rassemblement national de gagner en 2027. L’article Marine Le Pen peut-elle encore perdre l’élection présidentielle&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:12</t>
+        </is>
+      </c>
+      <c r="D687" s="3" t="inlineStr">
+        <is>
+          <t>Mgr Gallagher à Moscou : les permanences de la nouvelle Ostpolitik du Saint-Siège au service de la paix</t>
+        </is>
+      </c>
+      <c r="E687" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/31/leon-xiv-envoie-ministre-des-affaires-etrangeres-a-moscou-les-permanences-de-la-nouvelle-ostpolitik-du-saint-siege-au-service-de-la-paix/</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>L’archevêque Paul Richard Gallagher est arrivé à Moscou au même moment où Washington y dépêchait le directeur de la CIA. L’article Mgr Gallagher à Moscou&amp;#160;: les permanences de la nouvelle Ostpolitik du Saint-Siège au service de la paix est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:24</t>
+        </is>
+      </c>
+      <c r="D688" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Méthodologie de la dissertation en histoire</t>
+        </is>
+      </c>
+      <c r="E688" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-methodologie-de-la-dissertation-en-histoire-2/</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Joëlle Alazard et consacrée à la méthodologie de la dissertation en histoire. Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne – Méthodologie de la dissertation en histoire est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:20</t>
+        </is>
+      </c>
+      <c r="D689" s="3" t="inlineStr">
+        <is>
+          <t>Coup de pouce Agrégation interne – Méthodologie de l’épreuve 3</t>
+        </is>
+      </c>
+      <c r="E689" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/coup-de-pouce-agregation-interne-methodologie-de-lepreuve-3/</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Olivier Erudel et Camille Lambin et consacrée à la méthodologie de l&amp;#8217;épreuve 3 des écrits. Le [&amp;#8230;] L’article Coup de pouce Agrégation interne – Méthodologie de l&amp;rsquo;épreuve 3 est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>2026-06-26 14:29</t>
+        </is>
+      </c>
+      <c r="D690" s="3" t="inlineStr">
+        <is>
+          <t>Camille Morata – Aux sombres héros de la guerre: vie, mort et mémoires des footballeurs dans le premier conflit mondial</t>
+        </is>
+      </c>
+      <c r="E690" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/camille-morata-aux-sombres-heros-de-la-guerre-vie-mort-et-memoires-des-footballeurs-dans-le-premier-conflit-mondial/</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1222374881?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 16:39</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:29</t>
+        </is>
+      </c>
+      <c r="D691" s="3" t="inlineStr">
+        <is>
+          <t>Julien Beaufils – Le foot en RDA: politique, société, culture.</t>
+        </is>
+      </c>
+      <c r="E691" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/julien-beaufils-le-foot-en-rda-politique-societe-culture/</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1222374882?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -22835,6 +23195,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E678" r:id="rId677"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E679" r:id="rId678"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E686" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E687" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E688" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E689" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E690" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E691" r:id="rId690"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G691"/>
+  <dimension ref="A1:G695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22182,7 +22182,6 @@
           <t>En cette rentrée 2026-2027, un nouveau programme scolaire entre en vigueur en maternelle, et c’est la huitième&amp;nbsp;fois depuis&amp;nbsp;1977. Pourquoi une telle inflation de textes officiels&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -22215,7 +22214,6 @@
           <t>Sous l’impulsion d’Emmanuel Macron, l’État a multiplié les mesures contraignantes pour les jeunes utilisateurs de réseaux, tout en épargnant largement les plateformes.</t>
         </is>
       </c>
-      <c r="G682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -22248,7 +22246,6 @@
           <t>Les «&amp;nbsp;comptes Trump&amp;nbsp;» promettent d’aider les jeunes mineurs, citoyens des États-Unis, à se constituer un patrimoine. Mais le dispositif pourrait surtout profiter aux familles aisées.</t>
         </is>
       </c>
-      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -22281,7 +22278,6 @@
           <t>Fin juillet, des dizaines de milliers de migrants ont pénétré à Ceuta. L’hypothèse d’un complot du gouvernement marocain a circulé, mais les sciences sociales décrivent plutôt un faisceau de mécanismes complexes.</t>
         </is>
       </c>
-      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="inlineStr">
@@ -22314,7 +22310,6 @@
           <t>Sans supervision, 700 agents d’OpenAI se sont ligués pour mener une opération de piratage sans précédent. L’article Quelles sont les leçons du piratage de Hugging Face par les agents d&amp;rsquo;OpenAI&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -22347,7 +22342,6 @@
           <t>Cinq mécanismes peuvent empêcher le Rassemblement national de gagner en 2027. L’article Marine Le Pen peut-elle encore perdre l’élection présidentielle&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -22380,7 +22374,6 @@
           <t>L’archevêque Paul Richard Gallagher est arrivé à Moscou au même moment où Washington y dépêchait le directeur de la CIA. L’article Mgr Gallagher à Moscou&amp;#160;: les permanences de la nouvelle Ostpolitik du Saint-Siège au service de la paix est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
@@ -22413,7 +22406,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Joëlle Alazard et consacrée à la méthodologie de la dissertation en histoire. Le podcast est proposé [&amp;#8230;] L’article Coup de pouce Agrégation interne – Méthodologie de la dissertation en histoire est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
@@ -22446,7 +22438,6 @@
           <t>Opération coup de pouce pour préparer l’Agrégation interne organisée par l’APHG pour ses adhérents de l’année 2026-2027 sous la forme de conférences et de séances de méthodologie des épreuves. Vous pouvez retrouver sur cette page une séance proposée par Olivier Erudel et Camille Lambin et consacrée à la méthodologie de l&amp;#8217;épreuve 3 des écrits. Le [&amp;#8230;] L’article Coup de pouce Agrégation interne – Méthodologie de l&amp;rsquo;épreuve 3 est apparu en premier sur APHG .</t>
         </is>
       </c>
-      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -22479,7 +22470,6 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1222374881?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
@@ -22512,7 +22502,138 @@
           <t xml:space="preserve">Ce café &amp;#8211; modèle hybride entre la visioconférence en public et l&amp;#8217;entretien &amp;#8211; est à retrouver en accès réservé aux adhérents et en version audio pour protéger le droit à l&amp;#8217;image des participants. &amp;#160; &amp;#60;div style= »padding:56.25% 0 0 0;position:relative; »&amp;#62;&amp;#60;iframe src= »https://player.vimeo.com/video/1222374882?title=0&amp;#38;amp;byline=0&amp;#38;amp;portrait=0&amp;#38;amp;badge=0&amp;#38;amp;autopause=0&amp;#38;amp;player_id=0&amp;#38;amp;app_id=58479&amp;#8243; frameborder= »0&amp;#8243; </t>
         </is>
       </c>
-      <c r="G691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:53</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:42</t>
+        </is>
+      </c>
+      <c r="D692" s="3" t="inlineStr">
+        <is>
+          <t>Le régime iranien craint un nouveau mouvement de protestation</t>
+        </is>
+      </c>
+      <c r="E692" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/01/le-regime-iranien-craint-un-nouveau-mouvement-de-protestation-1/</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>La stratégie de pression économique américaine va-t-elle faire plier Téhéran&amp;#160;? L’article Le régime iranien craint un nouveau mouvement de protestation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:53</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:30</t>
+        </is>
+      </c>
+      <c r="D693" s="3" t="inlineStr">
+        <is>
+          <t>Les universités européennes attirent de plus en plus d’étudiants internationaux</t>
+        </is>
+      </c>
+      <c r="E693" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/01/les-universites-europeennes-attirent-de-plus-en-plus-detudiants-internationaux/</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Face au durcissement des politiques migratoires et à des frais de scolarité élevés au Royaume-Uni et aux États-Unis, les inscriptions sont en hausse dans les universités européennes. L’article Les universités européennes attirent de plus en plus d’étudiants internationaux est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:53</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:30</t>
+        </is>
+      </c>
+      <c r="D694" s="3" t="inlineStr">
+        <is>
+          <t>Le vrai prédateur</t>
+        </is>
+      </c>
+      <c r="E694" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/01/le-vrai-predateur/</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Comment Mark Zuckerberg a utilisé les neurosciences pour transformer les vulnérabilités du cerveau des enfants en modèle économique. L’article Le vrai prédateur est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 13:53</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:30</t>
+        </is>
+      </c>
+      <c r="D695" s="3" t="inlineStr">
+        <is>
+          <t>En amont des midterms, le cercle rapproché de Trump se réduit</t>
+        </is>
+      </c>
+      <c r="E695" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/08/31/en-amont-des-midterms-le-cercle-rapproche-de-trump-se-reduit/</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Plus d'un responsable confirmé par le Sénat sur neuf a quitté l'administration Trump depuis janvier 2025, soit deux fois plus que lors de son premier mandat. L’article En amont des midterms, le cercle rapproché de Trump se réduit est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23206,6 +23327,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E689" r:id="rId688"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E690" r:id="rId689"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E691" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E692" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E693" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E694" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E695" r:id="rId694"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G695"/>
+  <dimension ref="A1:G704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22534,7 +22534,6 @@
           <t>La stratégie de pression économique américaine va-t-elle faire plier Téhéran&amp;#160;? L’article Le régime iranien craint un nouveau mouvement de protestation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
@@ -22567,7 +22566,6 @@
           <t>Face au durcissement des politiques migratoires et à des frais de scolarité élevés au Royaume-Uni et aux États-Unis, les inscriptions sont en hausse dans les universités européennes. L’article Les universités européennes attirent de plus en plus d’étudiants internationaux est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -22600,7 +22598,6 @@
           <t>Comment Mark Zuckerberg a utilisé les neurosciences pour transformer les vulnérabilités du cerveau des enfants en modèle économique. L’article Le vrai prédateur est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -22633,7 +22630,303 @@
           <t>Plus d'un responsable confirmé par le Sénat sur neuf a quitté l'administration Trump depuis janvier 2025, soit deux fois plus que lors de son premier mandat. L’article En amont des midterms, le cercle rapproché de Trump se réduit est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:01</t>
+        </is>
+      </c>
+      <c r="D696" s="3" t="inlineStr">
+        <is>
+          <t>Une rentrée sans toit : comment la crise du logement étudiant fragilise l’entrée dans l’âge adulte</t>
+        </is>
+      </c>
+      <c r="E696" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/une-rentree-sans-toit-comment-la-crise-du-logement-etudiant-fragilise-lentree-dans-lage-adulte-289101</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Le logement est une étape clé dans l’entrée dans l’âge adulte. Le manque d’ancrage résidentiel stable enclenche des retards en chaîne en matière de formation et d’emploi.</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:01</t>
+        </is>
+      </c>
+      <c r="D697" s="3" t="inlineStr">
+        <is>
+          <t>Vagues de chaleur à l’école : pourquoi rénover les murs ne suffira pas</t>
+        </is>
+      </c>
+      <c r="E697" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vagues-de-chaleur-a-lecole-pourquoi-renover-les-murs-ne-suffira-pas-289415</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>La fraîcheur d'une classe ne dépend pas seulement de la rénovation thermique des bâtiments&amp;nbsp;: elle dépend aussi de la matière dont ils sont faits et de la façon dont on les occupe.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:59</t>
+        </is>
+      </c>
+      <c r="D698" s="3" t="inlineStr">
+        <is>
+          <t>« Et clic, l’argent est là » : les usages du crédit digital en Côte d’Ivoire</t>
+        </is>
+      </c>
+      <c r="E698" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/et-clic-largent-est-la-les-usages-du-credit-digital-en-cote-divoire-290006</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Une enquête de terrain montre comment, en Côte d’Ivoire, le crédit digital permet de faire face aux imprévus sans bouleverser les pratiques budgétaires.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:04</t>
+        </is>
+      </c>
+      <c r="D699" s="3" t="inlineStr">
+        <is>
+          <t>Après le Pakistan, l’Ouzbékistan se dote d’avions de combat chinois</t>
+        </is>
+      </c>
+      <c r="E699" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/02/apres-le-pakistan-louzbekistan-se-dote-davions-de-combat-chinois/</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>L’achat par Tachkent d’appareils chinois témoigne de l’érosion de l’influence russe en Asie centrale. L’article Après le Pakistan, l’Ouzbékistan se dote d’avions de combat chinois est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:30</t>
+        </is>
+      </c>
+      <c r="D700" s="3" t="inlineStr">
+        <is>
+          <t>La France est l’un des pays européens qui dépense le moins pour l’éducation</t>
+        </is>
+      </c>
+      <c r="E700" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/02/la-france-est-lun-des-pays-europeens-qui-depense-le-moins-pour-leducation/</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Une part plus élevée de dépenses dans l’éducation ne se traduit toutefois pas toujours par de meilleurs résultats pour les élèves. L’article La France est l’un des pays européens qui dépense le moins pour l’éducation est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:02</t>
+        </is>
+      </c>
+      <c r="D701" s="3" t="inlineStr">
+        <is>
+          <t>La coalition Trump se défait dans les sondages</t>
+        </is>
+      </c>
+      <c r="E701" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/02/la-coalition-trump-se-defait-dans-les-sondages/</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Les grandes tendances politiques aux Etats-Unis à deux mois des midterms . L’article La coalition Trump se défait dans les sondages est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:32</t>
+        </is>
+      </c>
+      <c r="D702" s="3" t="inlineStr">
+        <is>
+          <t>Nous avons basculé dans le dernier tiers des années 2020</t>
+        </is>
+      </c>
+      <c r="E702" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/01/nous-avons-bascule-dans-le-dernier-tiers-des-annees-2020/</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>L’humanité est plus proche de la fin de la décennie que du 1er mai 2023. L’article Nous avons basculé dans le dernier tiers des années 2020 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:14</t>
+        </is>
+      </c>
+      <c r="D703" s="3" t="inlineStr">
+        <is>
+          <t>Au Venezuela, Trump ouvre l’ère de la recolonisation américaine</t>
+        </is>
+      </c>
+      <c r="E703" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/01/au-venezuela-trump-ouvre-lere-de-recolonisation-americaine/</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Analyses et projections de l’accord pétrolier présenté par la Maison-Blanche. L’article Au Venezuela, Trump ouvre l’ère de la recolonisation américaine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>2026-09-01 16:00</t>
+        </is>
+      </c>
+      <c r="D704" s="3" t="inlineStr">
+        <is>
+          <t>La progression russe en Ukraine est au plus bas depuis près de trois ans</t>
+        </is>
+      </c>
+      <c r="E704" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/01/la-progression-russe-en-ukraine-est-au-plus-bas-depuis-pres-de-trois-ans/</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>L’absence de succès majeurs pourrait conduire Poutine à une nouvelle escalade. L’article La progression russe en Ukraine est au plus bas depuis près de trois ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23331,6 +23624,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E693" r:id="rId692"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E694" r:id="rId693"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E695" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E696" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E697" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E698" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E699" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E700" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E701" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E702" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E703" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E704" r:id="rId703"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G704"/>
+  <dimension ref="A1:G710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22662,7 +22662,6 @@
           <t>Le logement est une étape clé dans l’entrée dans l’âge adulte. Le manque d’ancrage résidentiel stable enclenche des retards en chaîne en matière de formation et d’emploi.</t>
         </is>
       </c>
-      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -22695,7 +22694,6 @@
           <t>La fraîcheur d'une classe ne dépend pas seulement de la rénovation thermique des bâtiments&amp;nbsp;: elle dépend aussi de la matière dont ils sont faits et de la façon dont on les occupe.</t>
         </is>
       </c>
-      <c r="G697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
@@ -22728,7 +22726,6 @@
           <t>Une enquête de terrain montre comment, en Côte d’Ivoire, le crédit digital permet de faire face aux imprévus sans bouleverser les pratiques budgétaires.</t>
         </is>
       </c>
-      <c r="G698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -22761,7 +22758,6 @@
           <t>L’achat par Tachkent d’appareils chinois témoigne de l’érosion de l’influence russe en Asie centrale. L’article Après le Pakistan, l’Ouzbékistan se dote d’avions de combat chinois est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -22794,7 +22790,6 @@
           <t>Une part plus élevée de dépenses dans l’éducation ne se traduit toutefois pas toujours par de meilleurs résultats pour les élèves. L’article La France est l’un des pays européens qui dépense le moins pour l’éducation est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -22827,7 +22822,6 @@
           <t>Les grandes tendances politiques aux Etats-Unis à deux mois des midterms . L’article La coalition Trump se défait dans les sondages est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="inlineStr">
@@ -22860,7 +22854,6 @@
           <t>L’humanité est plus proche de la fin de la décennie que du 1er mai 2023. L’article Nous avons basculé dans le dernier tiers des années 2020 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -22893,7 +22886,6 @@
           <t>Analyses et projections de l’accord pétrolier présenté par la Maison-Blanche. L’article Au Venezuela, Trump ouvre l’ère de la recolonisation américaine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -22926,7 +22918,204 @@
           <t>L’absence de succès majeurs pourrait conduire Poutine à une nouvelle escalade. L’article La progression russe en Ukraine est au plus bas depuis près de trois ans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:04</t>
+        </is>
+      </c>
+      <c r="D705" s="3" t="inlineStr">
+        <is>
+          <t>Le Maghreb, un territoire à géométrie variable</t>
+        </is>
+      </c>
+      <c r="E705" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-maghreb-un-territoire-a-geometrie-variable-290265</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Que recouvre la notion de Maghreb&amp;nbsp;? Selon qui la définit, l’époque ou le point de vue, la réponse varie.</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:22</t>
+        </is>
+      </c>
+      <c r="D706" s="3" t="inlineStr">
+        <is>
+          <t>L’Union est toujours à la recherche d’une politique extérieure</t>
+        </is>
+      </c>
+      <c r="E706" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/03/lunion-est-toujours-a-la-recherche-dune-politique-exterieure/</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Un groupe de pays plaide pour réformer le processus décisionnel de la politique étrangère du bloc. L’article L’Union est toujours à la recherche d’une politique extérieure est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>2026-09-03 05:01</t>
+        </is>
+      </c>
+      <c r="D707" s="3" t="inlineStr">
+        <is>
+          <t>Cet îlot est-il français ?</t>
+        </is>
+      </c>
+      <c r="E707" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/03/cet-ilot-est-il-francais/</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Dans le Pacifique sud, le différend autour de Matthew et Hunter pourrait remettre en cause la stratégie indo-pacifique française. L’article Cet îlot est-il français&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:30</t>
+        </is>
+      </c>
+      <c r="D708" s="3" t="inlineStr">
+        <is>
+          <t>IA : la Corée du Sud veut transformer le boom des semi-conducteurs en cycle vertueux de croissance</t>
+        </is>
+      </c>
+      <c r="E708" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/03/ia-la-coree-du-sud-veut-transformer-le-boom-des-semi-conducteurs-en-cycle-vertueux-de-croissance/</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Séoul veut doubler l’an prochain son budget consacré aux puces, à l'IA et aux centres de données. L’article IA&amp;#160;: la Corée du Sud veut transformer le boom des semi-conducteurs en cycle vertueux de croissance est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:23</t>
+        </is>
+      </c>
+      <c r="D709" s="3" t="inlineStr">
+        <is>
+          <t>Le chaînon manquant : les réseaux sociaux au cœur de « l’attaque » contre Ceuta</t>
+        </is>
+      </c>
+      <c r="E709" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/02/le-chainon-manquant-les-reseaux-sociaux-au-coeur-de-lattaque-contre-ceuta/</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>La plus grave crise migratoire de l'histoire récente de l'Espagne s'est coordonnée sur Facebook et WhatsApp, toutes deux propriétés de Mark Zuckerberg. L’article Le chaînon manquant&amp;#160;: les réseaux sociaux au cœur de «&amp;#160;l’attaque&amp;#160;» contre Ceuta est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:13</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:09</t>
+        </is>
+      </c>
+      <c r="D710" s="3" t="inlineStr">
+        <is>
+          <t>Les particules élémentaires de la puissance européenne</t>
+        </is>
+      </c>
+      <c r="E710" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/02/les-particules-elementaires-de-la-puissance-europeenne/</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Après l’énergie et les minerais, l’Europe doit se réveiller face aux risques d’une autre dépendance structurelle&amp;#160;: les molécules critiques. L’article Les particules élémentaires de la puissance européenne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23633,6 +23822,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E702" r:id="rId701"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E703" r:id="rId702"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E704" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E705" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E706" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E707" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E708" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E709" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E710" r:id="rId709"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G710"/>
+  <dimension ref="A1:G719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22950,7 +22950,6 @@
           <t>Que recouvre la notion de Maghreb&amp;nbsp;? Selon qui la définit, l’époque ou le point de vue, la réponse varie.</t>
         </is>
       </c>
-      <c r="G705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -22983,7 +22982,6 @@
           <t>Un groupe de pays plaide pour réformer le processus décisionnel de la politique étrangère du bloc. L’article L’Union est toujours à la recherche d’une politique extérieure est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -23016,7 +23014,6 @@
           <t>Dans le Pacifique sud, le différend autour de Matthew et Hunter pourrait remettre en cause la stratégie indo-pacifique française. L’article Cet îlot est-il français&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -23049,7 +23046,6 @@
           <t>Séoul veut doubler l’an prochain son budget consacré aux puces, à l'IA et aux centres de données. L’article IA&amp;#160;: la Corée du Sud veut transformer le boom des semi-conducteurs en cycle vertueux de croissance est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -23082,7 +23078,6 @@
           <t>La plus grave crise migratoire de l'histoire récente de l'Espagne s'est coordonnée sur Facebook et WhatsApp, toutes deux propriétés de Mark Zuckerberg. L’article Le chaînon manquant&amp;#160;: les réseaux sociaux au cœur de «&amp;#160;l’attaque&amp;#160;» contre Ceuta est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -23115,7 +23110,303 @@
           <t>Après l’énergie et les minerais, l’Europe doit se réveiller face aux risques d’une autre dépendance structurelle&amp;#160;: les molécules critiques. L’article Les particules élémentaires de la puissance européenne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:33</t>
+        </is>
+      </c>
+      <c r="D711" s="3" t="inlineStr">
+        <is>
+          <t>Avant d’être ennemis, ils étaient amis… La bromance méconnue de Guillaume le Conquérant et Harold</t>
+        </is>
+      </c>
+      <c r="E711" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/avant-detre-ennemis-ils-etaient-amis-la-bromance-meconnue-de-guillaume-le-conquerant-et-harold-291174</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Avant de s’affronter à Hastings en 1066, Guillaume de Normandie et Harold Godwinson furent alliés et compagnons d’armes. La tapisserie de Bayeux raconte aussi cette étonnante histoire d’amitié.</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:50</t>
+        </is>
+      </c>
+      <c r="D712" s="3" t="inlineStr">
+        <is>
+          <t>Un cinéaste à réhabiliter : René Clair au programme du baccalauréat</t>
+        </is>
+      </c>
+      <c r="E712" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/un-cineaste-a-rehabiliter-rene-clair-au-programme-du-baccalaureat-288775</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Auteur d’une trentaine de films qui ont accompagné l’histoire du cinéma, de 1923 à 1966, René Clair est un cinéaste à redécouvrir.</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:50</t>
+        </is>
+      </c>
+      <c r="D713" s="3" t="inlineStr">
+        <is>
+          <t>Périscolaire : derrière le scandale des violences sexuelles, un secteur en manque de projet politique ?</t>
+        </is>
+      </c>
+      <c r="E713" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/periscolaire-derriere-le-scandale-des-violences-sexuelles-un-secteur-en-manque-de-projet-politique-290797</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Le scandale des violences dans le périscolaire a révélé des failles dans le recrutement et la formation des animateurs. Mais le secteur ne souffre-t-il pas, avant tout, d’un désintérêt global, qui freine son cadrage et sa régulation&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:49</t>
+        </is>
+      </c>
+      <c r="D714" s="3" t="inlineStr">
+        <is>
+          <t>Au Népal, le contrôle du Tibet par la Chine complique la prévention des crues</t>
+        </is>
+      </c>
+      <c r="E714" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/au-nepal-le-controle-du-tibet-par-la-chine-complique-la-prevention-des-crues-290961</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>La crue meurtrière à la frontière sino-népalaise a mis en évidence le manque de coopération et de partage de données entre Pékin et Katmandou.</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:21</t>
+        </is>
+      </c>
+      <c r="D715" s="3" t="inlineStr">
+        <is>
+          <t>Avec Astra, la boîte noire d’OpenAI devient encore plus noire</t>
+        </is>
+      </c>
+      <c r="E715" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/04/avec-astra-la-boite-noire-dopenai-devient-encore-plus-noire/</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Une analyse technique pour mesurer la puissance de GPT-6 Astra. L’article Avec Astra, la boîte noire d’OpenAI devient encore plus noire est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:00</t>
+        </is>
+      </c>
+      <c r="D716" s="3" t="inlineStr">
+        <is>
+          <t>La crise allemande commence par la voiture</t>
+        </is>
+      </c>
+      <c r="E716" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/04/la-crise-allemande-commence-par-la-voiture/</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Les chiffres et les données du bouleversement au cœur industriel de l’Europe. L’article La crise allemande commence par la voiture est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:00</t>
+        </is>
+      </c>
+      <c r="D717" s="3" t="inlineStr">
+        <is>
+          <t>Sur la violence spéculative de l’IA</t>
+        </is>
+      </c>
+      <c r="E717" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/04/sur-la-violence-speculative-de-lia/</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>L’extrême droite a trouvé une nouvelle arme redoutable&amp;#160;: le déjà-vu. L’article Sur la violence spéculative de l’IA est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:30</t>
+        </is>
+      </c>
+      <c r="D718" s="3" t="inlineStr">
+        <is>
+          <t>Économie russe : en 40 jours de frappes, l’Ukraine aurait causé des dégâts équivalant à 1 % du PIB, selon Poutine</t>
+        </is>
+      </c>
+      <c r="E718" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/04/economie-russe-en-40-jours-de-frappes-lukraine-aurait-cause-des-degats-equivalant-a-1-du-pib-selon-poutine/</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Ces surprenantes déclarations du président russe pourraient servir à justifier une nouvelle escalade en Ukraine. L’article Économie russe&amp;#160;: en 40 jours de frappes, l’Ukraine aurait causé des dégâts équivalant à 1&amp;#160;% du PIB, selon Poutine est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:06</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:02</t>
+        </is>
+      </c>
+      <c r="D719" s="3" t="inlineStr">
+        <is>
+          <t>Trump serait-il prêt à reconnaître de facto la Corée du Nord comme une puissance nucléaire ?</t>
+        </is>
+      </c>
+      <c r="E719" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/03/trump-serait-il-pret-a-reconnaitre-de-facto-la-coree-du-nord-comme-une-puissance-nucleaire/</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Faute de succès en Iran, Trump pourrait faire des concessions à Pyongyang lors d’une rencontre susceptible d’avoir lieu d’ici la fin de l’année. L’article Trump serait-il prêt à reconnaître de facto la Corée du Nord comme une puissance nucléaire&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23828,6 +24119,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E708" r:id="rId707"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E709" r:id="rId708"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E710" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E711" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E712" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E713" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E714" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E715" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E716" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E717" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E718" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E719" r:id="rId718"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G719"/>
+  <dimension ref="A1:G722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23142,7 +23142,6 @@
           <t>Avant de s’affronter à Hastings en 1066, Guillaume de Normandie et Harold Godwinson furent alliés et compagnons d’armes. La tapisserie de Bayeux raconte aussi cette étonnante histoire d’amitié.</t>
         </is>
       </c>
-      <c r="G711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="inlineStr">
@@ -23175,7 +23174,6 @@
           <t>Auteur d’une trentaine de films qui ont accompagné l’histoire du cinéma, de 1923 à 1966, René Clair est un cinéaste à redécouvrir.</t>
         </is>
       </c>
-      <c r="G712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -23208,7 +23206,6 @@
           <t>Le scandale des violences dans le périscolaire a révélé des failles dans le recrutement et la formation des animateurs. Mais le secteur ne souffre-t-il pas, avant tout, d’un désintérêt global, qui freine son cadrage et sa régulation&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -23241,7 +23238,6 @@
           <t>La crue meurtrière à la frontière sino-népalaise a mis en évidence le manque de coopération et de partage de données entre Pékin et Katmandou.</t>
         </is>
       </c>
-      <c r="G714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="inlineStr">
@@ -23274,7 +23270,6 @@
           <t>Une analyse technique pour mesurer la puissance de GPT-6 Astra. L’article Avec Astra, la boîte noire d’OpenAI devient encore plus noire est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -23307,7 +23302,6 @@
           <t>Les chiffres et les données du bouleversement au cœur industriel de l’Europe. L’article La crise allemande commence par la voiture est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="inlineStr">
@@ -23340,7 +23334,6 @@
           <t>L’extrême droite a trouvé une nouvelle arme redoutable&amp;#160;: le déjà-vu. L’article Sur la violence spéculative de l’IA est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="inlineStr">
@@ -23373,7 +23366,6 @@
           <t>Ces surprenantes déclarations du président russe pourraient servir à justifier une nouvelle escalade en Ukraine. L’article Économie russe&amp;#160;: en 40 jours de frappes, l’Ukraine aurait causé des dégâts équivalant à 1&amp;#160;% du PIB, selon Poutine est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -23406,7 +23398,105 @@
           <t>Faute de succès en Iran, Trump pourrait faire des concessions à Pyongyang lors d’une rencontre susceptible d’avoir lieu d’ici la fin de l’année. L’article Trump serait-il prêt à reconnaître de facto la Corée du Nord comme une puissance nucléaire&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05 12:19</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:30</t>
+        </is>
+      </c>
+      <c r="D720" s="3" t="inlineStr">
+        <is>
+          <t>Les pays européens retirent leur or des États-Unis</t>
+        </is>
+      </c>
+      <c r="E720" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/05/les-pays-europeens-retirent-leur-or-des-etats-unis/</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Trump pourrait-il inventer un prétexte pour saisir l'or détenu à New York&amp;#160;? L’article Les pays européens retirent leur or des États-Unis est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05 12:19</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>2026-09-04 16:22</t>
+        </is>
+      </c>
+      <c r="D721" s="3" t="inlineStr">
+        <is>
+          <t>Le scandale qui fait imploser Reform UK : comment Nigel Farage finance sa campagne avec des fonds étrangers</t>
+        </is>
+      </c>
+      <c r="E721" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/04/le-scandale-qui-fait-imploser-reform-uk-comment-nigel-farage-finance-sa-campagne-avec-des-fonds-etrangers/</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Les révélations portant sur les pratiques de Reform UK ont conduit à la démission de deux des conseillers les plus proches de Nigel Farage. L’article Le scandale qui fait imploser Reform UK&amp;#160;: comment Nigel Farage finance sa campagne avec des fonds étrangers est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05 12:19</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:36</t>
+        </is>
+      </c>
+      <c r="D722" s="3" t="inlineStr">
+        <is>
+          <t>Bernie Sanders : « Nous devons mettre l’IA en pause. IMMÉDIATEMENT »</t>
+        </is>
+      </c>
+      <c r="E722" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/04/bernie-sanders-nous-devons-mettre-lia-en-pause-immediatement/</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>«&amp;#160;L'avenir de l'humanité ne peut pas être laissé entre les mains d'une poignée d'oligarques de géants de la tech.&amp;#160;» L’article Bernie Sanders&amp;#160;: «&amp;#160;Nous devons mettre l’IA en pause. IMMÉDIATEMENT&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24128,6 +24218,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E717" r:id="rId716"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E718" r:id="rId717"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E719" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E720" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E721" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E722" r:id="rId721"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G722"/>
+  <dimension ref="A1:G725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23430,7 +23430,6 @@
           <t>Trump pourrait-il inventer un prétexte pour saisir l'or détenu à New York&amp;#160;? L’article Les pays européens retirent leur or des États-Unis est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -23463,7 +23462,6 @@
           <t>Les révélations portant sur les pratiques de Reform UK ont conduit à la démission de deux des conseillers les plus proches de Nigel Farage. L’article Le scandale qui fait imploser Reform UK&amp;#160;: comment Nigel Farage finance sa campagne avec des fonds étrangers est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="inlineStr">
@@ -23496,7 +23494,105 @@
           <t>«&amp;#160;L'avenir de l'humanité ne peut pas être laissé entre les mains d'une poignée d'oligarques de géants de la tech.&amp;#160;» L’article Bernie Sanders&amp;#160;: «&amp;#160;Nous devons mettre l’IA en pause. IMMÉDIATEMENT&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 12:34</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:30</t>
+        </is>
+      </c>
+      <c r="D723" s="3" t="inlineStr">
+        <is>
+          <t>L’AfD l’emportera-t-elle en Saxe-Anhalt ?</t>
+        </is>
+      </c>
+      <c r="E723" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/06/lafd-lemportera-t-elle-en-saxe-anhalt/</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Pour la première fois, les sondages placent l'extrême droite en position d'obtenir seule la majorité absolue dans un parlement régional allemand. L’article L’AfD l’emportera-t-elle en Saxe-Anhalt&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 12:34</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>2026-09-05 17:17</t>
+        </is>
+      </c>
+      <c r="D724" s="3" t="inlineStr">
+        <is>
+          <t>Faut-il avoir peur de l’Allemagne ?</t>
+        </is>
+      </c>
+      <c r="E724" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/05/faut-il-avoir-peur-de-lallemagne/</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>La question allemande a rarement paru aussi urgente depuis la fin de la Seconde Guerre mondiale. L’article Faut-il avoir peur de l’Allemagne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 12:34</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>2026-09-05 13:18</t>
+        </is>
+      </c>
+      <c r="D725" s="3" t="inlineStr">
+        <is>
+          <t>Le poids des poulets a été multiplié par quatre en 50 ans</t>
+        </is>
+      </c>
+      <c r="E725" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/05/le-poids-des-poulets-a-ete-multiplie-par-quatre-en-50-ans/</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Une personne consomme aujourd’hui six fois plus de poulets que ses grands-parents. L’article Le poids des poulets a été multiplié par quatre en 50 ans est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24221,6 +24317,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E720" r:id="rId719"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E721" r:id="rId720"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E722" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E723" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E724" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E725" r:id="rId724"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G725"/>
+  <dimension ref="A1:G735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23526,7 +23526,6 @@
           <t>Pour la première fois, les sondages placent l'extrême droite en position d'obtenir seule la majorité absolue dans un parlement régional allemand. L’article L’AfD l’emportera-t-elle en Saxe-Anhalt&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
@@ -23559,7 +23558,6 @@
           <t>La question allemande a rarement paru aussi urgente depuis la fin de la Seconde Guerre mondiale. L’article Faut-il avoir peur de l’Allemagne&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="inlineStr">
@@ -23592,7 +23590,336 @@
           <t>Une personne consomme aujourd’hui six fois plus de poulets que ses grands-parents. L’article Le poids des poulets a été multiplié par quatre en 50 ans est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:46</t>
+        </is>
+      </c>
+      <c r="D726" s="3" t="inlineStr">
+        <is>
+          <t>Fournitures scolaires : petite mythologie de la liste, de l’Antiquité à Roland Barthes</t>
+        </is>
+      </c>
+      <c r="E726" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/fournitures-scolaires-petite-mythologie-de-la-liste-de-lantiquite-a-roland-barthes-291191</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Avec ses allures d’inventaire, la liste de fournitures scolaires masque le rapport de pouvoir qu’elle pose et les questions économiques qu’elle soulève.</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>2026-09-06 17:28</t>
+        </is>
+      </c>
+      <c r="D727" s="3" t="inlineStr">
+        <is>
+          <t>Pour les écoles, la mère reste le parent à contacter en priorité : une charge mentale qui renforce les inégalités ?</t>
+        </is>
+      </c>
+      <c r="E727" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pour-les-ecoles-la-mere-reste-le-parent-a-contacter-en-priorite-une-charge-mentale-qui-renforce-les-inegalites-289081</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Lorsque les deux parents semblent également disponibles, les établissements scolaires ont 40&amp;nbsp;% plus de chances de contacter la mère plutôt que le père de l’élève, selon une étude réalisée aux États-Unis.</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>2026-09-06 17:26</t>
+        </is>
+      </c>
+      <c r="D728" s="3" t="inlineStr">
+        <is>
+          <t>Le dessin peut-il révéler qu’un enfant est victime d’abus sexuels ? Ce que disent vraiment les recherches</t>
+        </is>
+      </c>
+      <c r="E728" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/le-dessin-peut-il-reveler-quun-enfant-est-victime-dabus-sexuels-ce-que-disent-vraiment-les-recherches-290640</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Les enfants parlent difficilement, mais dessinent avec plaisir. Lorsque les mots leur manquent, le dessin pourrait-il parler à leur place&amp;nbsp;? Les recherches scientifiques les plus solides révèlent que ce n’est pas le cas.</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:47</t>
+        </is>
+      </c>
+      <c r="D729" s="3" t="inlineStr">
+        <is>
+          <t>Incendies en Algérie : l’exceptionnelle résilience du peuple comme ressource politique du pouvoir</t>
+        </is>
+      </c>
+      <c r="E729" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/incendies-en-algerie-lexceptionnelle-resilience-du-peuple-comme-ressource-politique-du-pouvoir-291087</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>En Algérie, les incendies révèlent les failles de l’État, mais aussi une solidarité citoyenne que le pouvoir célèbre tout en cherchant à la récupérer.</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>2026-09-06 17:27</t>
+        </is>
+      </c>
+      <c r="D730" s="3" t="inlineStr">
+        <is>
+          <t>La stratégie de Meta face à la justice américaine : éviter une défaite légale et reprendre le contrôle</t>
+        </is>
+      </c>
+      <c r="E730" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/la-strategie-de-meta-face-a-la-justice-americaine-eviter-une-defaite-legale-et-reprendre-le-controle-290868</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>L’accord entre Meta et la justice états-unienne met en évidence la capacité des entreprises du numérique à peser sur les efforts visant à réguler leurs activités.</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:24</t>
+        </is>
+      </c>
+      <c r="D731" s="3" t="inlineStr">
+        <is>
+          <t>La victoire de l’AfD révèle la fracture au sein des droites entre conservateurs et révolutionnaires</t>
+        </is>
+      </c>
+      <c r="E731" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/07/la-victoire-de-lafd-revele-la-fracture-au-sein-des-droites-entre-conservateurs-et-revolutionnaires/</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>De Vox à la Ligue, les réactions au succès historique de l’extrême droite en Saxe-Anhalt illustrent les divergences entre formations qui veulent prendre le pouvoir pour transformer le système de l’intérieur et celles qui assument une rupture beaucoup plus radicale. L’article La victoire de l’AfD révèle la fracture au sein des droites entre conservateurs et révolutionnaires est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:09</t>
+        </is>
+      </c>
+      <c r="D732" s="3" t="inlineStr">
+        <is>
+          <t>Comment l’AfD est devenu un parti de masse en Allemagne</t>
+        </is>
+      </c>
+      <c r="E732" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/07/comment-lafd-est-devenu-un-parti-de-masse-en-allemagne/</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>10 cartes et graphiques pour comprendre la victoire de l’extrême droite en Saxe-Anhalt. L’article Comment l’AfD est devenu un parti de masse en Allemagne est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:03</t>
+        </is>
+      </c>
+      <c r="D733" s="3" t="inlineStr">
+        <is>
+          <t>En Saxe-Anhalt « l’AfD a écrit l’histoire »</t>
+        </is>
+      </c>
+      <c r="E733" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/07/en-saxe-anhalt-afd-ecrit-histoire-ulrich-siegmund/</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Le discours d'une victoire inédite de l’extrême droite en Allemagne L’article En Saxe-Anhalt «&amp;#160;l&amp;rsquo;AfD a écrit l’histoire&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>2026-09-06 18:10</t>
+        </is>
+      </c>
+      <c r="D734" s="3" t="inlineStr">
+        <is>
+          <t>Le dépouillement des élections régionales en Saxe-Anhalt en direct</t>
+        </is>
+      </c>
+      <c r="E734" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/06/le-depouillement-des-elections-regionales-en-saxe-anhalt-en-direct/</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>L’AfD obtiendrait-elle une majorité absolue&amp;#160;? L’article Le dépouillement des élections régionales en Saxe-Anhalt en direct est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 14:44</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:16</t>
+        </is>
+      </c>
+      <c r="D735" s="3" t="inlineStr">
+        <is>
+          <t>L’AfD obtient le meilleur résultat de l’extrême droite en Allemagne depuis la Seconde Guerre mondiale</t>
+        </is>
+      </c>
+      <c r="E735" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/06/afd-obtient-le-meilleur-resultat-de-lextreme-droite-en-allemagne-depuis-la-seconde-guerre-mondiale-saxe-anhalt/</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Selon les premières projections, sans majorité absolue, l’AfD pourrait potentiellement gouverner le Saxe-Anhalt. L’article L’AfD obtient le meilleur résultat de l’extrême droite en Allemagne depuis la Seconde Guerre mondiale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24320,6 +24647,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E723" r:id="rId722"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E724" r:id="rId723"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E725" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E726" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E727" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E728" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E729" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E730" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E731" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E732" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E733" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E734" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E735" r:id="rId734"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G735"/>
+  <dimension ref="A1:G740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23622,7 +23622,6 @@
           <t>Avec ses allures d’inventaire, la liste de fournitures scolaires masque le rapport de pouvoir qu’elle pose et les questions économiques qu’elle soulève.</t>
         </is>
       </c>
-      <c r="G726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="inlineStr">
@@ -23655,7 +23654,6 @@
           <t>Lorsque les deux parents semblent également disponibles, les établissements scolaires ont 40&amp;nbsp;% plus de chances de contacter la mère plutôt que le père de l’élève, selon une étude réalisée aux États-Unis.</t>
         </is>
       </c>
-      <c r="G727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="inlineStr">
@@ -23688,7 +23686,6 @@
           <t>Les enfants parlent difficilement, mais dessinent avec plaisir. Lorsque les mots leur manquent, le dessin pourrait-il parler à leur place&amp;nbsp;? Les recherches scientifiques les plus solides révèlent que ce n’est pas le cas.</t>
         </is>
       </c>
-      <c r="G728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="inlineStr">
@@ -23721,7 +23718,6 @@
           <t>En Algérie, les incendies révèlent les failles de l’État, mais aussi une solidarité citoyenne que le pouvoir célèbre tout en cherchant à la récupérer.</t>
         </is>
       </c>
-      <c r="G729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="inlineStr">
@@ -23754,7 +23750,6 @@
           <t>L’accord entre Meta et la justice états-unienne met en évidence la capacité des entreprises du numérique à peser sur les efforts visant à réguler leurs activités.</t>
         </is>
       </c>
-      <c r="G730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="inlineStr">
@@ -23787,7 +23782,6 @@
           <t>De Vox à la Ligue, les réactions au succès historique de l’extrême droite en Saxe-Anhalt illustrent les divergences entre formations qui veulent prendre le pouvoir pour transformer le système de l’intérieur et celles qui assument une rupture beaucoup plus radicale. L’article La victoire de l’AfD révèle la fracture au sein des droites entre conservateurs et révolutionnaires est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="inlineStr">
@@ -23820,7 +23814,6 @@
           <t>10 cartes et graphiques pour comprendre la victoire de l’extrême droite en Saxe-Anhalt. L’article Comment l’AfD est devenu un parti de masse en Allemagne est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -23853,7 +23846,6 @@
           <t>Le discours d'une victoire inédite de l’extrême droite en Allemagne L’article En Saxe-Anhalt «&amp;#160;l&amp;rsquo;AfD a écrit l’histoire&amp;#160;» est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="inlineStr">
@@ -23886,7 +23878,6 @@
           <t>L’AfD obtiendrait-elle une majorité absolue&amp;#160;? L’article Le dépouillement des élections régionales en Saxe-Anhalt en direct est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="inlineStr">
@@ -23919,7 +23910,171 @@
           <t>Selon les premières projections, sans majorité absolue, l’AfD pourrait potentiellement gouverner le Saxe-Anhalt. L’article L’AfD obtient le meilleur résultat de l’extrême droite en Allemagne depuis la Seconde Guerre mondiale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:16</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>2026-09-08 05:06</t>
+        </is>
+      </c>
+      <c r="D736" s="3" t="inlineStr">
+        <is>
+          <t>Une intelligence surnaturelle est arrivée sur terre</t>
+        </is>
+      </c>
+      <c r="E736" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/08/une-intelligence-surnaturelle-est-arrivee-sur-terre/</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Selon le directeur scientifique d’OpenAI, l’IA est sur le point d’échapper à ses créateurs L’article Une intelligence surnaturelle est arrivée sur terre est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:16</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:30</t>
+        </is>
+      </c>
+      <c r="D737" s="3" t="inlineStr">
+        <is>
+          <t>En Europe, les plus de 65 ans devraient représenter près d’un tiers de la population en 2060</t>
+        </is>
+      </c>
+      <c r="E737" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/08/en-europe-les-plus-de-65-ans-devraient-representer-pres-dun-tiers-de-la-population-en-2060/</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Pour la première fois de l’histoire, le monde compte plus de seniors que de jeunes enfants. L’article En Europe, les plus de 65 ans devraient représenter près d’un tiers de la population en 2060 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:16</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:00</t>
+        </is>
+      </c>
+      <c r="D738" s="3" t="inlineStr">
+        <is>
+          <t>L’éducation aux mains de l’IA dans le Salvador de Bukele</t>
+        </is>
+      </c>
+      <c r="E738" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/07/leducation-aux-mains-de-lia-dans-le-salvador-de-bukele/</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Le président salvadorien prévoit de généraliser les tuteurs IA à toutes les écoles publiques du pays d'ici 18 mois. L’article L’éducation aux mains de l’IA dans le Salvador de Bukele est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:16</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>2026-09-07 16:03</t>
+        </is>
+      </c>
+      <c r="D739" s="3" t="inlineStr">
+        <is>
+          <t>Après la visite de Kushner et Witkoff à Moscou et Kiev, vers une reprise des négociations ?</t>
+        </is>
+      </c>
+      <c r="E739" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/07/apres-la-visite-de-kushner-et-witkoff-a-moscou-et-kiev-vers-une-reprise-des-negociations/</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>La tentative américaine de reprise du dialogue s’oppose toujours aux revendications maximalistes de Poutine. L’article Après la visite de Kushner et Witkoff à Moscou et Kiev, vers une reprise des négociations&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:16</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:30</t>
+        </is>
+      </c>
+      <c r="D740" s="3" t="inlineStr">
+        <is>
+          <t>La doctrine Milei pour unir l’extrême droite mondiale</t>
+        </is>
+      </c>
+      <c r="E740" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/07/la-doctrine-milei-pour-unir-lextreme-droite-mondiale/</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>L’intervention du président argentin au Forum de Madrid à Santiago du Chili. L’article La doctrine Milei pour unir l’extrême droite mondiale est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24657,6 +24812,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E733" r:id="rId732"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E734" r:id="rId733"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E735" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E736" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E737" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId739"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G740"/>
+  <dimension ref="A1:G756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23942,7 +23942,6 @@
           <t>Selon le directeur scientifique d’OpenAI, l’IA est sur le point d’échapper à ses créateurs L’article Une intelligence surnaturelle est arrivée sur terre est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="inlineStr">
@@ -23975,7 +23974,6 @@
           <t>Pour la première fois de l’histoire, le monde compte plus de seniors que de jeunes enfants. L’article En Europe, les plus de 65 ans devraient représenter près d’un tiers de la population en 2060 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="inlineStr">
@@ -24008,7 +24006,6 @@
           <t>Le président salvadorien prévoit de généraliser les tuteurs IA à toutes les écoles publiques du pays d'ici 18 mois. L’article L’éducation aux mains de l’IA dans le Salvador de Bukele est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -24041,7 +24038,6 @@
           <t>La tentative américaine de reprise du dialogue s’oppose toujours aux revendications maximalistes de Poutine. L’article Après la visite de Kushner et Witkoff à Moscou et Kiev, vers une reprise des négociations&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="inlineStr">
@@ -24074,7 +24070,534 @@
           <t>L’intervention du président argentin au Forum de Madrid à Santiago du Chili. L’article La doctrine Milei pour unir l’extrême droite mondiale est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>2026-09-09 11:16</t>
+        </is>
+      </c>
+      <c r="D741" s="3" t="inlineStr">
+        <is>
+          <t>Les survivants de la peste nous ont laissé des graffitis, de rares archives… et une leçon pour l’après-Covid</t>
+        </is>
+      </c>
+      <c r="E741" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-survivants-de-la-peste-nous-ont-laisse-des-graffitis-de-rares-archives-et-une-lecon-pour-lapres-covid-287596</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Pourquoi la Peste noire est-elle presque absente de nombreux témoignages médiévaux malgré son impact colossal&amp;nbsp;? L’histoire de sa mémoire offre de précieuses leçons pour la commémoration de la pandémie de Covid-19.</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:50</t>
+        </is>
+      </c>
+      <c r="D742" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi la France a interdit l’absinthe : l’histoire d’un bouc émissaire qualifié de « poison national »</t>
+        </is>
+      </c>
+      <c r="E742" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-la-france-a-interdit-labsinthe-lhistoire-dun-bouc-emissaire-qualifie-de-poison-national-287211</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Désigner un coupable face à un problème complexe est un réflexe ancien. L’histoire de l’interdiction de l’absinthe en France montre comment ce mécanisme fonctionne.</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:50</t>
+        </is>
+      </c>
+      <c r="D743" s="3" t="inlineStr">
+        <is>
+          <t>Pourquoi ne parle-t-on pas davantage de la guerre civile dans les classes espagnoles ?</t>
+        </is>
+      </c>
+      <c r="E743" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pourquoi-ne-parle-t-on-pas-davantage-de-la-guerre-civile-dans-les-classes-espagnoles-287980</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Quatre-vingt-dix&amp;nbsp;ans après le début de la guerre civile, son enseignement reste limité dans les écoles espagnoles. Et le manque de temps n’explique pas tout…</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:49</t>
+        </is>
+      </c>
+      <c r="D744" s="3" t="inlineStr">
+        <is>
+          <t>Derrière la tapisserie de Bayeux, les brodeuses effacées de l’Histoire</t>
+        </is>
+      </c>
+      <c r="E744" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/derriere-la-tapisserie-de-bayeux-les-brodeuses-effacees-de-lhistoire-286875</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>La tapisserie de Bayeux est souvent présentée comme un monument de l’histoire des rois et des conquérants. Pourtant, derrière cette fresque médiévale se cache le travail minutieux de femmes dont les noms ont été effacés de la mémoire.</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:09</t>
+        </is>
+      </c>
+      <c r="D745" s="3" t="inlineStr">
+        <is>
+          <t>L’intolérance au lactose est en réalité la norme chez l’humain, mais le racisme, le gouvernement des États-Unis et les intérêts commerciaux en ont fait un trouble</t>
+        </is>
+      </c>
+      <c r="E745" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/lintolerance-au-lactose-est-en-realite-la-norme-chez-lhumain-mais-le-racisme-le-gouvernement-des-etats-unis-et-les-interets-commerciaux-en-ont-fait-un-trouble-290654</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>La majorité de la population mondiale est intolérante au lactose. Mais la propagande états-unienne et les préjugés scientifiques ont fait du lait et des produits laitiers des aliments de base à l’échelle globale.</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:52</t>
+        </is>
+      </c>
+      <c r="D746" s="3" t="inlineStr">
+        <is>
+          <t>PISA 2025 et classements scolaires : nous posons-nous les bonnes questions ?</t>
+        </is>
+      </c>
+      <c r="E746" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pisa-2025-et-classements-scolaires-nous-posons-nous-les-bonnes-questions-291492</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Nos systèmes éducatifs parviennent-ils à transformer les capacités individuelles en possibilités collectives&amp;nbsp;? Loin de réduire l’éducation à quelques chiffres, c’est ce que les classements doivent chercher à mesurer.</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:10</t>
+        </is>
+      </c>
+      <c r="D747" s="3" t="inlineStr">
+        <is>
+          <t>Les agences privées de garde d’enfants : entre promesses aux parents et réalité du marché</t>
+        </is>
+      </c>
+      <c r="E747" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/les-agences-privees-de-garde-denfants-entre-promesses-aux-parents-et-realite-du-marche-290801</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Face à la pénurie de modes de garde, de nombreuses agences privées proposent leurs services aux familles. Les conditions d’emploi qu’elles proposent interrogent les lacunes du service public.</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:46</t>
+        </is>
+      </c>
+      <c r="D748" s="3" t="inlineStr">
+        <is>
+          <t>Vingt-cinq ans après le 11-Septembre : l’unité des États-Unis à l’épreuve des fractures</t>
+        </is>
+      </c>
+      <c r="E748" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/vingt-cinq-ans-apres-le-11-septembre-lunite-des-etats-unis-a-lepreuve-des-fractures-290865</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Vingt-cinq&amp;nbsp;ans après le 11-Septembre, la préparation de la commémoration aux États-Unis révèle les fractures persistantes autour de l’islam, de l’identité et de la mémoire nationales.</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:10</t>
+        </is>
+      </c>
+      <c r="D749" s="3" t="inlineStr">
+        <is>
+          <t>Allemagne : les multiples effets du triomphe de l’AfD en Saxe-Anhalt</t>
+        </is>
+      </c>
+      <c r="E749" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/allemagne-les-multiples-effets-du-triomphe-de-lafd-en-saxe-anhalt-291470</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Le parti d’extrême droite AfD est arrivé largement en tête en Saxe-Anhalt, échouant de peu à décrocher la majorité absolue.</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:37</t>
+        </is>
+      </c>
+      <c r="D750" s="3" t="inlineStr">
+        <is>
+          <t>L’Europe n’a représenté que 0,3 % des satellites mis en orbite en 2025</t>
+        </is>
+      </c>
+      <c r="E750" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/09/leurope-na-represente-que-03-des-satellites-mis-en-orbite-en-2025/</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>L’accès à l’économie spatiale, s’il se diversifie, est de plus en plus concentré aux États-Unis. L’article L&amp;rsquo;Europe n&amp;rsquo;a représenté que 0,3&amp;#160;% des satellites mis en orbite en 2025 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>2026-09-09 08:45</t>
+        </is>
+      </c>
+      <c r="D751" s="3" t="inlineStr">
+        <is>
+          <t>« Ils jouent avec nos vies » : l’appel d’un ingénieur de l’IA pour ralentir le développement des modèles</t>
+        </is>
+      </c>
+      <c r="E751" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/09/ils-jouent-avec-nos-vies-lappel-dun-ingenieur-de-lia-pour-ralentir-le-developpement-des-modeles/</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Selon l’un des principaux ingénieurs d’Anthropic, la probabilité que l’IA anéantisse l’humanité dans les prochaines années «&amp;#160;est supérieure à 10&amp;#160;%&amp;#160;». L’article «&amp;#160;Ils jouent avec nos vies&amp;#160;»&amp;#160;: l’appel d’un ingénieur de l’IA pour ralentir le développement des modèles est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:12</t>
+        </is>
+      </c>
+      <c r="D752" s="3" t="inlineStr">
+        <is>
+          <t>La guerre contre Trump sur les murs de Téhéran</t>
+        </is>
+      </c>
+      <c r="E752" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/09/la-guerre-contre-trump-sur-les-murs-de-teheran/</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Pour tenir la capitale, le régime des ayatollah a intensifié sa propagande L’article La guerre contre Trump sur les murs de Téhéran est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:30</t>
+        </is>
+      </c>
+      <c r="D753" s="3" t="inlineStr">
+        <is>
+          <t>Des « robots de laboratoire » aux « combattants » : comment l’APL se prépare au déploiement d’humanoïdes armés</t>
+        </is>
+      </c>
+      <c r="E753" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/09/des-robots-de-laboratoire-aux-combattants-comment-lapl-se-prepare-au-deploiement-dhumanoides-armes/</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Depuis 2024, l’Armée populaire de libération multiplie les réflexions et initiatives pour mettre au point les premiers robots humanoïdes à usage militaire. L’article Des «&amp;#160;robots de laboratoire&amp;#160;» aux «&amp;#160;combattants&amp;#160;»&amp;#160;: comment l’APL se prépare au déploiement d’humanoïdes armés est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>2026-09-08 16:10</t>
+        </is>
+      </c>
+      <c r="D754" s="3" t="inlineStr">
+        <is>
+          <t>En Israël, l’étau se referme-t-il autour de Netanyahou ?</t>
+        </is>
+      </c>
+      <c r="E754" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/08/en-israel-letau-se-referme-t-il-autour-de-netanyahou/</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Le Premier ministre israélien fait face à des révélations pointant son inaction en amont de l'attaque du Hamas du 7 octobre 2023. L’article En Israël, l’étau se referme-t-il autour de Netanyahou&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:31</t>
+        </is>
+      </c>
+      <c r="D755" s="3" t="inlineStr">
+        <is>
+          <t>Doctrine du nouvel homme fort du Vietnam</t>
+        </is>
+      </c>
+      <c r="E755" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/08/la-doctrine-du-nouvel-homme-fort-du-vietnam/</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>À Hanoi, Tô Lâm est en train de produire un nouveau mélange entre capitalisme et communisme L’article Doctrine du nouvel homme fort du Vietnam est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:20</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:22</t>
+        </is>
+      </c>
+      <c r="D756" s="3" t="inlineStr">
+        <is>
+          <t>Convaincu du soutien de Trump, Milei veut réactiver le dossier des Malouines à l’approche des élections</t>
+        </is>
+      </c>
+      <c r="E756" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/08/convaincu-du-soutien-de-trump-milei-veut-reactiver-le-dossier-des-malouines-a-lapproche-des-elections/</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Le président américain a déclaré fin août que la position de Washington vis-à-vis de l’archipel était en cours de réexamen. L’article Convaincu du soutien de Trump, Milei veut réactiver le dossier des Malouines à l&amp;rsquo;approche des élections est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24817,6 +25340,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E738" r:id="rId737"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E739" r:id="rId738"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E740" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E741" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E742" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E743" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E744" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E745" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E746" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E747" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E748" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E749" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E750" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E751" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E752" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E753" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E754" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E755" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E756" r:id="rId755"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G756"/>
+  <dimension ref="A1:G763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24102,7 +24102,6 @@
           <t>Pourquoi la Peste noire est-elle presque absente de nombreux témoignages médiévaux malgré son impact colossal&amp;nbsp;? L’histoire de sa mémoire offre de précieuses leçons pour la commémoration de la pandémie de Covid-19.</t>
         </is>
       </c>
-      <c r="G741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
@@ -24135,7 +24134,6 @@
           <t>Désigner un coupable face à un problème complexe est un réflexe ancien. L’histoire de l’interdiction de l’absinthe en France montre comment ce mécanisme fonctionne.</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="inlineStr">
@@ -24168,7 +24166,6 @@
           <t>Quatre-vingt-dix&amp;nbsp;ans après le début de la guerre civile, son enseignement reste limité dans les écoles espagnoles. Et le manque de temps n’explique pas tout…</t>
         </is>
       </c>
-      <c r="G743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -24201,7 +24198,6 @@
           <t>La tapisserie de Bayeux est souvent présentée comme un monument de l’histoire des rois et des conquérants. Pourtant, derrière cette fresque médiévale se cache le travail minutieux de femmes dont les noms ont été effacés de la mémoire.</t>
         </is>
       </c>
-      <c r="G744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -24234,7 +24230,6 @@
           <t>La majorité de la population mondiale est intolérante au lactose. Mais la propagande états-unienne et les préjugés scientifiques ont fait du lait et des produits laitiers des aliments de base à l’échelle globale.</t>
         </is>
       </c>
-      <c r="G745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
@@ -24267,7 +24262,6 @@
           <t>Nos systèmes éducatifs parviennent-ils à transformer les capacités individuelles en possibilités collectives&amp;nbsp;? Loin de réduire l’éducation à quelques chiffres, c’est ce que les classements doivent chercher à mesurer.</t>
         </is>
       </c>
-      <c r="G746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -24300,7 +24294,6 @@
           <t>Face à la pénurie de modes de garde, de nombreuses agences privées proposent leurs services aux familles. Les conditions d’emploi qu’elles proposent interrogent les lacunes du service public.</t>
         </is>
       </c>
-      <c r="G747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="inlineStr">
@@ -24333,7 +24326,6 @@
           <t>Vingt-cinq&amp;nbsp;ans après le 11-Septembre, la préparation de la commémoration aux États-Unis révèle les fractures persistantes autour de l’islam, de l’identité et de la mémoire nationales.</t>
         </is>
       </c>
-      <c r="G748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="inlineStr">
@@ -24366,7 +24358,6 @@
           <t>Le parti d’extrême droite AfD est arrivé largement en tête en Saxe-Anhalt, échouant de peu à décrocher la majorité absolue.</t>
         </is>
       </c>
-      <c r="G749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="inlineStr">
@@ -24399,7 +24390,6 @@
           <t>L’accès à l’économie spatiale, s’il se diversifie, est de plus en plus concentré aux États-Unis. L’article L&amp;rsquo;Europe n&amp;rsquo;a représenté que 0,3&amp;#160;% des satellites mis en orbite en 2025 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="inlineStr">
@@ -24432,7 +24422,6 @@
           <t>Selon l’un des principaux ingénieurs d’Anthropic, la probabilité que l’IA anéantisse l’humanité dans les prochaines années «&amp;#160;est supérieure à 10&amp;#160;%&amp;#160;». L’article «&amp;#160;Ils jouent avec nos vies&amp;#160;»&amp;#160;: l’appel d’un ingénieur de l’IA pour ralentir le développement des modèles est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="inlineStr">
@@ -24465,7 +24454,6 @@
           <t>Pour tenir la capitale, le régime des ayatollah a intensifié sa propagande L’article La guerre contre Trump sur les murs de Téhéran est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="inlineStr">
@@ -24498,7 +24486,6 @@
           <t>Depuis 2024, l’Armée populaire de libération multiplie les réflexions et initiatives pour mettre au point les premiers robots humanoïdes à usage militaire. L’article Des «&amp;#160;robots de laboratoire&amp;#160;» aux «&amp;#160;combattants&amp;#160;»&amp;#160;: comment l’APL se prépare au déploiement d’humanoïdes armés est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="inlineStr">
@@ -24531,7 +24518,6 @@
           <t>Le Premier ministre israélien fait face à des révélations pointant son inaction en amont de l'attaque du Hamas du 7 octobre 2023. L’article En Israël, l’étau se referme-t-il autour de Netanyahou&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="inlineStr">
@@ -24564,7 +24550,6 @@
           <t>À Hanoi, Tô Lâm est en train de produire un nouveau mélange entre capitalisme et communisme L’article Doctrine du nouvel homme fort du Vietnam est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="inlineStr">
@@ -24597,7 +24582,237 @@
           <t>Le président américain a déclaré fin août que la position de Washington vis-à-vis de l’archipel était en cours de réexamen. L’article Convaincu du soutien de Trump, Milei veut réactiver le dossier des Malouines à l&amp;rsquo;approche des élections est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:59</t>
+        </is>
+      </c>
+      <c r="D757" s="3" t="inlineStr">
+        <is>
+          <t>Ces hommes pionniers du féminisme, de Condorcet à Léon Blum</t>
+        </is>
+      </c>
+      <c r="E757" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/ces-hommes-pionniers-du-feminisme-de-condorcet-a-leon-blum-288547</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Depuis que des femmes luttent pour leurs droits, des hommes se tiennent à leurs côtés. Qui sont ces hommes qui se sont engagés, en France, de la fin du XVIIIᵉ&amp;nbsp;siècle au XXᵉ&amp;nbsp;siècle, pour l’émancipation des femmes&amp;nbsp;?</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:12</t>
+        </is>
+      </c>
+      <c r="D758" s="3" t="inlineStr">
+        <is>
+          <t>L’interdiction de quitter le territoire : le nouvel outil de la Chine dans la compétition internationale ?</t>
+        </is>
+      </c>
+      <c r="E758" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/linterdiction-de-quitter-le-territoire-le-nouvel-outil-de-la-chine-dans-la-competition-internationale-290461</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>La Chine durcit le contrôle des sorties du territoire pour protéger ses intérêts diplomatiques et technologiques, mais aussi pour renforcer l’emprise intérieure du PCC.</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:57</t>
+        </is>
+      </c>
+      <c r="D759" s="3" t="inlineStr">
+        <is>
+          <t>Trump va-t-il de nouveau frapper les nucléaire iranien ?</t>
+        </is>
+      </c>
+      <c r="E759" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/10/trump-va-t-il-de-nouveau-frapper-les-nucleaire-iranien/</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Pour la première fois en 20 ans, l’AIEA a voté hier le renvoi de l’Iran devant le Conseil de sécurité de l’ONU L’article Trump va-t-il de nouveau frapper les nucléaire iranien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:30</t>
+        </is>
+      </c>
+      <c r="D760" s="3" t="inlineStr">
+        <is>
+          <t>Les combats se rapprochent de la ville ukrainienne de Kramatorsk</t>
+        </is>
+      </c>
+      <c r="E760" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/10/les-combats-se-rapprochent-de-la-ville-ukrainienne-de-kramatorsk/</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>La chute de la ceinture de forteresses du Donbass risquerait de conduire à une accélération de l’armée russe L’article Les combats se rapprochent de la ville ukrainienne de Kramatorsk est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:00</t>
+        </is>
+      </c>
+      <c r="D761" s="3" t="inlineStr">
+        <is>
+          <t>Comment Poutine est en train de ruiner l’économie russe</t>
+        </is>
+      </c>
+      <c r="E761" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/10/comment-poutine-est-en-train-de-ruiner-leconomie-russe/</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>La plus lourde sanction ne vient pas d’ailleurs&amp;#160;: c’est le Kremlin L’article Comment Poutine est en train de ruiner l&amp;rsquo;économie russe est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:23</t>
+        </is>
+      </c>
+      <c r="D762" s="3" t="inlineStr">
+        <is>
+          <t>Le conflit entre les Houthis et Riyad est à son plus haut niveau de tensions depuis 2022</t>
+        </is>
+      </c>
+      <c r="E762" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/09/le-conflit-entre-les-houthis-et-riyad-est-a-son-plus-haut-niveau-de-tensions-depuis-2022/</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Une escalade pourrait compliquer les efforts de Trump visant à mettre fin à la guerre avec l’Iran L’article Le conflit entre les Houthis et Riyad est à son plus haut niveau de tensions depuis 2022 est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:17</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:51</t>
+        </is>
+      </c>
+      <c r="D763" s="3" t="inlineStr">
+        <is>
+          <t>Le discours de Merz contre l’AfD</t>
+        </is>
+      </c>
+      <c r="E763" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/09/le-discours-de-merz-contre-lafd/</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Après la victoire historique de l’extrême droite en Saxe-Anhalt, le chancelier accuse le parti d’extrême droite de vouloir un «&amp;#160;nettoyage ethnique&amp;#160;» en Allemagne L’article Le discours de Merz contre l’AfD est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -25356,6 +25571,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E754" r:id="rId753"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E755" r:id="rId754"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E756" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E757" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E758" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E759" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E760" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E761" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E762" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E763" r:id="rId762"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G763"/>
+  <dimension ref="A1:G773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24614,7 +24614,6 @@
           <t>Depuis que des femmes luttent pour leurs droits, des hommes se tiennent à leurs côtés. Qui sont ces hommes qui se sont engagés, en France, de la fin du XVIIIᵉ&amp;nbsp;siècle au XXᵉ&amp;nbsp;siècle, pour l’émancipation des femmes&amp;nbsp;?</t>
         </is>
       </c>
-      <c r="G757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="inlineStr">
@@ -24647,7 +24646,6 @@
           <t>La Chine durcit le contrôle des sorties du territoire pour protéger ses intérêts diplomatiques et technologiques, mais aussi pour renforcer l’emprise intérieure du PCC.</t>
         </is>
       </c>
-      <c r="G758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="inlineStr">
@@ -24680,7 +24678,6 @@
           <t>Pour la première fois en 20 ans, l’AIEA a voté hier le renvoi de l’Iran devant le Conseil de sécurité de l’ONU L’article Trump va-t-il de nouveau frapper les nucléaire iranien&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="inlineStr">
@@ -24713,7 +24710,6 @@
           <t>La chute de la ceinture de forteresses du Donbass risquerait de conduire à une accélération de l’armée russe L’article Les combats se rapprochent de la ville ukrainienne de Kramatorsk est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -24746,7 +24742,6 @@
           <t>La plus lourde sanction ne vient pas d’ailleurs&amp;#160;: c’est le Kremlin L’article Comment Poutine est en train de ruiner l&amp;rsquo;économie russe est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="inlineStr">
@@ -24779,7 +24774,6 @@
           <t>Une escalade pourrait compliquer les efforts de Trump visant à mettre fin à la guerre avec l’Iran L’article Le conflit entre les Houthis et Riyad est à son plus haut niveau de tensions depuis 2022 est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="inlineStr">
@@ -24812,7 +24806,336 @@
           <t>Après la victoire historique de l’extrême droite en Saxe-Anhalt, le chancelier accuse le parti d’extrême droite de vouloir un «&amp;#160;nettoyage ethnique&amp;#160;» en Allemagne L’article Le discours de Merz contre l’AfD est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G763" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Histoire</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:27</t>
+        </is>
+      </c>
+      <c r="D764" s="3" t="inlineStr">
+        <is>
+          <t>Après un incendie, les bâtiments historiques peuvent encore être sauvés, à condition d’agir vite</t>
+        </is>
+      </c>
+      <c r="E764" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/apres-un-incendie-les-batiments-historiques-peuvent-encore-etre-sauves-a-condition-dagir-vite-291793</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Après un incendie, les bâtiments historiques en pierre ou en brique peuvent souvent être sauvés. Mais pour éviter leur démolition, il faut évaluer rapidement les dégâts et consolider les murs.</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:58</t>
+        </is>
+      </c>
+      <c r="D765" s="3" t="inlineStr">
+        <is>
+          <t>PISA 2025 : l’IA est-elle responsable de la baisse des résultats ?</t>
+        </is>
+      </c>
+      <c r="E765" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/pisa-2025-lia-est-elle-responsable-de-la-baisse-des-resultats-291580</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Peut-on vraiment accuser l’IA d’une baisse de niveau alors que, parmi les systèmes éducatifs les plus performants selon PISA, les outils numériques tiennent une place très différente ?</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:24</t>
+        </is>
+      </c>
+      <c r="D766" s="3" t="inlineStr">
+        <is>
+          <t>Dans l’est de l’Angola, la guerre a bouleversé des siècles de gestion du feu</t>
+        </is>
+      </c>
+      <c r="E766" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/dans-lest-de-langola-la-guerre-a-bouleverse-des-siecles-de-gestion-du-feu-291791</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>La guerre civile en Angola a profondément modifié l’usage du feu dans les communautés rurales. Une étude montre que les surfaces brûlées ont diminué pendant le conflit, avant de fortement augmenter avec le retour de la paix.</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>The Conversation FR - International</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:58</t>
+        </is>
+      </c>
+      <c r="D767" s="3" t="inlineStr">
+        <is>
+          <t>Élections législatives en Suède : un vote sur la normalisation de l’extrême droite ?</t>
+        </is>
+      </c>
+      <c r="E767" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/elections-legislatives-en-suede-un-vote-sur-la-normalisation-de-lextreme-droite-291067</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>L’extrême droite soutient le gouvernement en place depuis quatre&amp;nbsp;ans, qui a mis en œuvre une bonne partie de son programme. Le scrutin du 13&amp;nbsp;septembre dira si la population suédoise soutient ce cap.</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:11</t>
+        </is>
+      </c>
+      <c r="D768" s="3" t="inlineStr">
+        <is>
+          <t>L’AfD affirme vouloir mettre le réarmement allemand au service de « campagnes offensives de remigration ».</t>
+        </is>
+      </c>
+      <c r="E768" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/11/lafd-affirme-vouloir-mettre-le-rearmement-allemand-au-service-de-campagnes-offensives-de-remigration/</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Pourquoi, malgré le scandale suscité, ce n’est pas vraiment un dérapage L’article L’AfD affirme vouloir mettre le réarmement allemand au service de «&amp;#160;campagnes offensives de remigration&amp;#160;». est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>2026-09-11 05:03</t>
+        </is>
+      </c>
+      <c r="D769" s="3" t="inlineStr">
+        <is>
+          <t>Le siècle du djihad</t>
+        </is>
+      </c>
+      <c r="E769" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/11/le-siecle-du-djihad/</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Vingt-cinq ans après le 11-Septembre, le djihadisme n’a jamais été aussi étendu L’article Le siècle du djihad est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:30</t>
+        </is>
+      </c>
+      <c r="D770" s="3" t="inlineStr">
+        <is>
+          <t>Les guerres post-2001 ont coûté 8 000 milliards de dollars aux États-Unis</t>
+        </is>
+      </c>
+      <c r="E770" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/11/les-guerres-post-2001-ont-coute-8-000-milliards-de-dollars-aux-etats-unis/</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Le coût des guerres contre le terrorisme avait à l'époque été largement sous-estimé L’article Les guerres post-2001 ont coûté 8 000 milliards de dollars aux États-Unis est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:16</t>
+        </is>
+      </c>
+      <c r="D771" s="3" t="inlineStr">
+        <is>
+          <t>La promesse de Trump de verser 5 000 dollars aux Américains en cas de victoire républicaine aux élections est sans précédent</t>
+        </is>
+      </c>
+      <c r="E771" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/10/la-promesse-de-trump-de-verser-5-000-dollars-aux-americains-en-cas-de-victoire-republicaine-aux-elections-est-sans-precedent/</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Le «&amp;#160;dividende&amp;#160;» promis par Trump coûterait environ 1 225 milliards de dollars L’article La promesse de Trump de verser 5 000 dollars aux Américains en cas de victoire républicaine aux élections est sans précédent est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:57</t>
+        </is>
+      </c>
+      <c r="D772" s="3" t="inlineStr">
+        <is>
+          <t>Trump va-t-il de nouveau frapper les installations nucléaires iraniennes ?</t>
+        </is>
+      </c>
+      <c r="E772" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/10/trump-va-t-il-de-nouveau-frapper-le-nucleaire-iranien/</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Pour la première fois en 20 ans, l’AIEA a voté hier le renvoi de l’Iran devant le Conseil de sécurité de l’ONU. L’article Trump va-t-il de nouveau frapper les installations nucléaires iraniennes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:52</t>
+        </is>
+      </c>
+      <c r="D773" s="3" t="inlineStr">
+        <is>
+          <t>PRIX SAMUEL PATY SESSION 2026-2027 : « Information et opinion(s) dans notre démocratie aujourd’hui » – COMMENT S’INSCRIRE ?</t>
+        </is>
+      </c>
+      <c r="E773" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/prix-samuel-paty-session-2026-2027-information-et-opinions-dans-notre-democratie-aujourdhui-comment-sinscrire/</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>PRIX SAMUEL PATY SESSION 2027 Comment inscrire vos élèves ? Le 9 septembre 2026 Initié par l’Association des Professeurs d’Histoire et de Géographie (APHG), porté par des professeurs, le Prix Samuel Paty souhaite rendre hommage à notre collègue assassiné le 16 octobre 2020. Centré sur les principes et valeurs démocratiques, au cœur de la construction intellectuelle et citoyenne [&amp;#8230;] L’article PRIX SAMUEL PATY SESSION 2026-2027 : « Information et opinion(s) dans notre démocratie aujourd&amp;rsqu</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -25578,6 +25901,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E761" r:id="rId760"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E762" r:id="rId761"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E763" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E764" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E765" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E766" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E767" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E768" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E769" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E770" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E771" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E772" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E773" r:id="rId772"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/veille.xlsx
+++ b/veille.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G773"/>
+  <dimension ref="A1:G780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24838,7 +24838,6 @@
           <t>Après un incendie, les bâtiments historiques en pierre ou en brique peuvent souvent être sauvés. Mais pour éviter leur démolition, il faut évaluer rapidement les dégâts et consolider les murs.</t>
         </is>
       </c>
-      <c r="G764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="inlineStr">
@@ -24871,7 +24870,6 @@
           <t>Peut-on vraiment accuser l’IA d’une baisse de niveau alors que, parmi les systèmes éducatifs les plus performants selon PISA, les outils numériques tiennent une place très différente ?</t>
         </is>
       </c>
-      <c r="G765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="inlineStr">
@@ -24904,7 +24902,6 @@
           <t>La guerre civile en Angola a profondément modifié l’usage du feu dans les communautés rurales. Une étude montre que les surfaces brûlées ont diminué pendant le conflit, avant de fortement augmenter avec le retour de la paix.</t>
         </is>
       </c>
-      <c r="G766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="inlineStr">
@@ -24937,7 +24934,6 @@
           <t>L’extrême droite soutient le gouvernement en place depuis quatre&amp;nbsp;ans, qui a mis en œuvre une bonne partie de son programme. Le scrutin du 13&amp;nbsp;septembre dira si la population suédoise soutient ce cap.</t>
         </is>
       </c>
-      <c r="G767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="inlineStr">
@@ -24970,7 +24966,6 @@
           <t>Pourquoi, malgré le scandale suscité, ce n’est pas vraiment un dérapage L’article L’AfD affirme vouloir mettre le réarmement allemand au service de «&amp;#160;campagnes offensives de remigration&amp;#160;». est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="inlineStr">
@@ -25003,7 +24998,6 @@
           <t>Vingt-cinq ans après le 11-Septembre, le djihadisme n’a jamais été aussi étendu L’article Le siècle du djihad est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="inlineStr">
@@ -25036,7 +25030,6 @@
           <t>Le coût des guerres contre le terrorisme avait à l'époque été largement sous-estimé L’article Les guerres post-2001 ont coûté 8 000 milliards de dollars aux États-Unis est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="inlineStr">
@@ -25069,7 +25062,6 @@
           <t>Le «&amp;#160;dividende&amp;#160;» promis par Trump coûterait environ 1 225 milliards de dollars L’article La promesse de Trump de verser 5 000 dollars aux Américains en cas de victoire républicaine aux élections est sans précédent est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="inlineStr">
@@ -25102,7 +25094,6 @@
           <t>Pour la première fois en 20 ans, l’AIEA a voté hier le renvoi de l’Iran devant le Conseil de sécurité de l’ONU. L’article Trump va-t-il de nouveau frapper les installations nucléaires iraniennes&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
         </is>
       </c>
-      <c r="G772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="inlineStr">
@@ -25135,7 +25126,237 @@
           <t>PRIX SAMUEL PATY SESSION 2027 Comment inscrire vos élèves ? Le 9 septembre 2026 Initié par l’Association des Professeurs d’Histoire et de Géographie (APHG), porté par des professeurs, le Prix Samuel Paty souhaite rendre hommage à notre collègue assassiné le 16 octobre 2020. Centré sur les principes et valeurs démocratiques, au cœur de la construction intellectuelle et citoyenne [&amp;#8230;] L’article PRIX SAMUEL PATY SESSION 2026-2027 : « Information et opinion(s) dans notre démocratie aujourd&amp;rsqu</t>
         </is>
       </c>
-      <c r="G773" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>The Conversation FR - Éducation</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:47</t>
+        </is>
+      </c>
+      <c r="D774" s="3" t="inlineStr">
+        <is>
+          <t>Coopération, confiance en soi, curiosité… Ce que PISA nous apprend des compétences sociales et émotionnelles des élèves</t>
+        </is>
+      </c>
+      <c r="E774" s="4" t="inlineStr">
+        <is>
+          <t>https://theconversation.com/cooperation-confiance-en-soi-curiosite-ce-que-pisa-nous-apprend-des-competences-sociales-et-emotionnelles-des-eleves-291692</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Si les enquêtes PISA documentent les performances scolaires des élèves, elles incitent à s’intéresser, au-delà des simples résultats, au développement de compétences sociales et émotionnelles.</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>2026-09-12 05:22</t>
+        </is>
+      </c>
+      <c r="D775" s="3" t="inlineStr">
+        <is>
+          <t>« Réaffirmer la clause relative à l’État ennemi » : comment Pékin et Moscou se servent de la Charte de l’ONU pour menacer le Japon</t>
+        </is>
+      </c>
+      <c r="E775" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/12/reaffirmer-la-clause-relative-a-letat-ennemi-comment-pekin-et-moscou-se-servent-de-la-charte-de-lonu-pour-menacer-le-japon-2/</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Les dépenses militaires chinoises sont cinq fois supérieures à celles du Japon L’article «&amp;#160;Réaffirmer la clause relative à l’État ennemi&amp;#160;»&amp;#160;: comment Pékin et Moscou se servent de la Charte de l’ONU pour menacer le Japon est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>2026-09-11 16:22</t>
+        </is>
+      </c>
+      <c r="D776" s="3" t="inlineStr">
+        <is>
+          <t>Claude, l’IA d’Anthropic, est utilisé pour tenter de développer des missiles et des armes biologiques</t>
+        </is>
+      </c>
+      <c r="E776" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/11/claude-lia-danthropic-est-utilise-pour-tenter-de-developper-des-missiles-et-des-armes-biologiques/</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>L’entreprise américaine assure avoir mis fin à chaque tentative L’article Claude, l’IA d’Anthropic, est utilisé pour tenter de développer des missiles et des armes biologiques est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>2026-09-11 16:10</t>
+        </is>
+      </c>
+      <c r="D777" s="3" t="inlineStr">
+        <is>
+          <t>L’IA est-elle un virus cognitif ?</t>
+        </is>
+      </c>
+      <c r="E777" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/11/lia-est-elle-un-virus-cognitif/</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Les géants de l’intelligence artificielle sapent systématiquement le bien commun le plus fondamental de toute société humaine&amp;#160;: notre cognition L’article L&amp;rsquo;IA est-elle un virus cognitif&amp;#160;? est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Le Grand Continent</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:52</t>
+        </is>
+      </c>
+      <c r="D778" s="3" t="inlineStr">
+        <is>
+          <t>Les Houthis ont pris le contrôle du détroit de Bab el-Mandeb</t>
+        </is>
+      </c>
+      <c r="E778" s="4" t="inlineStr">
+        <is>
+          <t>https://legrandcontinent.eu/fr/2026/09/11/les-houthis-ont-pris-le-controle-du-detroit-de-bab-el-mandeb/</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>La voie maritime est la principale alternative au détroit d’Ormuz L’article Les Houthis ont pris le contrôle du détroit de Bab el-Mandeb est apparu en premier sur Le Grand Continent .</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>2026-09-12 07:15</t>
+        </is>
+      </c>
+      <c r="D779" s="3" t="inlineStr">
+        <is>
+          <t>Édito 475 Août 2026 : FACE AUX DÉFIS DU MONDE, FAIRE CORPS ET COMMUNAUTÉ</t>
+        </is>
+      </c>
+      <c r="E779" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/edito-475-aout-2026-face-aux-defis-du-monde-faire-corps-et-communaute/</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>L&amp;#8217;URGENCE DU MONDE, NOTRE BOUSSOLE DE CITOYENS Le risque incendie a longtemps été circonscrit, en France, à quelques massifs identifiés, aux étés les plus secs, à une intensité que nos dispositifs de lutte savaient globalement contenir. Ce schéma ne tient plus : l&amp;#8217;allongement de la saison sèche, la baisse de l&amp;#8217;humidité des sols et des [&amp;#8230;] L’article Édito 475 Août 2026 : FACE AUX DÉFIS DU MONDE, FAIRE CORPS ET COMMUNAUTÉ est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 12:35</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>APHG</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>2026-09-12 07:07</t>
+        </is>
+      </c>
+      <c r="D780" s="3" t="inlineStr">
+        <is>
+          <t>Sommaire 475</t>
+        </is>
+      </c>
+      <c r="E780" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aphg.fr/sommaire-475/</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>ÉDITORIAL. Face aux défis du monde, faire corps et communauté, Joëlle ALAZARD ACTUALITÉS HOMMAGE. Au bonheur des discordances. Hommage à Carlo Ginzburg, Guillaume CALAFAT HOMMAGE. Yves Lacoste Kevin LIMONNIER/ Axel DUC HOMMAGE. Yves Marie Bercé Olivier PONCET HOMMAGE. Bertrand Vergé (1956-2026), Xavier DESBROSSE ENTRETIENS. Le Sénat récompense l&amp;#8217;histoire : entretiens avec Marion Aballéa et Sofian [&amp;#8230;] L’article Sommaire 475 est apparu en premier sur APHG .</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -25911,6 +26132,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E771" r:id="rId770"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E772" r:id="rId771"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E773" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E774" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E775" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E776" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E777" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E778" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E779" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E780" r:id="rId779"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
